--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0903\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92619844-EEFB-4425-ADD6-65D075F7B6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707DFDA1-C8B6-4E57-960C-600B0035C3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3651,7 +3651,7 @@
     <t>YardiReviewer</t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0908\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707DFDA1-C8B6-4E57-960C-600B0035C3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04E24F6-4AA8-4AEC-BB6E-21E9C83A0B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3651,7 +3651,7 @@
     <t>YardiReviewer</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0908\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04E24F6-4AA8-4AEC-BB6E-21E9C83A0B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAFD610-1CDA-4E3E-A162-F624B24175F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="1206">
   <si>
     <t>Name</t>
   </si>
@@ -3651,7 +3651,13 @@
     <t>YardiReviewer</t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>ASFAExists</t>
+  </si>
+  <si>
+    <t>Affidavit of Student Financial Assistance is present in the application, manual review required.</t>
   </si>
 </sst>
 </file>
@@ -8558,7 +8564,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C524"/>
+  <dimension ref="A1:C526"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -9514,363 +9520,376 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>141</v>
+        <v>1204</v>
       </c>
       <c r="B115" t="s">
-        <v>144</v>
+        <v>1205</v>
+      </c>
+      <c r="C115" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B116" t="s">
-        <v>145</v>
+        <v>144</v>
+      </c>
+      <c r="C116" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B117" t="s">
-        <v>146</v>
+        <v>145</v>
+      </c>
+      <c r="C117" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B118" t="s">
-        <v>518</v>
+        <v>146</v>
       </c>
       <c r="C118" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>595</v>
+        <v>139</v>
       </c>
       <c r="B119" t="s">
         <v>518</v>
       </c>
+      <c r="C119" t="s">
+        <v>596</v>
+      </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>140</v>
+        <v>595</v>
       </c>
       <c r="B120" t="s">
-        <v>123</v>
+        <v>518</v>
+      </c>
+      <c r="C120" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B121" t="s">
-        <v>535</v>
+        <v>123</v>
+      </c>
+      <c r="C121" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>124</v>
+        <v>535</v>
+      </c>
+      <c r="C122" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>573</v>
+        <v>126</v>
       </c>
       <c r="B123" t="s">
-        <v>574</v>
+        <v>124</v>
+      </c>
+      <c r="C123" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>484</v>
+        <v>573</v>
       </c>
       <c r="B124" t="s">
-        <v>1129</v>
+        <v>574</v>
+      </c>
+      <c r="C124" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>181</v>
+        <v>484</v>
       </c>
       <c r="B126" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" t="s">
-        <v>127</v>
-      </c>
-      <c r="B127" t="s">
-        <v>147</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="B128" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>704</v>
+        <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>703</v>
-      </c>
-      <c r="C130" t="s">
-        <v>597</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B131" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>131</v>
+        <v>704</v>
       </c>
       <c r="B132" t="s">
-        <v>151</v>
+        <v>703</v>
+      </c>
+      <c r="C132" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>564</v>
+        <v>130</v>
       </c>
       <c r="B133" t="s">
-        <v>600</v>
-      </c>
-      <c r="C133" t="s">
-        <v>604</v>
+        <v>150</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>575</v>
+        <v>131</v>
       </c>
       <c r="B134" t="s">
-        <v>576</v>
+        <v>151</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>623</v>
+        <v>564</v>
       </c>
       <c r="B135" t="s">
-        <v>624</v>
+        <v>600</v>
       </c>
       <c r="C135" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>483</v>
+        <v>575</v>
       </c>
       <c r="B136" t="s">
-        <v>1130</v>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>623</v>
+      </c>
+      <c r="B137" t="s">
+        <v>624</v>
+      </c>
+      <c r="C137" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
+        <v>483</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
         <v>613</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B140" t="s">
         <v>614</v>
       </c>
-      <c r="C138" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" t="s">
-        <v>616</v>
-      </c>
-      <c r="B139" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C139" t="s">
+      <c r="C140" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>153</v>
+        <v>616</v>
       </c>
       <c r="B141" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" t="s">
-        <v>154</v>
-      </c>
-      <c r="B142" t="s">
-        <v>158</v>
+        <v>1156</v>
+      </c>
+      <c r="C141" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B144" t="s">
-        <v>536</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>500</v>
+        <v>155</v>
       </c>
       <c r="B145" t="s">
-        <v>637</v>
-      </c>
-      <c r="C145" t="s">
-        <v>638</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>1098</v>
+        <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C146" t="s">
-        <v>597</v>
+        <v>536</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>581</v>
+        <v>500</v>
       </c>
       <c r="B147" t="s">
-        <v>582</v>
+        <v>637</v>
+      </c>
+      <c r="C147" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>482</v>
+        <v>1098</v>
       </c>
       <c r="B148" t="s">
-        <v>1157</v>
+        <v>1104</v>
+      </c>
+      <c r="C148" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
+        <v>581</v>
+      </c>
+      <c r="B149" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>185</v>
+        <v>482</v>
       </c>
       <c r="B150" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" t="s">
-        <v>160</v>
-      </c>
-      <c r="B151" t="s">
-        <v>162</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="B152" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>577</v>
+        <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>578</v>
+        <v>162</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>481</v>
+        <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>1131</v>
+        <v>163</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>625</v>
+        <v>577</v>
       </c>
       <c r="B155" t="s">
-        <v>626</v>
-      </c>
-      <c r="C155" t="s">
-        <v>597</v>
+        <v>578</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
+        <v>481</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>183</v>
+        <v>625</v>
       </c>
       <c r="B157" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" t="s">
-        <v>169</v>
-      </c>
-      <c r="B158" t="s">
-        <v>166</v>
-      </c>
-      <c r="C158" t="s">
-        <v>526</v>
+        <v>626</v>
+      </c>
+      <c r="C157" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B159" t="s">
-        <v>167</v>
-      </c>
-      <c r="C159" t="s">
-        <v>526</v>
+        <v>184</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B160" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C160" t="s">
         <v>526</v>
@@ -9878,97 +9897,97 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="B161" t="s">
-        <v>193</v>
+        <v>167</v>
+      </c>
+      <c r="C161" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="B162" t="s">
-        <v>192</v>
+        <v>168</v>
+      </c>
+      <c r="C162" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="B163" t="s">
-        <v>171</v>
-      </c>
-      <c r="C163" t="s">
-        <v>526</v>
+        <v>193</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>579</v>
+        <v>191</v>
       </c>
       <c r="B164" t="s">
-        <v>580</v>
+        <v>192</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>470</v>
+        <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>1132</v>
+        <v>171</v>
+      </c>
+      <c r="C165" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
+        <v>579</v>
+      </c>
+      <c r="B166" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>1160</v>
+        <v>470</v>
       </c>
       <c r="B167" t="s">
-        <v>783</v>
-      </c>
-      <c r="C167" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" t="s">
-        <v>586</v>
-      </c>
-      <c r="B168" t="s">
-        <v>846</v>
-      </c>
-      <c r="C168" t="s">
-        <v>587</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>628</v>
+        <v>1160</v>
       </c>
       <c r="B169" t="s">
-        <v>629</v>
+        <v>783</v>
       </c>
       <c r="C169" t="s">
-        <v>597</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>714</v>
+        <v>586</v>
       </c>
       <c r="B170" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C170" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>715</v>
+        <v>628</v>
       </c>
       <c r="B171" t="s">
-        <v>848</v>
+        <v>629</v>
       </c>
       <c r="C171" t="s">
         <v>597</v>
@@ -9976,10 +9995,10 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B172" t="s">
-        <v>700</v>
+        <v>847</v>
       </c>
       <c r="C172" t="s">
         <v>597</v>
@@ -9987,356 +10006,359 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>1088</v>
+        <v>715</v>
       </c>
       <c r="B173" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C173" t="s">
-        <v>1089</v>
+        <v>597</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" t="s">
+        <v>716</v>
+      </c>
+      <c r="B174" t="s">
+        <v>700</v>
+      </c>
+      <c r="C174" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>461</v>
+        <v>1088</v>
       </c>
       <c r="B175" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B176" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C176" t="s">
-        <v>1113</v>
+        <v>853</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>232</v>
+        <v>461</v>
       </c>
       <c r="B177" t="s">
-        <v>849</v>
-      </c>
-      <c r="C177" t="s">
-        <v>526</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>233</v>
+        <v>1111</v>
       </c>
       <c r="B178" t="s">
-        <v>850</v>
+        <v>1112</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1113</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B179" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C179" t="s">
-        <v>584</v>
+        <v>526</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>685</v>
+        <v>233</v>
       </c>
       <c r="B180" t="s">
-        <v>852</v>
-      </c>
-      <c r="C180" t="s">
-        <v>597</v>
+        <v>850</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B181" t="s">
-        <v>234</v>
+        <v>851</v>
+      </c>
+      <c r="C181" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>451</v>
+        <v>685</v>
       </c>
       <c r="B182" t="s">
-        <v>460</v>
+        <v>852</v>
+      </c>
+      <c r="C182" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B183" t="s">
-        <v>853</v>
-      </c>
-      <c r="C183" t="s">
-        <v>1090</v>
+        <v>234</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>237</v>
+        <v>451</v>
       </c>
       <c r="B184" t="s">
-        <v>854</v>
+        <v>460</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B185" t="s">
-        <v>855</v>
+        <v>853</v>
+      </c>
+      <c r="C185" t="s">
+        <v>1090</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B186" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B187" t="s">
-        <v>783</v>
+        <v>855</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="B188" t="s">
-        <v>853</v>
-      </c>
-      <c r="C188" t="s">
-        <v>1090</v>
+        <v>856</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="B189" t="s">
-        <v>300</v>
+        <v>783</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>589</v>
+        <v>272</v>
       </c>
       <c r="B190" t="s">
-        <v>1085</v>
+        <v>853</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1090</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>606</v>
+        <v>299</v>
       </c>
       <c r="B191" t="s">
-        <v>784</v>
+        <v>300</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>671</v>
+        <v>589</v>
       </c>
       <c r="B192" t="s">
-        <v>672</v>
-      </c>
-      <c r="C192" t="s">
-        <v>597</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>684</v>
+        <v>606</v>
       </c>
       <c r="B193" t="s">
-        <v>702</v>
-      </c>
-      <c r="C193" t="s">
-        <v>597</v>
+        <v>784</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>865</v>
+        <v>671</v>
       </c>
       <c r="B194" t="s">
-        <v>866</v>
+        <v>672</v>
+      </c>
+      <c r="C194" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>469</v>
+        <v>684</v>
       </c>
       <c r="B195" t="s">
-        <v>1133</v>
+        <v>702</v>
+      </c>
+      <c r="C195" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>1185</v>
+        <v>865</v>
       </c>
       <c r="B196" t="s">
-        <v>1186</v>
+        <v>866</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" t="s">
+        <v>469</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1133</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>682</v>
+        <v>1185</v>
       </c>
       <c r="B198" t="s">
-        <v>683</v>
-      </c>
-      <c r="C198" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" t="s">
-        <v>462</v>
-      </c>
-      <c r="B199" t="s">
-        <v>1106</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>242</v>
+        <v>682</v>
       </c>
       <c r="B200" t="s">
-        <v>857</v>
+        <v>683</v>
       </c>
       <c r="C200" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" ht="13.5" customHeight="1">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>244</v>
+        <v>462</v>
       </c>
       <c r="B201" t="s">
-        <v>858</v>
-      </c>
-      <c r="C201" t="s">
-        <v>601</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B202" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
+        <v>857</v>
+      </c>
+      <c r="C202" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="13.5" customHeight="1">
       <c r="A203" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B203" t="s">
-        <v>245</v>
+        <v>858</v>
+      </c>
+      <c r="C203" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B204" t="s">
-        <v>248</v>
+        <v>819</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B205" t="s">
-        <v>249</v>
-      </c>
-      <c r="C205" t="s">
-        <v>591</v>
+        <v>245</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>452</v>
+        <v>247</v>
       </c>
       <c r="B206" t="s">
-        <v>508</v>
+        <v>248</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B207" t="s">
-        <v>821</v>
+        <v>249</v>
+      </c>
+      <c r="C207" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>252</v>
+        <v>452</v>
       </c>
       <c r="B208" t="s">
-        <v>253</v>
+        <v>508</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B209" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B210" t="s">
-        <v>823</v>
+        <v>253</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B211" t="s">
-        <v>859</v>
-      </c>
-      <c r="C211" t="s">
-        <v>591</v>
+        <v>822</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B212" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B213" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C213" t="s">
         <v>591</v>
@@ -10344,267 +10366,267 @@
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B214" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B215" t="s">
-        <v>270</v>
+        <v>860</v>
+      </c>
+      <c r="C215" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B216" t="s">
-        <v>853</v>
-      </c>
-      <c r="C216" t="s">
-        <v>1090</v>
+        <v>825</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B217" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>607</v>
+        <v>271</v>
       </c>
       <c r="B218" t="s">
-        <v>784</v>
+        <v>853</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1090</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>480</v>
+        <v>273</v>
       </c>
       <c r="B219" t="s">
-        <v>1134</v>
+        <v>274</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B220" t="s">
-        <v>603</v>
-      </c>
-      <c r="C220" t="s">
-        <v>597</v>
+        <v>784</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" t="s">
+        <v>480</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1134</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>463</v>
+        <v>602</v>
       </c>
       <c r="B222" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3">
-      <c r="A223" t="s">
-        <v>453</v>
-      </c>
-      <c r="B223" t="s">
-        <v>509</v>
+        <v>603</v>
+      </c>
+      <c r="C222" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>267</v>
+        <v>463</v>
       </c>
       <c r="B224" t="s">
-        <v>785</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>268</v>
+        <v>453</v>
       </c>
       <c r="B225" t="s">
-        <v>786</v>
+        <v>509</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B226" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B227" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B228" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>608</v>
+        <v>275</v>
       </c>
       <c r="B229" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>479</v>
+        <v>277</v>
       </c>
       <c r="B230" t="s">
-        <v>1135</v>
+        <v>788</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" t="s">
+        <v>608</v>
+      </c>
+      <c r="B231" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="B232" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2">
-      <c r="A233" t="s">
-        <v>454</v>
-      </c>
-      <c r="B233" t="s">
-        <v>510</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>280</v>
+        <v>464</v>
       </c>
       <c r="B234" t="s">
-        <v>778</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>281</v>
+        <v>454</v>
       </c>
       <c r="B235" t="s">
-        <v>283</v>
+        <v>510</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B236" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B237" t="s">
-        <v>781</v>
+        <v>283</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B238" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B239" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B240" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>609</v>
+        <v>286</v>
       </c>
       <c r="B241" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>478</v>
+        <v>287</v>
       </c>
       <c r="B242" t="s">
-        <v>1136</v>
+        <v>783</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>1197</v>
+        <v>609</v>
       </c>
       <c r="B243" t="s">
-        <v>1198</v>
+        <v>784</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" t="s">
+        <v>478</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>465</v>
+        <v>1197</v>
       </c>
       <c r="B245" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" t="s">
-        <v>449</v>
-      </c>
-      <c r="B246" t="s">
-        <v>293</v>
-      </c>
-      <c r="C246" t="s">
-        <v>526</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B247" t="s">
-        <v>511</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>291</v>
+        <v>449</v>
       </c>
       <c r="B248" t="s">
-        <v>861</v>
+        <v>293</v>
       </c>
       <c r="C248" t="s">
         <v>526</v>
@@ -10612,306 +10634,306 @@
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>292</v>
+        <v>455</v>
       </c>
       <c r="B249" t="s">
-        <v>844</v>
+        <v>511</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>448</v>
+        <v>291</v>
       </c>
       <c r="B250" t="s">
-        <v>845</v>
+        <v>861</v>
+      </c>
+      <c r="C250" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B251" t="s">
-        <v>853</v>
-      </c>
-      <c r="C251" t="s">
-        <v>1087</v>
+        <v>844</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>295</v>
+        <v>448</v>
       </c>
       <c r="B252" t="s">
-        <v>862</v>
+        <v>845</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B253" t="s">
-        <v>863</v>
+        <v>853</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1087</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B254" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B255" t="s">
-        <v>783</v>
+        <v>863</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>610</v>
+        <v>297</v>
       </c>
       <c r="B256" t="s">
-        <v>784</v>
+        <v>864</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>477</v>
+        <v>298</v>
       </c>
       <c r="B257" t="s">
-        <v>1137</v>
+        <v>783</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" t="s">
+        <v>610</v>
+      </c>
+      <c r="B258" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>643</v>
+        <v>477</v>
       </c>
       <c r="B259" t="s">
-        <v>644</v>
-      </c>
-      <c r="C259" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3">
-      <c r="A260" t="s">
-        <v>494</v>
-      </c>
-      <c r="B260" t="s">
-        <v>497</v>
-      </c>
-      <c r="C260" t="s">
-        <v>524</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>495</v>
+        <v>643</v>
       </c>
       <c r="B261" t="s">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="C261" t="s">
-        <v>525</v>
+        <v>597</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>523</v>
+        <v>494</v>
       </c>
       <c r="B262" t="s">
-        <v>537</v>
+        <v>497</v>
+      </c>
+      <c r="C262" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>315</v>
+        <v>495</v>
       </c>
       <c r="B263" t="s">
-        <v>301</v>
+        <v>496</v>
+      </c>
+      <c r="C263" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>316</v>
+        <v>523</v>
       </c>
       <c r="B264" t="s">
-        <v>302</v>
-      </c>
-      <c r="C264" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>456</v>
+        <v>315</v>
       </c>
       <c r="B265" t="s">
-        <v>512</v>
+        <v>301</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B266" t="s">
-        <v>303</v>
+        <v>302</v>
+      </c>
+      <c r="C266" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>318</v>
+        <v>456</v>
       </c>
       <c r="B267" t="s">
-        <v>304</v>
+        <v>512</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B268" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B269" t="s">
-        <v>306</v>
-      </c>
-      <c r="C269" t="s">
-        <v>526</v>
+        <v>304</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B270" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B271" t="s">
-        <v>308</v>
+        <v>306</v>
+      </c>
+      <c r="C271" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B272" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B273" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B274" t="s">
-        <v>311</v>
-      </c>
-      <c r="C274" t="s">
-        <v>526</v>
+        <v>309</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B275" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B276" t="s">
-        <v>313</v>
+        <v>311</v>
+      </c>
+      <c r="C276" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B277" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>476</v>
+        <v>327</v>
       </c>
       <c r="B278" t="s">
-        <v>1138</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" t="s">
+        <v>328</v>
+      </c>
+      <c r="B279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>541</v>
+        <v>476</v>
       </c>
       <c r="B280" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" t="s">
-        <v>335</v>
-      </c>
-      <c r="B281" t="s">
-        <v>353</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>336</v>
+        <v>541</v>
       </c>
       <c r="B282" t="s">
-        <v>350</v>
+        <v>542</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B283" t="s">
-        <v>351</v>
-      </c>
-      <c r="C283" t="s">
-        <v>526</v>
+        <v>353</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>457</v>
+        <v>336</v>
       </c>
       <c r="B284" t="s">
-        <v>513</v>
+        <v>350</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B285" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C285" t="s">
         <v>526</v>
@@ -10919,91 +10941,88 @@
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>338</v>
+        <v>457</v>
       </c>
       <c r="B286" t="s">
-        <v>344</v>
+        <v>513</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B287" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C287" t="s">
-        <v>503</v>
+        <v>526</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B288" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B289" t="s">
-        <v>347</v>
+        <v>345</v>
+      </c>
+      <c r="C289" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B290" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B291" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B292" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>1014</v>
+        <v>342</v>
       </c>
       <c r="B293" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C293" t="s">
-        <v>1010</v>
+        <v>349</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>1016</v>
+        <v>343</v>
       </c>
       <c r="B294" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C294" t="s">
-        <v>1010</v>
+        <v>346</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="B295" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="C295" t="s">
         <v>1010</v>
@@ -11011,116 +11030,119 @@
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>475</v>
+        <v>1016</v>
       </c>
       <c r="B296" t="s">
-        <v>1139</v>
+        <v>1017</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>1190</v>
+        <v>1018</v>
       </c>
       <c r="B297" t="s">
-        <v>1191</v>
+        <v>1019</v>
+      </c>
+      <c r="C297" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" t="s">
+        <v>475</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>645</v>
+        <v>1190</v>
       </c>
       <c r="B299" t="s">
-        <v>663</v>
-      </c>
-      <c r="C299" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="A300" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B300" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C300" t="s">
-        <v>1010</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>1011</v>
+        <v>645</v>
       </c>
       <c r="B301" t="s">
-        <v>1012</v>
+        <v>663</v>
       </c>
       <c r="C301" t="s">
-        <v>1010</v>
+        <v>597</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="B302" t="s">
-        <v>1140</v>
+        <v>1009</v>
       </c>
       <c r="C302" t="s">
         <v>1010</v>
       </c>
     </row>
+    <row r="303" spans="1:3">
+      <c r="A303" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C303" t="s">
+        <v>1010</v>
+      </c>
+    </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>641</v>
+        <v>1013</v>
       </c>
       <c r="B304" t="s">
-        <v>642</v>
+        <v>1140</v>
       </c>
       <c r="C304" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3">
-      <c r="A305" t="s">
-        <v>466</v>
-      </c>
-      <c r="B305" t="s">
-        <v>467</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>361</v>
+        <v>641</v>
       </c>
       <c r="B306" t="s">
-        <v>372</v>
+        <v>642</v>
+      </c>
+      <c r="C306" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>362</v>
+        <v>466</v>
       </c>
       <c r="B307" t="s">
-        <v>373</v>
-      </c>
-      <c r="C307" t="s">
-        <v>526</v>
+        <v>467</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>514</v>
+        <v>361</v>
       </c>
       <c r="B308" t="s">
-        <v>515</v>
+        <v>372</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B309" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C309" t="s">
         <v>526</v>
@@ -11128,155 +11150,155 @@
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>364</v>
+        <v>514</v>
       </c>
       <c r="B310" t="s">
-        <v>375</v>
-      </c>
-      <c r="C310" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B311" t="s">
-        <v>527</v>
+        <v>374</v>
+      </c>
+      <c r="C311" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B312" t="s">
-        <v>376</v>
+        <v>375</v>
+      </c>
+      <c r="C312" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B313" t="s">
-        <v>377</v>
+        <v>527</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B314" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B315" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B316" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B317" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>698</v>
+        <v>370</v>
       </c>
       <c r="B318" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C318" t="s">
-        <v>597</v>
+        <v>380</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>1101</v>
+        <v>371</v>
       </c>
       <c r="B319" t="s">
-        <v>1102</v>
+        <v>381</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>473</v>
+        <v>698</v>
       </c>
       <c r="B320" t="s">
-        <v>1141</v>
+        <v>1084</v>
+      </c>
+      <c r="C320" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>550</v>
+        <v>1101</v>
       </c>
       <c r="B321" t="s">
-        <v>551</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>1193</v>
+        <v>473</v>
       </c>
       <c r="B322" t="s">
-        <v>1194</v>
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" t="s">
+        <v>550</v>
+      </c>
+      <c r="B323" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>468</v>
+        <v>1193</v>
       </c>
       <c r="B324" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3">
-      <c r="A325" t="s">
-        <v>388</v>
-      </c>
-      <c r="B325" t="s">
-        <v>399</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>389</v>
+        <v>468</v>
       </c>
       <c r="B326" t="s">
-        <v>400</v>
-      </c>
-      <c r="C326" t="s">
-        <v>526</v>
+        <v>467</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>458</v>
+        <v>388</v>
       </c>
       <c r="B327" t="s">
-        <v>516</v>
+        <v>399</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B328" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C328" t="s">
         <v>526</v>
@@ -11284,1448 +11306,1467 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>391</v>
+        <v>458</v>
       </c>
       <c r="B329" t="s">
-        <v>402</v>
-      </c>
-      <c r="C329" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B330" t="s">
-        <v>528</v>
+        <v>401</v>
+      </c>
+      <c r="C330" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B331" t="s">
-        <v>376</v>
+        <v>402</v>
+      </c>
+      <c r="C331" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B332" t="s">
-        <v>377</v>
+        <v>528</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B333" t="s">
-        <v>403</v>
+        <v>376</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B334" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B335" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B336" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>472</v>
+        <v>397</v>
       </c>
       <c r="B337" t="s">
-        <v>1141</v>
+        <v>380</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>557</v>
+        <v>398</v>
       </c>
       <c r="B338" t="s">
-        <v>551</v>
+        <v>381</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>1195</v>
+        <v>472</v>
       </c>
       <c r="B339" t="s">
-        <v>1196</v>
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" t="s">
+        <v>557</v>
+      </c>
+      <c r="B340" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>639</v>
+        <v>1195</v>
       </c>
       <c r="B341" t="s">
-        <v>640</v>
-      </c>
-      <c r="C341" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3">
-      <c r="A342" t="s">
-        <v>382</v>
-      </c>
-      <c r="B342" t="s">
-        <v>558</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>383</v>
+        <v>639</v>
       </c>
       <c r="B343" t="s">
-        <v>559</v>
+        <v>640</v>
       </c>
       <c r="C343" t="s">
-        <v>526</v>
+        <v>597</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>459</v>
+        <v>382</v>
       </c>
       <c r="B344" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B345" t="s">
-        <v>585</v>
+        <v>559</v>
+      </c>
+      <c r="C345" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>385</v>
+        <v>459</v>
       </c>
       <c r="B346" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B347" t="s">
-        <v>562</v>
+        <v>585</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>1118</v>
+        <v>385</v>
       </c>
       <c r="B348" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C348" t="s">
-        <v>1120</v>
+        <v>561</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>471</v>
+        <v>386</v>
       </c>
       <c r="B349" t="s">
-        <v>1142</v>
+        <v>562</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C350" t="s">
+        <v>1120</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
+        <v>471</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" t="s">
         <v>711</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B353" t="s">
         <v>712</v>
       </c>
-      <c r="C351" t="s">
+      <c r="C353" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
-      <c r="A352" t="s">
+    <row r="354" spans="1:3">
+      <c r="A354" t="s">
         <v>713</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B354" t="s">
         <v>1143</v>
       </c>
-      <c r="C352" t="s">
+      <c r="C354" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="354" spans="1:2">
-      <c r="A354" t="s">
+    <row r="356" spans="1:3">
+      <c r="A356" t="s">
         <v>718</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B356" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="355" spans="1:2">
-      <c r="A355" t="s">
+    <row r="357" spans="1:3">
+      <c r="A357" t="s">
         <v>720</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B357" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="356" spans="1:2">
-      <c r="A356" t="s">
+    <row r="358" spans="1:3">
+      <c r="A358" t="s">
         <v>722</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B358" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="357" spans="1:2">
-      <c r="A357" t="s">
+    <row r="359" spans="1:3">
+      <c r="A359" t="s">
         <v>724</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B359" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
-      <c r="A358" t="s">
+    <row r="360" spans="1:3">
+      <c r="A360" t="s">
         <v>726</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B360" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
-      <c r="A359" t="s">
+    <row r="361" spans="1:3">
+      <c r="A361" t="s">
         <v>728</v>
       </c>
-      <c r="B359" t="s">
+      <c r="B361" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
-      <c r="A360" t="s">
+    <row r="362" spans="1:3">
+      <c r="A362" t="s">
         <v>730</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B362" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
-      <c r="A361" t="s">
+    <row r="363" spans="1:3">
+      <c r="A363" t="s">
         <v>732</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B363" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="362" spans="1:2">
-      <c r="A362" t="s">
+    <row r="364" spans="1:3">
+      <c r="A364" t="s">
         <v>734</v>
       </c>
-      <c r="B362" t="s">
+      <c r="B364" t="s">
         <v>1180</v>
       </c>
     </row>
-    <row r="363" spans="1:2">
-      <c r="A363" t="s">
+    <row r="365" spans="1:3">
+      <c r="A365" t="s">
         <v>735</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B365" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="364" spans="1:2">
-      <c r="A364" t="s">
+    <row r="366" spans="1:3">
+      <c r="A366" t="s">
         <v>737</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B366" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="365" spans="1:2">
-      <c r="A365" t="s">
+    <row r="367" spans="1:3">
+      <c r="A367" t="s">
         <v>739</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B367" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="366" spans="1:2">
-      <c r="A366" t="s">
+    <row r="368" spans="1:3">
+      <c r="A368" t="s">
         <v>741</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B368" t="s">
         <v>742</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2">
-      <c r="A367" t="s">
-        <v>743</v>
-      </c>
-      <c r="B367" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
-      <c r="A368" t="s">
-        <v>745</v>
-      </c>
-      <c r="B368" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B369" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" t="s">
-        <v>1094</v>
+        <v>745</v>
       </c>
       <c r="B370" t="s">
-        <v>1095</v>
+        <v>746</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B371" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
-        <v>1117</v>
+        <v>1094</v>
       </c>
       <c r="B372" t="s">
-        <v>1144</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
-        <v>1168</v>
+        <v>749</v>
       </c>
       <c r="B373" t="s">
-        <v>1169</v>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1144</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
-        <v>751</v>
+        <v>1168</v>
       </c>
       <c r="B375" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="376" spans="1:2">
-      <c r="A376" t="s">
-        <v>753</v>
-      </c>
-      <c r="B376" t="s">
-        <v>754</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B377" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B378" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="B379" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B380" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B381" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B382" t="s">
-        <v>314</v>
+        <v>762</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B383" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B384" t="s">
-        <v>769</v>
+        <v>314</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B385" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B386" t="s">
-        <v>1145</v>
+        <v>769</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" t="s">
+        <v>770</v>
+      </c>
+      <c r="B387" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B388" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="389" spans="1:2">
-      <c r="A389" t="s">
-        <v>774</v>
-      </c>
-      <c r="B389" t="s">
-        <v>775</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B390" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B391" t="s">
-        <v>1181</v>
+        <v>775</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" t="s">
+        <v>776</v>
+      </c>
+      <c r="B392" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
-        <v>799</v>
+        <v>777</v>
       </c>
       <c r="B393" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="394" spans="1:2">
-      <c r="A394" t="s">
-        <v>798</v>
-      </c>
-      <c r="B394" t="s">
-        <v>797</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="B395" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="B396" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B397" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="B398" t="s">
-        <v>1178</v>
+        <v>794</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" t="s">
+        <v>791</v>
+      </c>
+      <c r="B399" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B400" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="401" spans="1:2">
-      <c r="A401" t="s">
-        <v>810</v>
-      </c>
-      <c r="B401" t="s">
-        <v>809</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B402" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="B403" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B404" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B405" t="s">
-        <v>1146</v>
+        <v>794</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" t="s">
+        <v>806</v>
+      </c>
+      <c r="B406" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="B407" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="408" spans="1:2">
-      <c r="A408" t="s">
-        <v>817</v>
-      </c>
-      <c r="B408" t="s">
-        <v>1110</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="409" spans="1:2">
       <c r="A409" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B409" t="s">
-        <v>1077</v>
+        <v>816</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B410" t="s">
-        <v>1070</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="B411" t="s">
-        <v>1056</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="B412" t="s">
-        <v>1057</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B413" t="s">
-        <v>1076</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B414" t="s">
-        <v>1075</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B415" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B416" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B417" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B418" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B419" t="s">
-        <v>825</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B420" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B421" t="s">
-        <v>274</v>
+        <v>825</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B422" t="s">
-        <v>784</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="B423" t="s">
-        <v>603</v>
+        <v>274</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="B424" t="s">
-        <v>1147</v>
+        <v>784</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" t="s">
-        <v>1192</v>
+        <v>830</v>
       </c>
       <c r="B425" t="s">
-        <v>1186</v>
+        <v>603</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
-        <v>1060</v>
+        <v>829</v>
       </c>
       <c r="B426" t="s">
-        <v>1058</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" t="s">
-        <v>1061</v>
+        <v>1192</v>
       </c>
       <c r="B427" t="s">
-        <v>1059</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="B428" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="B429" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="B430" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B431" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>1080</v>
+        <v>1068</v>
       </c>
       <c r="B432" t="s">
-        <v>1079</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>1081</v>
+        <v>1069</v>
       </c>
       <c r="B433" t="s">
-        <v>1082</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>1158</v>
+        <v>1080</v>
       </c>
       <c r="B434" t="s">
-        <v>1159</v>
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1082</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>899</v>
+        <v>1158</v>
       </c>
       <c r="B436" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="437" spans="1:2">
-      <c r="A437" t="s">
-        <v>918</v>
-      </c>
-      <c r="B437" t="s">
-        <v>880</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>917</v>
+        <v>899</v>
       </c>
       <c r="B438" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B439" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B440" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B441" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B442" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B443" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B444" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B445" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B446" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="B447" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B448" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="B449" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B450" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B451" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B452" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B453" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B454" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B455" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B456" t="s">
-        <v>1148</v>
+        <v>897</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>1162</v>
+        <v>901</v>
       </c>
       <c r="B457" t="s">
-        <v>1163</v>
+        <v>898</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" t="s">
+        <v>900</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1148</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>1121</v>
+        <v>1162</v>
       </c>
       <c r="B459" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="460" spans="1:2">
-      <c r="A460" t="s">
-        <v>937</v>
-      </c>
-      <c r="B460" t="s">
-        <v>922</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
-        <v>928</v>
+        <v>1121</v>
       </c>
       <c r="B461" t="s">
-        <v>923</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="B462" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B463" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B464" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="465" spans="1:2">
       <c r="A465" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B465" t="s">
-        <v>1182</v>
+        <v>925</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B466" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B467" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B468" t="s">
-        <v>1184</v>
+        <v>927</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B469" t="s">
-        <v>1149</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>1170</v>
+        <v>936</v>
       </c>
       <c r="B470" t="s">
-        <v>1171</v>
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" t="s">
+        <v>935</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1149</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" t="s">
         <v>942</v>
       </c>
-      <c r="B472" t="s">
+      <c r="B474" t="s">
         <v>944</v>
-      </c>
-    </row>
-    <row r="473" spans="1:2">
-      <c r="A473" t="s">
-        <v>952</v>
-      </c>
-      <c r="B473" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
+        <v>952</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" t="s">
         <v>943</v>
       </c>
-      <c r="B475" t="s">
+      <c r="B477" t="s">
         <v>945</v>
-      </c>
-    </row>
-    <row r="476" spans="1:2">
-      <c r="A476" t="s">
-        <v>953</v>
-      </c>
-      <c r="B476" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B478" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="479" spans="1:2">
-      <c r="A479" t="s">
-        <v>951</v>
-      </c>
-      <c r="B479" t="s">
-        <v>949</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B480" t="s">
-        <v>1152</v>
+        <v>948</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>1188</v>
+        <v>951</v>
       </c>
       <c r="B481" t="s">
-        <v>1189</v>
+        <v>949</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" t="s">
+        <v>947</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1152</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>962</v>
+        <v>1188</v>
       </c>
       <c r="B483" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="484" spans="1:2">
-      <c r="A484" t="s">
-        <v>963</v>
-      </c>
-      <c r="B484" t="s">
-        <v>956</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B485" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>1007</v>
+        <v>963</v>
       </c>
       <c r="B486" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B487" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>966</v>
+        <v>1007</v>
       </c>
       <c r="B488" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B489" t="s">
-        <v>961</v>
+        <v>959</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" t="s">
+        <v>966</v>
+      </c>
+      <c r="B490" t="s">
+        <v>960</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="B491" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="492" spans="1:2">
-      <c r="A492" t="s">
-        <v>983</v>
-      </c>
-      <c r="B492" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B493" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="B494" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B495" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B496" t="s">
-        <v>1153</v>
+        <v>976</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" t="s">
+        <v>982</v>
+      </c>
+      <c r="B497" t="s">
+        <v>977</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
-        <v>995</v>
+        <v>981</v>
       </c>
       <c r="B498" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="499" spans="1:2">
-      <c r="A499" t="s">
-        <v>990</v>
-      </c>
-      <c r="B499" t="s">
-        <v>985</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B500" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B501" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B502" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B503" t="s">
-        <v>1154</v>
+        <v>987</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" t="s">
+        <v>993</v>
+      </c>
+      <c r="B504" t="s">
+        <v>988</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B505" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="506" spans="1:2">
-      <c r="A506" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B506" t="s">
-        <v>998</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="B507" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B508" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B509" t="s">
-        <v>1001</v>
+        <v>999</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1000</v>
       </c>
     </row>
     <row r="511" spans="1:2">
       <c r="A511" t="s">
-        <v>1028</v>
+        <v>1005</v>
       </c>
       <c r="B511" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="512" spans="1:2">
-      <c r="A512" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B512" t="s">
-        <v>1030</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>1045</v>
+        <v>1028</v>
       </c>
       <c r="B513" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B514" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="B515" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B516" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="B517" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B518" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B519" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B520" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="521" spans="1:2">
       <c r="A521" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B521" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B522" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B523" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" t="s">
         <v>1043</v>
       </c>
-      <c r="B524" t="s">
+      <c r="B526" t="s">
         <v>1042</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A478:A479 A475:A476 A460:A470 A472:A473 A481">
+  <conditionalFormatting sqref="A480:A481 A477:A478 A462:A472 A474:A475 A483">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0909\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAFD610-1CDA-4E3E-A162-F624B24175F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F00E59-B860-4B6A-8912-EB4236BAFEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3651,13 +3651,13 @@
     <t>YardiReviewer</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>ASFAExists</t>
   </si>
   <si>
     <t>Affidavit of Student Financial Assistance is present in the application, manual review required.</t>
+  </si>
+  <si>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4126,7 +4126,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -9520,10 +9520,10 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B115" t="s">
         <v>1204</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1205</v>
       </c>
       <c r="C115" t="s">
         <v>597</v>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0909\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F00E59-B860-4B6A-8912-EB4236BAFEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C5465E-39BD-478C-A5DB-1E73A4565A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21060" windowHeight="9615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3657,7 +3657,7 @@
     <t>Affidavit of Student Financial Assistance is present in the application, manual review required.</t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C5465E-39BD-478C-A5DB-1E73A4565A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0C673D-55EF-4314-8C5F-61F4DBD74A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21060" windowHeight="9615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3639,9 +3639,6 @@
     <t>Total Pay listed on the Work Number does not match the sum of each pay type on the Work Number.</t>
   </si>
   <si>
-    <t>DocumentTypeUserPrompt_GA.txt</t>
-  </si>
-  <si>
     <t>BackToSiteStates</t>
   </si>
   <si>
@@ -3657,7 +3654,10 @@
     <t>Affidavit of Student Financial Assistance is present in the application, manual review required.</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>DocumentTypeUserPrompt_AZ.txt</t>
   </si>
 </sst>
 </file>
@@ -4047,9 +4047,9 @@
   <dimension ref="A1:Z1005"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.5703125" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="26" width="8.7109375" customWidth="1"/>
   </cols>
@@ -4126,7 +4126,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -4150,7 +4150,7 @@
         <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
@@ -7572,26 +7572,26 @@
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B52" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B53" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B54" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
@@ -9520,10 +9520,10 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B115" t="s">
         <v>1203</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1204</v>
       </c>
       <c r="C115" t="s">
         <v>597</v>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0C673D-55EF-4314-8C5F-61F4DBD74A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED103809-4073-4F48-B2EB-7EFABECB4020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28260" windowHeight="13665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3654,10 +3654,10 @@
     <t>Affidavit of Student Financial Assistance is present in the application, manual review required.</t>
   </si>
   <si>
-    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>DocumentTypeUserPrompt_AZ.txt</t>
+  </si>
+  <si>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4126,7 +4126,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -4150,7 +4150,7 @@
         <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0914\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED103809-4073-4F48-B2EB-7EFABECB4020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668AEF73-ACD0-4E6E-8688-54DC3EEEAB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28260" windowHeight="13665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3657,7 +3657,7 @@
     <t>DocumentTypeUserPrompt_AZ.txt</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0914\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668AEF73-ACD0-4E6E-8688-54DC3EEEAB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB860014-17DB-4C70-9BAA-43AA819DFEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="Assets" sheetId="3" r:id="rId4"/>
     <sheet name="Findings" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$525</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="1204">
   <si>
     <t>Name</t>
   </si>
@@ -777,9 +780,6 @@
     <t>VOE_FrequencyCheck</t>
   </si>
   <si>
-    <t xml:space="preserve">Presently Employed has been listed as No on the Verification of Employment. Needs additional review. </t>
-  </si>
-  <si>
     <t>VOE_PresentlyEmployedCheck</t>
   </si>
   <si>
@@ -864,9 +864,6 @@
     <t>VOE_CommissionsBonusTipsPopulated</t>
   </si>
   <si>
-    <t>Commission, bonuses, tips, other amount has been populated. Needs additional review.</t>
-  </si>
-  <si>
     <t>OL_SalariedPayRateCheck</t>
   </si>
   <si>
@@ -1695,9 +1692,6 @@
     <t>SSBL_OverPayment</t>
   </si>
   <si>
-    <t>Manual review required, overpayment detected on SS/SSI benefit letter.</t>
-  </si>
-  <si>
     <t>Asset Self Certification</t>
   </si>
   <si>
@@ -1803,9 +1797,6 @@
     <t>EDC_hourly_and_paycheck</t>
   </si>
   <si>
-    <t>Newly added</t>
-  </si>
-  <si>
     <t>AS_HouseholdMemAbsent</t>
   </si>
   <si>
@@ -1839,24 +1830,12 @@
     <t>MID_MinorLessThan50Percent</t>
   </si>
   <si>
-    <t>A minor will live in the household less than 50% of the time. Manual review required.</t>
-  </si>
-  <si>
-    <t>The applicant has indicated all household contains all students by selecting 2 or 3 to Part A on the Student Certification. Manual review required.</t>
-  </si>
-  <si>
     <t>Raluca removed this check</t>
   </si>
   <si>
     <t>VOE_PayIncrease</t>
   </si>
   <si>
-    <t>Anticipated increase in the base pay over the next 12 months. Manual review required.</t>
-  </si>
-  <si>
-    <t>Raluca updated this check</t>
-  </si>
-  <si>
     <t>ICW_LiveInAttendant</t>
   </si>
   <si>
@@ -1947,9 +1926,6 @@
     <t>FailureEmailBodyActionReq</t>
   </si>
   <si>
-    <t>Income type included that cannot be validated with automation. Manual review required.</t>
-  </si>
-  <si>
     <t>SD_LLMExtractionJSONsFolder</t>
   </si>
   <si>
@@ -2016,9 +1992,6 @@
     <t>SCNE_EmploymentDocumented</t>
   </si>
   <si>
-    <t>Currently employment has been documented on the Self-Certification of Non-Employment. Manual review required.</t>
-  </si>
-  <si>
     <t>HHD_IsSigned</t>
   </si>
   <si>
@@ -2091,9 +2064,6 @@
     <t>VOE_Exists</t>
   </si>
   <si>
-    <t>Verification of Employment email receipt and clarification verification require manual review.</t>
-  </si>
-  <si>
     <t>PS_PayIncreaseAcrossPS</t>
   </si>
   <si>
@@ -2139,18 +2109,9 @@
     <t>SSBL_Incomplete</t>
   </si>
   <si>
-    <t xml:space="preserve">Assets exceed the asset limit, manual review required. </t>
-  </si>
-  <si>
-    <t>Applicant is a Dominium employee, manual review required.</t>
-  </si>
-  <si>
     <t>household member is temporarily absent, needs manual review.</t>
   </si>
   <si>
-    <t>Regular pay rate has increase across paystubs. Manual review required.</t>
-  </si>
-  <si>
     <t>Student Certification has inconsistent information. Please review answers in Part A to Part B for consistency.</t>
   </si>
   <si>
@@ -2160,12 +2121,6 @@
     <t>ICW_ZeroAnnualIncome</t>
   </si>
   <si>
-    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review required.</t>
-  </si>
-  <si>
-    <t>Applicant is a Dominium employee. Manual review required.</t>
-  </si>
-  <si>
     <t>Yardi_States</t>
   </si>
   <si>
@@ -2250,9 +2205,6 @@
     <t>CSEI_Qstn3IsYes</t>
   </si>
   <si>
-    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes, manual review is required.</t>
-  </si>
-  <si>
     <t>CSEI_Qstn4Check</t>
   </si>
   <si>
@@ -2394,9 +2346,6 @@
     <t>Highest Calculated Income on the Day Calculator does not match Verified Income on the ICW.</t>
   </si>
   <si>
-    <t>Multiple employment documents provided for same employment. Can't determine which employment document to use to validate Day Calculator. Manual review required.</t>
-  </si>
-  <si>
     <t>Employee Name listed on the Offer Letter, Day Calculator, and ICW do not match.</t>
   </si>
   <si>
@@ -2571,9 +2520,6 @@
     <t>ICW_Section811</t>
   </si>
   <si>
-    <t xml:space="preserve">This application is a Section 811 unit, manual review is required. </t>
-  </si>
-  <si>
     <t>Employee Name listed on Verification Services, Day Calculator, and ICW do not match.</t>
   </si>
   <si>
@@ -2640,15 +2586,9 @@
     <t>PS_PerfectAttendanceCAmount</t>
   </si>
   <si>
-    <t>Paystub lists YTD pay that is not in the current paystub so we cannot accurately predict income. Manual review required.</t>
-  </si>
-  <si>
     <t>ASC_GA_NoAssets</t>
   </si>
   <si>
-    <t xml:space="preserve">Checkbox documents household has no assets. Manual review required. </t>
-  </si>
-  <si>
     <t>ASC_GA_AssetsDisposedUnaswered</t>
   </si>
   <si>
@@ -2724,9 +2664,6 @@
     <t>Are all residents of the household full-time students has not been answered appropriately.</t>
   </si>
   <si>
-    <t>Documented that no household members are part of the original qualifying household. Manual review required.</t>
-  </si>
-  <si>
     <t>Not all adults have initialed the first line of Section Three – Signatures and Acknowledgements.</t>
   </si>
   <si>
@@ -2874,9 +2811,6 @@
     <t>LESExists</t>
   </si>
   <si>
-    <t xml:space="preserve">Bank Statements are present in the application, manual review required. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Leave and Earnings Statement is present in the application, manual review required. </t>
   </si>
   <si>
@@ -2925,9 +2859,6 @@
     <t>Date on the Release and Consent Form is not within 120 days of the move-in date. </t>
   </si>
   <si>
-    <t>Unable to validate findings for Release and Consent Form. Needs manual review. </t>
-  </si>
-  <si>
     <t>RCFExists</t>
   </si>
   <si>
@@ -3045,9 +2976,6 @@
     <t>Asset Current Balance listed on Verification Services does not match the ICW. </t>
   </si>
   <si>
-    <t>Unable to validate findings for Verification Services. Needs manual review. </t>
-  </si>
-  <si>
     <t>VSA_AssetAccount</t>
   </si>
   <si>
@@ -3069,18 +2997,12 @@
     <t>CSC_120days</t>
   </si>
   <si>
-    <t>Both 120 days of pay history available and 120 days of pay history not available data is populated on the Child Support Calcs. Achie cannot determine which data to use, manual review is required. </t>
-  </si>
-  <si>
     <t>TX - Newly added by Raluca</t>
   </si>
   <si>
     <t>CSC_ConsistentPayments</t>
   </si>
   <si>
-    <t>The consistent payments data is populated on Child Support Calcs but additional data tables are populated as well. Archie cannot determine which data to use, manual review is required. </t>
-  </si>
-  <si>
     <t>CSC_FindingError</t>
   </si>
   <si>
@@ -3168,9 +3090,6 @@
     <t>The date on the Asset Certification of Net Family Assets is not within 120 days of the move-in date. </t>
   </si>
   <si>
-    <t>Unable to validate findings for Asset Certification of Net Family Assets. Needs manual review. </t>
-  </si>
-  <si>
     <t>ACNFA_FindingError</t>
   </si>
   <si>
@@ -3210,9 +3129,6 @@
     <t>ACNFA_InterestRate</t>
   </si>
   <si>
-    <t>Presently Employed has been listed as No on the Employment Verification. Needs manual review.  </t>
-  </si>
-  <si>
     <t>Presently Employed was documented as Yes on the Employment Verification but no Date First Employed was provided. </t>
   </si>
   <si>
@@ -3273,9 +3189,6 @@
     <t>Date on the Employment Verification is not within 120 days of Move-In date.</t>
   </si>
   <si>
-    <t>Employment Verification email receipt and clarification verification require manual review.</t>
-  </si>
-  <si>
     <t>Not all fields have been documented appropriately on the Employment Verification.</t>
   </si>
   <si>
@@ -3288,21 +3201,12 @@
     <t>EV_TX_SeasonOrSporadic</t>
   </si>
   <si>
-    <t>Season or Sporadic work has been documented on the Employment Verification. Manual review required.  </t>
-  </si>
-  <si>
     <t>Asset Self Certification is missing from the application.</t>
   </si>
   <si>
-    <t>Social Security Benefits Letter is missing at least one page. Manual Review is required.</t>
-  </si>
-  <si>
     <t>Paystubs do not match Day Calculator with Employee Name, End date and Gross pay</t>
   </si>
   <si>
-    <t>The Annual Income is listed as zero. Manual review required.</t>
-  </si>
-  <si>
     <t>Implementing whis only in EDC.</t>
   </si>
   <si>
@@ -3411,111 +3315,9 @@
     <t>Regular Contributions Verification email receipt requires manual review.</t>
   </si>
   <si>
-    <t>Unable to validate Housing History Disclosure. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Income Calculation Worksheet. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Application Summary. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Member Information Document. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Income &amp; Asset Questionnaire. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Self Certification &amp; Worksheet. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Affidavit of Student Financial Assistance. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Student Certification. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate VAWA Acknowledgement. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Screening Document. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Paystub. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Employment. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Offer Letter. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Work Number. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self-Employment Certification. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Payment History. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Calcs. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Supplemental Security Income Letter. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Reccurring Cash Contribution. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Housing Demographic Reporting Form. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Self-Employment Income. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Profit/Loss Statement. Manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Household Asset Breakdown. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Employment Verification. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate the Certification of Student Status. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Regular Contributions Verification. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Bank Statements. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Leave and Earnings Statement. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate the Tenant Rights and Resource Guide (TRRG). Manual review required. </t>
-  </si>
-  <si>
     <t>Unable to validate the TSAHC. Manual review required. </t>
   </si>
   <si>
-    <t>Unable to validate Self Certification of Non Employment. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Annual Student Certification since there is Home unit . Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Zero Income. Needs manual review.</t>
-  </si>
-  <si>
     <t>EV_TX_ApplicantName</t>
   </si>
   <si>
@@ -3576,9 +3378,6 @@
     <t>None of the student options were documented.</t>
   </si>
   <si>
-    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Needs manual review.</t>
-  </si>
-  <si>
     <t>Annual Income is above the Income Limit listed on the Income Calculation Worksheet. Manual review required.</t>
   </si>
   <si>
@@ -3657,14 +3456,212 @@
     <t>DocumentTypeUserPrompt_AZ.txt</t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>Assets exceed HUD asset limit. Third party verification of all assets is required.</t>
+  </si>
+  <si>
+    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Updated by Raluca</t>
+  </si>
+  <si>
+    <t>Applicant is a Dominium employee. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Income type included that cannot be validated with automation. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Annual income is listed as zero. Confirm this is accurate and ensure the Certification of Zero Income is present in the file.</t>
+  </si>
+  <si>
+    <t>This application is a Section 811 unit. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Member Information Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant reported a minor will live in the household less than 50% of the time. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Current employment has been documented on the Self-Certification of Non-Employment. Verification of employment is needed.</t>
+  </si>
+  <si>
+    <t>Applicant has reported they have no assets. If applicant has income, confirm how the income is paid.</t>
+  </si>
+  <si>
+    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Raluca removed the check as per business requirement</t>
+  </si>
+  <si>
+    <t>Multiple sources of verification included for same income. Remove verification documents that are not being used in the calculation of income.</t>
+  </si>
+  <si>
+    <t>Regular pay rate has increased across paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Paystubs list YTD pay that is not paid on a current paystub so annual income cannot be accurately predicted. Clarify, with the employer, the pay type and how often it is received.</t>
+  </si>
+  <si>
+    <t>Unable to validate paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Verification of Employment - manual review is needed to ensure document was received via 3rd party.</t>
+  </si>
+  <si>
+    <t>Anticipated wage increase indicated on employment verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Offer Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Work Number. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self-Employment Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing History Disclosure. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Application Summary. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Self Certification &amp; Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self Certification of Non Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Income &amp; Asset Questionnaire. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Affidavit of Student Financial Assistance. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Annual Student Certification since there is Home unit . Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Zero Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate VAWA Acknowledgement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Screening Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Payment History. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Calcs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Reccurring Cash Contribution. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Self-Employment Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Household Asset Breakdown. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Employment Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate the Certification of Student Status. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Regular Contributions Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Bank Statements. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Leave and Earnings Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Profit/Loss Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant marked that no household members are part of the original qualifying household. Please have the applicant correct.</t>
+  </si>
+  <si>
+    <t>Bank statements are included in the file. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Commission, bonuses, tips, other amount has been populated. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Both 120 days of pay history available and 120 days of pay history not available data sections are populated on the Child Support Calculator. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
+  </si>
+  <si>
+    <t>The consistent payments data is populated on Child Support Calcs but additional data tables are populated as well. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
+  </si>
+  <si>
+    <t>Social Security Benefits Letter is missing at least one page. Upload missing page with final signed documents.</t>
+  </si>
+  <si>
+    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Season or Sporadic work has been documented on the Employment Verification. Manual review is needed.  </t>
+  </si>
+  <si>
+    <t>Unable to validate Release and Consent Form. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3688,13 +3685,25 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3709,7 +3718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3719,6 +3728,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4093,7 +4105,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1114</v>
+        <v>1081</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -4114,7 +4126,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1115</v>
+        <v>1082</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -4126,12 +4138,12 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1205</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B8" t="s">
         <v>206</v>
@@ -4150,16 +4162,16 @@
         <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>1204</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>1103</v>
+        <v>1070</v>
       </c>
       <c r="B12" t="s">
-        <v>1103</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -4167,7 +4179,7 @@
         <v>207</v>
       </c>
       <c r="B13" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
@@ -4180,10 +4192,10 @@
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B15" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
@@ -4191,7 +4203,7 @@
         <v>209</v>
       </c>
       <c r="B16" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
@@ -4199,7 +4211,7 @@
         <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
@@ -4207,7 +4219,7 @@
         <v>211</v>
       </c>
       <c r="B18" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C18" t="s">
         <v>226</v>
@@ -4229,7 +4241,7 @@
         <v>213</v>
       </c>
       <c r="B20" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C20" t="s">
         <v>228</v>
@@ -4240,7 +4252,7 @@
         <v>214</v>
       </c>
       <c r="B21" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C21" t="s">
         <v>229</v>
@@ -4251,7 +4263,7 @@
         <v>215</v>
       </c>
       <c r="B22" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
@@ -4259,7 +4271,7 @@
         <v>216</v>
       </c>
       <c r="B23" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
@@ -4267,7 +4279,7 @@
         <v>217</v>
       </c>
       <c r="B24" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
@@ -4275,15 +4287,15 @@
         <v>218</v>
       </c>
       <c r="B25" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B26" t="s">
-        <v>970</v>
+        <v>946</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
@@ -4291,50 +4303,50 @@
         <v>231</v>
       </c>
       <c r="B27" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1">
@@ -4347,221 +4359,221 @@
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1">
       <c r="A35" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B36" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1">
       <c r="A37" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1">
       <c r="A38" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B38" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1">
       <c r="A39" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B39" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1">
       <c r="A40" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1">
       <c r="A41" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1">
       <c r="A42" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1">
       <c r="A43" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B43" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1">
       <c r="A44" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="B44" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1">
       <c r="A45" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="B45" t="s">
-        <v>970</v>
+        <v>946</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
       <c r="B46" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1">
       <c r="A47" t="s">
-        <v>811</v>
+        <v>793</v>
       </c>
       <c r="B47" t="s">
-        <v>812</v>
+        <v>794</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
       <c r="B48" t="s">
-        <v>814</v>
+        <v>796</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>840</v>
+        <v>822</v>
       </c>
       <c r="B49" t="s">
-        <v>841</v>
+        <v>823</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>877</v>
+        <v>856</v>
       </c>
       <c r="B50" t="s">
-        <v>878</v>
+        <v>857</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>920</v>
+        <v>898</v>
       </c>
       <c r="B51" t="s">
-        <v>921</v>
+        <v>899</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>938</v>
+        <v>916</v>
       </c>
       <c r="B52" t="s">
-        <v>939</v>
+        <v>917</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>940</v>
+        <v>918</v>
       </c>
       <c r="B53" t="s">
-        <v>941</v>
+        <v>919</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>946</v>
+        <v>923</v>
       </c>
       <c r="B54" t="s">
-        <v>954</v>
+        <v>931</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1">
       <c r="A55" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="B55" t="s">
-        <v>969</v>
+        <v>945</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1">
       <c r="A56" t="s">
-        <v>971</v>
+        <v>947</v>
       </c>
       <c r="B56" t="s">
-        <v>971</v>
+        <v>947</v>
       </c>
       <c r="C56" t="s">
-        <v>972</v>
+        <v>948</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1">
       <c r="A57" t="s">
-        <v>989</v>
+        <v>965</v>
       </c>
       <c r="B57" t="s">
-        <v>989</v>
+        <v>965</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1">
       <c r="A58" t="s">
-        <v>1006</v>
+        <v>981</v>
       </c>
       <c r="B58" t="s">
-        <v>1091</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" t="s">
-        <v>1096</v>
+        <v>1063</v>
       </c>
       <c r="B59" t="s">
-        <v>1097</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" t="s">
-        <v>1026</v>
+        <v>999</v>
       </c>
       <c r="B60" t="s">
-        <v>1027</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
@@ -5527,10 +5539,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5538,15 +5550,15 @@
         <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5554,15 +5566,15 @@
         <v>225</v>
       </c>
       <c r="B4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5570,15 +5582,15 @@
         <v>223</v>
       </c>
       <c r="B6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B7" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5586,15 +5598,15 @@
         <v>219</v>
       </c>
       <c r="B8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5602,15 +5614,15 @@
         <v>222</v>
       </c>
       <c r="B10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -5626,47 +5638,47 @@
         <v>220</v>
       </c>
       <c r="B13" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B14" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B15" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B16" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B17" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B18" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5674,7 +5686,7 @@
         <v>229</v>
       </c>
       <c r="B19" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5682,23 +5694,23 @@
         <v>226</v>
       </c>
       <c r="B20" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B22" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5706,7 +5718,7 @@
         <v>227</v>
       </c>
       <c r="B23" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5714,55 +5726,55 @@
         <v>228</v>
       </c>
       <c r="B24" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B26" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -5770,95 +5782,95 @@
         <v>1040</v>
       </c>
       <c r="B31" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B34" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B35" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B36" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B37" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B38" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B39" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B40" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B41" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="B42" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -6058,10 +6070,10 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="B20" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
@@ -6069,23 +6081,23 @@
         <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="B22" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
@@ -7180,10 +7192,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="B3" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -7260,90 +7272,90 @@
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B13" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B14" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B15" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B16" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B17" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B18" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B19" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B20" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B21" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>1116</v>
+        <v>1083</v>
       </c>
       <c r="B22" t="s">
-        <v>1116</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B23" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1">
@@ -7380,218 +7392,218 @@
     </row>
     <row r="28" spans="1:2" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.25" customHeight="1">
       <c r="A30" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1">
       <c r="A31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.25" customHeight="1">
       <c r="A32" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B32" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B34" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B35" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B36" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1">
       <c r="A37" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B37" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1">
       <c r="A38" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B38" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1">
       <c r="A39" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B39" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1">
       <c r="A40" t="s">
-        <v>1187</v>
+        <v>1119</v>
       </c>
       <c r="B40" t="s">
-        <v>1187</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1">
       <c r="A41" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="B41" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1">
       <c r="A42" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B42" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1">
       <c r="A43" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B43" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1">
       <c r="A44" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="B44" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1">
       <c r="A45" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="B45" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>1022</v>
+        <v>995</v>
       </c>
       <c r="B46" t="s">
-        <v>1022</v>
+        <v>995</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1">
       <c r="A47" t="s">
-        <v>1023</v>
+        <v>996</v>
       </c>
       <c r="B47" t="s">
-        <v>1023</v>
+        <v>996</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>1024</v>
+        <v>997</v>
       </c>
       <c r="B48" t="s">
-        <v>1024</v>
+        <v>997</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>1025</v>
+        <v>998</v>
       </c>
       <c r="B49" t="s">
-        <v>1025</v>
+        <v>998</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>1092</v>
+        <v>1059</v>
       </c>
       <c r="B50" t="s">
-        <v>1092</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>1093</v>
+        <v>1060</v>
       </c>
       <c r="B51" t="s">
-        <v>1093</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1199</v>
+        <v>1131</v>
       </c>
       <c r="B52" t="s">
-        <v>1199</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1200</v>
+        <v>1132</v>
       </c>
       <c r="B53" t="s">
-        <v>1200</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1201</v>
+        <v>1133</v>
       </c>
       <c r="B54" t="s">
-        <v>1201</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
@@ -8564,12 +8576,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C526"/>
+  <dimension ref="A1:C525"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40.5703125" customWidth="1"/>
-    <col min="2" max="2" width="153.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="167.85546875" customWidth="1"/>
+    <col min="3" max="3" width="60.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
@@ -8590,95 +8602,95 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>1099</v>
+        <v>1066</v>
       </c>
       <c r="B5" t="s">
-        <v>1100</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B7" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="C7" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="B8" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="C8" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="B9" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="C9" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="B10" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C10" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="B11" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="C11" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="B12" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="C12" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>662</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1123</v>
+        <v>652</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>1163</v>
       </c>
       <c r="C13" t="s">
-        <v>597</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>174</v>
       </c>
-      <c r="B15" t="s">
-        <v>445</v>
+      <c r="B15" s="2" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -8702,7 +8714,7 @@
         <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>1179</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8713,94 +8725,100 @@
         <v>198</v>
       </c>
       <c r="C19" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B20" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>593</v>
-      </c>
-      <c r="B21" t="s">
-        <v>699</v>
+        <v>589</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>605</v>
-      </c>
-      <c r="B22" t="s">
-        <v>706</v>
+        <v>597</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>1139</v>
       </c>
       <c r="C22" t="s">
-        <v>597</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B23" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="C23" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>630</v>
-      </c>
-      <c r="B24" t="s">
-        <v>707</v>
+        <v>622</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1141</v>
       </c>
       <c r="C24" t="s">
-        <v>597</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>632</v>
-      </c>
-      <c r="B25" t="s">
-        <v>635</v>
+        <v>624</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>1142</v>
       </c>
       <c r="C25" t="s">
-        <v>597</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>705</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1086</v>
+        <v>691</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>1143</v>
       </c>
       <c r="C26" t="s">
-        <v>597</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>842</v>
-      </c>
-      <c r="B27" t="s">
-        <v>843</v>
+        <v>824</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>474</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1124</v>
+        <v>472</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1145</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8821,10 +8839,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B32" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8840,7 +8858,7 @@
         <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>1172</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -8848,7 +8866,7 @@
         <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -8856,7 +8874,7 @@
         <v>190</v>
       </c>
       <c r="B36" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -8893,48 +8911,48 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B41" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B42" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="B43" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C43" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="B44" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="C44" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>489</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1125</v>
+        <v>487</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1164</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -8950,7 +8968,7 @@
         <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>1177</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9001,7 +9019,7 @@
         <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -9014,45 +9032,48 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B56" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="B57" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>1020</v>
+        <v>993</v>
       </c>
       <c r="B58" t="s">
-        <v>1021</v>
+        <v>994</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>598</v>
-      </c>
-      <c r="B59" t="s">
-        <v>599</v>
+        <v>594</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>1147</v>
       </c>
       <c r="C59" t="s">
-        <v>597</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>488</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1126</v>
+        <v>486</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9060,7 +9081,7 @@
         <v>178</v>
       </c>
       <c r="B62" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -9071,7 +9092,7 @@
         <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -9082,7 +9103,7 @@
         <v>112</v>
       </c>
       <c r="C64" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -9093,7 +9114,7 @@
         <v>114</v>
       </c>
       <c r="C65" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -9104,7 +9125,7 @@
         <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -9115,7 +9136,7 @@
         <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -9126,7 +9147,7 @@
         <v>106</v>
       </c>
       <c r="C68" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -9134,7 +9155,7 @@
         <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>1173</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -9142,7 +9163,7 @@
         <v>195</v>
       </c>
       <c r="B70" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -9150,77 +9171,77 @@
         <v>196</v>
       </c>
       <c r="B71" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="C71" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B72" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B73" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B74" t="s">
-        <v>1174</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>487</v>
+        <v>638</v>
       </c>
       <c r="B75" t="s">
-        <v>1127</v>
+        <v>637</v>
+      </c>
+      <c r="C75" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>647</v>
+        <v>1097</v>
       </c>
       <c r="B76" t="s">
-        <v>646</v>
-      </c>
-      <c r="C76" t="s">
-        <v>597</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>1164</v>
+      <c r="A77" s="2" t="s">
+        <v>1100</v>
       </c>
       <c r="B77" t="s">
-        <v>1165</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>485</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>1167</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="2" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9236,7 +9257,7 @@
         <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -9249,62 +9270,62 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B84" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>657</v>
-      </c>
-      <c r="B85" t="s">
-        <v>658</v>
+        <v>648</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>1148</v>
       </c>
       <c r="C85" t="s">
-        <v>597</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="B86" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="C86" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="B87" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C87" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="B88" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="C88" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>486</v>
-      </c>
-      <c r="B89" t="s">
-        <v>1155</v>
+        <v>484</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>1166</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9312,29 +9333,29 @@
         <v>180</v>
       </c>
       <c r="B91" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="B92" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="C92" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="B93" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C93" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -9358,7 +9379,7 @@
         <v>132</v>
       </c>
       <c r="B96" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -9366,7 +9387,7 @@
         <v>133</v>
       </c>
       <c r="B97" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -9374,7 +9395,7 @@
         <v>134</v>
       </c>
       <c r="B98" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -9382,7 +9403,7 @@
         <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -9390,10 +9411,10 @@
         <v>136</v>
       </c>
       <c r="B100" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C100" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -9401,10 +9422,10 @@
         <v>137</v>
       </c>
       <c r="B101" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C101" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -9412,121 +9433,124 @@
         <v>138</v>
       </c>
       <c r="B102" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C102" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B103" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="B104" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C104" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>871</v>
+        <v>850</v>
       </c>
       <c r="B105" t="s">
-        <v>872</v>
+        <v>851</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="B106" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C106" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="B107" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="C107" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="B108" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="C108" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>485</v>
-      </c>
-      <c r="B109" t="s">
-        <v>1128</v>
+        <v>847</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>867</v>
+        <v>848</v>
       </c>
       <c r="B110" t="s">
-        <v>868</v>
+        <v>849</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>869</v>
+        <v>853</v>
       </c>
       <c r="B111" t="s">
-        <v>870</v>
+        <v>854</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>874</v>
+        <v>855</v>
       </c>
       <c r="B112" t="s">
-        <v>875</v>
+        <v>852</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>876</v>
-      </c>
-      <c r="B113" t="s">
-        <v>873</v>
+        <v>483</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>1165</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>1202</v>
+        <v>1134</v>
       </c>
       <c r="B115" t="s">
-        <v>1203</v>
+        <v>1135</v>
       </c>
       <c r="C115" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -9537,7 +9561,7 @@
         <v>144</v>
       </c>
       <c r="C116" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -9548,7 +9572,7 @@
         <v>145</v>
       </c>
       <c r="C117" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -9559,7 +9583,7 @@
         <v>146</v>
       </c>
       <c r="C118" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -9567,21 +9591,21 @@
         <v>139</v>
       </c>
       <c r="B119" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C119" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B120" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C120" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -9592,7 +9616,7 @@
         <v>123</v>
       </c>
       <c r="C121" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -9600,10 +9624,10 @@
         <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C122" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -9614,676 +9638,699 @@
         <v>124</v>
       </c>
       <c r="C123" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B124" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C124" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" t="s">
-        <v>484</v>
-      </c>
-      <c r="B126" t="s">
-        <v>1129</v>
+        <v>586</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>482</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>181</v>
+      </c>
+      <c r="B127" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>128</v>
+        <v>690</v>
       </c>
       <c r="B131" t="s">
-        <v>149</v>
+        <v>689</v>
+      </c>
+      <c r="C131" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>704</v>
+        <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>703</v>
-      </c>
-      <c r="C132" t="s">
-        <v>597</v>
+        <v>150</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>131</v>
-      </c>
-      <c r="B134" t="s">
-        <v>151</v>
+        <v>561</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B135" t="s">
-        <v>600</v>
-      </c>
-      <c r="C135" t="s">
-        <v>604</v>
+        <v>573</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>575</v>
+        <v>615</v>
       </c>
       <c r="B136" t="s">
-        <v>576</v>
+        <v>616</v>
+      </c>
+      <c r="C136" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>623</v>
-      </c>
-      <c r="B137" t="s">
-        <v>624</v>
-      </c>
-      <c r="C137" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" t="s">
-        <v>483</v>
-      </c>
-      <c r="B138" t="s">
-        <v>1130</v>
+        <v>481</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
+        <v>605</v>
+      </c>
+      <c r="B139" t="s">
+        <v>606</v>
+      </c>
+      <c r="C139" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B140" t="s">
-        <v>614</v>
+        <v>1170</v>
       </c>
       <c r="C140" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" t="s">
-        <v>616</v>
-      </c>
-      <c r="B141" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C141" t="s">
-        <v>615</v>
+        <v>607</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>153</v>
+      </c>
+      <c r="B142" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B143" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B144" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B145" t="s">
-        <v>159</v>
+        <v>534</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>156</v>
+        <v>498</v>
       </c>
       <c r="B146" t="s">
-        <v>536</v>
+        <v>628</v>
+      </c>
+      <c r="C146" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>500</v>
+        <v>1065</v>
       </c>
       <c r="B147" t="s">
-        <v>637</v>
+        <v>1071</v>
       </c>
       <c r="C147" t="s">
-        <v>638</v>
+        <v>593</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>1098</v>
+        <v>578</v>
       </c>
       <c r="B148" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C148" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>581</v>
+        <v>480</v>
       </c>
       <c r="B149" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" t="s">
-        <v>482</v>
-      </c>
-      <c r="B150" t="s">
-        <v>1157</v>
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
+        <v>185</v>
+      </c>
+      <c r="B151" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="B152" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B153" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>161</v>
+        <v>574</v>
       </c>
       <c r="B154" t="s">
-        <v>163</v>
+        <v>575</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>577</v>
+        <v>479</v>
       </c>
       <c r="B155" t="s">
-        <v>578</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>481</v>
+        <v>617</v>
       </c>
       <c r="B156" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" t="s">
-        <v>625</v>
-      </c>
-      <c r="B157" t="s">
-        <v>626</v>
-      </c>
-      <c r="C157" t="s">
-        <v>597</v>
+        <v>618</v>
+      </c>
+      <c r="C156" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
+        <v>183</v>
+      </c>
+      <c r="B158" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B159" t="s">
-        <v>184</v>
+        <v>166</v>
+      </c>
+      <c r="C159" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B160" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C160" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B161" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C161" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="B162" t="s">
-        <v>168</v>
-      </c>
-      <c r="C162" t="s">
-        <v>526</v>
+        <v>193</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B163" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="B164" t="s">
-        <v>192</v>
+        <v>171</v>
+      </c>
+      <c r="C164" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>170</v>
+        <v>576</v>
       </c>
       <c r="B165" t="s">
-        <v>171</v>
-      </c>
-      <c r="C165" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" t="s">
-        <v>579</v>
-      </c>
-      <c r="B166" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" t="s">
-        <v>470</v>
-      </c>
-      <c r="B167" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B169" t="s">
-        <v>783</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1161</v>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" s="6" customFormat="1">
+      <c r="A166" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B168" t="s">
+        <v>766</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" s="6" customFormat="1">
+      <c r="A169" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>1151</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>586</v>
+        <v>620</v>
       </c>
       <c r="B170" t="s">
-        <v>846</v>
+        <v>621</v>
       </c>
       <c r="C170" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" t="s">
-        <v>628</v>
-      </c>
-      <c r="B171" t="s">
-        <v>629</v>
-      </c>
-      <c r="C171" t="s">
-        <v>597</v>
+        <v>593</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" s="6" customFormat="1">
+      <c r="A171" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>1151</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>714</v>
+        <v>699</v>
       </c>
       <c r="B172" t="s">
-        <v>847</v>
+        <v>829</v>
       </c>
       <c r="C172" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>715</v>
-      </c>
-      <c r="B173" t="s">
-        <v>848</v>
-      </c>
-      <c r="C173" t="s">
-        <v>597</v>
+        <v>700</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>716</v>
+        <v>1055</v>
       </c>
       <c r="B174" t="s">
-        <v>700</v>
+        <v>834</v>
       </c>
       <c r="C174" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B175" t="s">
-        <v>853</v>
-      </c>
-      <c r="C175" t="s">
-        <v>1089</v>
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" t="s">
+        <v>459</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1072</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>461</v>
+        <v>1078</v>
       </c>
       <c r="B177" t="s">
-        <v>1105</v>
+        <v>1079</v>
+      </c>
+      <c r="C177" t="s">
+        <v>1080</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>1111</v>
+        <v>232</v>
       </c>
       <c r="B178" t="s">
-        <v>1112</v>
+        <v>830</v>
       </c>
       <c r="C178" t="s">
-        <v>1113</v>
+        <v>524</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B179" t="s">
-        <v>849</v>
-      </c>
-      <c r="C179" t="s">
-        <v>526</v>
+        <v>831</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B180" t="s">
-        <v>850</v>
+        <v>832</v>
+      </c>
+      <c r="C180" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>241</v>
+        <v>674</v>
       </c>
       <c r="B181" t="s">
-        <v>851</v>
+        <v>833</v>
       </c>
       <c r="C181" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="B182" t="s">
-        <v>852</v>
-      </c>
-      <c r="C182" t="s">
-        <v>597</v>
+        <v>234</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>235</v>
+        <v>449</v>
       </c>
       <c r="B183" t="s">
-        <v>234</v>
+        <v>458</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>451</v>
+        <v>236</v>
       </c>
       <c r="B184" t="s">
-        <v>460</v>
+        <v>834</v>
+      </c>
+      <c r="C184" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B185" t="s">
-        <v>853</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1090</v>
+        <v>835</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B186" t="s">
-        <v>854</v>
+        <v>836</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B187" t="s">
-        <v>855</v>
+        <v>837</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B188" t="s">
-        <v>856</v>
+        <v>766</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="B189" t="s">
-        <v>783</v>
+        <v>834</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="B190" t="s">
-        <v>853</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1090</v>
+        <v>298</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>299</v>
+        <v>585</v>
       </c>
       <c r="B191" t="s">
-        <v>300</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>589</v>
-      </c>
-      <c r="B192" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" t="s">
-        <v>606</v>
-      </c>
-      <c r="B193" t="s">
-        <v>784</v>
+        <v>598</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" s="6" customFormat="1">
+      <c r="A193" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>1151</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>671</v>
-      </c>
-      <c r="B194" t="s">
-        <v>672</v>
-      </c>
-      <c r="C194" t="s">
-        <v>597</v>
+        <v>673</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>684</v>
-      </c>
-      <c r="B195" t="s">
-        <v>702</v>
-      </c>
-      <c r="C195" t="s">
-        <v>597</v>
+        <v>846</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>865</v>
+        <v>1117</v>
       </c>
       <c r="B196" t="s">
-        <v>866</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>469</v>
-      </c>
-      <c r="B197" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="A198" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B198" t="s">
-        <v>1186</v>
+        <v>467</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" t="s">
+        <v>672</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>682</v>
+        <v>460</v>
       </c>
       <c r="B200" t="s">
-        <v>683</v>
-      </c>
-      <c r="C200" t="s">
-        <v>597</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>462</v>
+        <v>242</v>
       </c>
       <c r="B201" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3">
+        <v>838</v>
+      </c>
+      <c r="C201" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="13.5" customHeight="1">
       <c r="A202" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B202" t="s">
-        <v>857</v>
+        <v>839</v>
       </c>
       <c r="C202" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" ht="13.5" customHeight="1">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B203" t="s">
-        <v>858</v>
-      </c>
-      <c r="C203" t="s">
-        <v>601</v>
+        <v>801</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>243</v>
-      </c>
-      <c r="B204" t="s">
-        <v>819</v>
+        <v>245</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -10291,34 +10338,34 @@
         <v>246</v>
       </c>
       <c r="B205" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B206" t="s">
         <v>248</v>
       </c>
+      <c r="C206" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="B207" t="s">
-        <v>249</v>
-      </c>
-      <c r="C207" t="s">
-        <v>591</v>
+        <v>506</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>452</v>
+        <v>250</v>
       </c>
       <c r="B208" t="s">
-        <v>508</v>
+        <v>803</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -10326,15 +10373,15 @@
         <v>251</v>
       </c>
       <c r="B209" t="s">
-        <v>821</v>
+        <v>252</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B210" t="s">
-        <v>253</v>
+        <v>804</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -10342,7 +10389,7 @@
         <v>257</v>
       </c>
       <c r="B211" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -10350,7 +10397,10 @@
         <v>258</v>
       </c>
       <c r="B212" t="s">
-        <v>823</v>
+        <v>840</v>
+      </c>
+      <c r="C212" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -10358,10 +10408,7 @@
         <v>259</v>
       </c>
       <c r="B213" t="s">
-        <v>859</v>
-      </c>
-      <c r="C213" t="s">
-        <v>591</v>
+        <v>806</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -10369,7 +10416,10 @@
         <v>260</v>
       </c>
       <c r="B214" t="s">
-        <v>824</v>
+        <v>841</v>
+      </c>
+      <c r="C214" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -10377,604 +10427,631 @@
         <v>261</v>
       </c>
       <c r="B215" t="s">
-        <v>860</v>
-      </c>
-      <c r="C215" t="s">
-        <v>591</v>
+        <v>807</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B216" t="s">
-        <v>825</v>
+        <v>269</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B217" t="s">
-        <v>270</v>
+        <v>834</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>271</v>
-      </c>
-      <c r="B218" t="s">
-        <v>853</v>
-      </c>
-      <c r="C218" t="s">
-        <v>1090</v>
+        <v>272</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>273</v>
-      </c>
-      <c r="B219" t="s">
-        <v>274</v>
+        <v>599</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>607</v>
-      </c>
-      <c r="B220" t="s">
-        <v>784</v>
+        <v>596</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>480</v>
-      </c>
-      <c r="B221" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3">
-      <c r="A222" t="s">
-        <v>602</v>
-      </c>
-      <c r="B222" t="s">
-        <v>603</v>
-      </c>
-      <c r="C222" t="s">
-        <v>597</v>
+        <v>478</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" t="s">
+        <v>461</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1074</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="B224" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>453</v>
+        <v>266</v>
       </c>
       <c r="B225" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
       <c r="A226" t="s">
         <v>267</v>
       </c>
       <c r="B226" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B227" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B228" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
       <c r="A229" t="s">
         <v>275</v>
       </c>
       <c r="B229" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>277</v>
-      </c>
-      <c r="B230" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2">
+        <v>600</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>608</v>
-      </c>
-      <c r="B231" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2">
-      <c r="A232" t="s">
-        <v>479</v>
-      </c>
-      <c r="B232" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2">
+        <v>477</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" t="s">
+        <v>462</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B234" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>454</v>
+        <v>278</v>
       </c>
       <c r="B235" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
       <c r="A236" t="s">
+        <v>279</v>
+      </c>
+      <c r="B236" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" t="s">
         <v>280</v>
       </c>
-      <c r="B236" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2">
-      <c r="A237" t="s">
-        <v>281</v>
-      </c>
       <c r="B237" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
       <c r="A238" t="s">
         <v>282</v>
       </c>
       <c r="B238" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
       <c r="A239" t="s">
+        <v>283</v>
+      </c>
+      <c r="B239" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" t="s">
         <v>284</v>
       </c>
-      <c r="B239" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2">
-      <c r="A240" t="s">
-        <v>285</v>
-      </c>
       <c r="B240" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B241" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>287</v>
-      </c>
-      <c r="B242" t="s">
-        <v>783</v>
+        <v>601</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>609</v>
+        <v>1129</v>
       </c>
       <c r="B243" t="s">
-        <v>784</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>478</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B245" t="s">
-        <v>1198</v>
+        <v>476</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" t="s">
+        <v>463</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1076</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="B247" t="s">
-        <v>1109</v>
+        <v>291</v>
+      </c>
+      <c r="C247" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B248" t="s">
-        <v>293</v>
-      </c>
-      <c r="C248" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>455</v>
+        <v>289</v>
       </c>
       <c r="B249" t="s">
-        <v>511</v>
+        <v>842</v>
+      </c>
+      <c r="C249" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B250" t="s">
-        <v>861</v>
-      </c>
-      <c r="C250" t="s">
-        <v>526</v>
+        <v>825</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>292</v>
+        <v>446</v>
       </c>
       <c r="B251" t="s">
-        <v>844</v>
+        <v>826</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>448</v>
+        <v>292</v>
       </c>
       <c r="B252" t="s">
-        <v>845</v>
+        <v>834</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1054</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B253" t="s">
-        <v>853</v>
-      </c>
-      <c r="C253" t="s">
-        <v>1087</v>
+        <v>843</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B254" t="s">
-        <v>862</v>
+        <v>844</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B255" t="s">
-        <v>863</v>
+        <v>845</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B256" t="s">
-        <v>864</v>
+        <v>766</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>298</v>
-      </c>
-      <c r="B257" t="s">
-        <v>783</v>
+        <v>602</v>
+      </c>
+      <c r="B257" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>610</v>
-      </c>
-      <c r="B258" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259" t="s">
-        <v>477</v>
-      </c>
-      <c r="B259" t="s">
-        <v>1137</v>
+        <v>475</v>
+      </c>
+      <c r="B258" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" t="s">
+        <v>634</v>
+      </c>
+      <c r="B260" t="s">
+        <v>635</v>
+      </c>
+      <c r="C260" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>643</v>
+        <v>492</v>
       </c>
       <c r="B261" t="s">
-        <v>644</v>
+        <v>495</v>
       </c>
       <c r="C261" t="s">
-        <v>597</v>
+        <v>522</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
+        <v>493</v>
+      </c>
+      <c r="B262" t="s">
         <v>494</v>
       </c>
-      <c r="B262" t="s">
-        <v>497</v>
-      </c>
       <c r="C262" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="B263" t="s">
-        <v>496</v>
-      </c>
-      <c r="C263" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>523</v>
+        <v>313</v>
       </c>
       <c r="B264" t="s">
-        <v>537</v>
+        <v>299</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B265" t="s">
-        <v>301</v>
+        <v>300</v>
+      </c>
+      <c r="C265" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>316</v>
+        <v>454</v>
       </c>
       <c r="B266" t="s">
-        <v>302</v>
-      </c>
-      <c r="C266" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>456</v>
+        <v>315</v>
       </c>
       <c r="B267" t="s">
-        <v>512</v>
+        <v>301</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B268" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
+        <v>317</v>
+      </c>
+      <c r="B269" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" s="6" customFormat="1">
+      <c r="A270" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B270" s="6" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="270" spans="1:3">
-      <c r="A270" t="s">
-        <v>319</v>
-      </c>
-      <c r="B270" t="s">
-        <v>305</v>
+      <c r="C270" s="6" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B271" t="s">
-        <v>306</v>
-      </c>
-      <c r="C271" t="s">
-        <v>526</v>
+        <v>305</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B272" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B273" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
+        <v>322</v>
+      </c>
+      <c r="B274" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" s="6" customFormat="1">
+      <c r="A275" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B275" s="6" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="275" spans="1:3">
-      <c r="A275" t="s">
-        <v>324</v>
-      </c>
-      <c r="B275" t="s">
-        <v>310</v>
+      <c r="C275" s="6" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B276" t="s">
-        <v>311</v>
-      </c>
-      <c r="C276" t="s">
-        <v>526</v>
+        <v>310</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B277" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B278" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>328</v>
-      </c>
-      <c r="B279" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" t="s">
-        <v>476</v>
-      </c>
-      <c r="B280" t="s">
-        <v>1138</v>
+        <v>474</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" t="s">
+        <v>539</v>
+      </c>
+      <c r="B281" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>541</v>
+        <v>333</v>
       </c>
       <c r="B282" t="s">
-        <v>542</v>
+        <v>351</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B283" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B284" t="s">
-        <v>350</v>
+        <v>349</v>
+      </c>
+      <c r="C284" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>337</v>
+        <v>455</v>
       </c>
       <c r="B285" t="s">
-        <v>351</v>
-      </c>
-      <c r="C285" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>457</v>
+        <v>352</v>
       </c>
       <c r="B286" t="s">
-        <v>513</v>
+        <v>350</v>
+      </c>
+      <c r="C286" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="B287" t="s">
-        <v>352</v>
-      </c>
-      <c r="C287" t="s">
-        <v>526</v>
+        <v>342</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="B288" t="s">
-        <v>344</v>
+        <v>343</v>
+      </c>
+      <c r="C288" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="B289" t="s">
-        <v>345</v>
-      </c>
-      <c r="C289" t="s">
-        <v>503</v>
+        <v>344</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -10982,15 +11059,15 @@
         <v>339</v>
       </c>
       <c r="B290" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B291" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -10998,1777 +11075,1867 @@
         <v>340</v>
       </c>
       <c r="B292" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B293" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>343</v>
+        <v>987</v>
       </c>
       <c r="B294" t="s">
-        <v>346</v>
+        <v>988</v>
+      </c>
+      <c r="C294" t="s">
+        <v>984</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>1014</v>
+        <v>989</v>
       </c>
       <c r="B295" t="s">
-        <v>1015</v>
+        <v>990</v>
       </c>
       <c r="C295" t="s">
-        <v>1010</v>
+        <v>984</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>1016</v>
+        <v>991</v>
       </c>
       <c r="B296" t="s">
-        <v>1017</v>
+        <v>992</v>
       </c>
       <c r="C296" t="s">
-        <v>1010</v>
+        <v>984</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>1018</v>
+        <v>1122</v>
       </c>
       <c r="B297" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C297" t="s">
-        <v>1010</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>475</v>
-      </c>
-      <c r="B298" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3">
-      <c r="A299" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B299" t="s">
-        <v>1191</v>
+        <v>473</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" t="s">
+        <v>636</v>
+      </c>
+      <c r="B300" t="s">
+        <v>653</v>
+      </c>
+      <c r="C300" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>645</v>
-      </c>
-      <c r="B301" t="s">
-        <v>663</v>
-      </c>
-      <c r="C301" t="s">
-        <v>597</v>
+        <v>983</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B302" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C302" t="s">
-        <v>1010</v>
+        <v>985</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B303" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C303" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3">
-      <c r="A304" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B304" t="s">
+        <v>986</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C303" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="C304" t="s">
-        <v>1010</v>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" t="s">
+        <v>632</v>
+      </c>
+      <c r="B305" t="s">
+        <v>633</v>
+      </c>
+      <c r="C305" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>641</v>
+        <v>464</v>
       </c>
       <c r="B306" t="s">
-        <v>642</v>
-      </c>
-      <c r="C306" t="s">
-        <v>597</v>
+        <v>465</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>466</v>
+        <v>359</v>
       </c>
       <c r="B307" t="s">
-        <v>467</v>
+        <v>370</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B308" t="s">
-        <v>372</v>
+        <v>371</v>
+      </c>
+      <c r="C308" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>362</v>
+        <v>512</v>
       </c>
       <c r="B309" t="s">
-        <v>373</v>
-      </c>
-      <c r="C309" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>514</v>
+        <v>361</v>
       </c>
       <c r="B310" t="s">
-        <v>515</v>
+        <v>372</v>
+      </c>
+      <c r="C310" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B311" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C311" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B312" t="s">
-        <v>375</v>
-      </c>
-      <c r="C312" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B313" t="s">
-        <v>527</v>
+        <v>374</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B314" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B315" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B316" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B317" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B318" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>371</v>
-      </c>
-      <c r="B319" t="s">
-        <v>381</v>
+        <v>687</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>698</v>
+        <v>1068</v>
       </c>
       <c r="B320" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C320" t="s">
-        <v>597</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B321" t="s">
-        <v>1102</v>
+        <v>548</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>473</v>
+        <v>1125</v>
       </c>
       <c r="B322" t="s">
-        <v>1141</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>550</v>
-      </c>
-      <c r="B323" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3">
-      <c r="A324" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B324" t="s">
-        <v>1194</v>
+        <v>471</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" t="s">
+        <v>466</v>
+      </c>
+      <c r="B325" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>468</v>
+        <v>386</v>
       </c>
       <c r="B326" t="s">
-        <v>467</v>
+        <v>397</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B327" t="s">
-        <v>399</v>
+        <v>398</v>
+      </c>
+      <c r="C327" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>389</v>
+        <v>456</v>
       </c>
       <c r="B328" t="s">
-        <v>400</v>
-      </c>
-      <c r="C328" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>458</v>
+        <v>388</v>
       </c>
       <c r="B329" t="s">
-        <v>516</v>
+        <v>399</v>
+      </c>
+      <c r="C329" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B330" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C330" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B331" t="s">
-        <v>402</v>
-      </c>
-      <c r="C331" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B332" t="s">
-        <v>528</v>
+        <v>374</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B333" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B334" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B335" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B336" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B337" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>398</v>
-      </c>
-      <c r="B338" t="s">
-        <v>381</v>
+        <v>554</v>
+      </c>
+      <c r="B338" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>472</v>
+        <v>1127</v>
       </c>
       <c r="B339" t="s">
-        <v>1141</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>557</v>
-      </c>
-      <c r="B340" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3">
-      <c r="A341" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B341" t="s">
-        <v>1196</v>
+        <v>470</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" t="s">
+        <v>630</v>
+      </c>
+      <c r="B342" t="s">
+        <v>631</v>
+      </c>
+      <c r="C342" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>639</v>
+        <v>380</v>
       </c>
       <c r="B343" t="s">
-        <v>640</v>
-      </c>
-      <c r="C343" t="s">
-        <v>597</v>
+        <v>555</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B344" t="s">
-        <v>558</v>
+        <v>556</v>
+      </c>
+      <c r="C344" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>383</v>
+        <v>457</v>
       </c>
       <c r="B345" t="s">
-        <v>559</v>
-      </c>
-      <c r="C345" t="s">
-        <v>526</v>
+        <v>557</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>459</v>
+        <v>382</v>
       </c>
       <c r="B346" t="s">
-        <v>560</v>
+        <v>582</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B347" t="s">
-        <v>585</v>
+        <v>558</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B348" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>386</v>
+        <v>1085</v>
       </c>
       <c r="B349" t="s">
-        <v>562</v>
+        <v>1086</v>
+      </c>
+      <c r="C349" t="s">
+        <v>1087</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B350" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C350" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3">
-      <c r="A351" t="s">
-        <v>471</v>
-      </c>
-      <c r="B351" t="s">
-        <v>1142</v>
+        <v>469</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" t="s">
+        <v>695</v>
+      </c>
+      <c r="B352" t="s">
+        <v>696</v>
+      </c>
+      <c r="C352" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>711</v>
-      </c>
-      <c r="B353" t="s">
-        <v>712</v>
-      </c>
-      <c r="C353" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3">
-      <c r="A354" t="s">
-        <v>713</v>
-      </c>
-      <c r="B354" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C354" t="s">
-        <v>597</v>
+        <v>697</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" t="s">
+        <v>702</v>
+      </c>
+      <c r="B355" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="B356" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="B357" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="B358" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="B359" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="B360" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="B361" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="B362" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="B363" t="s">
-        <v>733</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>734</v>
-      </c>
-      <c r="B364" t="s">
-        <v>1180</v>
+        <v>719</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="B365" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="B366" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
       <c r="B367" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
+        <v>726</v>
+      </c>
+      <c r="B368" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369" t="s">
+        <v>728</v>
+      </c>
+      <c r="B369" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370" t="s">
+        <v>730</v>
+      </c>
+      <c r="B370" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372" t="s">
+        <v>732</v>
+      </c>
+      <c r="B372" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" t="s">
+        <v>734</v>
+      </c>
+      <c r="B376" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" t="s">
+        <v>736</v>
+      </c>
+      <c r="B377" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" t="s">
+        <v>738</v>
+      </c>
+      <c r="B378" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" t="s">
+        <v>740</v>
+      </c>
+      <c r="B379" t="s">
         <v>741</v>
       </c>
-      <c r="B368" t="s">
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="A369" t="s">
+      <c r="B380" t="s">
         <v>743</v>
       </c>
-      <c r="B369" t="s">
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="A370" t="s">
+      <c r="B381" t="s">
         <v>745</v>
       </c>
-      <c r="B370" t="s">
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="371" spans="1:2">
-      <c r="A371" t="s">
+      <c r="B382" t="s">
         <v>747</v>
       </c>
-      <c r="B371" t="s">
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="372" spans="1:2">
-      <c r="A372" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B372" t="s">
+      <c r="B383" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384" t="s">
+        <v>749</v>
+      </c>
+      <c r="B384" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385" t="s">
+        <v>751</v>
+      </c>
+      <c r="B385" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3">
+      <c r="A386" t="s">
+        <v>753</v>
+      </c>
+      <c r="B386" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3">
+      <c r="A387" t="s">
+        <v>755</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" t="s">
+        <v>756</v>
+      </c>
+      <c r="B389" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" t="s">
+        <v>757</v>
+      </c>
+      <c r="B390" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391" t="s">
+        <v>759</v>
+      </c>
+      <c r="B391" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392" t="s">
+        <v>760</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" t="s">
+        <v>781</v>
+      </c>
+      <c r="B394" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395" t="s">
+        <v>780</v>
+      </c>
+      <c r="B395" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396" t="s">
+        <v>774</v>
+      </c>
+      <c r="B396" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397" t="s">
+        <v>772</v>
+      </c>
+      <c r="B397" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398" t="s">
+        <v>773</v>
+      </c>
+      <c r="B398" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399" t="s">
+        <v>778</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" t="s">
+        <v>785</v>
+      </c>
+      <c r="B401" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402" t="s">
+        <v>792</v>
+      </c>
+      <c r="B402" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403" t="s">
+        <v>786</v>
+      </c>
+      <c r="B403" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3">
+      <c r="A404" t="s">
+        <v>787</v>
+      </c>
+      <c r="B404" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405" t="s">
+        <v>788</v>
+      </c>
+      <c r="B405" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406" t="s">
+        <v>789</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408" t="s">
+        <v>797</v>
+      </c>
+      <c r="B408" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3">
+      <c r="A409" t="s">
+        <v>799</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3">
+      <c r="A410" t="s">
+        <v>800</v>
+      </c>
+      <c r="B410" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3">
+      <c r="A411" t="s">
+        <v>802</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3">
+      <c r="A412" t="s">
+        <v>808</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3">
+      <c r="A413" t="s">
+        <v>809</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3">
+      <c r="A414" t="s">
+        <v>810</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3">
+      <c r="A415" t="s">
+        <v>813</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3">
+      <c r="A416" t="s">
+        <v>814</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417" t="s">
+        <v>815</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3">
+      <c r="A418" t="s">
+        <v>816</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3">
+      <c r="A419" t="s">
+        <v>817</v>
+      </c>
+      <c r="B419" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3">
+      <c r="A420" t="s">
+        <v>818</v>
+      </c>
+      <c r="B420" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3">
+      <c r="A421" t="s">
+        <v>819</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3">
+      <c r="A422" t="s">
+        <v>820</v>
+      </c>
+      <c r="B422" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3">
+      <c r="A423" t="s">
+        <v>821</v>
+      </c>
+      <c r="B423" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3">
+      <c r="A424" t="s">
+        <v>812</v>
+      </c>
+      <c r="B424" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3">
+      <c r="A425" t="s">
+        <v>811</v>
+      </c>
+      <c r="B425" s="5" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3">
+      <c r="A426" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3">
+      <c r="A427" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3">
+      <c r="A428" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3">
+      <c r="A429" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3">
+      <c r="A430" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3">
+      <c r="A431" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3">
+      <c r="A432" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3">
+      <c r="A433" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3">
+      <c r="A434" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B434" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3">
+      <c r="A435" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437" t="s">
+        <v>877</v>
+      </c>
+      <c r="B437" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3">
+      <c r="A438" t="s">
+        <v>896</v>
+      </c>
+      <c r="B438" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3">
+      <c r="A439" t="s">
+        <v>895</v>
+      </c>
+      <c r="B439" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3">
+      <c r="A440" t="s">
+        <v>894</v>
+      </c>
+      <c r="B440" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3">
+      <c r="A441" t="s">
+        <v>893</v>
+      </c>
+      <c r="B441" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3">
+      <c r="A442" t="s">
+        <v>892</v>
+      </c>
+      <c r="B442" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3">
+      <c r="A443" t="s">
+        <v>891</v>
+      </c>
+      <c r="B443" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3">
+      <c r="A444" t="s">
+        <v>890</v>
+      </c>
+      <c r="B444" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3">
+      <c r="A445" t="s">
+        <v>889</v>
+      </c>
+      <c r="B445" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3">
+      <c r="A446" t="s">
+        <v>888</v>
+      </c>
+      <c r="B446" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3">
+      <c r="A447" t="s">
+        <v>887</v>
+      </c>
+      <c r="B447" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448" t="s">
+        <v>897</v>
+      </c>
+      <c r="B448" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3">
+      <c r="A449" t="s">
+        <v>886</v>
+      </c>
+      <c r="B449" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3">
+      <c r="A450" t="s">
+        <v>885</v>
+      </c>
+      <c r="B450" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3">
+      <c r="A451" t="s">
+        <v>884</v>
+      </c>
+      <c r="B451" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3">
+      <c r="A452" t="s">
+        <v>883</v>
+      </c>
+      <c r="B452" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C452" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3">
+      <c r="A453" t="s">
+        <v>882</v>
+      </c>
+      <c r="B453" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3">
+      <c r="A454" t="s">
+        <v>881</v>
+      </c>
+      <c r="B454" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3">
+      <c r="A455" t="s">
+        <v>880</v>
+      </c>
+      <c r="B455" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3">
+      <c r="A456" t="s">
+        <v>879</v>
+      </c>
+      <c r="B456" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3">
+      <c r="A457" t="s">
         <v>1095</v>
       </c>
-    </row>
-    <row r="373" spans="1:2">
-      <c r="A373" t="s">
-        <v>749</v>
-      </c>
-      <c r="B373" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="374" spans="1:2">
-      <c r="A374" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B374" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2">
-      <c r="A375" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B375" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="377" spans="1:2">
-      <c r="A377" t="s">
-        <v>751</v>
-      </c>
-      <c r="B377" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="378" spans="1:2">
-      <c r="A378" t="s">
-        <v>753</v>
-      </c>
-      <c r="B378" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="379" spans="1:2">
-      <c r="A379" t="s">
-        <v>755</v>
-      </c>
-      <c r="B379" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="380" spans="1:2">
-      <c r="A380" t="s">
-        <v>757</v>
-      </c>
-      <c r="B380" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="381" spans="1:2">
-      <c r="A381" t="s">
-        <v>759</v>
-      </c>
-      <c r="B381" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2">
-      <c r="A382" t="s">
-        <v>761</v>
-      </c>
-      <c r="B382" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2">
-      <c r="A383" t="s">
-        <v>763</v>
-      </c>
-      <c r="B383" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="384" spans="1:2">
-      <c r="A384" t="s">
-        <v>765</v>
-      </c>
-      <c r="B384" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="385" spans="1:2">
-      <c r="A385" t="s">
-        <v>766</v>
-      </c>
-      <c r="B385" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="386" spans="1:2">
-      <c r="A386" t="s">
-        <v>768</v>
-      </c>
-      <c r="B386" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="387" spans="1:2">
-      <c r="A387" t="s">
-        <v>770</v>
-      </c>
-      <c r="B387" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="388" spans="1:2">
-      <c r="A388" t="s">
-        <v>772</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="390" spans="1:2">
-      <c r="A390" t="s">
-        <v>773</v>
-      </c>
-      <c r="B390" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="391" spans="1:2">
-      <c r="A391" t="s">
-        <v>774</v>
-      </c>
-      <c r="B391" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="392" spans="1:2">
-      <c r="A392" t="s">
-        <v>776</v>
-      </c>
-      <c r="B392" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="393" spans="1:2">
-      <c r="A393" t="s">
-        <v>777</v>
-      </c>
-      <c r="B393" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="395" spans="1:2">
-      <c r="A395" t="s">
-        <v>799</v>
-      </c>
-      <c r="B395" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="396" spans="1:2">
-      <c r="A396" t="s">
-        <v>798</v>
-      </c>
-      <c r="B396" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="397" spans="1:2">
-      <c r="A397" t="s">
-        <v>792</v>
-      </c>
-      <c r="B397" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="398" spans="1:2">
-      <c r="A398" t="s">
-        <v>790</v>
-      </c>
-      <c r="B398" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="399" spans="1:2">
-      <c r="A399" t="s">
-        <v>791</v>
-      </c>
-      <c r="B399" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="400" spans="1:2">
-      <c r="A400" t="s">
-        <v>796</v>
-      </c>
-      <c r="B400" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="402" spans="1:2">
-      <c r="A402" t="s">
-        <v>803</v>
-      </c>
-      <c r="B402" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="403" spans="1:2">
-      <c r="A403" t="s">
-        <v>810</v>
-      </c>
-      <c r="B403" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="404" spans="1:2">
-      <c r="A404" t="s">
-        <v>804</v>
-      </c>
-      <c r="B404" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="405" spans="1:2">
-      <c r="A405" t="s">
-        <v>805</v>
-      </c>
-      <c r="B405" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="406" spans="1:2">
-      <c r="A406" t="s">
-        <v>806</v>
-      </c>
-      <c r="B406" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="407" spans="1:2">
-      <c r="A407" t="s">
-        <v>807</v>
-      </c>
-      <c r="B407" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="409" spans="1:2">
-      <c r="A409" t="s">
-        <v>815</v>
-      </c>
-      <c r="B409" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="410" spans="1:2">
-      <c r="A410" t="s">
-        <v>817</v>
-      </c>
-      <c r="B410" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="411" spans="1:2">
-      <c r="A411" t="s">
-        <v>818</v>
-      </c>
-      <c r="B411" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="412" spans="1:2">
-      <c r="A412" t="s">
-        <v>820</v>
-      </c>
-      <c r="B412" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="413" spans="1:2">
-      <c r="A413" t="s">
-        <v>826</v>
-      </c>
-      <c r="B413" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="414" spans="1:2">
-      <c r="A414" t="s">
-        <v>827</v>
-      </c>
-      <c r="B414" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="415" spans="1:2">
-      <c r="A415" t="s">
-        <v>828</v>
-      </c>
-      <c r="B415" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="416" spans="1:2">
-      <c r="A416" t="s">
-        <v>831</v>
-      </c>
-      <c r="B416" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="417" spans="1:2">
-      <c r="A417" t="s">
-        <v>832</v>
-      </c>
-      <c r="B417" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="418" spans="1:2">
-      <c r="A418" t="s">
-        <v>833</v>
-      </c>
-      <c r="B418" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="419" spans="1:2">
-      <c r="A419" t="s">
-        <v>834</v>
-      </c>
-      <c r="B419" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="420" spans="1:2">
-      <c r="A420" t="s">
-        <v>835</v>
-      </c>
-      <c r="B420" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="421" spans="1:2">
-      <c r="A421" t="s">
-        <v>836</v>
-      </c>
-      <c r="B421" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="422" spans="1:2">
-      <c r="A422" t="s">
-        <v>837</v>
-      </c>
-      <c r="B422" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="423" spans="1:2">
-      <c r="A423" t="s">
-        <v>838</v>
-      </c>
-      <c r="B423" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="424" spans="1:2">
-      <c r="A424" t="s">
-        <v>839</v>
-      </c>
-      <c r="B424" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="425" spans="1:2">
-      <c r="A425" t="s">
-        <v>830</v>
-      </c>
-      <c r="B425" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="426" spans="1:2">
-      <c r="A426" t="s">
-        <v>829</v>
-      </c>
-      <c r="B426" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="427" spans="1:2">
-      <c r="A427" t="s">
+      <c r="B457" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3">
+      <c r="A458" t="s">
+        <v>878</v>
+      </c>
+      <c r="B458" s="5" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C458" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3">
+      <c r="A460" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3">
+      <c r="A461" t="s">
+        <v>915</v>
+      </c>
+      <c r="B461" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3">
+      <c r="A462" t="s">
+        <v>906</v>
+      </c>
+      <c r="B462" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3">
+      <c r="A463" t="s">
+        <v>907</v>
+      </c>
+      <c r="B463" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3">
+      <c r="A464" t="s">
+        <v>908</v>
+      </c>
+      <c r="B464" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3">
+      <c r="A465" t="s">
+        <v>911</v>
+      </c>
+      <c r="B465" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3">
+      <c r="A466" t="s">
+        <v>909</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3">
+      <c r="A467" t="s">
+        <v>912</v>
+      </c>
+      <c r="B467" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3">
+      <c r="A468" t="s">
+        <v>910</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3">
+      <c r="A469" t="s">
+        <v>914</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3">
+      <c r="A470" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3">
+      <c r="A471" t="s">
+        <v>913</v>
+      </c>
+      <c r="B471" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C471" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3">
+      <c r="A473" t="s">
+        <v>920</v>
+      </c>
+      <c r="B473" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C473" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" s="6" customFormat="1">
+      <c r="A474" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="B474" s="6" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C474" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" s="6" customFormat="1">
+      <c r="A476" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="B476" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="C476" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3">
+      <c r="A477" t="s">
+        <v>930</v>
+      </c>
+      <c r="B477" s="5" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C477" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3">
+      <c r="A479" t="s">
+        <v>927</v>
+      </c>
+      <c r="B479" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3">
+      <c r="A480" t="s">
+        <v>928</v>
+      </c>
+      <c r="B480" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3">
+      <c r="A481" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3">
+      <c r="A482" t="s">
+        <v>924</v>
+      </c>
+      <c r="B482" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C482" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484" t="s">
+        <v>938</v>
+      </c>
+      <c r="B484" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3">
+      <c r="A485" t="s">
+        <v>939</v>
+      </c>
+      <c r="B485" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3">
+      <c r="A486" t="s">
+        <v>940</v>
+      </c>
+      <c r="B486" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3">
+      <c r="A487" t="s">
+        <v>982</v>
+      </c>
+      <c r="B487" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3">
+      <c r="A488" t="s">
+        <v>941</v>
+      </c>
+      <c r="B488" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3">
+      <c r="A489" t="s">
+        <v>942</v>
+      </c>
+      <c r="B489" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3">
+      <c r="A490" t="s">
+        <v>943</v>
+      </c>
+      <c r="B490" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C490" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3">
+      <c r="A492" t="s">
+        <v>954</v>
+      </c>
+      <c r="B492" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3">
+      <c r="A493" t="s">
+        <v>959</v>
+      </c>
+      <c r="B493" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3">
+      <c r="A494" t="s">
+        <v>955</v>
+      </c>
+      <c r="B494" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3">
+      <c r="A495" t="s">
+        <v>956</v>
+      </c>
+      <c r="B495" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3">
+      <c r="A496" t="s">
+        <v>958</v>
+      </c>
+      <c r="B496" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3">
+      <c r="A497" t="s">
+        <v>957</v>
+      </c>
+      <c r="B497" s="7" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C497" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3">
+      <c r="A499" t="s">
+        <v>971</v>
+      </c>
+      <c r="B499" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3">
+      <c r="A500" t="s">
+        <v>966</v>
+      </c>
+      <c r="B500" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3">
+      <c r="A501" t="s">
+        <v>967</v>
+      </c>
+      <c r="B501" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3">
+      <c r="A502" t="s">
+        <v>968</v>
+      </c>
+      <c r="B502" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3">
+      <c r="A503" t="s">
+        <v>969</v>
+      </c>
+      <c r="B503" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" s="6" customFormat="1">
+      <c r="A504" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="B504" s="6" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C504" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" s="6" customFormat="1">
+      <c r="A506" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="B506" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="C506" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3">
+      <c r="A507" t="s">
+        <v>977</v>
+      </c>
+      <c r="B507" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3">
+      <c r="A508" t="s">
+        <v>978</v>
+      </c>
+      <c r="B508" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3">
+      <c r="A509" t="s">
+        <v>979</v>
+      </c>
+      <c r="B509" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3">
+      <c r="A510" t="s">
+        <v>980</v>
+      </c>
+      <c r="B510" s="7" t="s">
         <v>1192</v>
       </c>
-      <c r="B427" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="428" spans="1:2">
-      <c r="A428" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B428" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="429" spans="1:2">
-      <c r="A429" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B429" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="430" spans="1:2">
-      <c r="A430" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B430" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="431" spans="1:2">
-      <c r="A431" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B431" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="432" spans="1:2">
-      <c r="A432" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B432" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="433" spans="1:2">
-      <c r="A433" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B433" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="434" spans="1:2">
-      <c r="A434" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B434" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="435" spans="1:2">
-      <c r="A435" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B435" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="436" spans="1:2">
-      <c r="A436" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B436" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="438" spans="1:2">
-      <c r="A438" t="s">
-        <v>899</v>
-      </c>
-      <c r="B438" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="439" spans="1:2">
-      <c r="A439" t="s">
-        <v>918</v>
-      </c>
-      <c r="B439" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="440" spans="1:2">
-      <c r="A440" t="s">
-        <v>917</v>
-      </c>
-      <c r="B440" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="441" spans="1:2">
-      <c r="A441" t="s">
-        <v>916</v>
-      </c>
-      <c r="B441" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="442" spans="1:2">
-      <c r="A442" t="s">
-        <v>915</v>
-      </c>
-      <c r="B442" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="443" spans="1:2">
-      <c r="A443" t="s">
-        <v>914</v>
-      </c>
-      <c r="B443" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="444" spans="1:2">
-      <c r="A444" t="s">
-        <v>913</v>
-      </c>
-      <c r="B444" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="445" spans="1:2">
-      <c r="A445" t="s">
-        <v>912</v>
-      </c>
-      <c r="B445" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="446" spans="1:2">
-      <c r="A446" t="s">
-        <v>911</v>
-      </c>
-      <c r="B446" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="447" spans="1:2">
-      <c r="A447" t="s">
-        <v>910</v>
-      </c>
-      <c r="B447" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="448" spans="1:2">
-      <c r="A448" t="s">
-        <v>909</v>
-      </c>
-      <c r="B448" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="449" spans="1:2">
-      <c r="A449" t="s">
-        <v>919</v>
-      </c>
-      <c r="B449" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="450" spans="1:2">
-      <c r="A450" t="s">
-        <v>908</v>
-      </c>
-      <c r="B450" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="451" spans="1:2">
-      <c r="A451" t="s">
-        <v>907</v>
-      </c>
-      <c r="B451" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="452" spans="1:2">
-      <c r="A452" t="s">
-        <v>906</v>
-      </c>
-      <c r="B452" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="453" spans="1:2">
-      <c r="A453" t="s">
-        <v>905</v>
-      </c>
-      <c r="B453" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="454" spans="1:2">
-      <c r="A454" t="s">
-        <v>904</v>
-      </c>
-      <c r="B454" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="455" spans="1:2">
-      <c r="A455" t="s">
-        <v>903</v>
-      </c>
-      <c r="B455" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="456" spans="1:2">
-      <c r="A456" t="s">
-        <v>902</v>
-      </c>
-      <c r="B456" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="457" spans="1:2">
-      <c r="A457" t="s">
-        <v>901</v>
-      </c>
-      <c r="B457" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="458" spans="1:2">
-      <c r="A458" t="s">
-        <v>900</v>
-      </c>
-      <c r="B458" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="459" spans="1:2">
-      <c r="A459" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B459" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="461" spans="1:2">
-      <c r="A461" t="s">
-        <v>1121</v>
-      </c>
-      <c r="B461" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="462" spans="1:2">
-      <c r="A462" t="s">
-        <v>937</v>
-      </c>
-      <c r="B462" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="463" spans="1:2">
-      <c r="A463" t="s">
-        <v>928</v>
-      </c>
-      <c r="B463" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="464" spans="1:2">
-      <c r="A464" t="s">
-        <v>929</v>
-      </c>
-      <c r="B464" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="465" spans="1:2">
-      <c r="A465" t="s">
-        <v>930</v>
-      </c>
-      <c r="B465" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="466" spans="1:2">
-      <c r="A466" t="s">
-        <v>933</v>
-      </c>
-      <c r="B466" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="467" spans="1:2">
-      <c r="A467" t="s">
-        <v>931</v>
-      </c>
-      <c r="B467" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="468" spans="1:2">
-      <c r="A468" t="s">
-        <v>934</v>
-      </c>
-      <c r="B468" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="469" spans="1:2">
-      <c r="A469" t="s">
-        <v>932</v>
-      </c>
-      <c r="B469" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="470" spans="1:2">
-      <c r="A470" t="s">
-        <v>936</v>
-      </c>
-      <c r="B470" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="471" spans="1:2">
-      <c r="A471" t="s">
-        <v>935</v>
-      </c>
-      <c r="B471" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="472" spans="1:2">
-      <c r="A472" t="s">
-        <v>1170</v>
-      </c>
-      <c r="B472" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="474" spans="1:2">
-      <c r="A474" t="s">
-        <v>942</v>
-      </c>
-      <c r="B474" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="475" spans="1:2">
-      <c r="A475" t="s">
-        <v>952</v>
-      </c>
-      <c r="B475" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="477" spans="1:2">
-      <c r="A477" t="s">
-        <v>943</v>
-      </c>
-      <c r="B477" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="478" spans="1:2">
-      <c r="A478" t="s">
-        <v>953</v>
-      </c>
-      <c r="B478" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="480" spans="1:2">
-      <c r="A480" t="s">
-        <v>950</v>
-      </c>
-      <c r="B480" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="481" spans="1:2">
-      <c r="A481" t="s">
-        <v>951</v>
-      </c>
-      <c r="B481" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="482" spans="1:2">
-      <c r="A482" t="s">
-        <v>947</v>
-      </c>
-      <c r="B482" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="483" spans="1:2">
-      <c r="A483" t="s">
-        <v>1188</v>
-      </c>
-      <c r="B483" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="485" spans="1:2">
-      <c r="A485" t="s">
-        <v>962</v>
-      </c>
-      <c r="B485" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="486" spans="1:2">
-      <c r="A486" t="s">
-        <v>963</v>
-      </c>
-      <c r="B486" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="487" spans="1:2">
-      <c r="A487" t="s">
-        <v>964</v>
-      </c>
-      <c r="B487" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="488" spans="1:2">
-      <c r="A488" t="s">
+      <c r="C510" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3">
+      <c r="A512" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3">
+      <c r="A513" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3">
+      <c r="A514" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3">
+      <c r="A515" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3">
+      <c r="A516" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3">
+      <c r="A517" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B517" t="s">
         <v>1007</v>
       </c>
-      <c r="B488" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="489" spans="1:2">
-      <c r="A489" t="s">
-        <v>965</v>
-      </c>
-      <c r="B489" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="490" spans="1:2">
-      <c r="A490" t="s">
-        <v>966</v>
-      </c>
-      <c r="B490" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="491" spans="1:2">
-      <c r="A491" t="s">
-        <v>967</v>
-      </c>
-      <c r="B491" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="493" spans="1:2">
-      <c r="A493" t="s">
-        <v>978</v>
-      </c>
-      <c r="B493" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="494" spans="1:2">
-      <c r="A494" t="s">
-        <v>983</v>
-      </c>
-      <c r="B494" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="495" spans="1:2">
-      <c r="A495" t="s">
-        <v>979</v>
-      </c>
-      <c r="B495" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="496" spans="1:2">
-      <c r="A496" t="s">
-        <v>980</v>
-      </c>
-      <c r="B496" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="497" spans="1:2">
-      <c r="A497" t="s">
-        <v>982</v>
-      </c>
-      <c r="B497" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="498" spans="1:2">
-      <c r="A498" t="s">
-        <v>981</v>
-      </c>
-      <c r="B498" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="500" spans="1:2">
-      <c r="A500" t="s">
-        <v>995</v>
-      </c>
-      <c r="B500" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="501" spans="1:2">
-      <c r="A501" t="s">
-        <v>990</v>
-      </c>
-      <c r="B501" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="502" spans="1:2">
-      <c r="A502" t="s">
-        <v>991</v>
-      </c>
-      <c r="B502" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="503" spans="1:2">
-      <c r="A503" t="s">
-        <v>992</v>
-      </c>
-      <c r="B503" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="504" spans="1:2">
-      <c r="A504" t="s">
-        <v>993</v>
-      </c>
-      <c r="B504" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="505" spans="1:2">
-      <c r="A505" t="s">
-        <v>994</v>
-      </c>
-      <c r="B505" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="507" spans="1:2">
-      <c r="A507" t="s">
-        <v>996</v>
-      </c>
-      <c r="B507" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="508" spans="1:2">
-      <c r="A508" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B508" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="509" spans="1:2">
-      <c r="A509" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B509" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="510" spans="1:2">
-      <c r="A510" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B510" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="511" spans="1:2">
-      <c r="A511" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B511" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="513" spans="1:2">
-      <c r="A513" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B513" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="514" spans="1:2">
-      <c r="A514" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B514" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="515" spans="1:2">
-      <c r="A515" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B515" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="516" spans="1:2">
-      <c r="A516" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B516" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="517" spans="1:2">
-      <c r="A517" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B517" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="518" spans="1:2">
+    </row>
+    <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>1047</v>
+        <v>1020</v>
       </c>
       <c r="B518" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="519" spans="1:2">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>1048</v>
+        <v>1021</v>
       </c>
       <c r="B519" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="520" spans="1:2">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>1049</v>
+        <v>1022</v>
       </c>
       <c r="B520" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="521" spans="1:2">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>1050</v>
+        <v>1023</v>
       </c>
       <c r="B521" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="522" spans="1:2">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>1051</v>
+        <v>1024</v>
       </c>
       <c r="B522" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="523" spans="1:2">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>1052</v>
+        <v>1025</v>
       </c>
       <c r="B523" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="524" spans="1:2">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>1053</v>
+        <v>1026</v>
       </c>
       <c r="B524" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="525" spans="1:2">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3">
       <c r="A525" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B525" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="526" spans="1:2">
-      <c r="A526" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1042</v>
+        <v>1015</v>
+      </c>
+      <c r="B525" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C525" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A480:A481 A477:A478 A462:A472 A474:A475 A483">
+  <autoFilter ref="A1:C525" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
+  <conditionalFormatting sqref="A479:A481 A476:A477 A461:A471 A473:A474">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0917\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB860014-17DB-4C70-9BAA-43AA819DFEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B421EADC-F564-428C-98C6-8E766477E33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3456,9 +3456,6 @@
     <t>DocumentTypeUserPrompt_AZ.txt</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>Assets exceed HUD asset limit. Third party verification of all assets is required.</t>
   </si>
   <si>
@@ -3655,6 +3652,9 @@
   </si>
   <si>
     <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4138,7 +4138,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1137</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -8679,10 +8679,10 @@
         <v>652</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C13" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8741,10 +8741,10 @@
         <v>589</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C21" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8752,10 +8752,10 @@
         <v>597</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C22" t="s">
         <v>1139</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8774,10 +8774,10 @@
         <v>622</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C24" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8785,10 +8785,10 @@
         <v>624</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C25" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8796,10 +8796,10 @@
         <v>691</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C26" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8807,10 +8807,10 @@
         <v>824</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C27" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8818,7 +8818,7 @@
         <v>472</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8952,7 +8952,7 @@
         <v>487</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9059,10 +9059,10 @@
         <v>594</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C59" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -9070,10 +9070,10 @@
         <v>486</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C60" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9241,7 +9241,7 @@
         <v>485</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9281,10 +9281,10 @@
         <v>648</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C85" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -9325,7 +9325,7 @@
         <v>484</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9504,10 +9504,10 @@
         <v>847</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C109" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -9539,7 +9539,7 @@
         <v>483</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -9657,7 +9657,7 @@
         <v>482</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9724,10 +9724,10 @@
         <v>561</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C134" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -9754,7 +9754,7 @@
         <v>481</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -9773,7 +9773,7 @@
         <v>608</v>
       </c>
       <c r="B140" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C140" t="s">
         <v>607</v>
@@ -9846,7 +9846,7 @@
         <v>480</v>
       </c>
       <c r="B149" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -9886,7 +9886,7 @@
         <v>479</v>
       </c>
       <c r="B155" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -9981,10 +9981,10 @@
         <v>468</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -10006,7 +10006,7 @@
         <v>827</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -10028,7 +10028,7 @@
         <v>828</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -10047,10 +10047,10 @@
         <v>700</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -10215,10 +10215,10 @@
         <v>598</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="6" customFormat="1">
@@ -10229,7 +10229,7 @@
         <v>662</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -10237,10 +10237,10 @@
         <v>673</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -10248,10 +10248,10 @@
         <v>846</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -10267,10 +10267,10 @@
         <v>467</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -10278,10 +10278,10 @@
         <v>672</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -10327,10 +10327,10 @@
         <v>245</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -10454,10 +10454,10 @@
         <v>272</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -10465,10 +10465,10 @@
         <v>599</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -10476,10 +10476,10 @@
         <v>596</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -10487,10 +10487,10 @@
         <v>478</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -10554,10 +10554,10 @@
         <v>600</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -10565,10 +10565,10 @@
         <v>477</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -10648,10 +10648,10 @@
         <v>601</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -10667,10 +10667,10 @@
         <v>476</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -10775,10 +10775,10 @@
         <v>602</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -10786,10 +10786,10 @@
         <v>475</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -10967,10 +10967,10 @@
         <v>474</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -11132,10 +11132,10 @@
         <v>473</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -11154,10 +11154,10 @@
         <v>983</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -11165,10 +11165,10 @@
         <v>985</v>
       </c>
       <c r="B302" s="7" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -11176,10 +11176,10 @@
         <v>986</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -11311,10 +11311,10 @@
         <v>687</v>
       </c>
       <c r="B319" s="7" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -11330,10 +11330,10 @@
         <v>548</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -11349,10 +11349,10 @@
         <v>471</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -11473,10 +11473,10 @@
         <v>554</v>
       </c>
       <c r="B338" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -11492,10 +11492,10 @@
         <v>470</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -11576,10 +11576,10 @@
         <v>469</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -11598,10 +11598,10 @@
         <v>697</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -11681,10 +11681,10 @@
         <v>719</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -11764,10 +11764,10 @@
         <v>1084</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -11863,10 +11863,10 @@
         <v>755</v>
       </c>
       <c r="B387" s="7" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11946,10 +11946,10 @@
         <v>778</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11997,10 +11997,10 @@
         <v>789</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -12024,10 +12024,10 @@
         <v>800</v>
       </c>
       <c r="B410" s="7" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -12043,10 +12043,10 @@
         <v>808</v>
       </c>
       <c r="B412" s="7" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -12126,10 +12126,10 @@
         <v>820</v>
       </c>
       <c r="B422" s="7" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -12137,10 +12137,10 @@
         <v>821</v>
       </c>
       <c r="B423" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -12148,10 +12148,10 @@
         <v>812</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -12159,10 +12159,10 @@
         <v>811</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -12234,10 +12234,10 @@
         <v>1051</v>
       </c>
       <c r="B434" s="7" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -12373,10 +12373,10 @@
         <v>883</v>
       </c>
       <c r="B452" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -12424,10 +12424,10 @@
         <v>878</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -12523,10 +12523,10 @@
         <v>913</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -12534,10 +12534,10 @@
         <v>920</v>
       </c>
       <c r="B473" s="7" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="6" customFormat="1">
@@ -12545,10 +12545,10 @@
         <v>929</v>
       </c>
       <c r="B474" s="6" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="476" spans="1:3" s="6" customFormat="1">
@@ -12559,7 +12559,7 @@
         <v>922</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -12567,10 +12567,10 @@
         <v>930</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12602,10 +12602,10 @@
         <v>924</v>
       </c>
       <c r="B482" s="7" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -12661,10 +12661,10 @@
         <v>943</v>
       </c>
       <c r="B490" s="7" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12712,10 +12712,10 @@
         <v>957</v>
       </c>
       <c r="B497" s="7" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12766,7 +12766,7 @@
         <v>1090</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="6" customFormat="1">
@@ -12777,7 +12777,7 @@
         <v>973</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12809,10 +12809,10 @@
         <v>980</v>
       </c>
       <c r="B510" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12924,10 +12924,10 @@
         <v>1015</v>
       </c>
       <c r="B525" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0917\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B421EADC-F564-428C-98C6-8E766477E33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBE1C8F-0FB4-4E6C-90E3-D7E8AD8716E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3654,7 +3654,7 @@
     <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0918\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBE1C8F-0FB4-4E6C-90E3-D7E8AD8716E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F4296D-FC3A-4E12-8825-77EC655F214C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3654,7 +3654,7 @@
     <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0918\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F4296D-FC3A-4E12-8825-77EC655F214C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6B0C54-09B6-4CA6-BF8B-DF21306A78A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3459,174 +3459,30 @@
     <t>Assets exceed HUD asset limit. Third party verification of all assets is required.</t>
   </si>
   <si>
-    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Updated by Raluca</t>
   </si>
   <si>
-    <t>Applicant is a Dominium employee. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Income type included that cannot be validated with automation. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Annual income is listed as zero. Confirm this is accurate and ensure the Certification of Zero Income is present in the file.</t>
   </si>
   <si>
-    <t>This application is a Section 811 unit. Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Unable to validate Income Calculation Worksheet. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Member Information Document. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Applicant reported a minor will live in the household less than 50% of the time. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Current employment has been documented on the Self-Certification of Non-Employment. Verification of employment is needed.</t>
   </si>
   <si>
     <t>Applicant has reported they have no assets. If applicant has income, confirm how the income is paid.</t>
   </si>
   <si>
-    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Raluca removed the check as per business requirement</t>
   </si>
   <si>
     <t>Multiple sources of verification included for same income. Remove verification documents that are not being used in the calculation of income.</t>
   </si>
   <si>
-    <t>Regular pay rate has increased across paystubs. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Paystubs list YTD pay that is not paid on a current paystub so annual income cannot be accurately predicted. Clarify, with the employer, the pay type and how often it is received.</t>
   </si>
   <si>
-    <t>Unable to validate paystubs. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Verification of Employment - manual review is needed to ensure document was received via 3rd party.</t>
-  </si>
-  <si>
-    <t>Anticipated wage increase indicated on employment verification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Employment. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Offer Letter. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Work Number. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self-Employment Certification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Housing History Disclosure. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Application Summary. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Self Certification &amp; Worksheet. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self Certification of Non Employment. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Income &amp; Asset Questionnaire. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Affidavit of Student Financial Assistance. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Student Certification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Annual Student Certification since there is Home unit . Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Zero Income. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate VAWA Acknowledgement. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Screening Document. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Payment History. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Calcs. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Reccurring Cash Contribution. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Self-Employment Income. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Household Asset Breakdown. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Employment Verification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate the Certification of Student Status. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Regular Contributions Verification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Bank Statements. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Leave and Earnings Statement. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Profit/Loss Statement. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Applicant marked that no household members are part of the original qualifying household. Please have the applicant correct.</t>
   </si>
   <si>
-    <t>Bank statements are included in the file. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Commission, bonuses, tips, other amount has been populated. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Both 120 days of pay history available and 120 days of pay history not available data sections are populated on the Child Support Calculator. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
   </si>
   <si>
@@ -3636,25 +3492,169 @@
     <t>Social Security Benefits Letter is missing at least one page. Upload missing page with final signed documents.</t>
   </si>
   <si>
-    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed. </t>
-  </si>
-  <si>
     <t>Season or Sporadic work has been documented on the Employment Verification. Manual review is needed.  </t>
   </si>
   <si>
-    <t>Unable to validate Release and Consent Form. Manual review is needed. </t>
-  </si>
-  <si>
     <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
   </si>
   <si>
-    <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
-  </si>
-  <si>
     <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing History Disclosure. manual review required.</t>
+  </si>
+  <si>
+    <t>Live-In Attendant documented on the Income Calculation Worksheet. manual review required.</t>
+  </si>
+  <si>
+    <t>Applicant is a Dominium employee. manual review required.</t>
+  </si>
+  <si>
+    <t>Income type included that cannot be validated with automation. manual review required.</t>
+  </si>
+  <si>
+    <t>This application is a Section 811 unit. manual review required. </t>
+  </si>
+  <si>
+    <t>Unable to validate Income Calculation Worksheet. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Application Summary. manual review required.</t>
+  </si>
+  <si>
+    <t>Applicant reported a minor will live in the household less than 50% of the time. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Member Information Document. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Income &amp; Asset Questionnaire. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self Certification of Non Employment. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Self Certification &amp; Worksheet. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Affidavit of Student Financial Assistance. manual review required.</t>
+  </si>
+  <si>
+    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Student Certification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Annual Student Certification since there is Home unit . manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Zero Income. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate VAWA Acknowledgement. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Screening Document. manual review required.</t>
+  </si>
+  <si>
+    <t>Regular pay rate has increased across paystubs. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate paystubs. manual review required.</t>
+  </si>
+  <si>
+    <t>Verification of Employment - manual review required to ensure document was received via 3rd party.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. manual review required.</t>
+  </si>
+  <si>
+    <t>Commission, bonuses, tips, other amount has been populated. manual review required.</t>
+  </si>
+  <si>
+    <t>Anticipated wage increase indicated on employment verification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Employment. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Offer Letter. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Work Number. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self-Employment Certification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Payment History. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Calcs. manual review required.</t>
+  </si>
+  <si>
+    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Supplemental Security Income Letter. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Reccurring Cash Contribution. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing Demographic Reporting Form. manual review required.</t>
+  </si>
+  <si>
+    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Self-Employment Income. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Profit/Loss Statement. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Applicant/Tenant Release and Consent. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Household Asset Breakdown. manual review required.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. manual review required. </t>
+  </si>
+  <si>
+    <t>Unable to validate Employment Verification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate the Certification of Student Status. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Regular Contributions Verification. manual review required.</t>
+  </si>
+  <si>
+    <t>Bank statements are included in the file. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Bank Statements. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Leave and Earnings Statement. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Veterans Affairs Benefits Letter. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Release and Consent Form. manual review required. </t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. manual review required. </t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Certification of Net Family Assets. manual review required. </t>
   </si>
 </sst>
 </file>
@@ -4138,7 +4138,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1203</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -8679,10 +8679,10 @@
         <v>652</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1162</v>
+        <v>1152</v>
       </c>
       <c r="C13" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8744,7 +8744,7 @@
         <v>1137</v>
       </c>
       <c r="C21" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8752,10 +8752,10 @@
         <v>597</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C22" t="s">
         <v>1138</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8774,10 +8774,10 @@
         <v>622</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1140</v>
+        <v>1154</v>
       </c>
       <c r="C24" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8785,10 +8785,10 @@
         <v>624</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1141</v>
+        <v>1155</v>
       </c>
       <c r="C25" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8796,10 +8796,10 @@
         <v>691</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="C26" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8807,10 +8807,10 @@
         <v>824</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="C27" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8818,7 +8818,7 @@
         <v>472</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8952,7 +8952,7 @@
         <v>487</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9059,10 +9059,10 @@
         <v>594</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
       <c r="C59" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -9070,10 +9070,10 @@
         <v>486</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1145</v>
+        <v>1160</v>
       </c>
       <c r="C60" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9241,7 +9241,7 @@
         <v>485</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9281,10 +9281,10 @@
         <v>648</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="C85" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -9325,7 +9325,7 @@
         <v>484</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9504,10 +9504,10 @@
         <v>847</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="C109" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -9539,7 +9539,7 @@
         <v>483</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -9657,7 +9657,7 @@
         <v>482</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9724,10 +9724,10 @@
         <v>561</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>1149</v>
+        <v>1165</v>
       </c>
       <c r="C134" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -9754,7 +9754,7 @@
         <v>481</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -9773,7 +9773,7 @@
         <v>608</v>
       </c>
       <c r="B140" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C140" t="s">
         <v>607</v>
@@ -9846,7 +9846,7 @@
         <v>480</v>
       </c>
       <c r="B149" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -9886,7 +9886,7 @@
         <v>479</v>
       </c>
       <c r="B155" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -9981,10 +9981,10 @@
         <v>468</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -10006,7 +10006,7 @@
         <v>827</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -10028,7 +10028,7 @@
         <v>828</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -10047,10 +10047,10 @@
         <v>700</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>1140</v>
+        <v>1154</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -10215,10 +10215,10 @@
         <v>598</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="6" customFormat="1">
@@ -10229,7 +10229,7 @@
         <v>662</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -10237,10 +10237,10 @@
         <v>673</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>1152</v>
+        <v>1171</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -10248,10 +10248,10 @@
         <v>846</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>1153</v>
+        <v>1144</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -10267,10 +10267,10 @@
         <v>467</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>1154</v>
+        <v>1172</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -10278,10 +10278,10 @@
         <v>672</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>1155</v>
+        <v>1173</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -10327,10 +10327,10 @@
         <v>245</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>1192</v>
+        <v>1174</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -10454,10 +10454,10 @@
         <v>272</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>1193</v>
+        <v>1175</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -10465,10 +10465,10 @@
         <v>599</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -10476,10 +10476,10 @@
         <v>596</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>1156</v>
+        <v>1176</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -10487,10 +10487,10 @@
         <v>478</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>1157</v>
+        <v>1177</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -10554,10 +10554,10 @@
         <v>600</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -10565,10 +10565,10 @@
         <v>477</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>1158</v>
+        <v>1178</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -10648,10 +10648,10 @@
         <v>601</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -10667,10 +10667,10 @@
         <v>476</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>1159</v>
+        <v>1179</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -10775,10 +10775,10 @@
         <v>602</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -10786,10 +10786,10 @@
         <v>475</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -10967,10 +10967,10 @@
         <v>474</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>1161</v>
+        <v>1181</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -11132,10 +11132,10 @@
         <v>473</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>1173</v>
+        <v>1182</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -11154,10 +11154,10 @@
         <v>983</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>1194</v>
+        <v>1146</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -11165,10 +11165,10 @@
         <v>985</v>
       </c>
       <c r="B302" s="7" t="s">
-        <v>1195</v>
+        <v>1147</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -11176,10 +11176,10 @@
         <v>986</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>1174</v>
+        <v>1183</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -11311,10 +11311,10 @@
         <v>687</v>
       </c>
       <c r="B319" s="7" t="s">
-        <v>1196</v>
+        <v>1148</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -11330,10 +11330,10 @@
         <v>548</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -11349,10 +11349,10 @@
         <v>471</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -11473,10 +11473,10 @@
         <v>554</v>
       </c>
       <c r="B338" s="7" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -11492,10 +11492,10 @@
         <v>470</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -11576,10 +11576,10 @@
         <v>469</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>1176</v>
+        <v>1186</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -11598,10 +11598,10 @@
         <v>697</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -11681,10 +11681,10 @@
         <v>719</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>1197</v>
+        <v>1188</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -11764,10 +11764,10 @@
         <v>1084</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>1178</v>
+        <v>1189</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -11863,10 +11863,10 @@
         <v>755</v>
       </c>
       <c r="B387" s="7" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11946,10 +11946,10 @@
         <v>778</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11997,10 +11997,10 @@
         <v>789</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -12024,10 +12024,10 @@
         <v>800</v>
       </c>
       <c r="B410" s="7" t="s">
-        <v>1155</v>
+        <v>1173</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -12043,10 +12043,10 @@
         <v>808</v>
       </c>
       <c r="B412" s="7" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -12126,10 +12126,10 @@
         <v>820</v>
       </c>
       <c r="B422" s="7" t="s">
-        <v>1193</v>
+        <v>1175</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -12137,10 +12137,10 @@
         <v>821</v>
       </c>
       <c r="B423" s="7" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -12148,10 +12148,10 @@
         <v>812</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1156</v>
+        <v>1176</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -12159,10 +12159,10 @@
         <v>811</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -12234,10 +12234,10 @@
         <v>1051</v>
       </c>
       <c r="B434" s="7" t="s">
-        <v>1199</v>
+        <v>1149</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -12373,10 +12373,10 @@
         <v>883</v>
       </c>
       <c r="B452" s="7" t="s">
-        <v>1188</v>
+        <v>1145</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -12424,10 +12424,10 @@
         <v>878</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -12523,10 +12523,10 @@
         <v>913</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -12534,10 +12534,10 @@
         <v>920</v>
       </c>
       <c r="B473" s="7" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="6" customFormat="1">
@@ -12545,10 +12545,10 @@
         <v>929</v>
       </c>
       <c r="B474" s="6" t="s">
-        <v>1184</v>
+        <v>1198</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="476" spans="1:3" s="6" customFormat="1">
@@ -12559,7 +12559,7 @@
         <v>922</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -12567,10 +12567,10 @@
         <v>930</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>1185</v>
+        <v>1199</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12602,10 +12602,10 @@
         <v>924</v>
       </c>
       <c r="B482" s="7" t="s">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -12661,10 +12661,10 @@
         <v>943</v>
       </c>
       <c r="B490" s="7" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12712,10 +12712,10 @@
         <v>957</v>
       </c>
       <c r="B497" s="7" t="s">
-        <v>1201</v>
+        <v>1150</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12766,7 +12766,7 @@
         <v>1090</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="6" customFormat="1">
@@ -12777,7 +12777,7 @@
         <v>973</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12809,10 +12809,10 @@
         <v>980</v>
       </c>
       <c r="B510" s="7" t="s">
-        <v>1191</v>
+        <v>1202</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12924,10 +12924,10 @@
         <v>1015</v>
       </c>
       <c r="B525" s="7" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0918\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6B0C54-09B6-4CA6-BF8B-DF21306A78A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454D657D-5E9E-4BEC-9F9C-08D7DBFA4CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3498,9 +3498,6 @@
     <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>Unable to validate Housing History Disclosure. manual review required.</t>
   </si>
   <si>
@@ -3655,6 +3652,9 @@
   </si>
   <si>
     <t>Unable to validate Asset Certification of Net Family Assets. manual review required. </t>
+  </si>
+  <si>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4138,7 +4138,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1151</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -8679,7 +8679,7 @@
         <v>652</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C13" t="s">
         <v>1138</v>
@@ -8752,7 +8752,7 @@
         <v>597</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C22" t="s">
         <v>1138</v>
@@ -8774,7 +8774,7 @@
         <v>622</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C24" t="s">
         <v>1138</v>
@@ -8785,7 +8785,7 @@
         <v>624</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C25" t="s">
         <v>1138</v>
@@ -8807,7 +8807,7 @@
         <v>824</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C27" t="s">
         <v>1138</v>
@@ -8818,7 +8818,7 @@
         <v>472</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8952,7 +8952,7 @@
         <v>487</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9059,7 +9059,7 @@
         <v>594</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C59" t="s">
         <v>1138</v>
@@ -9070,7 +9070,7 @@
         <v>486</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C60" t="s">
         <v>1138</v>
@@ -9241,7 +9241,7 @@
         <v>485</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9325,7 +9325,7 @@
         <v>484</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9539,7 +9539,7 @@
         <v>483</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -9657,7 +9657,7 @@
         <v>482</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9724,7 +9724,7 @@
         <v>561</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C134" t="s">
         <v>1138</v>
@@ -9754,7 +9754,7 @@
         <v>481</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -9773,7 +9773,7 @@
         <v>608</v>
       </c>
       <c r="B140" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C140" t="s">
         <v>607</v>
@@ -9846,7 +9846,7 @@
         <v>480</v>
       </c>
       <c r="B149" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -9886,7 +9886,7 @@
         <v>479</v>
       </c>
       <c r="B155" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -9981,7 +9981,7 @@
         <v>468</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>1142</v>
@@ -10047,7 +10047,7 @@
         <v>700</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>1138</v>
@@ -10237,7 +10237,7 @@
         <v>673</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>1138</v>
@@ -10267,7 +10267,7 @@
         <v>467</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>1138</v>
@@ -10278,7 +10278,7 @@
         <v>672</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>1138</v>
@@ -10327,7 +10327,7 @@
         <v>245</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>1138</v>
@@ -10454,7 +10454,7 @@
         <v>272</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>1138</v>
@@ -10476,7 +10476,7 @@
         <v>596</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>1138</v>
@@ -10487,7 +10487,7 @@
         <v>478</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>1138</v>
@@ -10565,7 +10565,7 @@
         <v>477</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>1138</v>
@@ -10667,7 +10667,7 @@
         <v>476</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>1138</v>
@@ -10786,7 +10786,7 @@
         <v>475</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>1138</v>
@@ -10967,7 +10967,7 @@
         <v>474</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>1138</v>
@@ -11132,7 +11132,7 @@
         <v>473</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>1138</v>
@@ -11176,7 +11176,7 @@
         <v>986</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>1138</v>
@@ -11330,7 +11330,7 @@
         <v>548</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>1138</v>
@@ -11349,7 +11349,7 @@
         <v>471</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>1138</v>
@@ -11473,7 +11473,7 @@
         <v>554</v>
       </c>
       <c r="B338" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>1138</v>
@@ -11492,7 +11492,7 @@
         <v>470</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>1138</v>
@@ -11576,7 +11576,7 @@
         <v>469</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>1138</v>
@@ -11598,7 +11598,7 @@
         <v>697</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>1138</v>
@@ -11681,7 +11681,7 @@
         <v>719</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>1138</v>
@@ -11764,7 +11764,7 @@
         <v>1084</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>1138</v>
@@ -11863,7 +11863,7 @@
         <v>755</v>
       </c>
       <c r="B387" s="7" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>1138</v>
@@ -11946,7 +11946,7 @@
         <v>778</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>1138</v>
@@ -11997,7 +11997,7 @@
         <v>789</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>1138</v>
@@ -12024,7 +12024,7 @@
         <v>800</v>
       </c>
       <c r="B410" s="7" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>1138</v>
@@ -12043,7 +12043,7 @@
         <v>808</v>
       </c>
       <c r="B412" s="7" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>1138</v>
@@ -12126,7 +12126,7 @@
         <v>820</v>
       </c>
       <c r="B422" s="7" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>1138</v>
@@ -12148,7 +12148,7 @@
         <v>812</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>1138</v>
@@ -12159,7 +12159,7 @@
         <v>811</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>1138</v>
@@ -12424,7 +12424,7 @@
         <v>878</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>1138</v>
@@ -12523,7 +12523,7 @@
         <v>913</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>1138</v>
@@ -12534,7 +12534,7 @@
         <v>920</v>
       </c>
       <c r="B473" s="7" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>1138</v>
@@ -12545,7 +12545,7 @@
         <v>929</v>
       </c>
       <c r="B474" s="6" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C474" s="6" t="s">
         <v>1142</v>
@@ -12567,7 +12567,7 @@
         <v>930</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>1138</v>
@@ -12602,7 +12602,7 @@
         <v>924</v>
       </c>
       <c r="B482" s="7" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>1138</v>
@@ -12661,7 +12661,7 @@
         <v>943</v>
       </c>
       <c r="B490" s="7" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>1138</v>
@@ -12809,7 +12809,7 @@
         <v>980</v>
       </c>
       <c r="B510" s="7" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>1138</v>
@@ -12924,7 +12924,7 @@
         <v>1015</v>
       </c>
       <c r="B525" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>1138</v>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0921\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454D657D-5E9E-4BEC-9F9C-08D7DBFA4CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C61315E-96C5-4FBD-A71C-F7E2FDBE298D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3654,7 +3654,7 @@
     <t>Unable to validate Asset Certification of Net Family Assets. manual review required. </t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0921\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C61315E-96C5-4FBD-A71C-F7E2FDBE298D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944A3408-3D3B-406B-A065-7977F8EED28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3654,7 +3654,7 @@
     <t>Unable to validate Asset Certification of Net Family Assets. manual review required. </t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\RALUCA.ILINCA.AZUREAI-JUMP2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944A3408-3D3B-406B-A065-7977F8EED28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F05B601-A09D-47A3-989B-893882386427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -2841,9 +2841,6 @@
     <t>Veterans Benefits Letter</t>
   </si>
   <si>
-    <t xml:space="preserve">The Release and Consent for is missing from the application. </t>
-  </si>
-  <si>
     <t xml:space="preserve">All adults have not been listed on the Applicant/Resident Name line of the Release and Consent Form. </t>
   </si>
   <si>
@@ -3498,163 +3495,166 @@
     <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
   </si>
   <si>
-    <t>Unable to validate Housing History Disclosure. manual review required.</t>
-  </si>
-  <si>
-    <t>Live-In Attendant documented on the Income Calculation Worksheet. manual review required.</t>
-  </si>
-  <si>
-    <t>Applicant is a Dominium employee. manual review required.</t>
-  </si>
-  <si>
-    <t>Income type included that cannot be validated with automation. manual review required.</t>
-  </si>
-  <si>
-    <t>This application is a Section 811 unit. manual review required. </t>
-  </si>
-  <si>
-    <t>Unable to validate Income Calculation Worksheet. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Application Summary. manual review required.</t>
-  </si>
-  <si>
-    <t>Applicant reported a minor will live in the household less than 50% of the time. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Member Information Document. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Income &amp; Asset Questionnaire. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self Certification of Non Employment. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Self Certification &amp; Worksheet. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Affidavit of Student Financial Assistance. manual review required.</t>
-  </si>
-  <si>
-    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Student Certification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Annual Student Certification since there is Home unit . manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Zero Income. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate VAWA Acknowledgement. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Screening Document. manual review required.</t>
-  </si>
-  <si>
-    <t>Regular pay rate has increased across paystubs. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate paystubs. manual review required.</t>
-  </si>
-  <si>
-    <t>Verification of Employment - manual review required to ensure document was received via 3rd party.</t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. manual review required.</t>
-  </si>
-  <si>
-    <t>Commission, bonuses, tips, other amount has been populated. manual review required.</t>
-  </si>
-  <si>
-    <t>Anticipated wage increase indicated on employment verification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Employment. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Offer Letter. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Work Number. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self-Employment Certification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Payment History. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Calcs. manual review required.</t>
-  </si>
-  <si>
-    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Supplemental Security Income Letter. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Reccurring Cash Contribution. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Housing Demographic Reporting Form. manual review required.</t>
-  </si>
-  <si>
-    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Self-Employment Income. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Profit/Loss Statement. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate findings for Applicant/Tenant Release and Consent. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Household Asset Breakdown. manual review required.</t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. manual review required. </t>
-  </si>
-  <si>
-    <t>Unable to validate Employment Verification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate the Certification of Student Status. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Regular Contributions Verification. manual review required.</t>
-  </si>
-  <si>
-    <t>Bank statements are included in the file. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Bank Statements. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Leave and Earnings Statement. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Veterans Affairs Benefits Letter. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Release and Consent Form. manual review required. </t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. manual review required. </t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Certification of Net Family Assets. manual review required. </t>
-  </si>
-  <si>
     <t>C:\Users\RALUCA.ILINCA.AZUREAI-JUMP2\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing History Disclosure. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant is a Dominium employee. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Income type included that cannot be validated with automation. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>This application is a Section 811 unit. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Application Summary. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant reported a minor will live in the household less than 50% of the time. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Member Information Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Income &amp; Asset Questionnaire. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self Certification of Non Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Self Certification &amp; Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Affidavit of Student Financial Assistance. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Annual Student Certification since there is Home unit . Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Zero Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate VAWA Acknowledgement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Screening Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Regular pay rate has increased across paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Verification of Employment - manual review is needed to ensure document was received via 3rd party.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Commission, bonuses, tips, other amount has been populated. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Anticipated wage increase indicated on employment verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Offer Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Work Number. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self-Employment Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Payment History. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Calcs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Reccurring Cash Contribution. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Self-Employment Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Profit/Loss Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Household Asset Breakdown. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Employment Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate the Certification of Student Status. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Regular Contributions Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Bank statements are included in the file. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Bank Statements. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Leave and Earnings Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Release and Consent Form is missing from the application. </t>
+  </si>
+  <si>
+    <t>Unable to validate Release and Consent Form. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
 </sst>
 </file>
@@ -4105,7 +4105,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -4126,7 +4126,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -4138,7 +4138,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1203</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -4162,16 +4162,16 @@
         <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B12" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -4295,7 +4295,7 @@
         <v>403</v>
       </c>
       <c r="B26" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
@@ -4450,7 +4450,7 @@
         <v>701</v>
       </c>
       <c r="B45" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
@@ -4527,53 +4527,53 @@
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1">
       <c r="A55" t="s">
+        <v>943</v>
+      </c>
+      <c r="B55" t="s">
         <v>944</v>
-      </c>
-      <c r="B55" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1">
       <c r="A56" t="s">
+        <v>946</v>
+      </c>
+      <c r="B56" t="s">
+        <v>946</v>
+      </c>
+      <c r="C56" t="s">
         <v>947</v>
-      </c>
-      <c r="B56" t="s">
-        <v>947</v>
-      </c>
-      <c r="C56" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1">
       <c r="A57" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B57" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1">
       <c r="A58" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B58" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B59" t="s">
         <v>1063</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" t="s">
+        <v>998</v>
+      </c>
+      <c r="B60" t="s">
         <v>999</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B22" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1">
@@ -7488,10 +7488,10 @@
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1">
       <c r="A40" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B40" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1">
@@ -7536,74 +7536,74 @@
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B46" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1">
       <c r="A47" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B47" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B48" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B49" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B50" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B51" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B52" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B53" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B54" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B5" t="s">
         <v>1066</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8682,7 +8682,7 @@
         <v>1151</v>
       </c>
       <c r="C13" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8714,7 +8714,7 @@
         <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8741,10 +8741,10 @@
         <v>589</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C21" t="s">
         <v>1137</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8755,7 +8755,7 @@
         <v>1152</v>
       </c>
       <c r="C22" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8777,7 +8777,7 @@
         <v>1153</v>
       </c>
       <c r="C24" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8788,7 +8788,7 @@
         <v>1154</v>
       </c>
       <c r="C25" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8796,10 +8796,10 @@
         <v>691</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C26" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8810,7 +8810,7 @@
         <v>1155</v>
       </c>
       <c r="C27" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8858,7 +8858,7 @@
         <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -8968,7 +8968,7 @@
         <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9048,10 +9048,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>992</v>
+      </c>
+      <c r="B58" t="s">
         <v>993</v>
-      </c>
-      <c r="B58" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -9062,7 +9062,7 @@
         <v>1158</v>
       </c>
       <c r="C59" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -9073,7 +9073,7 @@
         <v>1159</v>
       </c>
       <c r="C60" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9155,7 +9155,7 @@
         <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -9198,7 +9198,7 @@
         <v>496</v>
       </c>
       <c r="B74" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -9214,26 +9214,26 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B76" t="s">
         <v>1097</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B77" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B78" t="s">
         <v>1108</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -9281,10 +9281,10 @@
         <v>648</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C85" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -9333,7 +9333,7 @@
         <v>180</v>
       </c>
       <c r="B91" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -9504,10 +9504,10 @@
         <v>847</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C109" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -9544,10 +9544,10 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B115" t="s">
         <v>1134</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1135</v>
       </c>
       <c r="C115" t="s">
         <v>593</v>
@@ -9727,7 +9727,7 @@
         <v>1164</v>
       </c>
       <c r="C134" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -9824,10 +9824,10 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B147" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C147" t="s">
         <v>593</v>
@@ -9984,18 +9984,18 @@
         <v>1169</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B168" t="s">
         <v>766</v>
       </c>
       <c r="C168" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="169" spans="1:3" s="6" customFormat="1">
@@ -10006,7 +10006,7 @@
         <v>827</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -10028,7 +10028,7 @@
         <v>828</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -10050,18 +10050,18 @@
         <v>1153</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B174" t="s">
         <v>834</v>
       </c>
       <c r="C174" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -10069,18 +10069,18 @@
         <v>459</v>
       </c>
       <c r="B176" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B177" t="s">
         <v>1078</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
         <v>1079</v>
-      </c>
-      <c r="C177" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -10148,7 +10148,7 @@
         <v>834</v>
       </c>
       <c r="C184" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -10191,7 +10191,7 @@
         <v>834</v>
       </c>
       <c r="C189" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -10207,7 +10207,7 @@
         <v>585</v>
       </c>
       <c r="B191" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -10215,10 +10215,10 @@
         <v>598</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="6" customFormat="1">
@@ -10229,7 +10229,7 @@
         <v>662</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -10240,7 +10240,7 @@
         <v>1170</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -10248,18 +10248,18 @@
         <v>846</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B196" t="s">
         <v>1117</v>
-      </c>
-      <c r="B196" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -10270,7 +10270,7 @@
         <v>1171</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -10281,7 +10281,7 @@
         <v>1172</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -10289,7 +10289,7 @@
         <v>460</v>
       </c>
       <c r="B200" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -10330,7 +10330,7 @@
         <v>1173</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -10446,7 +10446,7 @@
         <v>834</v>
       </c>
       <c r="C217" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -10457,7 +10457,7 @@
         <v>1174</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -10465,10 +10465,10 @@
         <v>599</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -10479,7 +10479,7 @@
         <v>1175</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -10490,7 +10490,7 @@
         <v>1176</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -10498,7 +10498,7 @@
         <v>461</v>
       </c>
       <c r="B223" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -10554,10 +10554,10 @@
         <v>600</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -10568,7 +10568,7 @@
         <v>1177</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -10576,7 +10576,7 @@
         <v>462</v>
       </c>
       <c r="B233" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -10648,18 +10648,18 @@
         <v>601</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B243" t="s">
         <v>1129</v>
-      </c>
-      <c r="B243" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -10670,7 +10670,7 @@
         <v>1178</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -10678,7 +10678,7 @@
         <v>463</v>
       </c>
       <c r="B246" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -10735,7 +10735,7 @@
         <v>834</v>
       </c>
       <c r="C252" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -10775,10 +10775,10 @@
         <v>602</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -10789,7 +10789,7 @@
         <v>1179</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -10970,7 +10970,7 @@
         <v>1180</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -11088,43 +11088,43 @@
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
+        <v>986</v>
+      </c>
+      <c r="B294" t="s">
         <v>987</v>
       </c>
-      <c r="B294" t="s">
-        <v>988</v>
-      </c>
       <c r="C294" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
+        <v>988</v>
+      </c>
+      <c r="B295" t="s">
         <v>989</v>
       </c>
-      <c r="B295" t="s">
-        <v>990</v>
-      </c>
       <c r="C295" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
+        <v>990</v>
+      </c>
+      <c r="B296" t="s">
         <v>991</v>
       </c>
-      <c r="B296" t="s">
-        <v>992</v>
-      </c>
       <c r="C296" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B297" t="s">
         <v>1122</v>
-      </c>
-      <c r="B297" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -11135,7 +11135,7 @@
         <v>1181</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -11151,35 +11151,35 @@
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B302" s="7" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>1182</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -11311,18 +11311,18 @@
         <v>687</v>
       </c>
       <c r="B319" s="7" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B320" t="s">
         <v>1068</v>
-      </c>
-      <c r="B320" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -11333,15 +11333,15 @@
         <v>1183</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B322" t="s">
         <v>1125</v>
-      </c>
-      <c r="B322" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -11352,7 +11352,7 @@
         <v>1184</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -11476,15 +11476,15 @@
         <v>1183</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B339" t="s">
         <v>1127</v>
-      </c>
-      <c r="B339" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -11495,7 +11495,7 @@
         <v>1184</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -11562,13 +11562,13 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B349" t="s">
         <v>1085</v>
       </c>
-      <c r="B349" t="s">
+      <c r="C349" t="s">
         <v>1086</v>
-      </c>
-      <c r="C349" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -11579,7 +11579,7 @@
         <v>1185</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -11601,7 +11601,7 @@
         <v>1186</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -11673,7 +11673,7 @@
         <v>718</v>
       </c>
       <c r="B363" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -11684,7 +11684,7 @@
         <v>1187</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -11737,10 +11737,10 @@
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B371" t="s">
         <v>1061</v>
-      </c>
-      <c r="B371" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -11753,21 +11753,21 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B373" t="s">
         <v>1101</v>
-      </c>
-      <c r="B373" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B374" s="5" t="s">
         <v>1188</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -11866,7 +11866,7 @@
         <v>1189</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11898,7 +11898,7 @@
         <v>760</v>
       </c>
       <c r="B392" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -11949,7 +11949,7 @@
         <v>1190</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -12000,7 +12000,7 @@
         <v>1191</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -12016,7 +12016,7 @@
         <v>799</v>
       </c>
       <c r="B409" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -12027,7 +12027,7 @@
         <v>1172</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -12035,7 +12035,7 @@
         <v>802</v>
       </c>
       <c r="B411" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -12046,7 +12046,7 @@
         <v>1192</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -12054,7 +12054,7 @@
         <v>809</v>
       </c>
       <c r="B413" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -12062,7 +12062,7 @@
         <v>810</v>
       </c>
       <c r="B414" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -12070,7 +12070,7 @@
         <v>813</v>
       </c>
       <c r="B415" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -12078,7 +12078,7 @@
         <v>814</v>
       </c>
       <c r="B416" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -12086,7 +12086,7 @@
         <v>815</v>
       </c>
       <c r="B417" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -12094,7 +12094,7 @@
         <v>816</v>
       </c>
       <c r="B418" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -12102,7 +12102,7 @@
         <v>817</v>
       </c>
       <c r="B419" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -12118,7 +12118,7 @@
         <v>819</v>
       </c>
       <c r="B421" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -12129,7 +12129,7 @@
         <v>1174</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -12137,10 +12137,10 @@
         <v>821</v>
       </c>
       <c r="B423" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -12151,7 +12151,7 @@
         <v>1175</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -12162,90 +12162,90 @@
         <v>1193</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B426" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B427" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B428" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B429" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B430" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B431" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B432" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B433" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B434" s="7" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B435" t="s">
         <v>1091</v>
-      </c>
-      <c r="B435" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -12373,10 +12373,10 @@
         <v>883</v>
       </c>
       <c r="B452" s="7" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -12413,10 +12413,10 @@
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B457" t="s">
         <v>1095</v>
-      </c>
-      <c r="B457" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -12427,15 +12427,15 @@
         <v>1194</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B460" t="s">
         <v>1088</v>
-      </c>
-      <c r="B460" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -12483,7 +12483,7 @@
         <v>909</v>
       </c>
       <c r="B466" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -12499,7 +12499,7 @@
         <v>910</v>
       </c>
       <c r="B468" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -12507,15 +12507,15 @@
         <v>914</v>
       </c>
       <c r="B469" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B470" t="s">
         <v>1103</v>
-      </c>
-      <c r="B470" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -12526,7 +12526,7 @@
         <v>1195</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -12537,7 +12537,7 @@
         <v>1196</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="6" customFormat="1">
@@ -12548,7 +12548,7 @@
         <v>1197</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="476" spans="1:3" s="6" customFormat="1">
@@ -12559,7 +12559,7 @@
         <v>922</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -12570,7 +12570,7 @@
         <v>1198</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12591,10 +12591,10 @@
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B481" t="s">
         <v>1120</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -12605,329 +12605,329 @@
         <v>1199</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B484" t="s">
-        <v>932</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B485" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B486" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B487" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B488" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B489" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B490" s="7" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B492" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="493" spans="1:3">
       <c r="A493" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B493" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B494" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B495" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B496" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B497" s="7" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="499" spans="1:3">
       <c r="A499" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B499" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="500" spans="1:3">
       <c r="A500" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B500" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B501" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B502" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B503" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="6" customFormat="1">
       <c r="A504" s="6" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B504" s="6" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="6" customFormat="1">
       <c r="A506" s="6" t="s">
+        <v>971</v>
+      </c>
+      <c r="B506" s="6" t="s">
         <v>972</v>
       </c>
-      <c r="B506" s="6" t="s">
-        <v>973</v>
-      </c>
       <c r="C506" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="507" spans="1:3">
       <c r="A507" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B507" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="508" spans="1:3">
       <c r="A508" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B508" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B509" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B510" s="7" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="512" spans="1:3">
       <c r="A512" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B512" t="s">
         <v>1001</v>
-      </c>
-      <c r="B512" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B513" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B514" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B515" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B516" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B517" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B518" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B519" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B520" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B521" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B522" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B523" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B524" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B525" s="7" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0922\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F05B601-A09D-47A3-989B-893882386427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6267AC0-4ABC-412D-8DB0-893D884D0C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3495,9 +3495,6 @@
     <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
   </si>
   <si>
-    <t>C:\Users\RALUCA.ILINCA.AZUREAI-JUMP2\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>Unable to validate Housing History Disclosure. Manual review is needed.</t>
   </si>
   <si>
@@ -3655,6 +3652,9 @@
   </si>
   <si>
     <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4138,7 +4138,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1150</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -8679,7 +8679,7 @@
         <v>652</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C13" t="s">
         <v>1137</v>
@@ -8752,7 +8752,7 @@
         <v>597</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C22" t="s">
         <v>1137</v>
@@ -8774,7 +8774,7 @@
         <v>622</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C24" t="s">
         <v>1137</v>
@@ -8785,7 +8785,7 @@
         <v>624</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C25" t="s">
         <v>1137</v>
@@ -8807,7 +8807,7 @@
         <v>824</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C27" t="s">
         <v>1137</v>
@@ -8818,7 +8818,7 @@
         <v>472</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8952,7 +8952,7 @@
         <v>487</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9059,7 +9059,7 @@
         <v>594</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C59" t="s">
         <v>1137</v>
@@ -9070,7 +9070,7 @@
         <v>486</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C60" t="s">
         <v>1137</v>
@@ -9241,7 +9241,7 @@
         <v>485</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9325,7 +9325,7 @@
         <v>484</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9539,7 +9539,7 @@
         <v>483</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -9657,7 +9657,7 @@
         <v>482</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9724,7 +9724,7 @@
         <v>561</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C134" t="s">
         <v>1137</v>
@@ -9754,7 +9754,7 @@
         <v>481</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -9773,7 +9773,7 @@
         <v>608</v>
       </c>
       <c r="B140" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C140" t="s">
         <v>607</v>
@@ -9846,7 +9846,7 @@
         <v>480</v>
       </c>
       <c r="B149" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -9886,7 +9886,7 @@
         <v>479</v>
       </c>
       <c r="B155" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -9981,7 +9981,7 @@
         <v>468</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>1141</v>
@@ -10047,7 +10047,7 @@
         <v>700</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>1137</v>
@@ -10237,7 +10237,7 @@
         <v>673</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>1137</v>
@@ -10267,7 +10267,7 @@
         <v>467</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>1137</v>
@@ -10278,7 +10278,7 @@
         <v>672</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>1137</v>
@@ -10327,7 +10327,7 @@
         <v>245</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>1137</v>
@@ -10454,7 +10454,7 @@
         <v>272</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>1137</v>
@@ -10476,7 +10476,7 @@
         <v>596</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>1137</v>
@@ -10487,7 +10487,7 @@
         <v>478</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>1137</v>
@@ -10565,7 +10565,7 @@
         <v>477</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>1137</v>
@@ -10667,7 +10667,7 @@
         <v>476</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>1137</v>
@@ -10786,7 +10786,7 @@
         <v>475</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>1137</v>
@@ -10967,7 +10967,7 @@
         <v>474</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>1137</v>
@@ -11132,7 +11132,7 @@
         <v>473</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>1137</v>
@@ -11176,7 +11176,7 @@
         <v>985</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>1137</v>
@@ -11330,7 +11330,7 @@
         <v>548</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>1137</v>
@@ -11349,7 +11349,7 @@
         <v>471</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>1137</v>
@@ -11473,7 +11473,7 @@
         <v>554</v>
       </c>
       <c r="B338" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>1137</v>
@@ -11492,7 +11492,7 @@
         <v>470</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>1137</v>
@@ -11576,7 +11576,7 @@
         <v>469</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>1137</v>
@@ -11598,7 +11598,7 @@
         <v>697</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>1137</v>
@@ -11681,7 +11681,7 @@
         <v>719</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>1137</v>
@@ -11764,7 +11764,7 @@
         <v>1083</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>1137</v>
@@ -11863,7 +11863,7 @@
         <v>755</v>
       </c>
       <c r="B387" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>1137</v>
@@ -11946,7 +11946,7 @@
         <v>778</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>1137</v>
@@ -11997,7 +11997,7 @@
         <v>789</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>1137</v>
@@ -12024,7 +12024,7 @@
         <v>800</v>
       </c>
       <c r="B410" s="7" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>1137</v>
@@ -12043,7 +12043,7 @@
         <v>808</v>
       </c>
       <c r="B412" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>1137</v>
@@ -12126,7 +12126,7 @@
         <v>820</v>
       </c>
       <c r="B422" s="7" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>1137</v>
@@ -12148,7 +12148,7 @@
         <v>812</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>1137</v>
@@ -12159,7 +12159,7 @@
         <v>811</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>1137</v>
@@ -12424,7 +12424,7 @@
         <v>878</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>1137</v>
@@ -12523,7 +12523,7 @@
         <v>913</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>1137</v>
@@ -12534,7 +12534,7 @@
         <v>920</v>
       </c>
       <c r="B473" s="7" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>1137</v>
@@ -12545,7 +12545,7 @@
         <v>929</v>
       </c>
       <c r="B474" s="6" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C474" s="6" t="s">
         <v>1141</v>
@@ -12567,7 +12567,7 @@
         <v>930</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>1137</v>
@@ -12602,7 +12602,7 @@
         <v>924</v>
       </c>
       <c r="B482" s="7" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>1137</v>
@@ -12613,7 +12613,7 @@
         <v>937</v>
       </c>
       <c r="B484" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -12661,7 +12661,7 @@
         <v>942</v>
       </c>
       <c r="B490" s="7" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>1137</v>
@@ -12809,7 +12809,7 @@
         <v>979</v>
       </c>
       <c r="B510" s="7" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>1137</v>
@@ -12924,7 +12924,7 @@
         <v>1014</v>
       </c>
       <c r="B525" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>1137</v>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0922\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6267AC0-4ABC-412D-8DB0-893D884D0C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868AC3E7-6D81-4507-80B5-C74D89C1523C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3654,7 +3654,7 @@
     <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868AC3E7-6D81-4507-80B5-C74D89C1523C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755044CC-ADCE-4822-9EAB-E8B11791927A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3654,7 +3654,7 @@
     <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0923\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755044CC-ADCE-4822-9EAB-E8B11791927A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9BC516-B282-406A-A6AA-77ECC865789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3654,7 +3654,7 @@
     <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
   <si>
-    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0923\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9BC516-B282-406A-A6AA-77ECC865789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76662D60-266C-45CA-84A1-9B0556D64F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="1206">
   <si>
     <t>Name</t>
   </si>
@@ -975,9 +975,6 @@
     <t>Name listed on the Self-Employment Certification and Profit/Lost Statement do not match.</t>
   </si>
   <si>
-    <t>Net Income displayed on the Profit/Loss Statement doe not match the calculated Net Income.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Amount listed on the Self-Employment Certification and Profit/Loss Statement do not line up as expected. Needs additional review. </t>
   </si>
   <si>
@@ -1530,9 +1527,6 @@
     <t xml:space="preserve">Profit Loss forms does not exist for Self-Employment Verification </t>
   </si>
   <si>
-    <t xml:space="preserve">1040, Schedulec forms does not exist for Self-Employment Verification </t>
-  </si>
-  <si>
     <t>IAQ_AssetsValueMatch</t>
   </si>
   <si>
@@ -1710,21 +1704,6 @@
     <t>SSIB_OverPayment</t>
   </si>
   <si>
-    <t xml:space="preserve">Name listed on the Verification of Reccurring Cash Contribution and ICW do not match. </t>
-  </si>
-  <si>
-    <t>Date listed on the Verification of Reccurring Cash Contribution is over 120 days in the past.</t>
-  </si>
-  <si>
-    <t>Date listed on the Verification of Reccurring Cash Contribution is not with in 120 days of Move-In date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification of Reccurring Cash Contribution has not been signed. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification of Reccurring Cash Contribution has not been dated appropriately. </t>
-  </si>
-  <si>
     <t>LLM_ImageQuality</t>
   </si>
   <si>
@@ -1791,9 +1770,6 @@
     <t>ICW check was removed from this check</t>
   </si>
   <si>
-    <t xml:space="preserve">Contributor and Amount listed on the Verification of Reccurring Cash Contribution and ICW do not match. </t>
-  </si>
-  <si>
     <t>EDC_hourly_and_paycheck</t>
   </si>
   <si>
@@ -2160,9 +2136,6 @@
     <t>CSEI_SupportingDocsExist</t>
   </si>
   <si>
-    <t>Supporting documents do not exist for the Certification of Self-Employmet Income.</t>
-  </si>
-  <si>
     <t>CSEI_MemName</t>
   </si>
   <si>
@@ -2307,9 +2280,6 @@
     <t>PL_DateCheckWithMoveIn</t>
   </si>
   <si>
-    <t>Date on the Profit/Loss Statement is not withing 120 days of the Move-In date.</t>
-  </si>
-  <si>
     <t>PL_FindingError</t>
   </si>
   <si>
@@ -3597,9 +3567,6 @@
     <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
   </si>
   <si>
-    <t>Unable to validate Verification of Reccurring Cash Contribution. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
   </si>
   <si>
@@ -3655,6 +3622,45 @@
   </si>
   <si>
     <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1040, Schedule C forms does not exist for Self-Employment Verification </t>
+  </si>
+  <si>
+    <t>Date on the Profit/Loss Statement is not within 120 days of the Move-In date.</t>
+  </si>
+  <si>
+    <t>Supporting documents do not exist for the Certification of Self-Employment Income.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name listed on the Verification of Recurring Cash Contribution and ICW do not match. </t>
+  </si>
+  <si>
+    <t>Date listed on the Verification of Recurring Cash Contribution is over 120 days in the past.</t>
+  </si>
+  <si>
+    <t>Date listed on the Verification of Recurring Cash Contribution is not with in 120 days of Move-In date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contributor and Amount listed on the Verification of Recurring Cash Contribution and ICW do not match. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verification of Recurring Cash Contribution has not been signed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verification of Recurring Cash Contribution has not been dated appropriately. </t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Recurring Cash Contribution. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>ManagerName</t>
+  </si>
+  <si>
+    <t>SE_003</t>
+  </si>
+  <si>
+    <t>Assign button was not found in Yardi.</t>
   </si>
 </sst>
 </file>
@@ -4105,7 +4111,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -4126,7 +4132,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1081</v>
+        <v>1071</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -4138,7 +4144,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1203</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -4162,16 +4168,16 @@
         <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>1135</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>1069</v>
+        <v>1059</v>
       </c>
       <c r="B12" t="s">
-        <v>1069</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -4179,7 +4185,7 @@
         <v>207</v>
       </c>
       <c r="B13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
@@ -4192,10 +4198,10 @@
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B15" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
@@ -4203,7 +4209,7 @@
         <v>209</v>
       </c>
       <c r="B16" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
@@ -4211,7 +4217,7 @@
         <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
@@ -4219,7 +4225,7 @@
         <v>211</v>
       </c>
       <c r="B18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C18" t="s">
         <v>226</v>
@@ -4241,7 +4247,7 @@
         <v>213</v>
       </c>
       <c r="B20" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C20" t="s">
         <v>228</v>
@@ -4252,7 +4258,7 @@
         <v>214</v>
       </c>
       <c r="B21" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C21" t="s">
         <v>229</v>
@@ -4263,7 +4269,7 @@
         <v>215</v>
       </c>
       <c r="B22" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
@@ -4271,7 +4277,7 @@
         <v>216</v>
       </c>
       <c r="B23" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
@@ -4279,7 +4285,7 @@
         <v>217</v>
       </c>
       <c r="B24" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
@@ -4287,15 +4293,15 @@
         <v>218</v>
       </c>
       <c r="B25" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B26" t="s">
-        <v>945</v>
+        <v>935</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
@@ -4303,7 +4309,7 @@
         <v>231</v>
       </c>
       <c r="B27" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
@@ -4343,10 +4349,10 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B32" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1">
@@ -4359,221 +4365,221 @@
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
+        <v>328</v>
+      </c>
+      <c r="B34" t="s">
         <v>329</v>
-      </c>
-      <c r="B34" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1">
       <c r="A35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B36" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1">
       <c r="A37" t="s">
+        <v>355</v>
+      </c>
+      <c r="B37" t="s">
         <v>356</v>
-      </c>
-      <c r="B37" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1">
       <c r="A38" t="s">
+        <v>403</v>
+      </c>
+      <c r="B38" t="s">
         <v>404</v>
-      </c>
-      <c r="B38" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1">
       <c r="A39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B39" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1">
       <c r="A40" t="s">
+        <v>353</v>
+      </c>
+      <c r="B40" t="s">
         <v>354</v>
-      </c>
-      <c r="B40" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1">
       <c r="A41" t="s">
+        <v>406</v>
+      </c>
+      <c r="B41" t="s">
         <v>407</v>
-      </c>
-      <c r="B41" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1">
       <c r="A42" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1">
       <c r="A43" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B43" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1">
       <c r="A44" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="B44" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1">
       <c r="A45" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="B45" t="s">
-        <v>945</v>
+        <v>935</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="B46" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1">
       <c r="A47" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="B47" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="B48" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="B49" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
       <c r="B50" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>898</v>
+        <v>888</v>
       </c>
       <c r="B51" t="s">
-        <v>899</v>
+        <v>889</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B52" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
       <c r="B53" t="s">
-        <v>919</v>
+        <v>909</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>923</v>
+        <v>913</v>
       </c>
       <c r="B54" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1">
       <c r="A55" t="s">
-        <v>943</v>
+        <v>933</v>
       </c>
       <c r="B55" t="s">
-        <v>944</v>
+        <v>934</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1">
       <c r="A56" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="B56" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="C56" t="s">
-        <v>947</v>
+        <v>937</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1">
       <c r="A57" t="s">
-        <v>964</v>
+        <v>954</v>
       </c>
       <c r="B57" t="s">
-        <v>964</v>
+        <v>954</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1">
       <c r="A58" t="s">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="B58" t="s">
-        <v>1057</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" t="s">
-        <v>1062</v>
+        <v>1052</v>
       </c>
       <c r="B59" t="s">
-        <v>1063</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" t="s">
-        <v>998</v>
+        <v>988</v>
       </c>
       <c r="B60" t="s">
-        <v>999</v>
+        <v>989</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
@@ -5539,10 +5545,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1" t="s">
         <v>419</v>
-      </c>
-      <c r="B1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5550,15 +5556,15 @@
         <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5566,15 +5572,15 @@
         <v>225</v>
       </c>
       <c r="B4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5582,15 +5588,15 @@
         <v>223</v>
       </c>
       <c r="B6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5598,15 +5604,15 @@
         <v>219</v>
       </c>
       <c r="B8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5614,15 +5620,15 @@
         <v>222</v>
       </c>
       <c r="B10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>425</v>
+      </c>
+      <c r="B11" t="s">
         <v>426</v>
-      </c>
-      <c r="B11" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -5638,47 +5644,47 @@
         <v>220</v>
       </c>
       <c r="B13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>428</v>
+      </c>
+      <c r="B16" t="s">
         <v>429</v>
-      </c>
-      <c r="B16" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B18" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5686,7 +5692,7 @@
         <v>229</v>
       </c>
       <c r="B19" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5694,23 +5700,23 @@
         <v>226</v>
       </c>
       <c r="B20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B21" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
+        <v>433</v>
+      </c>
+      <c r="B22" t="s">
         <v>434</v>
-      </c>
-      <c r="B22" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5718,7 +5724,7 @@
         <v>227</v>
       </c>
       <c r="B23" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5726,23 +5732,23 @@
         <v>228</v>
       </c>
       <c r="B24" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B25" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -5750,7 +5756,7 @@
         <v>265</v>
       </c>
       <c r="B27" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -5758,7 +5764,7 @@
         <v>277</v>
       </c>
       <c r="B28" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -5766,15 +5772,15 @@
         <v>288</v>
       </c>
       <c r="B29" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B30" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -5782,95 +5788,95 @@
         <v>1040</v>
       </c>
       <c r="B31" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B33" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B34" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B36" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B37" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B38" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B39" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B40" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B41" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="B42" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -6070,10 +6076,10 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="B20" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
@@ -6081,23 +6087,23 @@
         <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B22" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B23" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
@@ -6166,7 +6172,14 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A34" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1205</v>
+      </c>
+    </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="36" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="37" spans="1:2" ht="14.25" customHeight="1"/>
@@ -7192,10 +7205,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="B3" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -7272,90 +7285,90 @@
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B13" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B14" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B15" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B16" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B17" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B18" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B19" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B20" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>1082</v>
+        <v>1072</v>
       </c>
       <c r="B22" t="s">
-        <v>1082</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="B23" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1">
@@ -7416,197 +7429,204 @@
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1">
       <c r="A31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.25" customHeight="1">
       <c r="A32" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B32" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B34" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B35" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B36" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1">
       <c r="A37" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B37" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1">
       <c r="A38" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B38" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1">
       <c r="A39" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="B39" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1">
       <c r="A40" t="s">
-        <v>1118</v>
+        <v>1108</v>
       </c>
       <c r="B40" t="s">
-        <v>1118</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1">
       <c r="A41" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="B41" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1">
       <c r="A42" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B42" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1">
       <c r="A43" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="B43" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1">
       <c r="A44" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B44" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1">
       <c r="A45" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B45" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>994</v>
+        <v>984</v>
       </c>
       <c r="B46" t="s">
-        <v>994</v>
+        <v>984</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1">
       <c r="A47" t="s">
-        <v>995</v>
+        <v>985</v>
       </c>
       <c r="B47" t="s">
-        <v>995</v>
+        <v>985</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>996</v>
+        <v>986</v>
       </c>
       <c r="B48" t="s">
-        <v>996</v>
+        <v>986</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>997</v>
+        <v>987</v>
       </c>
       <c r="B49" t="s">
-        <v>997</v>
+        <v>987</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>1058</v>
+        <v>1048</v>
       </c>
       <c r="B50" t="s">
-        <v>1058</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="B51" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="B52" t="s">
-        <v>1130</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1131</v>
+        <v>1121</v>
       </c>
       <c r="B53" t="s">
-        <v>1131</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1132</v>
+        <v>1122</v>
       </c>
       <c r="B54" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A55" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1203</v>
+      </c>
+    </row>
     <row r="56" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="57" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="58" spans="1:2" ht="14.25" customHeight="1"/>
@@ -8602,87 +8622,87 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>1065</v>
+        <v>1055</v>
       </c>
       <c r="B5" t="s">
-        <v>1066</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="B7" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="C7" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="B8" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C8" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="B9" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="C9" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="B10" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="C10" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B11" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="C11" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="B12" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C12" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="C13" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8690,7 +8710,7 @@
         <v>174</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -8714,7 +8734,7 @@
         <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>1110</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8725,100 +8745,100 @@
         <v>198</v>
       </c>
       <c r="C19" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>489</v>
+      </c>
+      <c r="B20" t="s">
         <v>490</v>
-      </c>
-      <c r="B20" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1136</v>
+        <v>1126</v>
       </c>
       <c r="C21" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>1151</v>
+        <v>1141</v>
       </c>
       <c r="C22" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="B23" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C23" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1152</v>
+        <v>1142</v>
       </c>
       <c r="C24" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1153</v>
+        <v>1143</v>
       </c>
       <c r="C25" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1138</v>
+        <v>1128</v>
       </c>
       <c r="C26" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1154</v>
+        <v>1144</v>
       </c>
       <c r="C27" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1155</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8839,10 +8859,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B32" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8858,7 +8878,7 @@
         <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>1104</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -8866,7 +8886,7 @@
         <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -8874,7 +8894,7 @@
         <v>190</v>
       </c>
       <c r="B36" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -8911,48 +8931,48 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B41" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="B42" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B43" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="C43" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="B44" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="C44" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1156</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -8968,7 +8988,7 @@
         <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>1109</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9019,7 +9039,7 @@
         <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -9032,48 +9052,48 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="B56" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="B57" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="B58" t="s">
-        <v>993</v>
+        <v>983</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>1157</v>
+        <v>1147</v>
       </c>
       <c r="C59" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1158</v>
+        <v>1148</v>
       </c>
       <c r="C60" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9081,7 +9101,7 @@
         <v>178</v>
       </c>
       <c r="B62" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -9092,7 +9112,7 @@
         <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -9103,7 +9123,7 @@
         <v>112</v>
       </c>
       <c r="C64" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -9114,7 +9134,7 @@
         <v>114</v>
       </c>
       <c r="C65" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -9125,7 +9145,7 @@
         <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -9136,7 +9156,7 @@
         <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -9147,7 +9167,7 @@
         <v>106</v>
       </c>
       <c r="C68" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -9155,7 +9175,7 @@
         <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>1105</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -9163,7 +9183,7 @@
         <v>195</v>
       </c>
       <c r="B70" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -9171,77 +9191,77 @@
         <v>196</v>
       </c>
       <c r="B71" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C71" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>487</v>
+      </c>
+      <c r="B73" t="s">
         <v>488</v>
-      </c>
-      <c r="B73" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B74" t="s">
-        <v>1106</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="B75" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C75" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>1096</v>
+        <v>1086</v>
       </c>
       <c r="B76" t="s">
-        <v>1097</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
-        <v>1099</v>
+        <v>1089</v>
       </c>
       <c r="B77" t="s">
-        <v>1098</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>1107</v>
+        <v>1097</v>
       </c>
       <c r="B78" t="s">
-        <v>1108</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1159</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9257,7 +9277,7 @@
         <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -9270,62 +9290,62 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="B84" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>1139</v>
+        <v>1129</v>
       </c>
       <c r="C85" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="B86" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="C86" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="B87" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="C87" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="B88" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="C88" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1160</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9333,29 +9353,29 @@
         <v>180</v>
       </c>
       <c r="B91" t="s">
-        <v>1051</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="B92" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C92" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="B93" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C93" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -9379,7 +9399,7 @@
         <v>132</v>
       </c>
       <c r="B96" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -9387,7 +9407,7 @@
         <v>133</v>
       </c>
       <c r="B97" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -9395,7 +9415,7 @@
         <v>134</v>
       </c>
       <c r="B98" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -9403,7 +9423,7 @@
         <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -9411,10 +9431,10 @@
         <v>136</v>
       </c>
       <c r="B100" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C100" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -9422,10 +9442,10 @@
         <v>137</v>
       </c>
       <c r="B101" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C101" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -9433,124 +9453,124 @@
         <v>138</v>
       </c>
       <c r="B102" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C102" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="B103" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="B104" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="C104" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="B105" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B106" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="C106" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="B107" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="C107" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B108" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C108" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="C109" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="B110" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="B111" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>855</v>
+        <v>845</v>
       </c>
       <c r="B112" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1161</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>1133</v>
+        <v>1123</v>
       </c>
       <c r="B115" t="s">
-        <v>1134</v>
+        <v>1124</v>
       </c>
       <c r="C115" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -9561,7 +9581,7 @@
         <v>144</v>
       </c>
       <c r="C116" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -9572,7 +9592,7 @@
         <v>145</v>
       </c>
       <c r="C117" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -9583,7 +9603,7 @@
         <v>146</v>
       </c>
       <c r="C118" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -9591,21 +9611,21 @@
         <v>139</v>
       </c>
       <c r="B119" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C119" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="B120" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C120" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -9616,7 +9636,7 @@
         <v>123</v>
       </c>
       <c r="C121" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -9624,10 +9644,10 @@
         <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C122" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -9638,26 +9658,26 @@
         <v>124</v>
       </c>
       <c r="C123" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="B124" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="C124" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1162</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9694,13 +9714,13 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="B131" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="C131" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -9721,62 +9741,62 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>1163</v>
+        <v>1153</v>
       </c>
       <c r="C134" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B135" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B136" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C136" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1164</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="B139" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="C139" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="B140" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
       <c r="C140" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -9808,45 +9828,45 @@
         <v>156</v>
       </c>
       <c r="B145" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B146" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C146" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>1064</v>
+        <v>1054</v>
       </c>
       <c r="B147" t="s">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="C147" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="B148" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B149" t="s">
-        <v>1166</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -9875,29 +9895,29 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="B154" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B155" t="s">
-        <v>1167</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B156" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="C156" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -9916,7 +9936,7 @@
         <v>166</v>
       </c>
       <c r="C159" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -9927,7 +9947,7 @@
         <v>167</v>
       </c>
       <c r="C160" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -9938,7 +9958,7 @@
         <v>168</v>
       </c>
       <c r="C161" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -9965,122 +9985,122 @@
         <v>171</v>
       </c>
       <c r="C164" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="B165" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="166" spans="1:3" s="6" customFormat="1">
       <c r="A166" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>1168</v>
+        <v>1158</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>1092</v>
+        <v>1082</v>
       </c>
       <c r="B168" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="C168" t="s">
-        <v>1093</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="169" spans="1:3" s="6" customFormat="1">
       <c r="A169" s="6" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B170" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C170" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="171" spans="1:3" s="6" customFormat="1">
       <c r="A171" s="6" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="B172" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="C172" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>1152</v>
+        <v>1142</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>1054</v>
+        <v>1044</v>
       </c>
       <c r="B174" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="C174" t="s">
-        <v>1055</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B176" t="s">
-        <v>1071</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>1077</v>
+        <v>1067</v>
       </c>
       <c r="B177" t="s">
-        <v>1078</v>
+        <v>1068</v>
       </c>
       <c r="C177" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -10088,10 +10108,10 @@
         <v>232</v>
       </c>
       <c r="B178" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="C178" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -10099,7 +10119,7 @@
         <v>233</v>
       </c>
       <c r="B179" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -10107,21 +10127,21 @@
         <v>241</v>
       </c>
       <c r="B180" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="C180" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="B181" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="C181" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -10134,10 +10154,10 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B183" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -10145,10 +10165,10 @@
         <v>236</v>
       </c>
       <c r="B184" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="C184" t="s">
-        <v>1056</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -10156,7 +10176,7 @@
         <v>237</v>
       </c>
       <c r="B185" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -10164,7 +10184,7 @@
         <v>238</v>
       </c>
       <c r="B186" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -10172,7 +10192,7 @@
         <v>239</v>
       </c>
       <c r="B187" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -10180,7 +10200,7 @@
         <v>240</v>
       </c>
       <c r="B188" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -10188,10 +10208,10 @@
         <v>271</v>
       </c>
       <c r="B189" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="C189" t="s">
-        <v>1056</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -10204,92 +10224,92 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B191" t="s">
-        <v>1052</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="6" customFormat="1">
       <c r="A193" s="6" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>1169</v>
+        <v>1159</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>1143</v>
+        <v>1133</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>1116</v>
+        <v>1106</v>
       </c>
       <c r="B196" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>1170</v>
+        <v>1160</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>1171</v>
+        <v>1161</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B200" t="s">
-        <v>1072</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -10297,10 +10317,10 @@
         <v>242</v>
       </c>
       <c r="B201" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="C201" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.5" customHeight="1">
@@ -10308,10 +10328,10 @@
         <v>244</v>
       </c>
       <c r="B202" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="C202" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -10319,7 +10339,7 @@
         <v>243</v>
       </c>
       <c r="B203" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -10327,10 +10347,10 @@
         <v>245</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>1172</v>
+        <v>1162</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -10349,15 +10369,15 @@
         <v>248</v>
       </c>
       <c r="C206" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B207" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -10365,7 +10385,7 @@
         <v>250</v>
       </c>
       <c r="B208" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -10381,7 +10401,7 @@
         <v>256</v>
       </c>
       <c r="B210" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -10389,7 +10409,7 @@
         <v>257</v>
       </c>
       <c r="B211" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -10397,10 +10417,10 @@
         <v>258</v>
       </c>
       <c r="B212" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="C212" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -10408,7 +10428,7 @@
         <v>259</v>
       </c>
       <c r="B213" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -10416,10 +10436,10 @@
         <v>260</v>
       </c>
       <c r="B214" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="C214" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -10427,7 +10447,7 @@
         <v>261</v>
       </c>
       <c r="B215" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -10443,10 +10463,10 @@
         <v>270</v>
       </c>
       <c r="B217" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="C217" t="s">
-        <v>1056</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -10454,59 +10474,59 @@
         <v>272</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>1173</v>
+        <v>1163</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>1174</v>
+        <v>1164</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>1175</v>
+        <v>1165</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B223" t="s">
-        <v>1073</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B224" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -10514,7 +10534,7 @@
         <v>266</v>
       </c>
       <c r="B225" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -10522,7 +10542,7 @@
         <v>267</v>
       </c>
       <c r="B226" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -10530,7 +10550,7 @@
         <v>274</v>
       </c>
       <c r="B227" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -10538,7 +10558,7 @@
         <v>273</v>
       </c>
       <c r="B228" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -10546,45 +10566,45 @@
         <v>275</v>
       </c>
       <c r="B229" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>1176</v>
+        <v>1166</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B233" t="s">
-        <v>1074</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B234" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -10592,7 +10612,7 @@
         <v>278</v>
       </c>
       <c r="B235" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -10608,7 +10628,7 @@
         <v>280</v>
       </c>
       <c r="B237" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -10616,7 +10636,7 @@
         <v>282</v>
       </c>
       <c r="B238" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -10624,7 +10644,7 @@
         <v>283</v>
       </c>
       <c r="B239" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -10632,7 +10652,7 @@
         <v>284</v>
       </c>
       <c r="B240" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -10640,64 +10660,64 @@
         <v>285</v>
       </c>
       <c r="B241" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>1128</v>
+        <v>1118</v>
       </c>
       <c r="B243" t="s">
-        <v>1129</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>1177</v>
+        <v>1167</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B246" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B247" t="s">
         <v>291</v>
       </c>
       <c r="C247" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B248" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -10705,10 +10725,10 @@
         <v>289</v>
       </c>
       <c r="B249" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="C249" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -10716,15 +10736,15 @@
         <v>290</v>
       </c>
       <c r="B250" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B251" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -10732,10 +10752,10 @@
         <v>292</v>
       </c>
       <c r="B252" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="C252" t="s">
-        <v>1053</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -10743,7 +10763,7 @@
         <v>293</v>
       </c>
       <c r="B253" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -10751,7 +10771,7 @@
         <v>294</v>
       </c>
       <c r="B254" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -10759,7 +10779,7 @@
         <v>295</v>
       </c>
       <c r="B255" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -10767,75 +10787,75 @@
         <v>296</v>
       </c>
       <c r="B256" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>1178</v>
+        <v>1168</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="B260" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C260" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B261" t="s">
-        <v>495</v>
+        <v>1193</v>
       </c>
       <c r="C261" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
+        <v>492</v>
+      </c>
+      <c r="B262" t="s">
         <v>493</v>
       </c>
-      <c r="B262" t="s">
-        <v>494</v>
-      </c>
       <c r="C262" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B263" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B264" t="s">
         <v>299</v>
@@ -10843,26 +10863,26 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B265" t="s">
         <v>300</v>
       </c>
       <c r="C265" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B266" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B267" t="s">
         <v>301</v>
@@ -10870,7 +10890,7 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B268" t="s">
         <v>302</v>
@@ -10878,7 +10898,7 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B269" t="s">
         <v>303</v>
@@ -10886,18 +10906,18 @@
     </row>
     <row r="270" spans="1:3" s="6" customFormat="1">
       <c r="A270" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>304</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B271" t="s">
         <v>305</v>
@@ -10905,7 +10925,7 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B272" t="s">
         <v>306</v>
@@ -10913,7 +10933,7 @@
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B273" t="s">
         <v>307</v>
@@ -10921,7 +10941,7 @@
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B274" t="s">
         <v>308</v>
@@ -10929,949 +10949,949 @@
     </row>
     <row r="275" spans="1:3" s="6" customFormat="1">
       <c r="A275" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>309</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B276" t="s">
-        <v>310</v>
+        <v>736</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B277" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B278" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>1179</v>
+        <v>1169</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B281" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B282" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B283" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B284" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C284" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B285" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B286" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C286" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B287" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B288" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C288" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B289" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B290" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B291" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B292" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B293" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>986</v>
+        <v>976</v>
       </c>
       <c r="B294" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="C294" t="s">
-        <v>983</v>
+        <v>973</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>988</v>
+        <v>978</v>
       </c>
       <c r="B295" t="s">
-        <v>989</v>
+        <v>979</v>
       </c>
       <c r="C295" t="s">
-        <v>983</v>
+        <v>973</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="B296" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="C296" t="s">
-        <v>983</v>
+        <v>973</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
       <c r="B297" t="s">
-        <v>1122</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="B300" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="C300" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>982</v>
+        <v>972</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>1145</v>
+        <v>1135</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>984</v>
+        <v>974</v>
       </c>
       <c r="B302" s="7" t="s">
-        <v>1146</v>
+        <v>1136</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>985</v>
+        <v>975</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>1181</v>
+        <v>1171</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B305" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="C305" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
+        <v>463</v>
+      </c>
+      <c r="B306" t="s">
         <v>464</v>
-      </c>
-      <c r="B306" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B307" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B308" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C308" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B309" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B310" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C310" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B311" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C311" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B312" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B313" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B314" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B315" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B316" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B317" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B318" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B319" s="7" t="s">
-        <v>1147</v>
+        <v>1137</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>1067</v>
+        <v>1057</v>
       </c>
       <c r="B320" t="s">
-        <v>1068</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>1182</v>
+        <v>1172</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>1124</v>
+        <v>1114</v>
       </c>
       <c r="B322" t="s">
-        <v>1125</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B325" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B326" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B327" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C327" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B328" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B329" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C329" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B330" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C330" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B331" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B332" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B333" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B334" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B335" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B336" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B337" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B338" s="7" t="s">
-        <v>1182</v>
+        <v>1172</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>1126</v>
+        <v>1116</v>
       </c>
       <c r="B339" t="s">
-        <v>1127</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B342" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="C342" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B343" t="s">
-        <v>555</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B344" t="s">
-        <v>556</v>
+        <v>1197</v>
       </c>
       <c r="C344" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B345" t="s">
-        <v>557</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B346" t="s">
-        <v>582</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B347" t="s">
-        <v>558</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B348" t="s">
-        <v>559</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>1084</v>
+        <v>1074</v>
       </c>
       <c r="B349" t="s">
-        <v>1085</v>
+        <v>1075</v>
       </c>
       <c r="C349" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>1184</v>
+        <v>1202</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="B352" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="C352" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>1185</v>
+        <v>1174</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="B355" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="B356" t="s">
-        <v>705</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="B357" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="B358" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="B359" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="B360" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="B361" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="B362" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="B363" t="s">
-        <v>1111</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>1186</v>
+        <v>1175</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="B365" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="B366" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="B367" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="B368" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="B369" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="B370" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="B371" t="s">
-        <v>1061</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="B372" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="B373" t="s">
-        <v>1101</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>1187</v>
+        <v>1176</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="B376" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="B377" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="B378" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="B379" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="B380" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="B381" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="B382" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="B383" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="B384" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="B385" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="B386" t="s">
-        <v>754</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="B387" s="7" t="s">
-        <v>1188</v>
+        <v>1177</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="B389" t="s">
         <v>305</v>
@@ -11879,15 +11899,15 @@
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="B390" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="B391" t="s">
         <v>307</v>
@@ -11895,1039 +11915,1039 @@
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="B392" t="s">
-        <v>1112</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="B394" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="B395" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="B396" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="B397" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="B398" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>1189</v>
+        <v>1178</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="B401" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="B402" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="B403" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B404" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="B405" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>1190</v>
+        <v>1179</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="B408" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="B409" t="s">
-        <v>1076</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="B410" s="7" t="s">
-        <v>1171</v>
+        <v>1161</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="B411" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="B412" s="7" t="s">
-        <v>1191</v>
+        <v>1180</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="B413" t="s">
-        <v>1027</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="B414" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="B415" t="s">
-        <v>1045</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="B416" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="B417" t="s">
-        <v>1043</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="B418" t="s">
-        <v>1042</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
       <c r="B419" t="s">
-        <v>1041</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="B420" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="B421" t="s">
-        <v>1047</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="B422" s="7" t="s">
-        <v>1173</v>
+        <v>1163</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="B423" s="7" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1174</v>
+        <v>1164</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>1192</v>
+        <v>1181</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>1123</v>
+        <v>1113</v>
       </c>
       <c r="B426" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B427" t="s">
-        <v>1028</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="B428" t="s">
-        <v>1029</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>1033</v>
+        <v>1023</v>
       </c>
       <c r="B429" t="s">
-        <v>1032</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>1037</v>
+        <v>1027</v>
       </c>
       <c r="B430" t="s">
-        <v>1034</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>1038</v>
+        <v>1028</v>
       </c>
       <c r="B431" t="s">
-        <v>1035</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>1039</v>
+        <v>1029</v>
       </c>
       <c r="B432" t="s">
-        <v>1036</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>1049</v>
+        <v>1039</v>
       </c>
       <c r="B433" t="s">
-        <v>1048</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B434" s="7" t="s">
-        <v>1148</v>
+        <v>1138</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="B435" t="s">
-        <v>1091</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>877</v>
+        <v>867</v>
       </c>
       <c r="B437" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>896</v>
+        <v>886</v>
       </c>
       <c r="B438" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="B439" t="s">
-        <v>860</v>
+        <v>850</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>894</v>
+        <v>884</v>
       </c>
       <c r="B440" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>893</v>
+        <v>883</v>
       </c>
       <c r="B441" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>892</v>
+        <v>882</v>
       </c>
       <c r="B442" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>891</v>
+        <v>881</v>
       </c>
       <c r="B443" t="s">
-        <v>864</v>
+        <v>854</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>890</v>
+        <v>880</v>
       </c>
       <c r="B444" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>889</v>
+        <v>879</v>
       </c>
       <c r="B445" t="s">
-        <v>866</v>
+        <v>856</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="B446" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>887</v>
+        <v>877</v>
       </c>
       <c r="B447" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>897</v>
+        <v>887</v>
       </c>
       <c r="B448" t="s">
-        <v>869</v>
+        <v>859</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
       <c r="B449" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="B450" t="s">
-        <v>871</v>
+        <v>861</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="B451" t="s">
-        <v>872</v>
+        <v>862</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>883</v>
+        <v>873</v>
       </c>
       <c r="B452" s="7" t="s">
-        <v>1144</v>
+        <v>1134</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>882</v>
+        <v>872</v>
       </c>
       <c r="B453" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="B454" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="B455" t="s">
-        <v>875</v>
+        <v>865</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="B456" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>1094</v>
+        <v>1084</v>
       </c>
       <c r="B457" t="s">
-        <v>1095</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>1193</v>
+        <v>1182</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="B460" t="s">
-        <v>1088</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>915</v>
+        <v>905</v>
       </c>
       <c r="B461" t="s">
-        <v>900</v>
+        <v>890</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="B462" t="s">
-        <v>901</v>
+        <v>891</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="B463" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="B464" t="s">
-        <v>903</v>
+        <v>893</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>911</v>
+        <v>901</v>
       </c>
       <c r="B465" t="s">
-        <v>904</v>
+        <v>894</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="B466" t="s">
-        <v>1113</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="B467" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B468" t="s">
-        <v>1114</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
       <c r="B469" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>1102</v>
+        <v>1092</v>
       </c>
       <c r="B470" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>913</v>
+        <v>903</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>1194</v>
+        <v>1183</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B473" s="7" t="s">
-        <v>1195</v>
+        <v>1184</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="6" customFormat="1">
       <c r="A474" s="6" t="s">
-        <v>929</v>
+        <v>919</v>
       </c>
       <c r="B474" s="6" t="s">
-        <v>1196</v>
+        <v>1185</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="476" spans="1:3" s="6" customFormat="1">
       <c r="A476" s="6" t="s">
-        <v>921</v>
+        <v>911</v>
       </c>
       <c r="B476" s="6" t="s">
-        <v>922</v>
+        <v>912</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
-        <v>930</v>
+        <v>920</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>1197</v>
+        <v>1186</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
-        <v>927</v>
+        <v>917</v>
       </c>
       <c r="B479" t="s">
-        <v>925</v>
+        <v>915</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
-        <v>928</v>
+        <v>918</v>
       </c>
       <c r="B480" t="s">
-        <v>926</v>
+        <v>916</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>1119</v>
+        <v>1109</v>
       </c>
       <c r="B481" t="s">
-        <v>1120</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
-        <v>924</v>
+        <v>914</v>
       </c>
       <c r="B482" s="7" t="s">
-        <v>1198</v>
+        <v>1187</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" t="s">
-        <v>937</v>
+        <v>927</v>
       </c>
       <c r="B484" t="s">
-        <v>1199</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
-        <v>938</v>
+        <v>928</v>
       </c>
       <c r="B485" t="s">
-        <v>932</v>
+        <v>922</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
-        <v>939</v>
+        <v>929</v>
       </c>
       <c r="B486" t="s">
-        <v>933</v>
+        <v>923</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
-        <v>981</v>
+        <v>971</v>
       </c>
       <c r="B487" t="s">
-        <v>934</v>
+        <v>924</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="B488" t="s">
-        <v>935</v>
+        <v>925</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>941</v>
+        <v>931</v>
       </c>
       <c r="B489" t="s">
-        <v>936</v>
+        <v>926</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>942</v>
+        <v>932</v>
       </c>
       <c r="B490" s="7" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" t="s">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="B492" t="s">
-        <v>948</v>
+        <v>938</v>
       </c>
     </row>
     <row r="493" spans="1:3">
       <c r="A493" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
       <c r="B493" t="s">
-        <v>949</v>
+        <v>939</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
       <c r="B494" t="s">
-        <v>950</v>
+        <v>940</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>955</v>
+        <v>945</v>
       </c>
       <c r="B495" t="s">
-        <v>951</v>
+        <v>941</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
       <c r="B496" t="s">
-        <v>952</v>
+        <v>942</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
-        <v>956</v>
+        <v>946</v>
       </c>
       <c r="B497" s="7" t="s">
-        <v>1149</v>
+        <v>1139</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="499" spans="1:3">
       <c r="A499" t="s">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="B499" t="s">
-        <v>959</v>
+        <v>949</v>
       </c>
     </row>
     <row r="500" spans="1:3">
       <c r="A500" t="s">
-        <v>965</v>
+        <v>955</v>
       </c>
       <c r="B500" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="B501" t="s">
-        <v>961</v>
+        <v>951</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B502" t="s">
-        <v>962</v>
+        <v>952</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="B503" t="s">
-        <v>963</v>
+        <v>953</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="6" customFormat="1">
       <c r="A504" s="6" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="B504" s="6" t="s">
-        <v>1089</v>
+        <v>1079</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="6" customFormat="1">
       <c r="A506" s="6" t="s">
-        <v>971</v>
+        <v>961</v>
       </c>
       <c r="B506" s="6" t="s">
-        <v>972</v>
+        <v>962</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="507" spans="1:3">
       <c r="A507" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="B507" t="s">
-        <v>973</v>
+        <v>963</v>
       </c>
     </row>
     <row r="508" spans="1:3">
       <c r="A508" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="B508" t="s">
-        <v>974</v>
+        <v>964</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="B509" t="s">
-        <v>975</v>
+        <v>965</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="B510" s="7" t="s">
-        <v>1201</v>
+        <v>1190</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="512" spans="1:3">
       <c r="A512" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="B512" t="s">
-        <v>1001</v>
+        <v>991</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513" t="s">
-        <v>1015</v>
+        <v>1005</v>
       </c>
       <c r="B513" t="s">
-        <v>1002</v>
+        <v>992</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
-        <v>1016</v>
+        <v>1006</v>
       </c>
       <c r="B514" t="s">
-        <v>1003</v>
+        <v>993</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>1017</v>
+        <v>1007</v>
       </c>
       <c r="B515" t="s">
-        <v>1004</v>
+        <v>994</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>1026</v>
+        <v>1016</v>
       </c>
       <c r="B516" t="s">
-        <v>1005</v>
+        <v>995</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>1018</v>
+        <v>1008</v>
       </c>
       <c r="B517" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>1019</v>
+        <v>1009</v>
       </c>
       <c r="B518" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B519" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="B520" t="s">
-        <v>1009</v>
+        <v>999</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>1022</v>
+        <v>1012</v>
       </c>
       <c r="B521" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="B522" t="s">
-        <v>1011</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="B523" t="s">
-        <v>1012</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>1025</v>
+        <v>1015</v>
       </c>
       <c r="B524" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
-        <v>1014</v>
+        <v>1004</v>
       </c>
       <c r="B525" s="7" t="s">
-        <v>1202</v>
+        <v>1191</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76662D60-266C-45CA-84A1-9B0556D64F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA94916D-F124-4078-BD69-CB9C735082DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3621,9 +3621,6 @@
     <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t xml:space="preserve">1040, Schedule C forms does not exist for Self-Employment Verification </t>
   </si>
   <si>
@@ -3661,6 +3658,9 @@
   </si>
   <si>
     <t>Assign button was not found in Yardi.</t>
+  </si>
+  <si>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4144,7 +4144,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1192</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -6174,10 +6174,10 @@
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B34" t="s">
         <v>1204</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1"/>
@@ -7621,10 +7621,10 @@
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1">
       <c r="A55" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B55" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.25" customHeight="1"/>
@@ -10828,7 +10828,7 @@
         <v>491</v>
       </c>
       <c r="B261" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C261" t="s">
         <v>520</v>
@@ -11534,7 +11534,7 @@
         <v>379</v>
       </c>
       <c r="B343" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -11542,7 +11542,7 @@
         <v>380</v>
       </c>
       <c r="B344" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C344" t="s">
         <v>522</v>
@@ -11553,7 +11553,7 @@
         <v>456</v>
       </c>
       <c r="B345" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -11561,7 +11561,7 @@
         <v>381</v>
       </c>
       <c r="B346" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -11569,7 +11569,7 @@
         <v>382</v>
       </c>
       <c r="B347" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -11577,7 +11577,7 @@
         <v>383</v>
       </c>
       <c r="B348" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -11596,7 +11596,7 @@
         <v>468</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>1127</v>
@@ -11637,7 +11637,7 @@
         <v>696</v>
       </c>
       <c r="B356" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -11875,7 +11875,7 @@
         <v>744</v>
       </c>
       <c r="B386" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="387" spans="1:3">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA94916D-F124-4078-BD69-CB9C735082DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0D4BEC-57F3-4A4E-9F4C-1A0EFBAB68D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3660,7 +3660,7 @@
     <t>Assign button was not found in Yardi.</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1001\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0D4BEC-57F3-4A4E-9F4C-1A0EFBAB68D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FE66E4-F798-479E-85DC-FC8EBAF3014A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3660,7 +3660,7 @@
     <t>Assign button was not found in Yardi.</t>
   </si>
   <si>
-    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1001\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FE66E4-F798-479E-85DC-FC8EBAF3014A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F99069-74C7-4429-99EE-547FFF9C8C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11340" yWindow="240" windowWidth="13485" windowHeight="12405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3660,7 +3660,7 @@
     <t>Assign button was not found in Yardi.</t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1007\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F99069-74C7-4429-99EE-547FFF9C8C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0EA44B-A0E5-476C-9605-AD96821BA98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11340" yWindow="240" windowWidth="13485" windowHeight="12405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="735" windowWidth="21495" windowHeight="10875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3660,7 +3660,7 @@
     <t>Assign button was not found in Yardi.</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1007\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0EA44B-A0E5-476C-9605-AD96821BA98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110B3355-9D8B-4D98-B571-8856FE6767A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="735" windowWidth="21495" windowHeight="10875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="1208">
   <si>
     <t>Name</t>
   </si>
@@ -3661,6 +3661,12 @@
   </si>
   <si>
     <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>DelayAfterTime</t>
+  </si>
+  <si>
+    <t>ElementTimeout</t>
   </si>
 </sst>
 </file>
@@ -7150,7 +7156,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z1015"/>
+  <dimension ref="A1:Z1017"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -7573,62 +7579,76 @@
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>987</v>
+        <v>1206</v>
       </c>
       <c r="B49" t="s">
-        <v>987</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>1048</v>
+        <v>1207</v>
       </c>
       <c r="B50" t="s">
-        <v>1048</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>1049</v>
+        <v>987</v>
       </c>
       <c r="B51" t="s">
-        <v>1049</v>
+        <v>987</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1120</v>
+        <v>1048</v>
       </c>
       <c r="B52" t="s">
-        <v>1120</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1121</v>
+        <v>1049</v>
       </c>
       <c r="B53" t="s">
-        <v>1121</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B54" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1">
       <c r="A55" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A56" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A57" t="s">
         <v>1202</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B57" t="s">
         <v>1202</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="57" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="58" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="59" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
@@ -8587,6 +8607,8 @@
     <row r="1013" ht="14.25" customHeight="1"/>
     <row r="1014" ht="14.25" customHeight="1"/>
     <row r="1015" ht="14.25" customHeight="1"/>
+    <row r="1016" ht="14.25" customHeight="1"/>
+    <row r="1017" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110B3355-9D8B-4D98-B571-8856FE6767A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785766A1-5F66-428F-9302-D4366F4EEFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3660,13 +3660,13 @@
     <t>Assign button was not found in Yardi.</t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>DelayAfterTime</t>
   </si>
   <si>
     <t>ElementTimeout</t>
+  </si>
+  <si>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4150,7 +4150,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -7579,18 +7579,18 @@
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B49" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B50" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1014\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785766A1-5F66-428F-9302-D4366F4EEFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8174209E-61A1-4FE0-9BD8-B90486D56657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3666,7 +3666,7 @@
     <t>ElementTimeout</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1014\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8174209E-61A1-4FE0-9BD8-B90486D56657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99576DFB-D16C-4633-80D3-E36A412B827D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="28260" windowHeight="13665" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1209">
   <si>
     <t>Name</t>
   </si>
@@ -3666,14 +3666,17 @@
     <t>ElementTimeout</t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>UnsupportedIncomeTypesFilePath</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3703,6 +3706,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3730,7 +3738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3743,6 +3751,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7649,7 +7658,14 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="58" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A58" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>1208</v>
+      </c>
+    </row>
     <row r="59" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="61" spans="1:2" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99576DFB-D16C-4633-80D3-E36A412B827D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19FC9AC-3E1E-4DB1-91B5-C46E93573A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="28260" windowHeight="13665" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3666,10 +3666,10 @@
     <t>ElementTimeout</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>UnsupportedIncomeTypesFilePath</t>
+  </si>
+  <si>
+    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4159,7 +4159,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -7660,10 +7660,10 @@
     </row>
     <row r="58" spans="1:2" ht="14.25" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19FC9AC-3E1E-4DB1-91B5-C46E93573A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D916EA8C-F29D-4B87-9B78-FCAB61CD2C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="16740" windowHeight="8250" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1210">
   <si>
     <t>Name</t>
   </si>
@@ -3669,7 +3669,10 @@
     <t>UnsupportedIncomeTypesFilePath</t>
   </si>
   <si>
-    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>TX_VSAVerificationProperties</t>
   </si>
 </sst>
 </file>
@@ -7666,7 +7669,14 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="59" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A59" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1209</v>
+      </c>
+    </row>
     <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="61" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="62" spans="1:2" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D916EA8C-F29D-4B87-9B78-FCAB61CD2C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F0857E-F12D-4A46-AE7D-A85A54D746FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="16740" windowHeight="8250" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1211">
   <si>
     <t>Name</t>
   </si>
@@ -3673,13 +3673,16 @@
   </si>
   <si>
     <t>TX_VSAVerificationProperties</t>
+  </si>
+  <si>
+    <t>TX_NoAssetsCheckProperties</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3710,8 +3713,15 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -3741,7 +3751,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3755,6 +3765,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7171,23 +7182,23 @@
   <dimension ref="A1:Z1017"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="60.28515625" customWidth="1"/>
-    <col min="4" max="26" width="65.42578125" customWidth="1"/>
+    <col min="1" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="26" width="65.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="1"/>
@@ -7214,84 +7225,104 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>684</v>
       </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
@@ -7300,388 +7331,493 @@
       <c r="B12" s="2" t="s">
         <v>205</v>
       </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>500</v>
       </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>501</v>
       </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>502</v>
       </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A17" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A18" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A19" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A20" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A21" t="s">
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A22" t="s">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A23" t="s">
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A24" t="s">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A24" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A25" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A25" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="14.25" customHeight="1">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:4" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="14.25" customHeight="1">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:4" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>230</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="14.25" customHeight="1">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>254</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A29" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A30" t="s">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A30" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A31" t="s">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A31" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A32" t="s">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A32" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="14.25" customHeight="1">
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>515</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A34" t="s">
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A34" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="14.25" customHeight="1">
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A36" t="s">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A36" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A37" t="s">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A37" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A38" t="s">
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A38" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A39" t="s">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A39" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A40" t="s">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A40" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>1108</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A41" t="s">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A41" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A42" t="s">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A42" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A43" t="s">
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A43" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A44" t="s">
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A44" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A45" t="s">
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A45" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A46" t="s">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A46" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>984</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A47" t="s">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A47" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A48" t="s">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A48" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>986</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A49" t="s">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A49" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>1205</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A50" t="s">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A50" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>1206</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A51" t="s">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A51" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A52" t="s">
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+    </row>
+    <row r="52" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A52" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>1048</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A53" t="s">
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A53" s="2" t="s">
         <v>1049</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>1049</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A54" t="s">
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A54" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>1120</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A55" t="s">
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A55" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>1121</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A56" t="s">
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A56" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A57" t="s">
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A57" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>1202</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A58" s="8" t="s">
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A58" s="9" t="s">
         <v>1207</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="9" t="s">
         <v>1207</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A59" t="s">
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A59" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>1209</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="61" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="62" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="63" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="64" spans="1:2" ht="14.25" customHeight="1"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A60" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="62" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="63" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="64" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="65" ht="14.25" customHeight="1"/>
     <row r="66" ht="14.25" customHeight="1"/>
     <row r="67" ht="14.25" customHeight="1"/>
@@ -9228,45 +9364,45 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>195</v>
+        <v>494</v>
       </c>
       <c r="B70" t="s">
-        <v>669</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B71" t="s">
-        <v>670</v>
-      </c>
-      <c r="C71" t="s">
-        <v>522</v>
+        <v>669</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>513</v>
+        <v>196</v>
       </c>
       <c r="B72" t="s">
-        <v>671</v>
+        <v>670</v>
+      </c>
+      <c r="C72" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s">
-        <v>488</v>
+        <v>671</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B74" t="s">
-        <v>1096</v>
+        <v>488</v>
       </c>
     </row>
     <row r="75" spans="1:3">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F0857E-F12D-4A46-AE7D-A85A54D746FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3CEBC6-4E14-4B1F-8367-2E21DE97E982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="1393">
   <si>
     <t>Name</t>
   </si>
@@ -3676,6 +3676,552 @@
   </si>
   <si>
     <t>TX_NoAssetsCheckProperties</t>
+  </si>
+  <si>
+    <t>The Certification Questionnaire is missing for one or more adult household members. </t>
+  </si>
+  <si>
+    <t>Name has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>Unit Number has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>Property Name has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>One of the Move-In, Recertification, or Addition of Household checkboxes has not been selected. </t>
+  </si>
+  <si>
+    <t>Question 1 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 1 has been answered Yes, but the PHA Name has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 1 has been answered Yes. Upload HAP contract with final signed documents. </t>
+  </si>
+  <si>
+    <t>Question 2 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 2 has been answered Yes, but the Program Name and/or the Organization Providing Rental Assistance has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 3 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 3 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 4 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 4 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 5 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 5 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 6 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 6 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 7 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 7 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 8 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 8 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 9 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 9 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 9 has been answered Yes, but one or more household member names listed in the income section does not match the ICW. </t>
+  </si>
+  <si>
+    <t>Question 10 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 10 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 11 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 11 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 12 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 12 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 13 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 13 has not been fully completed. </t>
+  </si>
+  <si>
+    <t>Question 14 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 14 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 15 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 15 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 16 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 16 has been answered Yes, but Monthly Net Income has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 17 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 17 has been answered Yes, but Amount Per Semester has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 18 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 19 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>One or more income types documented on the Certification Questionnaire do not match the income information listed on the ICW. </t>
+  </si>
+  <si>
+    <t>Question 20 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 20 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 21 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 21 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 22 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 22 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 23 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 23 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 24 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 24 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 25 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 25 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 26 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 26 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 27 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 27 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 28 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 28 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 29 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 29 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 30 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 30 has been answered Yes, but Cash Value has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 31 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 31 has been answered Yes, but Cash Value has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 32 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 32 has been answered Yes. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Question 33 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 33 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 34 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 34 has been answered Yes, but Current Balance has not been provided. </t>
+  </si>
+  <si>
+    <t>Question 35 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 35 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>Question 36 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 36 has been answered Yes, but Amount Received has not been provided. </t>
+  </si>
+  <si>
+    <t>One or more asset type(s), source(s), and/or cash value(s) documented on the Certification Questionnaire do not match the asset information listed on the ICW. </t>
+  </si>
+  <si>
+    <t>Question 37 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>Question 37 has been answered No, but one or more of Questions 38–54 have been completed. </t>
+  </si>
+  <si>
+    <t>Question 37 has been answered Yes, but the required student certification questions have not been completed. </t>
+  </si>
+  <si>
+    <t>Question 39 has been answered Yes, but the required questions have not been completed. </t>
+  </si>
+  <si>
+    <t>Application is for a HOME/SHTF unit, but Questions 45–50 have not been fully completed. </t>
+  </si>
+  <si>
+    <t>Questions 51–54 have not been completed. </t>
+  </si>
+  <si>
+    <t>Certification Questionnaire has not been signed. </t>
+  </si>
+  <si>
+    <t>Printed Name has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>Certification Questionnaire has not been dated. </t>
+  </si>
+  <si>
+    <t>Date listed on the Certification Questionnaire is not within 120 days of Move-In date. </t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Certification Questionnaire. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>CQExists</t>
+  </si>
+  <si>
+    <t>CQ_Name</t>
+  </si>
+  <si>
+    <t>CQ_UnitNumber</t>
+  </si>
+  <si>
+    <t>CQ_PropertyName</t>
+  </si>
+  <si>
+    <t>CQ_Checkboxes</t>
+  </si>
+  <si>
+    <t>CQ_Q1Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q1YesNoPHAName</t>
+  </si>
+  <si>
+    <t>CQ_Q2YesNoProgramName</t>
+  </si>
+  <si>
+    <t>CQ_Q3NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q5NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q6NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q7NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q8NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q9NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q10NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q2NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q1NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q4NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q3Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q4Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q5Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q6Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q7Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q8Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q9Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q10Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q9YesNoICWNamesMatch</t>
+  </si>
+  <si>
+    <t>CQ_Q11NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q11Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q19NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q18NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q17Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q17NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q12NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q12Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q13NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q13Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q14NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q14Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q15NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q15Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q16NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q16Yes</t>
+  </si>
+  <si>
+    <t>CQ_IncomeType</t>
+  </si>
+  <si>
+    <t>CQ_Q20NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q20Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q30NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q31NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q32NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q33NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q34NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q35NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q36NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q37NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q30Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q31Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q34Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q21NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q21Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q22NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q22Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q23NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q23Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q24NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q24Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q25Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q25NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q26NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q26Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q27NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q27Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q28NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q28Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q29NotYesNo</t>
+  </si>
+  <si>
+    <t>CQ_Q29Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q32Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q37Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q39Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q33Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q35Yes</t>
+  </si>
+  <si>
+    <t>CQ_Q36Yes</t>
+  </si>
+  <si>
+    <t>CQ_AssetType</t>
+  </si>
+  <si>
+    <t>CQ_Q37No</t>
+  </si>
+  <si>
+    <t>CQ_HomeSHTF</t>
+  </si>
+  <si>
+    <t>CQ_Q51-54NotCompleted</t>
+  </si>
+  <si>
+    <t>CQ_NotSigned</t>
+  </si>
+  <si>
+    <t>CQ_PrintedName</t>
+  </si>
+  <si>
+    <t>CQ_NotDated</t>
+  </si>
+  <si>
+    <t>CQ_CheckMoveInDate</t>
+  </si>
+  <si>
+    <t>CQ_FindingError</t>
+  </si>
+  <si>
+    <t>CQ</t>
+  </si>
+  <si>
+    <t>Certification Questionnaire</t>
   </si>
 </sst>
 </file>
@@ -4611,7 +5157,14 @@
         <v>989</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="61" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A61" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1392</v>
+      </c>
+    </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="63" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="64" spans="1:3" ht="14.25" customHeight="1"/>
@@ -8780,7 +9333,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C525"/>
+  <dimension ref="A1:C616"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -13134,6 +13687,726 @@
         <v>1127</v>
       </c>
     </row>
+    <row r="527" spans="1:3">
+      <c r="A527" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3">
+      <c r="A528" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B583" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B586" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B587" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B589" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B591" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B596" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B597" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B600" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1300</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C525" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
   <conditionalFormatting sqref="A479:A481 A476:A477 A461:A471 A473:A474">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3CEBC6-4E14-4B1F-8367-2E21DE97E982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB46C1E-A073-4D2A-9011-0C1AEFFD02E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Findings" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$525</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$526</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="1393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="1394">
   <si>
     <t>Name</t>
   </si>
@@ -3675,9 +3675,6 @@
     <t>TX_VSAVerificationProperties</t>
   </si>
   <si>
-    <t>TX_NoAssetsCheckProperties</t>
-  </si>
-  <si>
     <t>The Certification Questionnaire is missing for one or more adult household members. </t>
   </si>
   <si>
@@ -4222,6 +4219,12 @@
   </si>
   <si>
     <t>Certification Questionnaire</t>
+  </si>
+  <si>
+    <t>ThirdPartyVerification</t>
+  </si>
+  <si>
+    <t>Third party verification of assets is missing from the application and this property requires asset verification. Manual review required.</t>
   </si>
 </sst>
 </file>
@@ -5159,10 +5162,10 @@
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1">
       <c r="A61" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B61" t="s">
         <v>1391</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1"/>
@@ -7732,7 +7735,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z1017"/>
+  <dimension ref="A1:Z1016"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
@@ -8279,70 +8282,70 @@
     </row>
     <row r="52" spans="1:4" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>1048</v>
+        <v>1120</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1048</v>
+        <v>1120</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>1049</v>
+        <v>1121</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1049</v>
+        <v>1121</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
     </row>
     <row r="54" spans="1:4" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>1121</v>
+        <v>1202</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1121</v>
+        <v>1202</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A56" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>1122</v>
+      <c r="A56" s="9" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>1207</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="1:4" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>1202</v>
+        <v>1048</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1202</v>
+        <v>1048</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A58" s="9" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>1207</v>
+      <c r="A58" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>1049</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -8357,16 +8360,7 @@
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A60" s="2" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-    </row>
+    <row r="60" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="61" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="62" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="63" spans="1:4" ht="14.25" customHeight="1"/>
@@ -9323,7 +9317,6 @@
     <row r="1014" ht="14.25" customHeight="1"/>
     <row r="1015" ht="14.25" customHeight="1"/>
     <row r="1016" ht="14.25" customHeight="1"/>
-    <row r="1017" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9333,7 +9326,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C616"/>
+  <dimension ref="A1:C617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -9365,23 +9358,20 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>611</v>
-      </c>
-      <c r="B7" t="s">
-        <v>646</v>
-      </c>
-      <c r="C7" t="s">
-        <v>585</v>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1393</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="B8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C8" t="s">
         <v>585</v>
@@ -9389,10 +9379,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B9" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C9" t="s">
         <v>585</v>
@@ -9400,10 +9390,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C10" t="s">
         <v>585</v>
@@ -9411,10 +9401,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="B11" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C11" t="s">
         <v>585</v>
@@ -9422,10 +9412,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>675</v>
+        <v>651</v>
       </c>
       <c r="B12" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="C12" t="s">
         <v>585</v>
@@ -9433,83 +9423,83 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>675</v>
+      </c>
+      <c r="B13" t="s">
+        <v>676</v>
+      </c>
+      <c r="C13" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>644</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>1140</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>174</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" t="s">
-        <v>69</v>
+        <v>174</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="B18" t="s">
-        <v>1100</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C19" t="s">
-        <v>578</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>489</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s">
-        <v>490</v>
+        <v>198</v>
+      </c>
+      <c r="C20" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>581</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1127</v>
+        <v>489</v>
+      </c>
+      <c r="B21" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>1141</v>
+        <v>1126</v>
       </c>
       <c r="C22" t="s">
         <v>1127</v>
@@ -9517,32 +9507,32 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>601</v>
-      </c>
-      <c r="B23" t="s">
-        <v>602</v>
+        <v>589</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>1141</v>
       </c>
       <c r="C23" t="s">
-        <v>585</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>614</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>1142</v>
+        <v>601</v>
+      </c>
+      <c r="B24" t="s">
+        <v>602</v>
       </c>
       <c r="C24" t="s">
-        <v>1127</v>
+        <v>585</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C25" t="s">
         <v>1127</v>
@@ -9550,10 +9540,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>683</v>
+        <v>616</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="C26" t="s">
         <v>1127</v>
@@ -9561,10 +9551,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>814</v>
+        <v>683</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1144</v>
+        <v>1128</v>
       </c>
       <c r="C27" t="s">
         <v>1127</v>
@@ -9572,133 +9562,133 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>814</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>471</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>1145</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>175</v>
-      </c>
-      <c r="B30" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>497</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>498</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>497</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>1094</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>672</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>673</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>555</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>556</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="B42" t="s">
-        <v>680</v>
+        <v>556</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>603</v>
+        <v>576</v>
       </c>
       <c r="B43" t="s">
-        <v>604</v>
-      </c>
-      <c r="C43" t="s">
-        <v>585</v>
+        <v>680</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>677</v>
+        <v>603</v>
       </c>
       <c r="B44" t="s">
-        <v>678</v>
+        <v>604</v>
       </c>
       <c r="C44" t="s">
         <v>585</v>
@@ -9706,158 +9696,158 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>677</v>
+      </c>
+      <c r="B45" t="s">
+        <v>678</v>
+      </c>
+      <c r="C45" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>486</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>1146</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>177</v>
-      </c>
-      <c r="B47" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>1099</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" t="s">
-        <v>522</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="C55" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>557</v>
+        <v>101</v>
       </c>
       <c r="B56" t="s">
-        <v>558</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>667</v>
+        <v>557</v>
       </c>
       <c r="B57" t="s">
-        <v>668</v>
+        <v>558</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>982</v>
+        <v>667</v>
       </c>
       <c r="B58" t="s">
-        <v>983</v>
+        <v>668</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>586</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1127</v>
+        <v>982</v>
+      </c>
+      <c r="B59" t="s">
+        <v>983</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>485</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>1148</v>
+        <v>586</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>1147</v>
       </c>
       <c r="C60" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>178</v>
-      </c>
-      <c r="B62" t="s">
-        <v>525</v>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>485</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
-      </c>
-      <c r="C63" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
         <v>522</v>
@@ -9865,10 +9855,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C65" t="s">
         <v>522</v>
@@ -9876,10 +9866,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C66" t="s">
         <v>522</v>
@@ -9887,10 +9877,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
         <v>522</v>
@@ -9898,10 +9888,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C68" t="s">
         <v>522</v>
@@ -9909,158 +9899,158 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B69" t="s">
-        <v>1095</v>
+        <v>106</v>
+      </c>
+      <c r="C69" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>494</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>195</v>
+        <v>494</v>
       </c>
       <c r="B71" t="s">
-        <v>669</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B72" t="s">
-        <v>670</v>
-      </c>
-      <c r="C72" t="s">
-        <v>522</v>
+        <v>669</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>513</v>
+        <v>196</v>
       </c>
       <c r="B73" t="s">
-        <v>671</v>
+        <v>670</v>
+      </c>
+      <c r="C73" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="B74" t="s">
-        <v>488</v>
+        <v>671</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>630</v>
+        <v>487</v>
       </c>
       <c r="B75" t="s">
-        <v>629</v>
-      </c>
-      <c r="C75" t="s">
-        <v>585</v>
+        <v>488</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>630</v>
+      </c>
+      <c r="B76" t="s">
+        <v>629</v>
+      </c>
+      <c r="C76" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
         <v>1086</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B77" t="s">
         <v>1087</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B79" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
         <v>484</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>1149</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>152</v>
-      </c>
-      <c r="B81" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B82" t="s">
-        <v>526</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B83" t="s">
-        <v>117</v>
+        <v>526</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>559</v>
+        <v>118</v>
       </c>
       <c r="B84" t="s">
-        <v>560</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>640</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1127</v>
+        <v>559</v>
+      </c>
+      <c r="B85" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>658</v>
-      </c>
-      <c r="B86" t="s">
-        <v>659</v>
+        <v>640</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="C86" t="s">
-        <v>585</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B87" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C87" t="s">
         <v>585</v>
@@ -10068,10 +10058,10 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B88" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C88" t="s">
         <v>585</v>
@@ -10079,37 +10069,37 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
+        <v>656</v>
+      </c>
+      <c r="B89" t="s">
+        <v>661</v>
+      </c>
+      <c r="C89" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
         <v>483</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>1150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" t="s">
-        <v>180</v>
-      </c>
-      <c r="B91" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>639</v>
+        <v>180</v>
       </c>
       <c r="B92" t="s">
-        <v>652</v>
-      </c>
-      <c r="C92" t="s">
-        <v>585</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B93" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="C93" t="s">
         <v>585</v>
@@ -10117,80 +10107,80 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>119</v>
+        <v>637</v>
       </c>
       <c r="B94" t="s">
-        <v>121</v>
+        <v>638</v>
+      </c>
+      <c r="C94" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B95" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B96" t="s">
-        <v>527</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B98" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B99" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>441</v>
-      </c>
-      <c r="C100" t="s">
-        <v>580</v>
+        <v>530</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B101" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C101" t="s">
-        <v>495</v>
+        <v>580</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B102" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C102" t="s">
         <v>495</v>
@@ -10198,48 +10188,48 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>561</v>
+        <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>562</v>
+        <v>444</v>
+      </c>
+      <c r="C103" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>605</v>
+        <v>561</v>
       </c>
       <c r="B104" t="s">
-        <v>606</v>
-      </c>
-      <c r="C104" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>840</v>
+        <v>605</v>
       </c>
       <c r="B105" t="s">
-        <v>841</v>
+        <v>606</v>
+      </c>
+      <c r="C105" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>631</v>
+        <v>840</v>
       </c>
       <c r="B106" t="s">
-        <v>632</v>
-      </c>
-      <c r="C106" t="s">
-        <v>585</v>
+        <v>841</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B107" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C107" t="s">
         <v>585</v>
@@ -10247,10 +10237,10 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B108" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C108" t="s">
         <v>585</v>
@@ -10258,75 +10248,75 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>837</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>1130</v>
+        <v>636</v>
+      </c>
+      <c r="B109" t="s">
+        <v>635</v>
       </c>
       <c r="C109" t="s">
-        <v>1127</v>
+        <v>585</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>838</v>
-      </c>
-      <c r="B110" t="s">
-        <v>839</v>
+        <v>837</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B111" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B112" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
+        <v>845</v>
+      </c>
+      <c r="B113" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
         <v>482</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B114" s="2" t="s">
         <v>1151</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C115" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>141</v>
+        <v>1123</v>
       </c>
       <c r="B116" t="s">
-        <v>144</v>
+        <v>1124</v>
       </c>
       <c r="C116" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B117" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C117" t="s">
         <v>578</v>
@@ -10334,10 +10324,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C118" t="s">
         <v>578</v>
@@ -10345,32 +10335,32 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B119" t="s">
-        <v>514</v>
+        <v>146</v>
       </c>
       <c r="C119" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>583</v>
+        <v>139</v>
       </c>
       <c r="B120" t="s">
         <v>514</v>
       </c>
       <c r="C120" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>140</v>
+        <v>583</v>
       </c>
       <c r="B121" t="s">
-        <v>123</v>
+        <v>514</v>
       </c>
       <c r="C121" t="s">
         <v>578</v>
@@ -10378,10 +10368,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B122" t="s">
-        <v>531</v>
+        <v>123</v>
       </c>
       <c r="C122" t="s">
         <v>578</v>
@@ -10389,10 +10379,10 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B123" t="s">
-        <v>124</v>
+        <v>531</v>
       </c>
       <c r="C123" t="s">
         <v>578</v>
@@ -10400,10 +10390,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>563</v>
+        <v>126</v>
       </c>
       <c r="B124" t="s">
-        <v>564</v>
+        <v>124</v>
       </c>
       <c r="C124" t="s">
         <v>578</v>
@@ -10411,277 +10401,277 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
+        <v>563</v>
+      </c>
+      <c r="B125" t="s">
+        <v>564</v>
+      </c>
+      <c r="C125" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
         <v>481</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B126" s="2" t="s">
         <v>1152</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" t="s">
-        <v>181</v>
-      </c>
-      <c r="B127" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="B128" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>682</v>
+        <v>128</v>
       </c>
       <c r="B131" t="s">
-        <v>681</v>
-      </c>
-      <c r="C131" t="s">
-        <v>585</v>
+        <v>149</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>130</v>
+        <v>682</v>
       </c>
       <c r="B132" t="s">
-        <v>150</v>
+        <v>681</v>
+      </c>
+      <c r="C132" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B133" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>554</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C134" t="s">
-        <v>1127</v>
+        <v>131</v>
+      </c>
+      <c r="B134" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>565</v>
-      </c>
-      <c r="B135" t="s">
-        <v>566</v>
+        <v>554</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>607</v>
+        <v>565</v>
       </c>
       <c r="B136" t="s">
-        <v>608</v>
-      </c>
-      <c r="C136" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
+        <v>607</v>
+      </c>
+      <c r="B137" t="s">
+        <v>608</v>
+      </c>
+      <c r="C137" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
         <v>480</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B138" s="2" t="s">
         <v>1154</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" t="s">
-        <v>597</v>
-      </c>
-      <c r="B139" t="s">
-        <v>598</v>
-      </c>
-      <c r="C139" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B140" t="s">
-        <v>1155</v>
+        <v>598</v>
       </c>
       <c r="C140" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
-      <c r="A142" t="s">
-        <v>153</v>
-      </c>
-      <c r="B142" t="s">
-        <v>157</v>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>600</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C141" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B144" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B145" t="s">
-        <v>532</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>496</v>
+        <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>620</v>
-      </c>
-      <c r="C146" t="s">
-        <v>621</v>
+        <v>532</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>1054</v>
+        <v>496</v>
       </c>
       <c r="B147" t="s">
-        <v>1060</v>
+        <v>620</v>
       </c>
       <c r="C147" t="s">
-        <v>585</v>
+        <v>621</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>571</v>
+        <v>1054</v>
       </c>
       <c r="B148" t="s">
-        <v>572</v>
+        <v>1060</v>
+      </c>
+      <c r="C148" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
+        <v>571</v>
+      </c>
+      <c r="B149" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
         <v>479</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B150" t="s">
         <v>1156</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" t="s">
-        <v>185</v>
-      </c>
-      <c r="B151" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B152" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>567</v>
+        <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>568</v>
+        <v>163</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>478</v>
+        <v>567</v>
       </c>
       <c r="B155" t="s">
-        <v>1157</v>
+        <v>568</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
+        <v>478</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
         <v>609</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B157" t="s">
         <v>610</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C157" t="s">
         <v>585</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" t="s">
-        <v>183</v>
-      </c>
-      <c r="B158" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B159" t="s">
-        <v>166</v>
-      </c>
-      <c r="C159" t="s">
-        <v>522</v>
+        <v>184</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C160" t="s">
         <v>522</v>
@@ -10689,10 +10679,10 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B161" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C161" t="s">
         <v>522</v>
@@ -10700,312 +10690,312 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="B162" t="s">
-        <v>193</v>
+        <v>168</v>
+      </c>
+      <c r="C162" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B163" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B164" t="s">
-        <v>171</v>
-      </c>
-      <c r="C164" t="s">
-        <v>522</v>
+        <v>192</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
+        <v>170</v>
+      </c>
+      <c r="B165" t="s">
+        <v>171</v>
+      </c>
+      <c r="C165" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
         <v>569</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B166" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="166" spans="1:3" s="6" customFormat="1">
-      <c r="A166" s="6" t="s">
+    <row r="167" spans="1:3" s="6" customFormat="1">
+      <c r="A167" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="B166" s="6" t="s">
+      <c r="B167" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="C166" s="6" t="s">
+      <c r="C167" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
-      <c r="A168" t="s">
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
         <v>1082</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B169" t="s">
         <v>756</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C169" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="169" spans="1:3" s="6" customFormat="1">
-      <c r="A169" s="6" t="s">
+    <row r="170" spans="1:3" s="6" customFormat="1">
+      <c r="A170" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="B169" s="6" t="s">
+      <c r="B170" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="C169" s="6" t="s">
+      <c r="C170" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
-      <c r="A170" t="s">
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
         <v>612</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B171" t="s">
         <v>613</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C171" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="171" spans="1:3" s="6" customFormat="1">
-      <c r="A171" s="6" t="s">
+    <row r="172" spans="1:3" s="6" customFormat="1">
+      <c r="A172" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="B171" s="6" t="s">
+      <c r="B172" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="C171" s="6" t="s">
+      <c r="C172" s="6" t="s">
         <v>1131</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" t="s">
-        <v>691</v>
-      </c>
-      <c r="B172" t="s">
-        <v>819</v>
-      </c>
-      <c r="C172" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>692</v>
-      </c>
-      <c r="B173" s="7" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>1127</v>
+        <v>691</v>
+      </c>
+      <c r="B173" t="s">
+        <v>819</v>
+      </c>
+      <c r="C173" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
+        <v>692</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" t="s">
         <v>1044</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B175" t="s">
         <v>824</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C175" t="s">
         <v>1045</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176" t="s">
-        <v>458</v>
-      </c>
-      <c r="B176" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>1067</v>
+        <v>458</v>
       </c>
       <c r="B177" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C177" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>232</v>
+        <v>1067</v>
       </c>
       <c r="B178" t="s">
-        <v>820</v>
+        <v>1068</v>
       </c>
       <c r="C178" t="s">
-        <v>522</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B179" t="s">
-        <v>821</v>
+        <v>820</v>
+      </c>
+      <c r="C179" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B180" t="s">
-        <v>822</v>
-      </c>
-      <c r="C180" t="s">
-        <v>574</v>
+        <v>821</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>666</v>
+        <v>241</v>
       </c>
       <c r="B181" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C181" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>235</v>
+        <v>666</v>
       </c>
       <c r="B182" t="s">
-        <v>234</v>
+        <v>823</v>
+      </c>
+      <c r="C182" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>448</v>
+        <v>235</v>
       </c>
       <c r="B183" t="s">
-        <v>457</v>
+        <v>234</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>236</v>
+        <v>448</v>
       </c>
       <c r="B184" t="s">
-        <v>824</v>
-      </c>
-      <c r="C184" t="s">
-        <v>1046</v>
+        <v>457</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B185" t="s">
-        <v>825</v>
+        <v>824</v>
+      </c>
+      <c r="C185" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B186" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B187" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B188" t="s">
-        <v>756</v>
+        <v>827</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="B189" t="s">
-        <v>824</v>
-      </c>
-      <c r="C189" t="s">
-        <v>1046</v>
+        <v>756</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="B190" t="s">
-        <v>298</v>
+        <v>824</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>577</v>
+        <v>297</v>
       </c>
       <c r="B191" t="s">
-        <v>1042</v>
+        <v>298</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
+        <v>577</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" t="s">
         <v>590</v>
       </c>
-      <c r="B192" s="7" t="s">
+      <c r="B193" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C192" s="2" t="s">
+      <c r="C193" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="193" spans="1:3" s="6" customFormat="1">
-      <c r="A193" s="6" t="s">
+    <row r="194" spans="1:3" s="6" customFormat="1">
+      <c r="A194" s="6" t="s">
         <v>653</v>
       </c>
-      <c r="B193" s="6" t="s">
+      <c r="B194" s="6" t="s">
         <v>654</v>
       </c>
-      <c r="C193" s="6" t="s">
+      <c r="C194" s="6" t="s">
         <v>1131</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" t="s">
-        <v>665</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>836</v>
+        <v>665</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>1133</v>
+        <v>1159</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>1127</v>
@@ -11013,216 +11003,216 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B196" t="s">
-        <v>1107</v>
+        <v>836</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" t="s">
         <v>466</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B198" s="7" t="s">
         <v>1160</v>
       </c>
-      <c r="C197" s="2" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" t="s">
-        <v>664</v>
-      </c>
-      <c r="B199" s="7" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C199" s="2" t="s">
+      <c r="C198" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>459</v>
-      </c>
-      <c r="B200" t="s">
-        <v>1062</v>
+        <v>664</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
+        <v>459</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" t="s">
         <v>242</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B202" t="s">
         <v>828</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C202" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="13.5" customHeight="1">
-      <c r="A202" t="s">
+    <row r="203" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A203" t="s">
         <v>244</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B203" t="s">
         <v>829</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C203" t="s">
         <v>587</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" t="s">
-        <v>243</v>
-      </c>
-      <c r="B203" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>245</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>1127</v>
+        <v>243</v>
+      </c>
+      <c r="B204" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>246</v>
-      </c>
-      <c r="B205" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B206" t="s">
-        <v>248</v>
-      </c>
-      <c r="C206" t="s">
-        <v>579</v>
+        <v>247</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>449</v>
+        <v>249</v>
       </c>
       <c r="B207" t="s">
-        <v>504</v>
+        <v>248</v>
+      </c>
+      <c r="C207" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>250</v>
+        <v>449</v>
       </c>
       <c r="B208" t="s">
-        <v>793</v>
+        <v>504</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B209" t="s">
-        <v>252</v>
+        <v>793</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B210" t="s">
-        <v>794</v>
+        <v>252</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B211" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B212" t="s">
-        <v>830</v>
-      </c>
-      <c r="C212" t="s">
-        <v>579</v>
+        <v>795</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B213" t="s">
-        <v>796</v>
+        <v>830</v>
+      </c>
+      <c r="C213" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B214" t="s">
-        <v>831</v>
-      </c>
-      <c r="C214" t="s">
-        <v>579</v>
+        <v>796</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B215" t="s">
-        <v>797</v>
+        <v>831</v>
+      </c>
+      <c r="C215" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B216" t="s">
-        <v>269</v>
+        <v>797</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B217" t="s">
-        <v>824</v>
-      </c>
-      <c r="C217" t="s">
-        <v>1046</v>
+        <v>269</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>272</v>
-      </c>
-      <c r="B218" s="7" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>1127</v>
+        <v>270</v>
+      </c>
+      <c r="B218" t="s">
+        <v>824</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>591</v>
+        <v>272</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>1132</v>
+        <v>1163</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>1127</v>
@@ -11230,10 +11220,10 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>1164</v>
+        <v>1132</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>1127</v>
@@ -11241,625 +11231,625 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>477</v>
+        <v>588</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="223" spans="1:3">
-      <c r="A223" t="s">
-        <v>460</v>
-      </c>
-      <c r="B223" t="s">
-        <v>1063</v>
+    <row r="222" spans="1:3">
+      <c r="A222" t="s">
+        <v>477</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B224" t="s">
-        <v>505</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>266</v>
+        <v>450</v>
       </c>
       <c r="B225" t="s">
-        <v>757</v>
+        <v>505</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B226" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B227" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B228" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B229" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>592</v>
-      </c>
-      <c r="B230" s="7" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>1127</v>
+        <v>275</v>
+      </c>
+      <c r="B230" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>476</v>
+        <v>592</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
-      <c r="A233" t="s">
-        <v>461</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1064</v>
+    <row r="232" spans="1:3">
+      <c r="A232" t="s">
+        <v>476</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B234" t="s">
-        <v>506</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>278</v>
+        <v>451</v>
       </c>
       <c r="B235" t="s">
-        <v>751</v>
+        <v>506</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B236" t="s">
-        <v>281</v>
+        <v>751</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B237" t="s">
-        <v>752</v>
+        <v>281</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B238" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B239" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B240" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B241" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>593</v>
-      </c>
-      <c r="B242" s="7" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>1127</v>
+        <v>285</v>
+      </c>
+      <c r="B242" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B243" t="s">
-        <v>1119</v>
+        <v>593</v>
+      </c>
+      <c r="B243" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" t="s">
         <v>475</v>
       </c>
-      <c r="B244" s="7" t="s">
+      <c r="B245" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="C244" s="2" t="s">
+      <c r="C245" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" t="s">
-        <v>462</v>
-      </c>
-      <c r="B246" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="B247" t="s">
-        <v>291</v>
-      </c>
-      <c r="C247" t="s">
-        <v>522</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B248" t="s">
-        <v>507</v>
+        <v>291</v>
+      </c>
+      <c r="C248" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>289</v>
+        <v>452</v>
       </c>
       <c r="B249" t="s">
-        <v>832</v>
-      </c>
-      <c r="C249" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B250" t="s">
-        <v>815</v>
+        <v>832</v>
+      </c>
+      <c r="C250" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>445</v>
+        <v>290</v>
       </c>
       <c r="B251" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>292</v>
+        <v>445</v>
       </c>
       <c r="B252" t="s">
-        <v>824</v>
-      </c>
-      <c r="C252" t="s">
-        <v>1043</v>
+        <v>816</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B253" t="s">
-        <v>833</v>
+        <v>824</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1043</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B254" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B255" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B256" t="s">
-        <v>756</v>
+        <v>835</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>594</v>
-      </c>
-      <c r="B257" s="7" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>1127</v>
+        <v>296</v>
+      </c>
+      <c r="B257" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>474</v>
+        <v>594</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>1168</v>
+        <v>1132</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
-      <c r="A260" t="s">
-        <v>626</v>
-      </c>
-      <c r="B260" t="s">
-        <v>627</v>
-      </c>
-      <c r="C260" t="s">
-        <v>585</v>
+    <row r="259" spans="1:3">
+      <c r="A259" t="s">
+        <v>474</v>
+      </c>
+      <c r="B259" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>491</v>
+        <v>626</v>
       </c>
       <c r="B261" t="s">
-        <v>1192</v>
+        <v>627</v>
       </c>
       <c r="C261" t="s">
-        <v>520</v>
+        <v>585</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B262" t="s">
-        <v>493</v>
+        <v>1192</v>
       </c>
       <c r="C262" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>519</v>
+        <v>492</v>
       </c>
       <c r="B263" t="s">
-        <v>533</v>
+        <v>493</v>
+      </c>
+      <c r="C263" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>312</v>
+        <v>519</v>
       </c>
       <c r="B264" t="s">
-        <v>299</v>
+        <v>533</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B265" t="s">
-        <v>300</v>
-      </c>
-      <c r="C265" t="s">
-        <v>522</v>
+        <v>299</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>453</v>
+        <v>313</v>
       </c>
       <c r="B266" t="s">
-        <v>508</v>
+        <v>300</v>
+      </c>
+      <c r="C266" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>314</v>
+        <v>453</v>
       </c>
       <c r="B267" t="s">
-        <v>301</v>
+        <v>508</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B268" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
+        <v>315</v>
+      </c>
+      <c r="B269" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" t="s">
         <v>316</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B270" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="270" spans="1:3" s="6" customFormat="1">
-      <c r="A270" s="6" t="s">
+    <row r="271" spans="1:3" s="6" customFormat="1">
+      <c r="A271" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="B270" s="6" t="s">
+      <c r="B271" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C270" s="6" t="s">
+      <c r="C271" s="6" t="s">
         <v>522</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3">
-      <c r="A271" t="s">
-        <v>318</v>
-      </c>
-      <c r="B271" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B272" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B273" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
+        <v>320</v>
+      </c>
+      <c r="B274" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" t="s">
         <v>321</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B275" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="275" spans="1:3" s="6" customFormat="1">
-      <c r="A275" s="6" t="s">
+    <row r="276" spans="1:3" s="6" customFormat="1">
+      <c r="A276" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="B275" s="6" t="s">
+      <c r="B276" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="C275" s="6" t="s">
+      <c r="C276" s="6" t="s">
         <v>522</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3">
-      <c r="A276" t="s">
-        <v>323</v>
-      </c>
-      <c r="B276" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B277" t="s">
-        <v>310</v>
+        <v>736</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B278" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
+        <v>325</v>
+      </c>
+      <c r="B279" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" t="s">
         <v>473</v>
       </c>
-      <c r="B279" s="7" t="s">
+      <c r="B280" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="C279" s="2" t="s">
+      <c r="C280" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" t="s">
-        <v>537</v>
-      </c>
-      <c r="B281" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>332</v>
+        <v>537</v>
       </c>
       <c r="B282" t="s">
-        <v>350</v>
+        <v>538</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B283" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B284" t="s">
-        <v>348</v>
-      </c>
-      <c r="C284" t="s">
-        <v>522</v>
+        <v>347</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>454</v>
+        <v>334</v>
       </c>
       <c r="B285" t="s">
-        <v>509</v>
+        <v>348</v>
+      </c>
+      <c r="C285" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>351</v>
+        <v>454</v>
       </c>
       <c r="B286" t="s">
-        <v>349</v>
-      </c>
-      <c r="C286" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="B287" t="s">
-        <v>341</v>
+        <v>349</v>
+      </c>
+      <c r="C287" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="B288" t="s">
-        <v>342</v>
-      </c>
-      <c r="C288" t="s">
-        <v>499</v>
+        <v>341</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B289" t="s">
-        <v>343</v>
+        <v>342</v>
+      </c>
+      <c r="C289" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B290" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B291" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B292" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B293" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>976</v>
+        <v>340</v>
       </c>
       <c r="B294" t="s">
-        <v>977</v>
-      </c>
-      <c r="C294" t="s">
-        <v>973</v>
+        <v>343</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B295" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C295" t="s">
         <v>973</v>
@@ -11867,10 +11857,10 @@
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B296" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C296" t="s">
         <v>973</v>
@@ -11878,51 +11868,51 @@
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>1111</v>
+        <v>980</v>
       </c>
       <c r="B297" t="s">
-        <v>1112</v>
+        <v>981</v>
+      </c>
+      <c r="C297" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" t="s">
         <v>472</v>
       </c>
-      <c r="B298" s="5" t="s">
+      <c r="B299" s="5" t="s">
         <v>1170</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="C299" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="A300" t="s">
-        <v>628</v>
-      </c>
-      <c r="B300" t="s">
-        <v>645</v>
-      </c>
-      <c r="C300" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>972</v>
-      </c>
-      <c r="B301" s="7" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>1127</v>
+        <v>628</v>
+      </c>
+      <c r="B301" t="s">
+        <v>645</v>
+      </c>
+      <c r="C301" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B302" s="7" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>1127</v>
@@ -11930,78 +11920,78 @@
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>975</v>
-      </c>
-      <c r="B303" s="5" t="s">
-        <v>1171</v>
+        <v>974</v>
+      </c>
+      <c r="B303" s="7" t="s">
+        <v>1136</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
-      <c r="A305" t="s">
-        <v>624</v>
-      </c>
-      <c r="B305" t="s">
-        <v>625</v>
-      </c>
-      <c r="C305" t="s">
-        <v>585</v>
+    <row r="304" spans="1:3">
+      <c r="A304" t="s">
+        <v>975</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>463</v>
+        <v>624</v>
       </c>
       <c r="B306" t="s">
-        <v>464</v>
+        <v>625</v>
+      </c>
+      <c r="C306" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>358</v>
+        <v>463</v>
       </c>
       <c r="B307" t="s">
-        <v>369</v>
+        <v>464</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B308" t="s">
-        <v>370</v>
-      </c>
-      <c r="C308" t="s">
-        <v>522</v>
+        <v>369</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>510</v>
+        <v>359</v>
       </c>
       <c r="B309" t="s">
-        <v>511</v>
+        <v>370</v>
+      </c>
+      <c r="C309" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>360</v>
+        <v>510</v>
       </c>
       <c r="B310" t="s">
-        <v>371</v>
-      </c>
-      <c r="C310" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B311" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C311" t="s">
         <v>522</v>
@@ -12009,161 +11999,161 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B312" t="s">
-        <v>523</v>
+        <v>372</v>
+      </c>
+      <c r="C312" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B313" t="s">
-        <v>373</v>
+        <v>523</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B314" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B315" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B316" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B317" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B318" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>679</v>
-      </c>
-      <c r="B319" s="7" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>1127</v>
+        <v>368</v>
+      </c>
+      <c r="B319" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B320" t="s">
-        <v>1058</v>
+        <v>679</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>546</v>
-      </c>
-      <c r="B321" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C321" s="2" t="s">
-        <v>1127</v>
+        <v>1057</v>
+      </c>
+      <c r="B321" t="s">
+        <v>1058</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B322" t="s">
-        <v>1115</v>
+        <v>546</v>
+      </c>
+      <c r="B322" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B323" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" t="s">
         <v>470</v>
       </c>
-      <c r="B323" s="5" t="s">
+      <c r="B324" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C323" s="2" t="s">
+      <c r="C324" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3">
-      <c r="A325" t="s">
-        <v>465</v>
-      </c>
-      <c r="B325" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>385</v>
+        <v>465</v>
       </c>
       <c r="B326" t="s">
-        <v>396</v>
+        <v>464</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B327" t="s">
-        <v>397</v>
-      </c>
-      <c r="C327" t="s">
-        <v>522</v>
+        <v>396</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>455</v>
+        <v>386</v>
       </c>
       <c r="B328" t="s">
-        <v>512</v>
+        <v>397</v>
+      </c>
+      <c r="C328" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>387</v>
+        <v>455</v>
       </c>
       <c r="B329" t="s">
-        <v>398</v>
-      </c>
-      <c r="C329" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B330" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C330" t="s">
         <v>522</v>
@@ -12171,730 +12161,730 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B331" t="s">
-        <v>524</v>
+        <v>399</v>
+      </c>
+      <c r="C331" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B332" t="s">
-        <v>373</v>
+        <v>524</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B333" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B334" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B335" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B336" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B337" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>552</v>
-      </c>
-      <c r="B338" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C338" s="2" t="s">
-        <v>1127</v>
+        <v>395</v>
+      </c>
+      <c r="B338" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B339" t="s">
-        <v>1117</v>
+        <v>552</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" t="s">
         <v>469</v>
       </c>
-      <c r="B340" s="5" t="s">
+      <c r="B341" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C340" s="2" t="s">
+      <c r="C341" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3">
-      <c r="A342" t="s">
-        <v>622</v>
-      </c>
-      <c r="B342" t="s">
-        <v>623</v>
-      </c>
-      <c r="C342" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>379</v>
+        <v>622</v>
       </c>
       <c r="B343" t="s">
-        <v>1195</v>
+        <v>623</v>
+      </c>
+      <c r="C343" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B344" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C344" t="s">
-        <v>522</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>456</v>
+        <v>380</v>
       </c>
       <c r="B345" t="s">
-        <v>1197</v>
+        <v>1196</v>
+      </c>
+      <c r="C345" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>381</v>
+        <v>456</v>
       </c>
       <c r="B346" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B347" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B348" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>1074</v>
+        <v>383</v>
       </c>
       <c r="B349" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C349" t="s">
-        <v>1076</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C350" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351" t="s">
         <v>468</v>
       </c>
-      <c r="B350" s="5" t="s">
+      <c r="B351" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="C350" s="2" t="s">
+      <c r="C351" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3">
-      <c r="A352" t="s">
-        <v>687</v>
-      </c>
-      <c r="B352" t="s">
-        <v>688</v>
-      </c>
-      <c r="C352" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
+        <v>687</v>
+      </c>
+      <c r="B353" t="s">
+        <v>688</v>
+      </c>
+      <c r="C353" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" t="s">
         <v>689</v>
       </c>
-      <c r="B353" s="5" t="s">
+      <c r="B354" s="5" t="s">
         <v>1174</v>
       </c>
-      <c r="C353" s="2" t="s">
+      <c r="C354" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3">
-      <c r="A355" t="s">
-        <v>694</v>
-      </c>
-      <c r="B355" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B356" t="s">
-        <v>1194</v>
+        <v>695</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B357" t="s">
-        <v>698</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B358" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B359" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B360" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B361" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B362" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B363" t="s">
-        <v>1101</v>
+        <v>708</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>710</v>
-      </c>
-      <c r="B364" s="7" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>1127</v>
+        <v>709</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>711</v>
-      </c>
-      <c r="B365" t="s">
-        <v>712</v>
+        <v>710</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B366" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B367" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B368" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B369" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B370" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>1050</v>
+        <v>721</v>
       </c>
       <c r="B371" t="s">
-        <v>1051</v>
+        <v>722</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>723</v>
+        <v>1050</v>
       </c>
       <c r="B372" t="s">
-        <v>724</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>1090</v>
+        <v>723</v>
       </c>
       <c r="B373" t="s">
-        <v>1091</v>
+        <v>724</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375" t="s">
         <v>1073</v>
       </c>
-      <c r="B374" s="5" t="s">
+      <c r="B375" s="5" t="s">
         <v>1176</v>
       </c>
-      <c r="C374" s="2" t="s">
+      <c r="C375" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3">
-      <c r="A376" t="s">
-        <v>725</v>
-      </c>
-      <c r="B376" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B377" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B378" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B379" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B380" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B381" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B382" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B383" t="s">
-        <v>311</v>
+        <v>738</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B384" t="s">
-        <v>741</v>
+        <v>311</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B385" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B386" t="s">
-        <v>1193</v>
+        <v>743</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
+        <v>744</v>
+      </c>
+      <c r="B387" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388" t="s">
         <v>745</v>
       </c>
-      <c r="B387" s="7" t="s">
+      <c r="B388" s="7" t="s">
         <v>1177</v>
       </c>
-      <c r="C387" s="2" t="s">
+      <c r="C388" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3">
-      <c r="A389" t="s">
-        <v>746</v>
-      </c>
-      <c r="B389" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B390" t="s">
-        <v>748</v>
+        <v>305</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B391" t="s">
-        <v>307</v>
+        <v>748</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
+        <v>749</v>
+      </c>
+      <c r="B392" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393" t="s">
         <v>750</v>
       </c>
-      <c r="B392" t="s">
+      <c r="B393" t="s">
         <v>1102</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3">
-      <c r="A394" t="s">
-        <v>771</v>
-      </c>
-      <c r="B394" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B395" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="B396" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B397" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B398" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
+        <v>763</v>
+      </c>
+      <c r="B399" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400" t="s">
         <v>768</v>
       </c>
-      <c r="B399" s="5" t="s">
+      <c r="B400" s="5" t="s">
         <v>1178</v>
       </c>
-      <c r="C399" s="2" t="s">
+      <c r="C400" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3">
-      <c r="A401" t="s">
-        <v>775</v>
-      </c>
-      <c r="B401" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="B402" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="B403" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B404" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B405" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
+        <v>778</v>
+      </c>
+      <c r="B406" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407" t="s">
         <v>779</v>
       </c>
-      <c r="B406" s="5" t="s">
+      <c r="B407" s="5" t="s">
         <v>1179</v>
       </c>
-      <c r="C406" s="2" t="s">
+      <c r="C407" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3">
-      <c r="A408" t="s">
-        <v>787</v>
-      </c>
-      <c r="B408" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B409" t="s">
-        <v>1066</v>
+        <v>788</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>790</v>
-      </c>
-      <c r="B410" s="7" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C410" s="2" t="s">
-        <v>1127</v>
+        <v>789</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>792</v>
-      </c>
-      <c r="B411" t="s">
-        <v>1030</v>
+        <v>790</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>798</v>
-      </c>
-      <c r="B412" s="7" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C412" s="2" t="s">
-        <v>1127</v>
+        <v>792</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1030</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>799</v>
-      </c>
-      <c r="B413" t="s">
-        <v>1017</v>
+        <v>798</v>
+      </c>
+      <c r="B413" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C413" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B414" t="s">
-        <v>1036</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B415" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B416" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B417" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B418" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B419" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B420" t="s">
-        <v>797</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B421" t="s">
-        <v>1037</v>
+        <v>797</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>810</v>
-      </c>
-      <c r="B422" s="7" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C422" s="2" t="s">
-        <v>1127</v>
+        <v>809</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1037</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B423" s="7" t="s">
-        <v>1132</v>
+        <v>1163</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>1127</v>
@@ -12902,10 +12892,10 @@
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1164</v>
+        <v>1132</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>1127</v>
@@ -12913,10 +12903,10 @@
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>801</v>
-      </c>
-      <c r="B425" s="5" t="s">
-        <v>1181</v>
+        <v>802</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>1164</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>1127</v>
@@ -12924,823 +12914,826 @@
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B426" t="s">
-        <v>1107</v>
+        <v>801</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>1020</v>
+        <v>1113</v>
       </c>
       <c r="B427" t="s">
-        <v>1018</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B428" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B429" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B430" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B431" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B432" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>1039</v>
+        <v>1029</v>
       </c>
       <c r="B433" t="s">
-        <v>1038</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B434" s="7" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C434" s="2" t="s">
-        <v>1127</v>
+        <v>1039</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1038</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B435" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C435" s="2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3">
+      <c r="A436" t="s">
         <v>1080</v>
       </c>
-      <c r="B435" t="s">
+      <c r="B436" t="s">
         <v>1081</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3">
-      <c r="A437" t="s">
-        <v>867</v>
-      </c>
-      <c r="B437" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>886</v>
+        <v>867</v>
       </c>
       <c r="B438" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B439" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B440" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B441" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B442" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B443" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B444" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B445" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B446" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B447" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>887</v>
+        <v>877</v>
       </c>
       <c r="B448" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="B449" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B450" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B451" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>873</v>
-      </c>
-      <c r="B452" s="7" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C452" s="2" t="s">
-        <v>1127</v>
+        <v>874</v>
+      </c>
+      <c r="B452" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>872</v>
-      </c>
-      <c r="B453" t="s">
-        <v>863</v>
+        <v>873</v>
+      </c>
+      <c r="B453" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C453" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B454" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B455" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B456" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>1084</v>
+        <v>869</v>
       </c>
       <c r="B457" t="s">
-        <v>1085</v>
+        <v>866</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3">
+      <c r="A459" t="s">
         <v>868</v>
       </c>
-      <c r="B458" s="5" t="s">
+      <c r="B459" s="5" t="s">
         <v>1182</v>
       </c>
-      <c r="C458" s="2" t="s">
+      <c r="C459" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3">
-      <c r="A460" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B460" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>905</v>
+        <v>1077</v>
       </c>
       <c r="B461" t="s">
-        <v>890</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="B462" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B463" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B464" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B465" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B466" t="s">
-        <v>1103</v>
+        <v>894</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B467" t="s">
-        <v>895</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B468" t="s">
-        <v>1104</v>
+        <v>895</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B469" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>1092</v>
+        <v>904</v>
       </c>
       <c r="B470" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3">
+      <c r="A472" t="s">
         <v>903</v>
       </c>
-      <c r="B471" s="5" t="s">
+      <c r="B472" s="5" t="s">
         <v>1183</v>
       </c>
-      <c r="C471" s="2" t="s">
+      <c r="C472" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="473" spans="1:3">
-      <c r="A473" t="s">
+    <row r="474" spans="1:3">
+      <c r="A474" t="s">
         <v>910</v>
       </c>
-      <c r="B473" s="7" t="s">
+      <c r="B474" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="C473" s="2" t="s">
+      <c r="C474" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="474" spans="1:3" s="6" customFormat="1">
-      <c r="A474" s="6" t="s">
+    <row r="475" spans="1:3" s="6" customFormat="1">
+      <c r="A475" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="B474" s="6" t="s">
+      <c r="B475" s="6" t="s">
         <v>1185</v>
       </c>
-      <c r="C474" s="6" t="s">
+      <c r="C475" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="476" spans="1:3" s="6" customFormat="1">
-      <c r="A476" s="6" t="s">
+    <row r="477" spans="1:3" s="6" customFormat="1">
+      <c r="A477" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="B476" s="6" t="s">
+      <c r="B477" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="C476" s="6" t="s">
+      <c r="C477" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="477" spans="1:3">
-      <c r="A477" t="s">
+    <row r="478" spans="1:3">
+      <c r="A478" t="s">
         <v>920</v>
       </c>
-      <c r="B477" s="5" t="s">
+      <c r="B478" s="5" t="s">
         <v>1186</v>
       </c>
-      <c r="C477" s="2" t="s">
+      <c r="C478" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3">
-      <c r="A479" t="s">
-        <v>917</v>
-      </c>
-      <c r="B479" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B480" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>1109</v>
+        <v>918</v>
       </c>
       <c r="B481" t="s">
-        <v>1110</v>
+        <v>916</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3">
+      <c r="A483" t="s">
         <v>914</v>
       </c>
-      <c r="B482" s="7" t="s">
+      <c r="B483" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="C482" s="2" t="s">
+      <c r="C483" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3">
-      <c r="A484" t="s">
-        <v>927</v>
-      </c>
-      <c r="B484" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B485" t="s">
-        <v>922</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B486" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
-        <v>971</v>
+        <v>929</v>
       </c>
       <c r="B487" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>930</v>
+        <v>971</v>
       </c>
       <c r="B488" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B489" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
+        <v>931</v>
+      </c>
+      <c r="B490" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3">
+      <c r="A491" t="s">
         <v>932</v>
       </c>
-      <c r="B490" s="7" t="s">
+      <c r="B491" s="7" t="s">
         <v>1189</v>
       </c>
-      <c r="C490" s="2" t="s">
+      <c r="C491" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3">
-      <c r="A492" t="s">
-        <v>943</v>
-      </c>
-      <c r="B492" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="493" spans="1:3">
       <c r="A493" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B493" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B494" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B495" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B496" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
+        <v>947</v>
+      </c>
+      <c r="B497" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3">
+      <c r="A498" t="s">
         <v>946</v>
       </c>
-      <c r="B497" s="7" t="s">
+      <c r="B498" s="7" t="s">
         <v>1139</v>
       </c>
-      <c r="C497" s="2" t="s">
+      <c r="C498" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3">
-      <c r="A499" t="s">
-        <v>960</v>
-      </c>
-      <c r="B499" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="500" spans="1:3">
       <c r="A500" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="B500" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B501" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B502" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
+        <v>957</v>
+      </c>
+      <c r="B503" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3">
+      <c r="A504" t="s">
         <v>958</v>
       </c>
-      <c r="B503" t="s">
+      <c r="B504" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="504" spans="1:3" s="6" customFormat="1">
-      <c r="A504" s="6" t="s">
+    <row r="505" spans="1:3" s="6" customFormat="1">
+      <c r="A505" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="B504" s="6" t="s">
+      <c r="B505" s="6" t="s">
         <v>1079</v>
       </c>
-      <c r="C504" s="6" t="s">
+      <c r="C505" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="506" spans="1:3" s="6" customFormat="1">
-      <c r="A506" s="6" t="s">
+    <row r="507" spans="1:3" s="6" customFormat="1">
+      <c r="A507" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="B506" s="6" t="s">
+      <c r="B507" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="C506" s="6" t="s">
+      <c r="C507" s="6" t="s">
         <v>1131</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3">
-      <c r="A507" t="s">
-        <v>966</v>
-      </c>
-      <c r="B507" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="508" spans="1:3">
       <c r="A508" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B508" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B509" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
+        <v>968</v>
+      </c>
+      <c r="B510" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3">
+      <c r="A511" t="s">
         <v>969</v>
       </c>
-      <c r="B510" s="7" t="s">
+      <c r="B511" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="C510" s="2" t="s">
+      <c r="C511" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3">
-      <c r="A512" t="s">
-        <v>990</v>
-      </c>
-      <c r="B512" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513" t="s">
-        <v>1005</v>
+        <v>990</v>
       </c>
       <c r="B513" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B514" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B515" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
       <c r="B516" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="B517" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B518" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B519" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B520" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B521" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B522" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B523" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B524" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3">
+      <c r="A526" t="s">
         <v>1004</v>
       </c>
-      <c r="B525" s="7" t="s">
+      <c r="B526" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C525" s="2" t="s">
+      <c r="C526" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3">
-      <c r="A527" t="s">
-        <v>1301</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="528" spans="1:3">
       <c r="A528" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B528" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B529" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="B530" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B531" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>1317</v>
+        <v>1304</v>
       </c>
       <c r="B532" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
-        <v>1307</v>
+        <v>1316</v>
       </c>
       <c r="B533" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -13748,39 +13741,39 @@
         <v>1306</v>
       </c>
       <c r="B534" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>1316</v>
+        <v>1305</v>
       </c>
       <c r="B535" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>1308</v>
+        <v>1315</v>
       </c>
       <c r="B536" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B537" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>1319</v>
+        <v>1308</v>
       </c>
       <c r="B538" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -13788,223 +13781,223 @@
         <v>1318</v>
       </c>
       <c r="B539" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="B540" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
       <c r="B541" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
       <c r="B542" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>1311</v>
+        <v>1320</v>
       </c>
       <c r="B543" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>1322</v>
+        <v>1310</v>
       </c>
       <c r="B544" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>1312</v>
+        <v>1321</v>
       </c>
       <c r="B545" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>1323</v>
+        <v>1311</v>
       </c>
       <c r="B546" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="B547" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>1324</v>
+        <v>1312</v>
       </c>
       <c r="B548" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
       <c r="B549" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>1325</v>
+        <v>1313</v>
       </c>
       <c r="B550" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="B551" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>1315</v>
+        <v>1326</v>
       </c>
       <c r="B552" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>1326</v>
+        <v>1314</v>
       </c>
       <c r="B553" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="B554" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B555" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="B556" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B557" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B558" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B559" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="B560" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B561" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="B562" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B563" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="B564" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B565" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
       <c r="B566" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -14012,7 +14005,7 @@
         <v>1332</v>
       </c>
       <c r="B567" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -14020,7 +14013,7 @@
         <v>1331</v>
       </c>
       <c r="B568" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -14028,103 +14021,103 @@
         <v>1330</v>
       </c>
       <c r="B569" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>1344</v>
+        <v>1329</v>
       </c>
       <c r="B570" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B571" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B572" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>1358</v>
+        <v>1345</v>
       </c>
       <c r="B573" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B574" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B575" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B576" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B577" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B578" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B579" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B580" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B581" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -14132,284 +14125,292 @@
         <v>1366</v>
       </c>
       <c r="B582" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="B583" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B584" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B585" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B586" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="B587" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B588" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B589" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B590" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>1347</v>
+        <v>1374</v>
       </c>
       <c r="B591" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>1355</v>
+        <v>1346</v>
       </c>
       <c r="B592" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="B593" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1356</v>
+        <v>1347</v>
       </c>
       <c r="B594" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="B595" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1376</v>
+        <v>1348</v>
       </c>
       <c r="B596" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="B597" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1379</v>
+        <v>1349</v>
       </c>
       <c r="B598" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>1351</v>
+        <v>1378</v>
       </c>
       <c r="B599" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1357</v>
+        <v>1350</v>
       </c>
       <c r="B600" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="B601" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1380</v>
+        <v>1351</v>
       </c>
       <c r="B602" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1353</v>
+        <v>1379</v>
       </c>
       <c r="B603" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>1381</v>
+        <v>1352</v>
       </c>
       <c r="B604" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B605" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>1354</v>
+        <v>1381</v>
       </c>
       <c r="B606" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>1383</v>
+        <v>1353</v>
       </c>
       <c r="B607" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="B608" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="B609" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
       <c r="B610" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B611" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="B612" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B613" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="B614" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B615" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="B616" t="s">
-        <v>1300</v>
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1299</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C525" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
-  <conditionalFormatting sqref="A479:A481 A476:A477 A461:A471 A473:A474">
+  <autoFilter ref="A1:C526" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
+  <conditionalFormatting sqref="A480:A482 A477:A478 A462:A472 A474:A475">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1021\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB46C1E-A073-4D2A-9011-0C1AEFFD02E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D836AE-B0E7-4772-9C4C-5686F5C81D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Findings" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$526</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$527</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="1394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1397">
   <si>
     <t>Name</t>
   </si>
@@ -3669,9 +3669,6 @@
     <t>UnsupportedIncomeTypesFilePath</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>TX_VSAVerificationProperties</t>
   </si>
   <si>
@@ -4225,6 +4222,18 @@
   </si>
   <si>
     <t>Third party verification of assets is missing from the application and this property requires asset verification. Manual review required.</t>
+  </si>
+  <si>
+    <t>ICW_IncomeNearLimit</t>
+  </si>
+  <si>
+    <t>Annual Income is within $2000 of the Income Limit listed on the Income Calculation Worksheet. Manual review needed.</t>
+  </si>
+  <si>
+    <t>Updated by Harman</t>
+  </si>
+  <si>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4722,7 +4731,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1208</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -5162,10 +5171,10 @@
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1">
       <c r="A61" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B61" t="s">
         <v>1390</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1"/>
@@ -8352,10 +8361,10 @@
     </row>
     <row r="59" spans="1:4" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -9326,7 +9335,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C617"/>
+  <dimension ref="A1:C618"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -9360,10 +9369,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B6" t="s">
         <v>1392</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9579,127 +9588,127 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>175</v>
-      </c>
-      <c r="B31" t="s">
-        <v>176</v>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1395</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>497</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>498</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>497</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>1094</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>672</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>673</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>555</v>
+        <v>85</v>
       </c>
       <c r="B42" t="s">
-        <v>556</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="B43" t="s">
-        <v>680</v>
+        <v>556</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>603</v>
+        <v>576</v>
       </c>
       <c r="B44" t="s">
-        <v>604</v>
-      </c>
-      <c r="C44" t="s">
-        <v>585</v>
+        <v>680</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>677</v>
+        <v>603</v>
       </c>
       <c r="B45" t="s">
-        <v>678</v>
+        <v>604</v>
       </c>
       <c r="C45" t="s">
         <v>585</v>
@@ -9707,158 +9716,158 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>677</v>
+      </c>
+      <c r="B46" t="s">
+        <v>678</v>
+      </c>
+      <c r="C46" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>486</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>1146</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>177</v>
-      </c>
-      <c r="B48" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="B49" t="s">
-        <v>1099</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" t="s">
-        <v>522</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="C56" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>557</v>
+        <v>101</v>
       </c>
       <c r="B57" t="s">
-        <v>558</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>667</v>
+        <v>557</v>
       </c>
       <c r="B58" t="s">
-        <v>668</v>
+        <v>558</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>982</v>
+        <v>667</v>
       </c>
       <c r="B59" t="s">
-        <v>983</v>
+        <v>668</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>586</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1127</v>
+        <v>982</v>
+      </c>
+      <c r="B60" t="s">
+        <v>983</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>485</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>1148</v>
+        <v>586</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>1147</v>
       </c>
       <c r="C61" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>178</v>
-      </c>
-      <c r="B63" t="s">
-        <v>525</v>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>485</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
-      </c>
-      <c r="C64" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C65" t="s">
         <v>522</v>
@@ -9866,10 +9875,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C66" t="s">
         <v>522</v>
@@ -9877,10 +9886,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C67" t="s">
         <v>522</v>
@@ -9888,10 +9897,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
         <v>522</v>
@@ -9899,10 +9908,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C69" t="s">
         <v>522</v>
@@ -9910,158 +9919,158 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B70" t="s">
-        <v>1095</v>
+        <v>106</v>
+      </c>
+      <c r="C70" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>494</v>
+        <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>195</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s">
-        <v>669</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B73" t="s">
-        <v>670</v>
-      </c>
-      <c r="C73" t="s">
-        <v>522</v>
+        <v>669</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>513</v>
+        <v>196</v>
       </c>
       <c r="B74" t="s">
-        <v>671</v>
+        <v>670</v>
+      </c>
+      <c r="C74" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="B75" t="s">
-        <v>488</v>
+        <v>671</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>630</v>
+        <v>487</v>
       </c>
       <c r="B76" t="s">
-        <v>629</v>
-      </c>
-      <c r="C76" t="s">
-        <v>585</v>
+        <v>488</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
+        <v>630</v>
+      </c>
+      <c r="B77" t="s">
+        <v>629</v>
+      </c>
+      <c r="C77" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
         <v>1086</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B78" t="s">
         <v>1087</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" t="s">
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
         <v>484</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B81" s="2" t="s">
         <v>1149</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" t="s">
-        <v>152</v>
-      </c>
-      <c r="B82" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B83" t="s">
-        <v>526</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B84" t="s">
-        <v>117</v>
+        <v>526</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>559</v>
+        <v>118</v>
       </c>
       <c r="B85" t="s">
-        <v>560</v>
+        <v>117</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>640</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1127</v>
+        <v>559</v>
+      </c>
+      <c r="B86" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>658</v>
-      </c>
-      <c r="B87" t="s">
-        <v>659</v>
+        <v>640</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="C87" t="s">
-        <v>585</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B88" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C88" t="s">
         <v>585</v>
@@ -10069,10 +10078,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B89" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C89" t="s">
         <v>585</v>
@@ -10080,37 +10089,37 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
+        <v>656</v>
+      </c>
+      <c r="B90" t="s">
+        <v>661</v>
+      </c>
+      <c r="C90" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
         <v>483</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>1150</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" t="s">
-        <v>180</v>
-      </c>
-      <c r="B92" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>639</v>
+        <v>180</v>
       </c>
       <c r="B93" t="s">
-        <v>652</v>
-      </c>
-      <c r="C93" t="s">
-        <v>585</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B94" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="C94" t="s">
         <v>585</v>
@@ -10118,80 +10127,80 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>119</v>
+        <v>637</v>
       </c>
       <c r="B95" t="s">
-        <v>121</v>
+        <v>638</v>
+      </c>
+      <c r="C95" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B96" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B97" t="s">
-        <v>527</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B98" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B99" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B100" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B101" t="s">
-        <v>441</v>
-      </c>
-      <c r="C101" t="s">
-        <v>580</v>
+        <v>530</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B102" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C102" t="s">
-        <v>495</v>
+        <v>580</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B103" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C103" t="s">
         <v>495</v>
@@ -10199,48 +10208,48 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>561</v>
+        <v>138</v>
       </c>
       <c r="B104" t="s">
-        <v>562</v>
+        <v>444</v>
+      </c>
+      <c r="C104" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>605</v>
+        <v>561</v>
       </c>
       <c r="B105" t="s">
-        <v>606</v>
-      </c>
-      <c r="C105" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>840</v>
+        <v>605</v>
       </c>
       <c r="B106" t="s">
-        <v>841</v>
+        <v>606</v>
+      </c>
+      <c r="C106" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>631</v>
+        <v>840</v>
       </c>
       <c r="B107" t="s">
-        <v>632</v>
-      </c>
-      <c r="C107" t="s">
-        <v>585</v>
+        <v>841</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B108" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C108" t="s">
         <v>585</v>
@@ -10248,10 +10257,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B109" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C109" t="s">
         <v>585</v>
@@ -10259,75 +10268,75 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>837</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>1130</v>
+        <v>636</v>
+      </c>
+      <c r="B110" t="s">
+        <v>635</v>
       </c>
       <c r="C110" t="s">
-        <v>1127</v>
+        <v>585</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>838</v>
-      </c>
-      <c r="B111" t="s">
-        <v>839</v>
+        <v>837</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B112" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B113" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
+        <v>845</v>
+      </c>
+      <c r="B114" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
         <v>482</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B115" s="2" t="s">
         <v>1151</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C116" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>141</v>
+        <v>1123</v>
       </c>
       <c r="B117" t="s">
-        <v>144</v>
+        <v>1124</v>
       </c>
       <c r="C117" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C118" t="s">
         <v>578</v>
@@ -10335,10 +10344,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C119" t="s">
         <v>578</v>
@@ -10346,32 +10355,32 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B120" t="s">
-        <v>514</v>
+        <v>146</v>
       </c>
       <c r="C120" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>583</v>
+        <v>139</v>
       </c>
       <c r="B121" t="s">
         <v>514</v>
       </c>
       <c r="C121" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>140</v>
+        <v>583</v>
       </c>
       <c r="B122" t="s">
-        <v>123</v>
+        <v>514</v>
       </c>
       <c r="C122" t="s">
         <v>578</v>
@@ -10379,10 +10388,10 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>531</v>
+        <v>123</v>
       </c>
       <c r="C123" t="s">
         <v>578</v>
@@ -10390,10 +10399,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>531</v>
       </c>
       <c r="C124" t="s">
         <v>578</v>
@@ -10401,10 +10410,10 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>563</v>
+        <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>564</v>
+        <v>124</v>
       </c>
       <c r="C125" t="s">
         <v>578</v>
@@ -10412,277 +10421,277 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
+        <v>563</v>
+      </c>
+      <c r="B126" t="s">
+        <v>564</v>
+      </c>
+      <c r="C126" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
         <v>481</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B127" s="2" t="s">
         <v>1152</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" t="s">
-        <v>181</v>
-      </c>
-      <c r="B128" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="B129" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B130" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>682</v>
+        <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>681</v>
-      </c>
-      <c r="C132" t="s">
-        <v>585</v>
+        <v>149</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>130</v>
+        <v>682</v>
       </c>
       <c r="B133" t="s">
-        <v>150</v>
+        <v>681</v>
+      </c>
+      <c r="C133" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>554</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C135" t="s">
-        <v>1127</v>
+        <v>131</v>
+      </c>
+      <c r="B135" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>565</v>
-      </c>
-      <c r="B136" t="s">
-        <v>566</v>
+        <v>554</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>607</v>
+        <v>565</v>
       </c>
       <c r="B137" t="s">
-        <v>608</v>
-      </c>
-      <c r="C137" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
+        <v>607</v>
+      </c>
+      <c r="B138" t="s">
+        <v>608</v>
+      </c>
+      <c r="C138" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
         <v>480</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B139" s="2" t="s">
         <v>1154</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" t="s">
-        <v>597</v>
-      </c>
-      <c r="B140" t="s">
-        <v>598</v>
-      </c>
-      <c r="C140" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B141" t="s">
-        <v>1155</v>
+        <v>598</v>
       </c>
       <c r="C141" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
-      <c r="A143" t="s">
-        <v>153</v>
-      </c>
-      <c r="B143" t="s">
-        <v>157</v>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>600</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C142" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B144" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B145" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B146" t="s">
-        <v>532</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>496</v>
+        <v>156</v>
       </c>
       <c r="B147" t="s">
-        <v>620</v>
-      </c>
-      <c r="C147" t="s">
-        <v>621</v>
+        <v>532</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>1054</v>
+        <v>496</v>
       </c>
       <c r="B148" t="s">
-        <v>1060</v>
+        <v>620</v>
       </c>
       <c r="C148" t="s">
-        <v>585</v>
+        <v>621</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>571</v>
+        <v>1054</v>
       </c>
       <c r="B149" t="s">
-        <v>572</v>
+        <v>1060</v>
+      </c>
+      <c r="C149" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
+        <v>571</v>
+      </c>
+      <c r="B150" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
         <v>479</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B151" t="s">
         <v>1156</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" t="s">
-        <v>185</v>
-      </c>
-      <c r="B152" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B153" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B154" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>567</v>
+        <v>161</v>
       </c>
       <c r="B155" t="s">
-        <v>568</v>
+        <v>163</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>478</v>
+        <v>567</v>
       </c>
       <c r="B156" t="s">
-        <v>1157</v>
+        <v>568</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
+        <v>478</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
         <v>609</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>610</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C158" t="s">
         <v>585</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" t="s">
-        <v>183</v>
-      </c>
-      <c r="B159" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B160" t="s">
-        <v>166</v>
-      </c>
-      <c r="C160" t="s">
-        <v>522</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B161" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C161" t="s">
         <v>522</v>
@@ -10690,10 +10699,10 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B162" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C162" t="s">
         <v>522</v>
@@ -10701,312 +10710,312 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="B163" t="s">
-        <v>193</v>
+        <v>168</v>
+      </c>
+      <c r="C163" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B164" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B165" t="s">
-        <v>171</v>
-      </c>
-      <c r="C165" t="s">
-        <v>522</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
+        <v>170</v>
+      </c>
+      <c r="B166" t="s">
+        <v>171</v>
+      </c>
+      <c r="C166" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
         <v>569</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B167" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="167" spans="1:3" s="6" customFormat="1">
-      <c r="A167" s="6" t="s">
+    <row r="168" spans="1:3" s="6" customFormat="1">
+      <c r="A168" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="B167" s="6" t="s">
+      <c r="B168" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="C167" s="6" t="s">
+      <c r="C168" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
-      <c r="A169" t="s">
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
         <v>1082</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B170" t="s">
         <v>756</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C170" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="170" spans="1:3" s="6" customFormat="1">
-      <c r="A170" s="6" t="s">
+    <row r="171" spans="1:3" s="6" customFormat="1">
+      <c r="A171" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="B170" s="6" t="s">
+      <c r="B171" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="C170" s="6" t="s">
+      <c r="C171" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
-      <c r="A171" t="s">
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
         <v>612</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B172" t="s">
         <v>613</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C172" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="172" spans="1:3" s="6" customFormat="1">
-      <c r="A172" s="6" t="s">
+    <row r="173" spans="1:3" s="6" customFormat="1">
+      <c r="A173" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="B173" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="C172" s="6" t="s">
+      <c r="C173" s="6" t="s">
         <v>1131</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3">
-      <c r="A173" t="s">
-        <v>691</v>
-      </c>
-      <c r="B173" t="s">
-        <v>819</v>
-      </c>
-      <c r="C173" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>692</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>1127</v>
+        <v>691</v>
+      </c>
+      <c r="B174" t="s">
+        <v>819</v>
+      </c>
+      <c r="C174" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
+        <v>692</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" t="s">
         <v>1044</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B176" t="s">
         <v>824</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C176" t="s">
         <v>1045</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" t="s">
-        <v>458</v>
-      </c>
-      <c r="B177" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>1067</v>
+        <v>458</v>
       </c>
       <c r="B178" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C178" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>232</v>
+        <v>1067</v>
       </c>
       <c r="B179" t="s">
-        <v>820</v>
+        <v>1068</v>
       </c>
       <c r="C179" t="s">
-        <v>522</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B180" t="s">
-        <v>821</v>
+        <v>820</v>
+      </c>
+      <c r="C180" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B181" t="s">
-        <v>822</v>
-      </c>
-      <c r="C181" t="s">
-        <v>574</v>
+        <v>821</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>666</v>
+        <v>241</v>
       </c>
       <c r="B182" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C182" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>235</v>
+        <v>666</v>
       </c>
       <c r="B183" t="s">
-        <v>234</v>
+        <v>823</v>
+      </c>
+      <c r="C183" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>448</v>
+        <v>235</v>
       </c>
       <c r="B184" t="s">
-        <v>457</v>
+        <v>234</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>236</v>
+        <v>448</v>
       </c>
       <c r="B185" t="s">
-        <v>824</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1046</v>
+        <v>457</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B186" t="s">
-        <v>825</v>
+        <v>824</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B187" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B188" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B189" t="s">
-        <v>756</v>
+        <v>827</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="B190" t="s">
-        <v>824</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1046</v>
+        <v>756</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="B191" t="s">
-        <v>298</v>
+        <v>824</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>577</v>
+        <v>297</v>
       </c>
       <c r="B192" t="s">
-        <v>1042</v>
+        <v>298</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
+        <v>577</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
         <v>590</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B194" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C193" s="2" t="s">
+      <c r="C194" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="194" spans="1:3" s="6" customFormat="1">
-      <c r="A194" s="6" t="s">
+    <row r="195" spans="1:3" s="6" customFormat="1">
+      <c r="A195" s="6" t="s">
         <v>653</v>
       </c>
-      <c r="B194" s="6" t="s">
+      <c r="B195" s="6" t="s">
         <v>654</v>
       </c>
-      <c r="C194" s="6" t="s">
+      <c r="C195" s="6" t="s">
         <v>1131</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="A195" t="s">
-        <v>665</v>
-      </c>
-      <c r="B195" s="7" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>836</v>
+        <v>665</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>1133</v>
+        <v>1159</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>1127</v>
@@ -11014,216 +11023,216 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B197" t="s">
-        <v>1107</v>
+        <v>836</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" t="s">
         <v>466</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="B199" s="7" t="s">
         <v>1160</v>
       </c>
-      <c r="C198" s="2" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" t="s">
-        <v>664</v>
-      </c>
-      <c r="B200" s="7" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C200" s="2" t="s">
+      <c r="C199" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>459</v>
-      </c>
-      <c r="B201" t="s">
-        <v>1062</v>
+        <v>664</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
+        <v>459</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" t="s">
         <v>242</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B203" t="s">
         <v>828</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C203" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="13.5" customHeight="1">
-      <c r="A203" t="s">
+    <row r="204" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A204" t="s">
         <v>244</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B204" t="s">
         <v>829</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C204" t="s">
         <v>587</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" t="s">
-        <v>243</v>
-      </c>
-      <c r="B204" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>245</v>
-      </c>
-      <c r="B205" s="7" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>1127</v>
+        <v>243</v>
+      </c>
+      <c r="B205" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>246</v>
-      </c>
-      <c r="B206" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B207" t="s">
-        <v>248</v>
-      </c>
-      <c r="C207" t="s">
-        <v>579</v>
+        <v>247</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>449</v>
+        <v>249</v>
       </c>
       <c r="B208" t="s">
-        <v>504</v>
+        <v>248</v>
+      </c>
+      <c r="C208" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>250</v>
+        <v>449</v>
       </c>
       <c r="B209" t="s">
-        <v>793</v>
+        <v>504</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B210" t="s">
-        <v>252</v>
+        <v>793</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B211" t="s">
-        <v>794</v>
+        <v>252</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B212" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B213" t="s">
-        <v>830</v>
-      </c>
-      <c r="C213" t="s">
-        <v>579</v>
+        <v>795</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B214" t="s">
-        <v>796</v>
+        <v>830</v>
+      </c>
+      <c r="C214" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B215" t="s">
-        <v>831</v>
-      </c>
-      <c r="C215" t="s">
-        <v>579</v>
+        <v>796</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B216" t="s">
-        <v>797</v>
+        <v>831</v>
+      </c>
+      <c r="C216" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B217" t="s">
-        <v>269</v>
+        <v>797</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B218" t="s">
-        <v>824</v>
-      </c>
-      <c r="C218" t="s">
-        <v>1046</v>
+        <v>269</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>272</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>1127</v>
+        <v>270</v>
+      </c>
+      <c r="B219" t="s">
+        <v>824</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>591</v>
+        <v>272</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>1132</v>
+        <v>1163</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>1127</v>
@@ -11231,10 +11240,10 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>1164</v>
+        <v>1132</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>1127</v>
@@ -11242,625 +11251,625 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>477</v>
+        <v>588</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
-      <c r="A224" t="s">
-        <v>460</v>
-      </c>
-      <c r="B224" t="s">
-        <v>1063</v>
+    <row r="223" spans="1:3">
+      <c r="A223" t="s">
+        <v>477</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B225" t="s">
-        <v>505</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>266</v>
+        <v>450</v>
       </c>
       <c r="B226" t="s">
-        <v>757</v>
+        <v>505</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B227" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B228" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B229" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B230" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>592</v>
-      </c>
-      <c r="B231" s="7" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>1127</v>
+        <v>275</v>
+      </c>
+      <c r="B231" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>476</v>
+        <v>592</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="234" spans="1:3">
-      <c r="A234" t="s">
-        <v>461</v>
-      </c>
-      <c r="B234" t="s">
-        <v>1064</v>
+    <row r="233" spans="1:3">
+      <c r="A233" t="s">
+        <v>476</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B235" t="s">
-        <v>506</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>278</v>
+        <v>451</v>
       </c>
       <c r="B236" t="s">
-        <v>751</v>
+        <v>506</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B237" t="s">
-        <v>281</v>
+        <v>751</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B238" t="s">
-        <v>752</v>
+        <v>281</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B239" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B240" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B241" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B242" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>593</v>
-      </c>
-      <c r="B243" s="7" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>1127</v>
+        <v>285</v>
+      </c>
+      <c r="B243" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1119</v>
+        <v>593</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" t="s">
         <v>475</v>
       </c>
-      <c r="B245" s="7" t="s">
+      <c r="B246" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="C245" s="2" t="s">
+      <c r="C246" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247" t="s">
-        <v>462</v>
-      </c>
-      <c r="B247" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="B248" t="s">
-        <v>291</v>
-      </c>
-      <c r="C248" t="s">
-        <v>522</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B249" t="s">
-        <v>507</v>
+        <v>291</v>
+      </c>
+      <c r="C249" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>289</v>
+        <v>452</v>
       </c>
       <c r="B250" t="s">
-        <v>832</v>
-      </c>
-      <c r="C250" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B251" t="s">
-        <v>815</v>
+        <v>832</v>
+      </c>
+      <c r="C251" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>445</v>
+        <v>290</v>
       </c>
       <c r="B252" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>292</v>
+        <v>445</v>
       </c>
       <c r="B253" t="s">
-        <v>824</v>
-      </c>
-      <c r="C253" t="s">
-        <v>1043</v>
+        <v>816</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B254" t="s">
-        <v>833</v>
+        <v>824</v>
+      </c>
+      <c r="C254" t="s">
+        <v>1043</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B255" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B256" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B257" t="s">
-        <v>756</v>
+        <v>835</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>594</v>
-      </c>
-      <c r="B258" s="7" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>1127</v>
+        <v>296</v>
+      </c>
+      <c r="B258" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>474</v>
+        <v>594</v>
       </c>
       <c r="B259" s="7" t="s">
-        <v>1168</v>
+        <v>1132</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
-      <c r="A261" t="s">
-        <v>626</v>
-      </c>
-      <c r="B261" t="s">
-        <v>627</v>
-      </c>
-      <c r="C261" t="s">
-        <v>585</v>
+    <row r="260" spans="1:3">
+      <c r="A260" t="s">
+        <v>474</v>
+      </c>
+      <c r="B260" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>491</v>
+        <v>626</v>
       </c>
       <c r="B262" t="s">
-        <v>1192</v>
+        <v>627</v>
       </c>
       <c r="C262" t="s">
-        <v>520</v>
+        <v>585</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B263" t="s">
-        <v>493</v>
+        <v>1192</v>
       </c>
       <c r="C263" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>519</v>
+        <v>492</v>
       </c>
       <c r="B264" t="s">
-        <v>533</v>
+        <v>493</v>
+      </c>
+      <c r="C264" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>312</v>
+        <v>519</v>
       </c>
       <c r="B265" t="s">
-        <v>299</v>
+        <v>533</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B266" t="s">
-        <v>300</v>
-      </c>
-      <c r="C266" t="s">
-        <v>522</v>
+        <v>299</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>453</v>
+        <v>313</v>
       </c>
       <c r="B267" t="s">
-        <v>508</v>
+        <v>300</v>
+      </c>
+      <c r="C267" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>314</v>
+        <v>453</v>
       </c>
       <c r="B268" t="s">
-        <v>301</v>
+        <v>508</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B269" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
+        <v>315</v>
+      </c>
+      <c r="B270" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" t="s">
         <v>316</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B271" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="271" spans="1:3" s="6" customFormat="1">
-      <c r="A271" s="6" t="s">
+    <row r="272" spans="1:3" s="6" customFormat="1">
+      <c r="A272" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="B271" s="6" t="s">
+      <c r="B272" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C271" s="6" t="s">
+      <c r="C272" s="6" t="s">
         <v>522</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3">
-      <c r="A272" t="s">
-        <v>318</v>
-      </c>
-      <c r="B272" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B273" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B274" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
+        <v>320</v>
+      </c>
+      <c r="B275" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" t="s">
         <v>321</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B276" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="276" spans="1:3" s="6" customFormat="1">
-      <c r="A276" s="6" t="s">
+    <row r="277" spans="1:3" s="6" customFormat="1">
+      <c r="A277" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="B276" s="6" t="s">
+      <c r="B277" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="C276" s="6" t="s">
+      <c r="C277" s="6" t="s">
         <v>522</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3">
-      <c r="A277" t="s">
-        <v>323</v>
-      </c>
-      <c r="B277" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B278" t="s">
-        <v>310</v>
+        <v>736</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B279" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
+        <v>325</v>
+      </c>
+      <c r="B280" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" t="s">
         <v>473</v>
       </c>
-      <c r="B280" s="7" t="s">
+      <c r="B281" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="C280" s="2" t="s">
+      <c r="C281" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3">
-      <c r="A282" t="s">
-        <v>537</v>
-      </c>
-      <c r="B282" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>332</v>
+        <v>537</v>
       </c>
       <c r="B283" t="s">
-        <v>350</v>
+        <v>538</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B284" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B285" t="s">
-        <v>348</v>
-      </c>
-      <c r="C285" t="s">
-        <v>522</v>
+        <v>347</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>454</v>
+        <v>334</v>
       </c>
       <c r="B286" t="s">
-        <v>509</v>
+        <v>348</v>
+      </c>
+      <c r="C286" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>351</v>
+        <v>454</v>
       </c>
       <c r="B287" t="s">
-        <v>349</v>
-      </c>
-      <c r="C287" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="B288" t="s">
-        <v>341</v>
+        <v>349</v>
+      </c>
+      <c r="C288" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="B289" t="s">
-        <v>342</v>
-      </c>
-      <c r="C289" t="s">
-        <v>499</v>
+        <v>341</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B290" t="s">
-        <v>343</v>
+        <v>342</v>
+      </c>
+      <c r="C290" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B291" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B292" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B293" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B294" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>976</v>
+        <v>340</v>
       </c>
       <c r="B295" t="s">
-        <v>977</v>
-      </c>
-      <c r="C295" t="s">
-        <v>973</v>
+        <v>343</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B296" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C296" t="s">
         <v>973</v>
@@ -11868,10 +11877,10 @@
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B297" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C297" t="s">
         <v>973</v>
@@ -11879,51 +11888,51 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>1111</v>
+        <v>980</v>
       </c>
       <c r="B298" t="s">
-        <v>1112</v>
+        <v>981</v>
+      </c>
+      <c r="C298" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" t="s">
         <v>472</v>
       </c>
-      <c r="B299" s="5" t="s">
+      <c r="B300" s="5" t="s">
         <v>1170</v>
       </c>
-      <c r="C299" s="2" t="s">
+      <c r="C300" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3">
-      <c r="A301" t="s">
-        <v>628</v>
-      </c>
-      <c r="B301" t="s">
-        <v>645</v>
-      </c>
-      <c r="C301" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>972</v>
-      </c>
-      <c r="B302" s="7" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>1127</v>
+        <v>628</v>
+      </c>
+      <c r="B302" t="s">
+        <v>645</v>
+      </c>
+      <c r="C302" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>1127</v>
@@ -11931,78 +11940,78 @@
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>975</v>
-      </c>
-      <c r="B304" s="5" t="s">
-        <v>1171</v>
+        <v>974</v>
+      </c>
+      <c r="B304" s="7" t="s">
+        <v>1136</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
-      <c r="A306" t="s">
-        <v>624</v>
-      </c>
-      <c r="B306" t="s">
-        <v>625</v>
-      </c>
-      <c r="C306" t="s">
-        <v>585</v>
+    <row r="305" spans="1:3">
+      <c r="A305" t="s">
+        <v>975</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>463</v>
+        <v>624</v>
       </c>
       <c r="B307" t="s">
-        <v>464</v>
+        <v>625</v>
+      </c>
+      <c r="C307" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>358</v>
+        <v>463</v>
       </c>
       <c r="B308" t="s">
-        <v>369</v>
+        <v>464</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B309" t="s">
-        <v>370</v>
-      </c>
-      <c r="C309" t="s">
-        <v>522</v>
+        <v>369</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>510</v>
+        <v>359</v>
       </c>
       <c r="B310" t="s">
-        <v>511</v>
+        <v>370</v>
+      </c>
+      <c r="C310" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>360</v>
+        <v>510</v>
       </c>
       <c r="B311" t="s">
-        <v>371</v>
-      </c>
-      <c r="C311" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B312" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C312" t="s">
         <v>522</v>
@@ -12010,161 +12019,161 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B313" t="s">
-        <v>523</v>
+        <v>372</v>
+      </c>
+      <c r="C313" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B314" t="s">
-        <v>373</v>
+        <v>523</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B315" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B316" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B317" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B318" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B319" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>679</v>
-      </c>
-      <c r="B320" s="7" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>1127</v>
+        <v>368</v>
+      </c>
+      <c r="B320" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B321" t="s">
-        <v>1058</v>
+        <v>679</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>546</v>
-      </c>
-      <c r="B322" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C322" s="2" t="s">
-        <v>1127</v>
+        <v>1057</v>
+      </c>
+      <c r="B322" t="s">
+        <v>1058</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B323" t="s">
-        <v>1115</v>
+        <v>546</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B324" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" t="s">
         <v>470</v>
       </c>
-      <c r="B324" s="5" t="s">
+      <c r="B325" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C324" s="2" t="s">
+      <c r="C325" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3">
-      <c r="A326" t="s">
-        <v>465</v>
-      </c>
-      <c r="B326" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>385</v>
+        <v>465</v>
       </c>
       <c r="B327" t="s">
-        <v>396</v>
+        <v>464</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B328" t="s">
-        <v>397</v>
-      </c>
-      <c r="C328" t="s">
-        <v>522</v>
+        <v>396</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>455</v>
+        <v>386</v>
       </c>
       <c r="B329" t="s">
-        <v>512</v>
+        <v>397</v>
+      </c>
+      <c r="C329" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>387</v>
+        <v>455</v>
       </c>
       <c r="B330" t="s">
-        <v>398</v>
-      </c>
-      <c r="C330" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B331" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C331" t="s">
         <v>522</v>
@@ -12172,730 +12181,730 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B332" t="s">
-        <v>524</v>
+        <v>399</v>
+      </c>
+      <c r="C332" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B333" t="s">
-        <v>373</v>
+        <v>524</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B334" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B335" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B336" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B337" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B338" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>552</v>
-      </c>
-      <c r="B339" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C339" s="2" t="s">
-        <v>1127</v>
+        <v>395</v>
+      </c>
+      <c r="B339" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B340" t="s">
-        <v>1117</v>
+        <v>552</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B341" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" t="s">
         <v>469</v>
       </c>
-      <c r="B341" s="5" t="s">
+      <c r="B342" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C341" s="2" t="s">
+      <c r="C342" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3">
-      <c r="A343" t="s">
-        <v>622</v>
-      </c>
-      <c r="B343" t="s">
-        <v>623</v>
-      </c>
-      <c r="C343" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>379</v>
+        <v>622</v>
       </c>
       <c r="B344" t="s">
-        <v>1195</v>
+        <v>623</v>
+      </c>
+      <c r="C344" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B345" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C345" t="s">
-        <v>522</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>456</v>
+        <v>380</v>
       </c>
       <c r="B346" t="s">
-        <v>1197</v>
+        <v>1196</v>
+      </c>
+      <c r="C346" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>381</v>
+        <v>456</v>
       </c>
       <c r="B347" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B348" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B349" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>1074</v>
+        <v>383</v>
       </c>
       <c r="B350" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C350" t="s">
-        <v>1076</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C351" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" t="s">
         <v>468</v>
       </c>
-      <c r="B351" s="5" t="s">
+      <c r="B352" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="C351" s="2" t="s">
+      <c r="C352" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3">
-      <c r="A353" t="s">
-        <v>687</v>
-      </c>
-      <c r="B353" t="s">
-        <v>688</v>
-      </c>
-      <c r="C353" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
+        <v>687</v>
+      </c>
+      <c r="B354" t="s">
+        <v>688</v>
+      </c>
+      <c r="C354" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" t="s">
         <v>689</v>
       </c>
-      <c r="B354" s="5" t="s">
+      <c r="B355" s="5" t="s">
         <v>1174</v>
       </c>
-      <c r="C354" s="2" t="s">
+      <c r="C355" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3">
-      <c r="A356" t="s">
-        <v>694</v>
-      </c>
-      <c r="B356" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B357" t="s">
-        <v>1194</v>
+        <v>695</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B358" t="s">
-        <v>698</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B359" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B360" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B361" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B362" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B363" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B364" t="s">
-        <v>1101</v>
+        <v>708</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>710</v>
-      </c>
-      <c r="B365" s="7" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C365" s="2" t="s">
-        <v>1127</v>
+        <v>709</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>711</v>
-      </c>
-      <c r="B366" t="s">
-        <v>712</v>
+        <v>710</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B367" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B368" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B369" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B370" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B371" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>1050</v>
+        <v>721</v>
       </c>
       <c r="B372" t="s">
-        <v>1051</v>
+        <v>722</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>723</v>
+        <v>1050</v>
       </c>
       <c r="B373" t="s">
-        <v>724</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>1090</v>
+        <v>723</v>
       </c>
       <c r="B374" t="s">
-        <v>1091</v>
+        <v>724</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" t="s">
         <v>1073</v>
       </c>
-      <c r="B375" s="5" t="s">
+      <c r="B376" s="5" t="s">
         <v>1176</v>
       </c>
-      <c r="C375" s="2" t="s">
+      <c r="C376" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3">
-      <c r="A377" t="s">
-        <v>725</v>
-      </c>
-      <c r="B377" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B378" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B379" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B380" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B381" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B382" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B383" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B384" t="s">
-        <v>311</v>
+        <v>738</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B385" t="s">
-        <v>741</v>
+        <v>311</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B386" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B387" t="s">
-        <v>1193</v>
+        <v>743</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
+        <v>744</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" t="s">
         <v>745</v>
       </c>
-      <c r="B388" s="7" t="s">
+      <c r="B389" s="7" t="s">
         <v>1177</v>
       </c>
-      <c r="C388" s="2" t="s">
+      <c r="C389" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3">
-      <c r="A390" t="s">
-        <v>746</v>
-      </c>
-      <c r="B390" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B391" t="s">
-        <v>748</v>
+        <v>305</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B392" t="s">
-        <v>307</v>
+        <v>748</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
+        <v>749</v>
+      </c>
+      <c r="B393" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" t="s">
         <v>750</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B394" t="s">
         <v>1102</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3">
-      <c r="A395" t="s">
-        <v>771</v>
-      </c>
-      <c r="B395" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B396" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="B397" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B398" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B399" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
+        <v>763</v>
+      </c>
+      <c r="B400" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" t="s">
         <v>768</v>
       </c>
-      <c r="B400" s="5" t="s">
+      <c r="B401" s="5" t="s">
         <v>1178</v>
       </c>
-      <c r="C400" s="2" t="s">
+      <c r="C401" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3">
-      <c r="A402" t="s">
-        <v>775</v>
-      </c>
-      <c r="B402" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="B403" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="B404" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B405" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B406" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
+        <v>778</v>
+      </c>
+      <c r="B407" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408" t="s">
         <v>779</v>
       </c>
-      <c r="B407" s="5" t="s">
+      <c r="B408" s="5" t="s">
         <v>1179</v>
       </c>
-      <c r="C407" s="2" t="s">
+      <c r="C408" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3">
-      <c r="A409" t="s">
-        <v>787</v>
-      </c>
-      <c r="B409" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B410" t="s">
-        <v>1066</v>
+        <v>788</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>790</v>
-      </c>
-      <c r="B411" s="7" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C411" s="2" t="s">
-        <v>1127</v>
+        <v>789</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>792</v>
-      </c>
-      <c r="B412" t="s">
-        <v>1030</v>
+        <v>790</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>798</v>
-      </c>
-      <c r="B413" s="7" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C413" s="2" t="s">
-        <v>1127</v>
+        <v>792</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1030</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>799</v>
-      </c>
-      <c r="B414" t="s">
-        <v>1017</v>
+        <v>798</v>
+      </c>
+      <c r="B414" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C414" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B415" t="s">
-        <v>1036</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B416" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B417" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B418" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B419" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B420" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B421" t="s">
-        <v>797</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B422" t="s">
-        <v>1037</v>
+        <v>797</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>810</v>
-      </c>
-      <c r="B423" s="7" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C423" s="2" t="s">
-        <v>1127</v>
+        <v>809</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1037</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1132</v>
+        <v>1163</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>1127</v>
@@ -12903,10 +12912,10 @@
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="B425" s="7" t="s">
-        <v>1164</v>
+        <v>1132</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>1127</v>
@@ -12914,10 +12923,10 @@
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>801</v>
-      </c>
-      <c r="B426" s="5" t="s">
-        <v>1181</v>
+        <v>802</v>
+      </c>
+      <c r="B426" s="7" t="s">
+        <v>1164</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>1127</v>
@@ -12925,823 +12934,826 @@
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B427" t="s">
-        <v>1107</v>
+        <v>801</v>
+      </c>
+      <c r="B427" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>1020</v>
+        <v>1113</v>
       </c>
       <c r="B428" t="s">
-        <v>1018</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B429" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B430" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B431" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B432" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B433" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>1039</v>
+        <v>1029</v>
       </c>
       <c r="B434" t="s">
-        <v>1038</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B435" s="7" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C435" s="2" t="s">
-        <v>1127</v>
+        <v>1039</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1038</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B436" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437" t="s">
         <v>1080</v>
       </c>
-      <c r="B436" t="s">
+      <c r="B437" t="s">
         <v>1081</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3">
-      <c r="A438" t="s">
-        <v>867</v>
-      </c>
-      <c r="B438" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>886</v>
+        <v>867</v>
       </c>
       <c r="B439" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B440" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B441" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B442" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B443" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B444" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B445" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B446" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B447" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B448" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>887</v>
+        <v>877</v>
       </c>
       <c r="B449" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="B450" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B451" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B452" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>873</v>
-      </c>
-      <c r="B453" s="7" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C453" s="2" t="s">
-        <v>1127</v>
+        <v>874</v>
+      </c>
+      <c r="B453" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>872</v>
-      </c>
-      <c r="B454" t="s">
-        <v>863</v>
+        <v>873</v>
+      </c>
+      <c r="B454" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C454" s="2" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B455" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B456" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B457" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>1084</v>
+        <v>869</v>
       </c>
       <c r="B458" t="s">
-        <v>1085</v>
+        <v>866</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3">
+      <c r="A460" t="s">
         <v>868</v>
       </c>
-      <c r="B459" s="5" t="s">
+      <c r="B460" s="5" t="s">
         <v>1182</v>
       </c>
-      <c r="C459" s="2" t="s">
+      <c r="C460" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3">
-      <c r="A461" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B461" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>905</v>
+        <v>1077</v>
       </c>
       <c r="B462" t="s">
-        <v>890</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="B463" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B464" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B465" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B466" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B467" t="s">
-        <v>1103</v>
+        <v>894</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B468" t="s">
-        <v>895</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B469" t="s">
-        <v>1104</v>
+        <v>895</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B470" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>1092</v>
+        <v>904</v>
       </c>
       <c r="B471" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3">
+      <c r="A473" t="s">
         <v>903</v>
       </c>
-      <c r="B472" s="5" t="s">
+      <c r="B473" s="5" t="s">
         <v>1183</v>
       </c>
-      <c r="C472" s="2" t="s">
+      <c r="C473" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="474" spans="1:3">
-      <c r="A474" t="s">
+    <row r="475" spans="1:3">
+      <c r="A475" t="s">
         <v>910</v>
       </c>
-      <c r="B474" s="7" t="s">
+      <c r="B475" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="C474" s="2" t="s">
+      <c r="C475" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="475" spans="1:3" s="6" customFormat="1">
-      <c r="A475" s="6" t="s">
+    <row r="476" spans="1:3" s="6" customFormat="1">
+      <c r="A476" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="B475" s="6" t="s">
+      <c r="B476" s="6" t="s">
         <v>1185</v>
       </c>
-      <c r="C475" s="6" t="s">
+      <c r="C476" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="477" spans="1:3" s="6" customFormat="1">
-      <c r="A477" s="6" t="s">
+    <row r="478" spans="1:3" s="6" customFormat="1">
+      <c r="A478" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="B477" s="6" t="s">
+      <c r="B478" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="C477" s="6" t="s">
+      <c r="C478" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="478" spans="1:3">
-      <c r="A478" t="s">
+    <row r="479" spans="1:3">
+      <c r="A479" t="s">
         <v>920</v>
       </c>
-      <c r="B478" s="5" t="s">
+      <c r="B479" s="5" t="s">
         <v>1186</v>
       </c>
-      <c r="C478" s="2" t="s">
+      <c r="C479" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3">
-      <c r="A480" t="s">
-        <v>917</v>
-      </c>
-      <c r="B480" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B481" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
-        <v>1109</v>
+        <v>918</v>
       </c>
       <c r="B482" t="s">
-        <v>1110</v>
+        <v>916</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="A483" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484" t="s">
         <v>914</v>
       </c>
-      <c r="B483" s="7" t="s">
+      <c r="B484" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="C483" s="2" t="s">
+      <c r="C484" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3">
-      <c r="A485" t="s">
-        <v>927</v>
-      </c>
-      <c r="B485" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B486" t="s">
-        <v>922</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B487" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>971</v>
+        <v>929</v>
       </c>
       <c r="B488" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>930</v>
+        <v>971</v>
       </c>
       <c r="B489" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B490" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="491" spans="1:3">
       <c r="A491" t="s">
+        <v>931</v>
+      </c>
+      <c r="B491" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3">
+      <c r="A492" t="s">
         <v>932</v>
       </c>
-      <c r="B491" s="7" t="s">
+      <c r="B492" s="7" t="s">
         <v>1189</v>
       </c>
-      <c r="C491" s="2" t="s">
+      <c r="C492" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3">
-      <c r="A493" t="s">
-        <v>943</v>
-      </c>
-      <c r="B493" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B494" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B495" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B496" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B497" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="498" spans="1:3">
       <c r="A498" t="s">
+        <v>947</v>
+      </c>
+      <c r="B498" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3">
+      <c r="A499" t="s">
         <v>946</v>
       </c>
-      <c r="B498" s="7" t="s">
+      <c r="B499" s="7" t="s">
         <v>1139</v>
       </c>
-      <c r="C498" s="2" t="s">
+      <c r="C499" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3">
-      <c r="A500" t="s">
-        <v>960</v>
-      </c>
-      <c r="B500" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="B501" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B502" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B503" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="504" spans="1:3">
       <c r="A504" t="s">
+        <v>957</v>
+      </c>
+      <c r="B504" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3">
+      <c r="A505" t="s">
         <v>958</v>
       </c>
-      <c r="B504" t="s">
+      <c r="B505" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="505" spans="1:3" s="6" customFormat="1">
-      <c r="A505" s="6" t="s">
+    <row r="506" spans="1:3" s="6" customFormat="1">
+      <c r="A506" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="B505" s="6" t="s">
+      <c r="B506" s="6" t="s">
         <v>1079</v>
       </c>
-      <c r="C505" s="6" t="s">
+      <c r="C506" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="507" spans="1:3" s="6" customFormat="1">
-      <c r="A507" s="6" t="s">
+    <row r="508" spans="1:3" s="6" customFormat="1">
+      <c r="A508" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="B507" s="6" t="s">
+      <c r="B508" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="C507" s="6" t="s">
+      <c r="C508" s="6" t="s">
         <v>1131</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3">
-      <c r="A508" t="s">
-        <v>966</v>
-      </c>
-      <c r="B508" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B509" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B510" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="511" spans="1:3">
       <c r="A511" t="s">
+        <v>968</v>
+      </c>
+      <c r="B511" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3">
+      <c r="A512" t="s">
         <v>969</v>
       </c>
-      <c r="B511" s="7" t="s">
+      <c r="B512" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="C511" s="2" t="s">
+      <c r="C512" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3">
-      <c r="A513" t="s">
-        <v>990</v>
-      </c>
-      <c r="B513" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
-        <v>1005</v>
+        <v>990</v>
       </c>
       <c r="B514" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B515" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B516" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
       <c r="B517" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="B518" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B519" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B520" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B521" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B522" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B523" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B524" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B525" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="526" spans="1:3">
       <c r="A526" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3">
+      <c r="A527" t="s">
         <v>1004</v>
       </c>
-      <c r="B526" s="7" t="s">
+      <c r="B527" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C526" s="2" t="s">
+      <c r="C527" s="2" t="s">
         <v>1127</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3">
-      <c r="A528" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B529" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B530" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B531" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="B532" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
-        <v>1316</v>
+        <v>1303</v>
       </c>
       <c r="B533" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>1306</v>
+        <v>1315</v>
       </c>
       <c r="B534" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -13749,39 +13761,39 @@
         <v>1305</v>
       </c>
       <c r="B535" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>1315</v>
+        <v>1304</v>
       </c>
       <c r="B536" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
       <c r="B537" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B538" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>1318</v>
+        <v>1307</v>
       </c>
       <c r="B539" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -13789,223 +13801,223 @@
         <v>1317</v>
       </c>
       <c r="B540" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="B541" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
       <c r="B542" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>1320</v>
+        <v>1308</v>
       </c>
       <c r="B543" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
       <c r="B544" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
       <c r="B545" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>1311</v>
+        <v>1320</v>
       </c>
       <c r="B546" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>1322</v>
+        <v>1310</v>
       </c>
       <c r="B547" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>1312</v>
+        <v>1321</v>
       </c>
       <c r="B548" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>1323</v>
+        <v>1311</v>
       </c>
       <c r="B549" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="B550" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>1324</v>
+        <v>1312</v>
       </c>
       <c r="B551" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="B552" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>1314</v>
+        <v>1325</v>
       </c>
       <c r="B553" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1325</v>
+        <v>1313</v>
       </c>
       <c r="B554" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="B555" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B556" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="B557" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B558" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B559" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B560" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B561" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="B562" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B563" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="B564" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B565" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="B566" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>1332</v>
+        <v>1341</v>
       </c>
       <c r="B567" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -14013,7 +14025,7 @@
         <v>1331</v>
       </c>
       <c r="B568" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -14021,7 +14033,7 @@
         <v>1330</v>
       </c>
       <c r="B569" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -14029,103 +14041,103 @@
         <v>1329</v>
       </c>
       <c r="B570" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>1343</v>
+        <v>1328</v>
       </c>
       <c r="B571" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="B572" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B573" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>1357</v>
+        <v>1344</v>
       </c>
       <c r="B574" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="B575" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B576" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B577" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B578" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B579" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B580" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B581" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="B582" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -14133,284 +14145,292 @@
         <v>1365</v>
       </c>
       <c r="B583" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B584" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B585" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B586" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B587" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B588" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="B589" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B590" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B591" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>1346</v>
+        <v>1373</v>
       </c>
       <c r="B592" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>1354</v>
+        <v>1345</v>
       </c>
       <c r="B593" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="B594" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>1355</v>
+        <v>1346</v>
       </c>
       <c r="B595" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="B596" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>1375</v>
+        <v>1347</v>
       </c>
       <c r="B597" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1349</v>
+        <v>1374</v>
       </c>
       <c r="B598" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>1378</v>
+        <v>1348</v>
       </c>
       <c r="B599" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1350</v>
+        <v>1377</v>
       </c>
       <c r="B600" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1356</v>
+        <v>1349</v>
       </c>
       <c r="B601" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B602" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1379</v>
+        <v>1350</v>
       </c>
       <c r="B603" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>1352</v>
+        <v>1378</v>
       </c>
       <c r="B604" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>1380</v>
+        <v>1351</v>
       </c>
       <c r="B605" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B606" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>1353</v>
+        <v>1380</v>
       </c>
       <c r="B607" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>1382</v>
+        <v>1352</v>
       </c>
       <c r="B608" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="B609" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B610" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="B611" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B612" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B613" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="B614" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B615" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="B616" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B617" t="s">
-        <v>1299</v>
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1298</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C526" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
-  <conditionalFormatting sqref="A480:A482 A477:A478 A462:A472 A474:A475">
+  <autoFilter ref="A1:C527" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
+  <conditionalFormatting sqref="A481:A483 A478:A479 A463:A473 A475:A476">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1021\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D836AE-B0E7-4772-9C4C-5686F5C81D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407AD2FE-DEA9-4CE5-AC0E-AEF9B06F819B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -4233,7 +4233,7 @@
     <t>Updated by Harman</t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1022\Library\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407AD2FE-DEA9-4CE5-AC0E-AEF9B06F819B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A081F99-E0C1-4031-805C-91DB85B5C3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="17190" windowHeight="8550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -4233,7 +4233,7 @@
     <t>Updated by Harman</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1022\Library\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A081F99-E0C1-4031-805C-91DB85B5C3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E35182-DD1B-414A-BA41-BAAFDF469424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="17190" windowHeight="8550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -4233,7 +4233,7 @@
     <t>Updated by Harman</t>
   </si>
   <si>
-    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E35182-DD1B-414A-BA41-BAAFDF469424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2694CD-A8D0-4D31-B03F-86DCBAFAD7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -4233,7 +4233,7 @@
     <t>Updated by Harman</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bagi.Elangovan\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2694CD-A8D0-4D31-B03F-86DCBAFAD7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90B2D51-22DA-4A6A-891E-782A3E845F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -4233,7 +4233,7 @@
     <t>Updated by Harman</t>
   </si>
   <si>
-    <t>C:\Users\Bagi.Elangovan\Documents\AZApplicationReview\Prompts\</t>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90B2D51-22DA-4A6A-891E-782A3E845F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69E4BD3-BEF7-491E-BC4C-C563923EDDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28350" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Findings" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$527</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$D$528</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="1402">
   <si>
     <t>Name</t>
   </si>
@@ -4234,6 +4234,21 @@
   </si>
   <si>
     <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>ICW_StudentFinding</t>
+  </si>
+  <si>
+    <t>The applicant has indicated all household contains all students on the Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>FindingType</t>
+  </si>
+  <si>
+    <t>Weighted Finding</t>
+  </si>
+  <si>
+    <t>FYI Finding</t>
   </si>
 </sst>
 </file>
@@ -4309,7 +4324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4324,6 +4339,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9335,5102 +9351,6846 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C618"/>
+  <dimension ref="A1:D619"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="167.85546875" customWidth="1"/>
-    <col min="3" max="3" width="60.140625" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="60.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75">
+    <row r="1" spans="1:4" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="C1" s="1" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>187</v>
       </c>
       <c r="B3" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="C3" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>1055</v>
       </c>
       <c r="B5" t="s">
         <v>1056</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="C5" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>1391</v>
       </c>
       <c r="B6" t="s">
         <v>1392</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="C6" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>611</v>
       </c>
       <c r="B8" t="s">
         <v>646</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D8" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>641</v>
       </c>
       <c r="B9" t="s">
         <v>647</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D9" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>642</v>
       </c>
       <c r="B10" t="s">
         <v>648</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D10" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>643</v>
       </c>
       <c r="B11" t="s">
         <v>650</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D11" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>651</v>
       </c>
       <c r="B12" t="s">
         <v>649</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D12" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>675</v>
       </c>
       <c r="B13" t="s">
         <v>676</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D13" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>644</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>1140</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D14" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>174</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="C16" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>74</v>
       </c>
       <c r="B17" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="C17" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>173</v>
       </c>
       <c r="B18" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="C18" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>75</v>
       </c>
       <c r="B19" t="s">
         <v>1100</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="C19" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>197</v>
       </c>
       <c r="B20" t="s">
         <v>198</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D20" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>489</v>
       </c>
       <c r="B21" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="C21" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>581</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>1126</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D22" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>589</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>1141</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D23" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>601</v>
       </c>
       <c r="B24" t="s">
         <v>602</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D24" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>614</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>1142</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D25" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>616</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>1143</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D26" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>683</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>1128</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D27" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>814</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>1144</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D28" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D30" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
         <v>471</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>1145</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>1393</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>1394</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1395</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
+      <c r="C31" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
         <v>175</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
+      <c r="C33" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
         <v>76</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
+      <c r="C34" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
         <v>497</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
+      <c r="C35" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
         <v>77</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
+      <c r="C36" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
         <v>79</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>1094</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
+      <c r="C37" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
         <v>189</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
+      <c r="C38" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
         <v>190</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
+      <c r="C39" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
         <v>80</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
+      <c r="C40" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
         <v>82</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
+      <c r="C41" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
         <v>78</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
+      <c r="C42" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
         <v>85</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
+      <c r="C43" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
         <v>555</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
+      <c r="C44" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
         <v>576</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
+      <c r="C45" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
         <v>603</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>604</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D46" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
         <v>677</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>678</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D47" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
         <v>486</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>1146</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
+      <c r="C48" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
         <v>177</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
+      <c r="C50" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
         <v>87</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
+      <c r="C51" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
         <v>88</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
+      <c r="C52" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
         <v>96</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
+      <c r="C53" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
         <v>97</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B54" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
+      <c r="C54" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
         <v>98</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
+      <c r="C55" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
         <v>99</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B56" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
+      <c r="C56" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
         <v>100</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B57" t="s">
         <v>94</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C57" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D57" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
         <v>101</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B58" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
+      <c r="C58" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
         <v>557</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B59" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
+      <c r="C59" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
         <v>667</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
+      <c r="C60" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
         <v>982</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B61" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
+      <c r="C61" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
         <v>586</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B62" s="5" t="s">
         <v>1147</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D62" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
         <v>485</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B63" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C63" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D63" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
         <v>178</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B65" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
+      <c r="C65" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
         <v>102</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B66" t="s">
         <v>103</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D66" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
         <v>111</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>112</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D67" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
         <v>113</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
         <v>114</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D68" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
         <v>107</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
         <v>104</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C69" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D69" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
         <v>108</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B70" t="s">
         <v>105</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D70" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
         <v>109</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B71" t="s">
         <v>106</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C71" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D71" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
         <v>110</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
         <v>1095</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
+      <c r="C72" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
         <v>494</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B73" t="s">
         <v>1096</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
+      <c r="C73" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
         <v>195</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
+      <c r="C74" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
         <v>196</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
         <v>670</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C75" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D75" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
         <v>513</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B76" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
+      <c r="C76" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
         <v>487</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B77" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
+      <c r="C77" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
         <v>630</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B78" t="s">
         <v>629</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C78" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D78" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
         <v>1086</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B79" t="s">
         <v>1087</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="2" t="s">
+      <c r="C79" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="2" t="s">
+      <c r="C80" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B81" t="s">
         <v>1098</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
+      <c r="C81" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
         <v>484</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>1149</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" t="s">
+      <c r="C82" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
         <v>152</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B84" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" t="s">
+      <c r="C84" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
         <v>116</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B85" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" t="s">
+      <c r="C85" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
         <v>118</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B86" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" t="s">
+      <c r="C86" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
         <v>559</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B87" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" t="s">
+      <c r="C87" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
         <v>640</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B88" s="5" t="s">
         <v>1129</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C88" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D88" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" t="s">
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
         <v>658</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
         <v>659</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C89" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D89" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" t="s">
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
         <v>657</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>660</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C90" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D90" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" t="s">
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
         <v>656</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>661</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C91" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D91" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" t="s">
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
         <v>483</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B92" s="2" t="s">
         <v>1150</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" t="s">
+      <c r="C92" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
         <v>180</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B94" t="s">
         <v>1041</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" t="s">
+      <c r="C94" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
         <v>639</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B95" t="s">
         <v>652</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C95" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D95" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" t="s">
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
         <v>637</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>638</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C96" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D96" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" t="s">
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
         <v>119</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B97" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" t="s">
+      <c r="C97" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
         <v>120</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B98" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" t="s">
+      <c r="C98" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
         <v>132</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B99" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" t="s">
+      <c r="C99" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
         <v>133</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B100" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" t="s">
+      <c r="C100" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
         <v>134</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B101" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" t="s">
+      <c r="C101" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
         <v>135</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B102" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" t="s">
+      <c r="C102" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
         <v>136</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B103" t="s">
         <v>441</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C103" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D103" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
-      <c r="A103" t="s">
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
         <v>137</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B104" t="s">
         <v>443</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C104" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D104" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
-      <c r="A104" t="s">
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
         <v>138</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B105" t="s">
         <v>444</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C105" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D105" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
-      <c r="A105" t="s">
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
         <v>561</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B106" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" t="s">
+      <c r="C106" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
         <v>605</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B107" t="s">
         <v>606</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C107" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D107" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
-      <c r="A107" t="s">
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
         <v>840</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B108" t="s">
         <v>841</v>
       </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" t="s">
+      <c r="C108" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
         <v>631</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B109" t="s">
         <v>632</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C109" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D109" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
-      <c r="A109" t="s">
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
         <v>634</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B110" t="s">
         <v>633</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C110" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D110" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
-      <c r="A110" t="s">
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
         <v>636</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B111" t="s">
         <v>635</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C111" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D111" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
-      <c r="A111" t="s">
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
         <v>837</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B112" s="5" t="s">
         <v>1130</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C112" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D112" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
-      <c r="A112" t="s">
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
         <v>838</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B113" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" t="s">
+      <c r="C113" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
         <v>843</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B114" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" t="s">
+      <c r="C114" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
         <v>845</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B115" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" t="s">
+      <c r="C115" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
         <v>482</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B116" s="2" t="s">
         <v>1151</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" t="s">
+      <c r="C116" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
         <v>1123</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B118" t="s">
         <v>1124</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C118" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D118" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" t="s">
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
         <v>141</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B119" t="s">
         <v>144</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C119" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D119" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" t="s">
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
         <v>142</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B120" t="s">
         <v>145</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C120" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D120" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" t="s">
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
         <v>143</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B121" t="s">
         <v>146</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C121" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D121" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" t="s">
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
         <v>139</v>
-      </c>
-      <c r="B121" t="s">
-        <v>514</v>
-      </c>
-      <c r="C121" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" t="s">
-        <v>583</v>
       </c>
       <c r="B122" t="s">
         <v>514</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D122" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>583</v>
+      </c>
+      <c r="B123" t="s">
+        <v>514</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D123" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" t="s">
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
         <v>140</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B124" t="s">
         <v>123</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C124" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D124" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" t="s">
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
         <v>125</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B125" t="s">
         <v>531</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C125" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D125" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" t="s">
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
         <v>126</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B126" t="s">
         <v>124</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C126" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D126" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" t="s">
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
         <v>563</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B127" t="s">
         <v>564</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C127" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D127" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
-      <c r="A127" t="s">
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
         <v>481</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B128" s="2" t="s">
         <v>1152</v>
       </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" t="s">
+      <c r="C128" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
         <v>181</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B130" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" t="s">
+      <c r="C130" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
         <v>127</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B131" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" t="s">
+      <c r="C131" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
         <v>129</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B132" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" t="s">
+      <c r="C132" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
         <v>128</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B133" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" t="s">
+      <c r="C133" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
         <v>682</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B134" t="s">
         <v>681</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C134" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D134" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
-      <c r="A134" t="s">
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
         <v>130</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B135" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" t="s">
+      <c r="C135" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
         <v>131</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B136" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" t="s">
+      <c r="C136" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
         <v>554</v>
       </c>
-      <c r="B136" s="5" t="s">
+      <c r="B137" s="5" t="s">
         <v>1153</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C137" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D137" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
-      <c r="A137" t="s">
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
         <v>565</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B138" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" t="s">
+      <c r="C138" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
         <v>607</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B139" t="s">
         <v>608</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C139" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D139" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
-      <c r="A139" t="s">
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
         <v>480</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B140" s="2" t="s">
         <v>1154</v>
       </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" t="s">
+      <c r="C140" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
         <v>597</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B142" t="s">
         <v>598</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C142" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D142" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
-      <c r="A142" t="s">
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
         <v>600</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B143" t="s">
         <v>1155</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C143" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D143" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
-      <c r="A144" t="s">
+    <row r="145" spans="1:4">
+      <c r="A145" t="s">
         <v>153</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B145" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" t="s">
+      <c r="C145" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" t="s">
         <v>154</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B146" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" t="s">
+      <c r="C146" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" t="s">
         <v>155</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B147" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" t="s">
+      <c r="C147" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" t="s">
         <v>156</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B148" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" t="s">
+      <c r="C148" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" t="s">
         <v>496</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B149" t="s">
         <v>620</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C149" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D149" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
-      <c r="A149" t="s">
+    <row r="150" spans="1:4">
+      <c r="A150" t="s">
         <v>1054</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B150" t="s">
         <v>1060</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C150" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D150" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
-      <c r="A150" t="s">
+    <row r="151" spans="1:4">
+      <c r="A151" t="s">
         <v>571</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B151" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" t="s">
+      <c r="C151" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" t="s">
         <v>479</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B152" t="s">
         <v>1156</v>
       </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" t="s">
+      <c r="C152" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" t="s">
         <v>185</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B154" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" t="s">
+      <c r="C154" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" t="s">
         <v>160</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B155" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" t="s">
+      <c r="C155" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" t="s">
         <v>161</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B156" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" t="s">
+      <c r="C156" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" t="s">
         <v>567</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B157" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" t="s">
+      <c r="C157" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" t="s">
         <v>478</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>1157</v>
       </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" t="s">
+      <c r="C158" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" t="s">
         <v>609</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B159" t="s">
         <v>610</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C159" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D159" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
-      <c r="A160" t="s">
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
         <v>183</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B161" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161" t="s">
+      <c r="C161" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
         <v>169</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B162" t="s">
         <v>166</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C162" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D162" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
-      <c r="A162" t="s">
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
         <v>164</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B163" t="s">
         <v>167</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C163" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D163" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
-      <c r="A163" t="s">
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
         <v>165</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B164" t="s">
         <v>168</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C164" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D164" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
-      <c r="A164" t="s">
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
         <v>194</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B165" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" t="s">
+      <c r="C165" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" t="s">
         <v>191</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B166" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" t="s">
+      <c r="C166" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
         <v>170</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B167" t="s">
         <v>171</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C167" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D167" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
-      <c r="A167" t="s">
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
         <v>569</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B168" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" s="6" customFormat="1">
-      <c r="A168" s="6" t="s">
+      <c r="C168" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" s="6" customFormat="1">
+      <c r="A169" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="B168" s="6" t="s">
+      <c r="B169" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="C168" s="6" t="s">
+      <c r="C169" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D169" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
-      <c r="A170" t="s">
+    <row r="171" spans="1:4">
+      <c r="A171" t="s">
         <v>1082</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B171" t="s">
         <v>756</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C171" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D171" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="171" spans="1:3" s="6" customFormat="1">
-      <c r="A171" s="6" t="s">
+    <row r="172" spans="1:4" s="6" customFormat="1">
+      <c r="A172" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="B171" s="6" t="s">
+      <c r="B172" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="C171" s="6" t="s">
+      <c r="C172" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D172" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
-      <c r="A172" t="s">
+    <row r="173" spans="1:4">
+      <c r="A173" t="s">
         <v>612</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B173" t="s">
         <v>613</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C173" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D173" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="173" spans="1:3" s="6" customFormat="1">
-      <c r="A173" s="6" t="s">
+    <row r="174" spans="1:4" s="6" customFormat="1">
+      <c r="A174" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B174" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="C173" s="6" t="s">
+      <c r="C174" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D174" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
-      <c r="A174" t="s">
+    <row r="175" spans="1:4">
+      <c r="A175" t="s">
         <v>691</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B175" t="s">
         <v>819</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C175" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D175" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
-      <c r="A175" t="s">
+    <row r="176" spans="1:4">
+      <c r="A176" t="s">
         <v>692</v>
       </c>
-      <c r="B175" s="7" t="s">
+      <c r="B176" s="7" t="s">
         <v>1142</v>
       </c>
-      <c r="C175" s="2" t="s">
+      <c r="C176" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D176" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
-      <c r="A176" t="s">
+    <row r="177" spans="1:4">
+      <c r="A177" t="s">
         <v>1044</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B177" t="s">
         <v>824</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C177" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D177" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
-      <c r="A178" t="s">
+    <row r="179" spans="1:4">
+      <c r="A179" t="s">
         <v>458</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B179" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179" t="s">
+      <c r="C179" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" t="s">
         <v>1067</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B180" t="s">
         <v>1068</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C180" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D180" t="s">
         <v>1069</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
-      <c r="A180" t="s">
+    <row r="181" spans="1:4">
+      <c r="A181" t="s">
         <v>232</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B181" t="s">
         <v>820</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C181" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D181" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
-      <c r="A181" t="s">
+    <row r="182" spans="1:4">
+      <c r="A182" t="s">
         <v>233</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B182" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" t="s">
+      <c r="C182" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
         <v>241</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B183" t="s">
         <v>822</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C183" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D183" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
-      <c r="A183" t="s">
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
         <v>666</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B184" t="s">
         <v>823</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C184" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D184" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
-      <c r="A184" t="s">
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
         <v>235</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B185" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185" t="s">
+      <c r="C185" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" t="s">
         <v>448</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B186" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" t="s">
+      <c r="C186" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" t="s">
         <v>236</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B187" t="s">
         <v>824</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C187" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D187" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
-      <c r="A187" t="s">
+    <row r="188" spans="1:4">
+      <c r="A188" t="s">
         <v>237</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B188" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" t="s">
+      <c r="C188" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" t="s">
         <v>238</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B189" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189" t="s">
+      <c r="C189" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
         <v>239</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B190" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" t="s">
+      <c r="C190" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
         <v>240</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B191" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" t="s">
+      <c r="C191" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" t="s">
         <v>271</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B192" t="s">
         <v>824</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C192" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D192" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
-      <c r="A192" t="s">
+    <row r="193" spans="1:4">
+      <c r="A193" t="s">
         <v>297</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B193" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" t="s">
+      <c r="C193" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" t="s">
         <v>577</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B194" t="s">
         <v>1042</v>
       </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" t="s">
+      <c r="C194" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" t="s">
         <v>590</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="B195" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C194" s="2" t="s">
+      <c r="C195" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D195" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="195" spans="1:3" s="6" customFormat="1">
-      <c r="A195" s="6" t="s">
+    <row r="196" spans="1:4" s="6" customFormat="1">
+      <c r="A196" s="6" t="s">
         <v>653</v>
       </c>
-      <c r="B195" s="6" t="s">
+      <c r="B196" s="6" t="s">
         <v>654</v>
       </c>
-      <c r="C195" s="6" t="s">
+      <c r="C196" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D196" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
-      <c r="A196" t="s">
+    <row r="197" spans="1:4">
+      <c r="A197" t="s">
         <v>665</v>
       </c>
-      <c r="B196" s="7" t="s">
+      <c r="B197" s="7" t="s">
         <v>1159</v>
       </c>
-      <c r="C196" s="2" t="s">
+      <c r="C197" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D197" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
-      <c r="A197" t="s">
+    <row r="198" spans="1:4">
+      <c r="A198" t="s">
         <v>836</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B198" s="7" t="s">
         <v>1133</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="C198" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D198" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
-      <c r="A198" t="s">
+    <row r="199" spans="1:4">
+      <c r="A199" t="s">
         <v>1106</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B199" t="s">
         <v>1107</v>
       </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" t="s">
+      <c r="C199" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" t="s">
         <v>466</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B200" s="7" t="s">
         <v>1160</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C200" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D200" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
-      <c r="A201" t="s">
+    <row r="201" spans="1:4">
+      <c r="C201" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" t="s">
         <v>664</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B202" s="7" t="s">
         <v>1161</v>
       </c>
-      <c r="C201" s="2" t="s">
+      <c r="C202" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D202" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="202" spans="1:3">
-      <c r="A202" t="s">
+    <row r="203" spans="1:4">
+      <c r="A203" t="s">
         <v>459</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B203" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" t="s">
+      <c r="C203" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" t="s">
         <v>242</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B204" t="s">
         <v>828</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C204" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D204" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="13.5" customHeight="1">
-      <c r="A204" t="s">
+    <row r="205" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A205" t="s">
         <v>244</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B205" t="s">
         <v>829</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C205" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D205" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="205" spans="1:3">
-      <c r="A205" t="s">
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
         <v>243</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B206" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" t="s">
+      <c r="C206" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" t="s">
         <v>245</v>
       </c>
-      <c r="B206" s="7" t="s">
+      <c r="B207" s="7" t="s">
         <v>1162</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="C207" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D207" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="207" spans="1:3">
-      <c r="A207" t="s">
+    <row r="208" spans="1:4">
+      <c r="A208" t="s">
         <v>246</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B208" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" t="s">
+      <c r="C208" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" t="s">
         <v>249</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B209" t="s">
         <v>248</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C209" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D209" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="209" spans="1:3">
-      <c r="A209" t="s">
+    <row r="210" spans="1:4">
+      <c r="A210" t="s">
         <v>449</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B210" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="210" spans="1:3">
-      <c r="A210" t="s">
+      <c r="C210" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" t="s">
         <v>250</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B211" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="211" spans="1:3">
-      <c r="A211" t="s">
+      <c r="C211" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" t="s">
         <v>251</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B212" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="212" spans="1:3">
-      <c r="A212" t="s">
+      <c r="C212" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" t="s">
         <v>256</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B213" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="213" spans="1:3">
-      <c r="A213" t="s">
+      <c r="C213" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" t="s">
         <v>257</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B214" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214" t="s">
+      <c r="C214" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" t="s">
         <v>258</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B215" t="s">
         <v>830</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C215" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D215" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
-      <c r="A215" t="s">
+    <row r="216" spans="1:4">
+      <c r="A216" t="s">
         <v>259</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B216" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="216" spans="1:3">
-      <c r="A216" t="s">
+      <c r="C216" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" t="s">
         <v>260</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B217" t="s">
         <v>831</v>
       </c>
-      <c r="C216" t="s">
+      <c r="C217" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D217" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
-      <c r="A217" t="s">
+    <row r="218" spans="1:4">
+      <c r="A218" t="s">
         <v>261</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B218" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="218" spans="1:3">
-      <c r="A218" t="s">
+      <c r="C218" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" t="s">
         <v>268</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B219" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="219" spans="1:3">
-      <c r="A219" t="s">
+      <c r="C219" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" t="s">
         <v>270</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B220" t="s">
         <v>824</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C220" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D220" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="220" spans="1:3">
-      <c r="A220" t="s">
+    <row r="221" spans="1:4">
+      <c r="A221" t="s">
         <v>272</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B221" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="C220" s="2" t="s">
+      <c r="C221" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D221" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
-      <c r="A221" t="s">
+    <row r="222" spans="1:4">
+      <c r="A222" t="s">
         <v>591</v>
       </c>
-      <c r="B221" s="7" t="s">
+      <c r="B222" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C221" s="2" t="s">
+      <c r="C222" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D222" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
-      <c r="A222" t="s">
+    <row r="223" spans="1:4">
+      <c r="A223" t="s">
         <v>588</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B223" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="C222" s="2" t="s">
+      <c r="C223" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D223" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="223" spans="1:3">
-      <c r="A223" t="s">
+    <row r="224" spans="1:4">
+      <c r="A224" t="s">
         <v>477</v>
       </c>
-      <c r="B223" s="7" t="s">
+      <c r="B224" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="C223" s="2" t="s">
+      <c r="C224" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D224" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="225" spans="1:3">
-      <c r="A225" t="s">
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
         <v>460</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B226" t="s">
         <v>1063</v>
       </c>
-    </row>
-    <row r="226" spans="1:3">
-      <c r="A226" t="s">
+      <c r="C226" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
         <v>450</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B227" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="227" spans="1:3">
-      <c r="A227" t="s">
+      <c r="C227" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
         <v>266</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B228" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="228" spans="1:3">
-      <c r="A228" t="s">
+      <c r="C228" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
         <v>267</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B229" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="229" spans="1:3">
-      <c r="A229" t="s">
+      <c r="C229" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
         <v>274</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B230" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230" t="s">
+      <c r="C230" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
         <v>273</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B231" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="231" spans="1:3">
-      <c r="A231" t="s">
+      <c r="C231" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
         <v>275</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B232" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="232" spans="1:3">
-      <c r="A232" t="s">
+      <c r="C232" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
         <v>592</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B233" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C232" s="2" t="s">
+      <c r="C233" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D233" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
-      <c r="A233" t="s">
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
         <v>476</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B234" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="C234" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="235" spans="1:3">
-      <c r="A235" t="s">
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
         <v>461</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B236" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236" t="s">
+      <c r="C236" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
         <v>451</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B237" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237" t="s">
+      <c r="C237" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
         <v>278</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B238" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238" t="s">
+      <c r="C238" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
         <v>279</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B239" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239" t="s">
+      <c r="C239" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
         <v>280</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B240" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240" t="s">
+      <c r="C240" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
         <v>282</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B241" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" t="s">
+      <c r="C241" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
         <v>283</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B242" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242" t="s">
+      <c r="C242" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
         <v>284</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B243" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243" t="s">
+      <c r="C243" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
         <v>285</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B244" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244" t="s">
+      <c r="C244" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
         <v>593</v>
       </c>
-      <c r="B244" s="7" t="s">
+      <c r="B245" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C244" s="2" t="s">
+      <c r="C245" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D245" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="245" spans="1:3">
-      <c r="A245" t="s">
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
         <v>1118</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B246" t="s">
         <v>1119</v>
       </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" t="s">
+      <c r="C246" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
         <v>475</v>
       </c>
-      <c r="B246" s="7" t="s">
+      <c r="B247" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="C246" s="2" t="s">
+      <c r="C247" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D247" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="248" spans="1:3">
-      <c r="A248" t="s">
+    <row r="249" spans="1:4">
+      <c r="A249" t="s">
         <v>462</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B249" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249" t="s">
+      <c r="C249" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" t="s">
         <v>446</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B250" t="s">
         <v>291</v>
       </c>
-      <c r="C249" t="s">
+      <c r="C250" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D250" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="250" spans="1:3">
-      <c r="A250" t="s">
+    <row r="251" spans="1:4">
+      <c r="A251" t="s">
         <v>452</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B251" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251" t="s">
+      <c r="C251" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
         <v>289</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B252" t="s">
         <v>832</v>
       </c>
-      <c r="C251" t="s">
+      <c r="C252" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D252" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="252" spans="1:3">
-      <c r="A252" t="s">
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
         <v>290</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B253" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="253" spans="1:3">
-      <c r="A253" t="s">
+      <c r="C253" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
         <v>445</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B254" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="254" spans="1:3">
-      <c r="A254" t="s">
+      <c r="C254" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
         <v>292</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B255" t="s">
         <v>824</v>
       </c>
-      <c r="C254" t="s">
+      <c r="C255" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D255" t="s">
         <v>1043</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
-      <c r="A255" t="s">
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
         <v>293</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B256" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="A256" t="s">
+      <c r="C256" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" t="s">
         <v>294</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B257" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="257" spans="1:3">
-      <c r="A257" t="s">
+      <c r="C257" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" t="s">
         <v>295</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B258" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="258" spans="1:3">
-      <c r="A258" t="s">
+      <c r="C258" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" t="s">
         <v>296</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B259" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259" t="s">
+      <c r="C259" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" t="s">
         <v>594</v>
       </c>
-      <c r="B259" s="7" t="s">
+      <c r="B260" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C259" s="2" t="s">
+      <c r="C260" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D260" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
-      <c r="A260" t="s">
+    <row r="261" spans="1:4">
+      <c r="A261" t="s">
         <v>474</v>
       </c>
-      <c r="B260" s="7" t="s">
+      <c r="B261" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="C260" s="2" t="s">
+      <c r="C261" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D261" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
-      <c r="A262" t="s">
+    <row r="263" spans="1:4">
+      <c r="A263" t="s">
         <v>626</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B263" t="s">
         <v>627</v>
       </c>
-      <c r="C262" t="s">
+      <c r="C263" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D263" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
-      <c r="A263" t="s">
+    <row r="264" spans="1:4">
+      <c r="A264" t="s">
         <v>491</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B264" t="s">
         <v>1192</v>
       </c>
-      <c r="C263" t="s">
+      <c r="C264" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D264" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
-      <c r="A264" t="s">
+    <row r="265" spans="1:4">
+      <c r="A265" t="s">
         <v>492</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B265" t="s">
         <v>493</v>
       </c>
-      <c r="C264" t="s">
+      <c r="C265" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D265" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="265" spans="1:3">
-      <c r="A265" t="s">
+    <row r="266" spans="1:4">
+      <c r="A266" t="s">
         <v>519</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B266" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="266" spans="1:3">
-      <c r="A266" t="s">
+      <c r="C266" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" t="s">
         <v>312</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B267" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="267" spans="1:3">
-      <c r="A267" t="s">
+      <c r="C267" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" t="s">
         <v>313</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B268" t="s">
         <v>300</v>
       </c>
-      <c r="C267" t="s">
+      <c r="C268" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D268" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
-      <c r="A268" t="s">
+    <row r="269" spans="1:4">
+      <c r="A269" t="s">
         <v>453</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B269" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="269" spans="1:3">
-      <c r="A269" t="s">
+      <c r="C269" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" t="s">
         <v>314</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B270" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="270" spans="1:3">
-      <c r="A270" t="s">
+      <c r="C270" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" t="s">
         <v>315</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B271" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="271" spans="1:3">
-      <c r="A271" t="s">
+      <c r="C271" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" t="s">
         <v>316</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B272" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="272" spans="1:3" s="6" customFormat="1">
-      <c r="A272" s="6" t="s">
+      <c r="C272" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" s="6" customFormat="1">
+      <c r="A273" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="B272" s="6" t="s">
+      <c r="B273" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C272" s="6" t="s">
+      <c r="C273" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D273" s="6" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
-      <c r="A273" t="s">
+    <row r="274" spans="1:4">
+      <c r="A274" t="s">
         <v>318</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B274" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="274" spans="1:3">
-      <c r="A274" t="s">
+      <c r="C274" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" t="s">
         <v>319</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B275" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="275" spans="1:3">
-      <c r="A275" t="s">
+      <c r="C275" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" t="s">
         <v>320</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B276" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="276" spans="1:3">
-      <c r="A276" t="s">
+      <c r="C276" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" t="s">
         <v>321</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B277" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" s="6" customFormat="1">
-      <c r="A277" s="6" t="s">
+      <c r="C277" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" s="6" customFormat="1">
+      <c r="A278" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="B277" s="6" t="s">
+      <c r="B278" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="C277" s="6" t="s">
+      <c r="C278" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D278" s="6" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
-      <c r="A278" t="s">
+    <row r="279" spans="1:4">
+      <c r="A279" t="s">
         <v>323</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B279" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="279" spans="1:3">
-      <c r="A279" t="s">
+      <c r="C279" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" t="s">
         <v>324</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B280" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" t="s">
+      <c r="C280" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" t="s">
         <v>325</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B281" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" t="s">
+      <c r="C281" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" t="s">
         <v>473</v>
       </c>
-      <c r="B281" s="7" t="s">
+      <c r="B282" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="C281" s="2" t="s">
+      <c r="C282" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D282" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
-      <c r="A283" t="s">
+    <row r="284" spans="1:4">
+      <c r="A284" t="s">
         <v>537</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B284" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="284" spans="1:3">
-      <c r="A284" t="s">
+      <c r="C284" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" t="s">
         <v>332</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B285" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="285" spans="1:3">
-      <c r="A285" t="s">
+      <c r="C285" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" t="s">
         <v>333</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B286" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="286" spans="1:3">
-      <c r="A286" t="s">
+      <c r="C286" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" t="s">
         <v>334</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B287" t="s">
         <v>348</v>
       </c>
-      <c r="C286" t="s">
+      <c r="C287" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D287" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
-      <c r="A287" t="s">
+    <row r="288" spans="1:4">
+      <c r="A288" t="s">
         <v>454</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B288" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="288" spans="1:3">
-      <c r="A288" t="s">
+      <c r="C288" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" t="s">
         <v>351</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B289" t="s">
         <v>349</v>
       </c>
-      <c r="C288" t="s">
+      <c r="C289" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D289" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="289" spans="1:3">
-      <c r="A289" t="s">
+    <row r="290" spans="1:4">
+      <c r="A290" t="s">
         <v>335</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B290" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="290" spans="1:3">
-      <c r="A290" t="s">
+      <c r="C290" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" t="s">
         <v>352</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B291" t="s">
         <v>342</v>
       </c>
-      <c r="C290" t="s">
+      <c r="C291" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D291" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="291" spans="1:3">
-      <c r="A291" t="s">
+    <row r="292" spans="1:4">
+      <c r="A292" t="s">
         <v>336</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B292" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="292" spans="1:3">
-      <c r="A292" t="s">
+      <c r="C292" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" t="s">
         <v>338</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B293" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="293" spans="1:3">
-      <c r="A293" t="s">
+      <c r="C293" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" t="s">
         <v>337</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B294" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="294" spans="1:3">
-      <c r="A294" t="s">
+      <c r="C294" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" t="s">
         <v>339</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B295" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="295" spans="1:3">
-      <c r="A295" t="s">
+      <c r="C295" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" t="s">
         <v>340</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B296" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="296" spans="1:3">
-      <c r="A296" t="s">
+      <c r="C296" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" t="s">
         <v>976</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B297" t="s">
         <v>977</v>
       </c>
-      <c r="C296" t="s">
+      <c r="C297" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D297" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
-      <c r="A297" t="s">
+    <row r="298" spans="1:4">
+      <c r="A298" t="s">
         <v>978</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B298" t="s">
         <v>979</v>
       </c>
-      <c r="C297" t="s">
+      <c r="C298" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D298" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="298" spans="1:3">
-      <c r="A298" t="s">
+    <row r="299" spans="1:4">
+      <c r="A299" t="s">
         <v>980</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B299" t="s">
         <v>981</v>
       </c>
-      <c r="C298" t="s">
+      <c r="C299" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D299" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="299" spans="1:3">
-      <c r="A299" t="s">
+    <row r="300" spans="1:4">
+      <c r="A300" t="s">
         <v>1111</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B300" t="s">
         <v>1112</v>
       </c>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="A300" t="s">
+      <c r="C300" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" t="s">
         <v>472</v>
       </c>
-      <c r="B300" s="5" t="s">
+      <c r="B301" s="5" t="s">
         <v>1170</v>
       </c>
-      <c r="C300" s="2" t="s">
+      <c r="C301" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D301" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="302" spans="1:3">
-      <c r="A302" t="s">
+    <row r="303" spans="1:4">
+      <c r="A303" t="s">
         <v>628</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B303" t="s">
         <v>645</v>
       </c>
-      <c r="C302" t="s">
+      <c r="C303" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D303" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="303" spans="1:3">
-      <c r="A303" t="s">
+    <row r="304" spans="1:4">
+      <c r="A304" t="s">
         <v>972</v>
       </c>
-      <c r="B303" s="7" t="s">
+      <c r="B304" s="7" t="s">
         <v>1135</v>
       </c>
-      <c r="C303" s="2" t="s">
+      <c r="C304" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D304" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="304" spans="1:3">
-      <c r="A304" t="s">
+    <row r="305" spans="1:4">
+      <c r="A305" t="s">
         <v>974</v>
       </c>
-      <c r="B304" s="7" t="s">
+      <c r="B305" s="7" t="s">
         <v>1136</v>
       </c>
-      <c r="C304" s="2" t="s">
+      <c r="C305" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D305" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
-      <c r="A305" t="s">
+    <row r="306" spans="1:4">
+      <c r="A306" t="s">
         <v>975</v>
       </c>
-      <c r="B305" s="5" t="s">
+      <c r="B306" s="5" t="s">
         <v>1171</v>
       </c>
-      <c r="C305" s="2" t="s">
+      <c r="C306" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D306" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="307" spans="1:3">
-      <c r="A307" t="s">
+    <row r="307" spans="1:4">
+      <c r="C307" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" t="s">
         <v>624</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B308" t="s">
         <v>625</v>
       </c>
-      <c r="C307" t="s">
+      <c r="C308" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D308" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="308" spans="1:3">
-      <c r="A308" t="s">
+    <row r="309" spans="1:4">
+      <c r="A309" t="s">
         <v>463</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B309" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="309" spans="1:3">
-      <c r="A309" t="s">
+      <c r="C309" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" t="s">
         <v>358</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B310" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="310" spans="1:3">
-      <c r="A310" t="s">
+      <c r="C310" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" t="s">
         <v>359</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B311" t="s">
         <v>370</v>
       </c>
-      <c r="C310" t="s">
+      <c r="C311" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D311" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="311" spans="1:3">
-      <c r="A311" t="s">
+    <row r="312" spans="1:4">
+      <c r="A312" t="s">
         <v>510</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B312" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="312" spans="1:3">
-      <c r="A312" t="s">
+      <c r="C312" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" t="s">
         <v>360</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B313" t="s">
         <v>371</v>
       </c>
-      <c r="C312" t="s">
+      <c r="C313" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D313" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="313" spans="1:3">
-      <c r="A313" t="s">
+    <row r="314" spans="1:4">
+      <c r="A314" t="s">
         <v>361</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B314" t="s">
         <v>372</v>
       </c>
-      <c r="C313" t="s">
+      <c r="C314" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D314" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="314" spans="1:3">
-      <c r="A314" t="s">
+    <row r="315" spans="1:4">
+      <c r="A315" t="s">
         <v>362</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B315" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="315" spans="1:3">
-      <c r="A315" t="s">
+      <c r="C315" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" t="s">
         <v>363</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B316" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="316" spans="1:3">
-      <c r="A316" t="s">
+      <c r="C316" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" t="s">
         <v>364</v>
       </c>
-      <c r="B316" t="s">
+      <c r="B317" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="317" spans="1:3">
-      <c r="A317" t="s">
+      <c r="C317" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" t="s">
         <v>365</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B318" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="318" spans="1:3">
-      <c r="A318" t="s">
+      <c r="C318" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" t="s">
         <v>366</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B319" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="319" spans="1:3">
-      <c r="A319" t="s">
+      <c r="C319" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" t="s">
         <v>367</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B320" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="320" spans="1:3">
-      <c r="A320" t="s">
+      <c r="C320" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" t="s">
         <v>368</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B321" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="321" spans="1:3">
-      <c r="A321" t="s">
+      <c r="C321" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" t="s">
         <v>679</v>
       </c>
-      <c r="B321" s="7" t="s">
+      <c r="B322" s="7" t="s">
         <v>1137</v>
       </c>
-      <c r="C321" s="2" t="s">
+      <c r="C322" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D322" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
-      <c r="A322" t="s">
+    <row r="323" spans="1:4">
+      <c r="A323" t="s">
         <v>1057</v>
       </c>
-      <c r="B322" t="s">
+      <c r="B323" t="s">
         <v>1058</v>
       </c>
-    </row>
-    <row r="323" spans="1:3">
-      <c r="A323" t="s">
+      <c r="C323" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" t="s">
         <v>546</v>
       </c>
-      <c r="B323" s="7" t="s">
+      <c r="B324" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="C323" s="2" t="s">
+      <c r="C324" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D324" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
-      <c r="A324" t="s">
+    <row r="325" spans="1:4">
+      <c r="A325" t="s">
         <v>1114</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B325" t="s">
         <v>1115</v>
       </c>
-    </row>
-    <row r="325" spans="1:3">
-      <c r="A325" t="s">
+      <c r="C325" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" t="s">
         <v>470</v>
       </c>
-      <c r="B325" s="5" t="s">
+      <c r="B326" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C325" s="2" t="s">
+      <c r="C326" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D326" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
-      <c r="A327" t="s">
+    <row r="328" spans="1:4">
+      <c r="A328" t="s">
         <v>465</v>
       </c>
-      <c r="B327" t="s">
+      <c r="B328" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="328" spans="1:3">
-      <c r="A328" t="s">
+      <c r="C328" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" t="s">
         <v>385</v>
       </c>
-      <c r="B328" t="s">
+      <c r="B329" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="329" spans="1:3">
-      <c r="A329" t="s">
+      <c r="C329" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" t="s">
         <v>386</v>
       </c>
-      <c r="B329" t="s">
+      <c r="B330" t="s">
         <v>397</v>
       </c>
-      <c r="C329" t="s">
+      <c r="C330" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D330" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="330" spans="1:3">
-      <c r="A330" t="s">
+    <row r="331" spans="1:4">
+      <c r="A331" t="s">
         <v>455</v>
       </c>
-      <c r="B330" t="s">
+      <c r="B331" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="331" spans="1:3">
-      <c r="A331" t="s">
+      <c r="C331" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" t="s">
         <v>387</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B332" t="s">
         <v>398</v>
       </c>
-      <c r="C331" t="s">
+      <c r="C332" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D332" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="332" spans="1:3">
-      <c r="A332" t="s">
+    <row r="333" spans="1:4">
+      <c r="A333" t="s">
         <v>388</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B333" t="s">
         <v>399</v>
       </c>
-      <c r="C332" t="s">
+      <c r="C333" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D333" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="333" spans="1:3">
-      <c r="A333" t="s">
+    <row r="334" spans="1:4">
+      <c r="A334" t="s">
         <v>389</v>
       </c>
-      <c r="B333" t="s">
+      <c r="B334" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="334" spans="1:3">
-      <c r="A334" t="s">
+      <c r="C334" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" t="s">
         <v>390</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B335" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="335" spans="1:3">
-      <c r="A335" t="s">
+      <c r="C335" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" t="s">
         <v>391</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B336" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="336" spans="1:3">
-      <c r="A336" t="s">
+      <c r="C336" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" t="s">
         <v>392</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B337" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="337" spans="1:3">
-      <c r="A337" t="s">
+      <c r="C337" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" t="s">
         <v>393</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B338" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="338" spans="1:3">
-      <c r="A338" t="s">
+      <c r="C338" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" t="s">
         <v>394</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B339" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="339" spans="1:3">
-      <c r="A339" t="s">
+      <c r="C339" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" t="s">
         <v>395</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B340" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="340" spans="1:3">
-      <c r="A340" t="s">
+      <c r="C340" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" t="s">
         <v>552</v>
       </c>
-      <c r="B340" s="7" t="s">
+      <c r="B341" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="C340" s="2" t="s">
+      <c r="C341" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D341" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
-      <c r="A341" t="s">
+    <row r="342" spans="1:4">
+      <c r="A342" t="s">
         <v>1116</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B342" t="s">
         <v>1117</v>
       </c>
-    </row>
-    <row r="342" spans="1:3">
-      <c r="A342" t="s">
+      <c r="C342" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" t="s">
         <v>469</v>
       </c>
-      <c r="B342" s="5" t="s">
+      <c r="B343" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C342" s="2" t="s">
+      <c r="C343" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D343" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
-      <c r="A344" t="s">
+    <row r="345" spans="1:4">
+      <c r="A345" t="s">
         <v>622</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B345" t="s">
         <v>623</v>
       </c>
-      <c r="C344" t="s">
+      <c r="C345" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D345" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="345" spans="1:3">
-      <c r="A345" t="s">
+    <row r="346" spans="1:4">
+      <c r="A346" t="s">
         <v>379</v>
       </c>
-      <c r="B345" t="s">
+      <c r="B346" t="s">
         <v>1195</v>
       </c>
-    </row>
-    <row r="346" spans="1:3">
-      <c r="A346" t="s">
+      <c r="C346" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" t="s">
         <v>380</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B347" t="s">
         <v>1196</v>
       </c>
-      <c r="C346" t="s">
+      <c r="C347" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D347" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="347" spans="1:3">
-      <c r="A347" t="s">
+    <row r="348" spans="1:4">
+      <c r="A348" t="s">
         <v>456</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B348" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="348" spans="1:3">
-      <c r="A348" t="s">
+      <c r="C348" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" t="s">
         <v>381</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B349" t="s">
         <v>1198</v>
       </c>
-    </row>
-    <row r="349" spans="1:3">
-      <c r="A349" t="s">
+      <c r="C349" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" t="s">
         <v>382</v>
       </c>
-      <c r="B349" t="s">
+      <c r="B350" t="s">
         <v>1199</v>
       </c>
-    </row>
-    <row r="350" spans="1:3">
-      <c r="A350" t="s">
+      <c r="C350" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" t="s">
         <v>383</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B351" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="351" spans="1:3">
-      <c r="A351" t="s">
+      <c r="C351" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" t="s">
         <v>1074</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B352" t="s">
         <v>1075</v>
       </c>
-      <c r="C351" t="s">
+      <c r="C352" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D352" t="s">
         <v>1076</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
-      <c r="A352" t="s">
+    <row r="353" spans="1:4">
+      <c r="A353" t="s">
         <v>468</v>
       </c>
-      <c r="B352" s="5" t="s">
+      <c r="B353" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="C352" s="2" t="s">
+      <c r="C353" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D353" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="354" spans="1:3">
-      <c r="A354" t="s">
+    <row r="355" spans="1:4">
+      <c r="A355" t="s">
         <v>687</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B355" t="s">
         <v>688</v>
       </c>
-      <c r="C354" t="s">
+      <c r="C355" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D355" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="355" spans="1:3">
-      <c r="A355" t="s">
+    <row r="356" spans="1:4">
+      <c r="A356" t="s">
         <v>689</v>
       </c>
-      <c r="B355" s="5" t="s">
+      <c r="B356" s="5" t="s">
         <v>1174</v>
       </c>
-      <c r="C355" s="2" t="s">
+      <c r="C356" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D356" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="357" spans="1:3">
-      <c r="A357" t="s">
+    <row r="358" spans="1:4">
+      <c r="A358" t="s">
         <v>694</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B358" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="358" spans="1:3">
-      <c r="A358" t="s">
+      <c r="C358" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" t="s">
         <v>696</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B359" t="s">
         <v>1194</v>
       </c>
-    </row>
-    <row r="359" spans="1:3">
-      <c r="A359" t="s">
+      <c r="C359" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" t="s">
         <v>697</v>
       </c>
-      <c r="B359" t="s">
+      <c r="B360" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="360" spans="1:3">
-      <c r="A360" t="s">
+      <c r="C360" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" t="s">
         <v>699</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B361" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="361" spans="1:3">
-      <c r="A361" t="s">
+      <c r="C361" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" t="s">
         <v>701</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B362" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="362" spans="1:3">
-      <c r="A362" t="s">
+      <c r="C362" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" t="s">
         <v>703</v>
       </c>
-      <c r="B362" t="s">
+      <c r="B363" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="363" spans="1:3">
-      <c r="A363" t="s">
+      <c r="C363" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" t="s">
         <v>705</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B364" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="364" spans="1:3">
-      <c r="A364" t="s">
+      <c r="C364" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" t="s">
         <v>707</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B365" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="365" spans="1:3">
-      <c r="A365" t="s">
+      <c r="C365" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" t="s">
         <v>709</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B366" t="s">
         <v>1101</v>
       </c>
-    </row>
-    <row r="366" spans="1:3">
-      <c r="A366" t="s">
+      <c r="C366" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" t="s">
         <v>710</v>
       </c>
-      <c r="B366" s="7" t="s">
+      <c r="B367" s="7" t="s">
         <v>1175</v>
       </c>
-      <c r="C366" s="2" t="s">
+      <c r="C367" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D367" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="367" spans="1:3">
-      <c r="A367" t="s">
+    <row r="368" spans="1:4">
+      <c r="A368" t="s">
         <v>711</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B368" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="368" spans="1:3">
-      <c r="A368" t="s">
+      <c r="C368" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" t="s">
         <v>713</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B369" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="369" spans="1:3">
-      <c r="A369" t="s">
+      <c r="C369" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" t="s">
         <v>715</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B370" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="370" spans="1:3">
-      <c r="A370" t="s">
+      <c r="C370" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" t="s">
         <v>717</v>
       </c>
-      <c r="B370" t="s">
+      <c r="B371" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="371" spans="1:3">
-      <c r="A371" t="s">
+      <c r="C371" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" t="s">
         <v>719</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B372" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="372" spans="1:3">
-      <c r="A372" t="s">
+      <c r="C372" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" t="s">
         <v>721</v>
       </c>
-      <c r="B372" t="s">
+      <c r="B373" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="373" spans="1:3">
-      <c r="A373" t="s">
+      <c r="C373" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" t="s">
         <v>1050</v>
       </c>
-      <c r="B373" t="s">
+      <c r="B374" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="374" spans="1:3">
-      <c r="A374" t="s">
+      <c r="C374" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" t="s">
         <v>723</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B375" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="375" spans="1:3">
-      <c r="A375" t="s">
+      <c r="C375" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" t="s">
         <v>1090</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B376" t="s">
         <v>1091</v>
       </c>
-    </row>
-    <row r="376" spans="1:3">
-      <c r="A376" t="s">
+      <c r="C376" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" t="s">
         <v>1073</v>
       </c>
-      <c r="B376" s="5" t="s">
+      <c r="B377" s="5" t="s">
         <v>1176</v>
       </c>
-      <c r="C376" s="2" t="s">
+      <c r="C377" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D377" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="378" spans="1:3">
-      <c r="A378" t="s">
+    <row r="379" spans="1:4">
+      <c r="A379" t="s">
         <v>725</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B379" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="379" spans="1:3">
-      <c r="A379" t="s">
+      <c r="C379" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" t="s">
         <v>727</v>
       </c>
-      <c r="B379" t="s">
+      <c r="B380" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="380" spans="1:3">
-      <c r="A380" t="s">
+      <c r="C380" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" t="s">
         <v>729</v>
       </c>
-      <c r="B380" t="s">
+      <c r="B381" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="381" spans="1:3">
-      <c r="A381" t="s">
+      <c r="C381" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" t="s">
         <v>731</v>
       </c>
-      <c r="B381" t="s">
+      <c r="B382" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="382" spans="1:3">
-      <c r="A382" t="s">
+      <c r="C382" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" t="s">
         <v>733</v>
       </c>
-      <c r="B382" t="s">
+      <c r="B383" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="383" spans="1:3">
-      <c r="A383" t="s">
+      <c r="C383" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" t="s">
         <v>735</v>
       </c>
-      <c r="B383" t="s">
+      <c r="B384" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="384" spans="1:3">
-      <c r="A384" t="s">
+      <c r="C384" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" t="s">
         <v>737</v>
       </c>
-      <c r="B384" t="s">
+      <c r="B385" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="385" spans="1:3">
-      <c r="A385" t="s">
+      <c r="C385" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" t="s">
         <v>739</v>
       </c>
-      <c r="B385" t="s">
+      <c r="B386" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="386" spans="1:3">
-      <c r="A386" t="s">
+      <c r="C386" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" t="s">
         <v>740</v>
       </c>
-      <c r="B386" t="s">
+      <c r="B387" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="387" spans="1:3">
-      <c r="A387" t="s">
+      <c r="C387" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" t="s">
         <v>742</v>
       </c>
-      <c r="B387" t="s">
+      <c r="B388" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="388" spans="1:3">
-      <c r="A388" t="s">
+      <c r="C388" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" t="s">
         <v>744</v>
       </c>
-      <c r="B388" t="s">
+      <c r="B389" t="s">
         <v>1193</v>
       </c>
-    </row>
-    <row r="389" spans="1:3">
-      <c r="A389" t="s">
+      <c r="C389" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" t="s">
         <v>745</v>
       </c>
-      <c r="B389" s="7" t="s">
+      <c r="B390" s="7" t="s">
         <v>1177</v>
       </c>
-      <c r="C389" s="2" t="s">
+      <c r="C390" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D390" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="391" spans="1:3">
-      <c r="A391" t="s">
+    <row r="392" spans="1:4">
+      <c r="A392" t="s">
         <v>746</v>
       </c>
-      <c r="B391" t="s">
+      <c r="B392" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="392" spans="1:3">
-      <c r="A392" t="s">
+      <c r="C392" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" t="s">
         <v>747</v>
       </c>
-      <c r="B392" t="s">
+      <c r="B393" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="393" spans="1:3">
-      <c r="A393" t="s">
+      <c r="C393" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" t="s">
         <v>749</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B394" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="394" spans="1:3">
-      <c r="A394" t="s">
+      <c r="C394" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" t="s">
         <v>750</v>
       </c>
-      <c r="B394" t="s">
+      <c r="B395" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="396" spans="1:3">
-      <c r="A396" t="s">
+      <c r="C395" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" t="s">
         <v>771</v>
       </c>
-      <c r="B396" t="s">
+      <c r="B397" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="397" spans="1:3">
-      <c r="A397" t="s">
+      <c r="C397" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" t="s">
         <v>770</v>
       </c>
-      <c r="B397" t="s">
+      <c r="B398" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="398" spans="1:3">
-      <c r="A398" t="s">
+      <c r="C398" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" t="s">
         <v>764</v>
       </c>
-      <c r="B398" t="s">
+      <c r="B399" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="399" spans="1:3">
-      <c r="A399" t="s">
+      <c r="C399" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" t="s">
         <v>762</v>
       </c>
-      <c r="B399" t="s">
+      <c r="B400" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="400" spans="1:3">
-      <c r="A400" t="s">
+      <c r="C400" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" t="s">
         <v>763</v>
       </c>
-      <c r="B400" t="s">
+      <c r="B401" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="401" spans="1:3">
-      <c r="A401" t="s">
+      <c r="C401" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" t="s">
         <v>768</v>
       </c>
-      <c r="B401" s="5" t="s">
+      <c r="B402" s="5" t="s">
         <v>1178</v>
       </c>
-      <c r="C401" s="2" t="s">
+      <c r="C402" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D402" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="403" spans="1:3">
-      <c r="A403" t="s">
+    <row r="404" spans="1:4">
+      <c r="A404" t="s">
         <v>775</v>
       </c>
-      <c r="B403" t="s">
+      <c r="B404" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="404" spans="1:3">
-      <c r="A404" t="s">
+      <c r="C404" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" t="s">
         <v>782</v>
       </c>
-      <c r="B404" t="s">
+      <c r="B405" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="405" spans="1:3">
-      <c r="A405" t="s">
+      <c r="C405" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" t="s">
         <v>776</v>
       </c>
-      <c r="B405" t="s">
+      <c r="B406" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="406" spans="1:3">
-      <c r="A406" t="s">
+      <c r="C406" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" t="s">
         <v>777</v>
       </c>
-      <c r="B406" t="s">
+      <c r="B407" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="407" spans="1:3">
-      <c r="A407" t="s">
+      <c r="C407" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" t="s">
         <v>778</v>
       </c>
-      <c r="B407" t="s">
+      <c r="B408" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="408" spans="1:3">
-      <c r="A408" t="s">
+      <c r="C408" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" t="s">
         <v>779</v>
       </c>
-      <c r="B408" s="5" t="s">
+      <c r="B409" s="5" t="s">
         <v>1179</v>
       </c>
-      <c r="C408" s="2" t="s">
+      <c r="C409" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D409" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="410" spans="1:3">
-      <c r="A410" t="s">
+    <row r="411" spans="1:4">
+      <c r="A411" t="s">
         <v>787</v>
       </c>
-      <c r="B410" t="s">
+      <c r="B411" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="411" spans="1:3">
-      <c r="A411" t="s">
+      <c r="C411" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" t="s">
         <v>789</v>
       </c>
-      <c r="B411" t="s">
+      <c r="B412" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="412" spans="1:3">
-      <c r="A412" t="s">
+      <c r="C412" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" t="s">
         <v>790</v>
       </c>
-      <c r="B412" s="7" t="s">
+      <c r="B413" s="7" t="s">
         <v>1161</v>
       </c>
-      <c r="C412" s="2" t="s">
+      <c r="C413" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D413" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="413" spans="1:3">
-      <c r="A413" t="s">
+    <row r="414" spans="1:4">
+      <c r="A414" t="s">
         <v>792</v>
       </c>
-      <c r="B413" t="s">
+      <c r="B414" t="s">
         <v>1030</v>
       </c>
-    </row>
-    <row r="414" spans="1:3">
-      <c r="A414" t="s">
+      <c r="C414" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" t="s">
         <v>798</v>
       </c>
-      <c r="B414" s="7" t="s">
+      <c r="B415" s="7" t="s">
         <v>1180</v>
       </c>
-      <c r="C414" s="2" t="s">
+      <c r="C415" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D415" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="415" spans="1:3">
-      <c r="A415" t="s">
+    <row r="416" spans="1:4">
+      <c r="A416" t="s">
         <v>799</v>
       </c>
-      <c r="B415" t="s">
+      <c r="B416" t="s">
         <v>1017</v>
       </c>
-    </row>
-    <row r="416" spans="1:3">
-      <c r="A416" t="s">
+      <c r="C416" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" t="s">
         <v>800</v>
       </c>
-      <c r="B416" t="s">
+      <c r="B417" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="417" spans="1:3">
-      <c r="A417" t="s">
+      <c r="C417" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" t="s">
         <v>803</v>
       </c>
-      <c r="B417" t="s">
+      <c r="B418" t="s">
         <v>1035</v>
       </c>
-    </row>
-    <row r="418" spans="1:3">
-      <c r="A418" t="s">
+      <c r="C418" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" t="s">
         <v>804</v>
       </c>
-      <c r="B418" t="s">
+      <c r="B419" t="s">
         <v>1034</v>
       </c>
-    </row>
-    <row r="419" spans="1:3">
-      <c r="A419" t="s">
+      <c r="C419" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" t="s">
         <v>805</v>
       </c>
-      <c r="B419" t="s">
+      <c r="B420" t="s">
         <v>1033</v>
       </c>
-    </row>
-    <row r="420" spans="1:3">
-      <c r="A420" t="s">
+      <c r="C420" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" t="s">
         <v>806</v>
       </c>
-      <c r="B420" t="s">
+      <c r="B421" t="s">
         <v>1032</v>
       </c>
-    </row>
-    <row r="421" spans="1:3">
-      <c r="A421" t="s">
+      <c r="C421" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" t="s">
         <v>807</v>
       </c>
-      <c r="B421" t="s">
+      <c r="B422" t="s">
         <v>1031</v>
       </c>
-    </row>
-    <row r="422" spans="1:3">
-      <c r="A422" t="s">
+      <c r="C422" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" t="s">
         <v>808</v>
       </c>
-      <c r="B422" t="s">
+      <c r="B423" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="423" spans="1:3">
-      <c r="A423" t="s">
+      <c r="C423" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" t="s">
         <v>809</v>
       </c>
-      <c r="B423" t="s">
+      <c r="B424" t="s">
         <v>1037</v>
       </c>
-    </row>
-    <row r="424" spans="1:3">
-      <c r="A424" t="s">
+      <c r="C424" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" t="s">
         <v>810</v>
       </c>
-      <c r="B424" s="7" t="s">
+      <c r="B425" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="C424" s="2" t="s">
+      <c r="C425" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D425" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="425" spans="1:3">
-      <c r="A425" t="s">
+    <row r="426" spans="1:4">
+      <c r="A426" t="s">
         <v>811</v>
       </c>
-      <c r="B425" s="7" t="s">
+      <c r="B426" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C425" s="2" t="s">
+      <c r="C426" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D426" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="426" spans="1:3">
-      <c r="A426" t="s">
+    <row r="427" spans="1:4">
+      <c r="A427" t="s">
         <v>802</v>
       </c>
-      <c r="B426" s="7" t="s">
+      <c r="B427" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="C426" s="2" t="s">
+      <c r="C427" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D427" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="427" spans="1:3">
-      <c r="A427" t="s">
+    <row r="428" spans="1:4">
+      <c r="A428" t="s">
         <v>801</v>
       </c>
-      <c r="B427" s="5" t="s">
+      <c r="B428" s="5" t="s">
         <v>1181</v>
       </c>
-      <c r="C427" s="2" t="s">
+      <c r="C428" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D428" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="428" spans="1:3">
-      <c r="A428" t="s">
+    <row r="429" spans="1:4">
+      <c r="A429" t="s">
         <v>1113</v>
       </c>
-      <c r="B428" t="s">
+      <c r="B429" t="s">
         <v>1107</v>
       </c>
-    </row>
-    <row r="429" spans="1:3">
-      <c r="A429" t="s">
+      <c r="C429" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" t="s">
         <v>1020</v>
       </c>
-      <c r="B429" t="s">
+      <c r="B430" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="430" spans="1:3">
-      <c r="A430" t="s">
+      <c r="C430" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
+      <c r="A431" t="s">
         <v>1021</v>
       </c>
-      <c r="B430" t="s">
+      <c r="B431" t="s">
         <v>1019</v>
       </c>
-    </row>
-    <row r="431" spans="1:3">
-      <c r="A431" t="s">
+      <c r="C431" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4">
+      <c r="A432" t="s">
         <v>1023</v>
       </c>
-      <c r="B431" t="s">
+      <c r="B432" t="s">
         <v>1022</v>
       </c>
-    </row>
-    <row r="432" spans="1:3">
-      <c r="A432" t="s">
+      <c r="C432" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4">
+      <c r="A433" t="s">
         <v>1027</v>
       </c>
-      <c r="B432" t="s">
+      <c r="B433" t="s">
         <v>1024</v>
       </c>
-    </row>
-    <row r="433" spans="1:3">
-      <c r="A433" t="s">
+      <c r="C433" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
+      <c r="A434" t="s">
         <v>1028</v>
       </c>
-      <c r="B433" t="s">
+      <c r="B434" t="s">
         <v>1025</v>
       </c>
-    </row>
-    <row r="434" spans="1:3">
-      <c r="A434" t="s">
+      <c r="C434" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
+      <c r="A435" t="s">
         <v>1029</v>
       </c>
-      <c r="B434" t="s">
+      <c r="B435" t="s">
         <v>1026</v>
       </c>
-    </row>
-    <row r="435" spans="1:3">
-      <c r="A435" t="s">
+      <c r="C435" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436" t="s">
         <v>1039</v>
       </c>
-      <c r="B435" t="s">
+      <c r="B436" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="436" spans="1:3">
-      <c r="A436" t="s">
+      <c r="C436" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4">
+      <c r="A437" t="s">
         <v>1040</v>
       </c>
-      <c r="B436" s="7" t="s">
+      <c r="B437" s="7" t="s">
         <v>1138</v>
       </c>
-      <c r="C436" s="2" t="s">
+      <c r="C437" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D437" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="437" spans="1:3">
-      <c r="A437" t="s">
+    <row r="438" spans="1:4">
+      <c r="A438" t="s">
         <v>1080</v>
       </c>
-      <c r="B437" t="s">
+      <c r="B438" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="439" spans="1:3">
-      <c r="A439" t="s">
+      <c r="C438" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440" t="s">
         <v>867</v>
       </c>
-      <c r="B439" t="s">
+      <c r="B440" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="440" spans="1:3">
-      <c r="A440" t="s">
+      <c r="C440" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441" t="s">
         <v>886</v>
       </c>
-      <c r="B440" t="s">
+      <c r="B441" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="441" spans="1:3">
-      <c r="A441" t="s">
+      <c r="C441" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442" t="s">
         <v>885</v>
       </c>
-      <c r="B441" t="s">
+      <c r="B442" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="442" spans="1:3">
-      <c r="A442" t="s">
+      <c r="C442" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443" t="s">
         <v>884</v>
       </c>
-      <c r="B442" t="s">
+      <c r="B443" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="443" spans="1:3">
-      <c r="A443" t="s">
+      <c r="C443" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" t="s">
         <v>883</v>
       </c>
-      <c r="B443" t="s">
+      <c r="B444" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="444" spans="1:3">
-      <c r="A444" t="s">
+      <c r="C444" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" t="s">
         <v>882</v>
       </c>
-      <c r="B444" t="s">
+      <c r="B445" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="445" spans="1:3">
-      <c r="A445" t="s">
+      <c r="C445" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" t="s">
         <v>881</v>
       </c>
-      <c r="B445" t="s">
+      <c r="B446" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="446" spans="1:3">
-      <c r="A446" t="s">
+      <c r="C446" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" t="s">
         <v>880</v>
       </c>
-      <c r="B446" t="s">
+      <c r="B447" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="447" spans="1:3">
-      <c r="A447" t="s">
+      <c r="C447" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" t="s">
         <v>879</v>
       </c>
-      <c r="B447" t="s">
+      <c r="B448" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="448" spans="1:3">
-      <c r="A448" t="s">
+      <c r="C448" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" t="s">
         <v>878</v>
       </c>
-      <c r="B448" t="s">
+      <c r="B449" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="449" spans="1:3">
-      <c r="A449" t="s">
+      <c r="C449" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" t="s">
         <v>877</v>
       </c>
-      <c r="B449" t="s">
+      <c r="B450" t="s">
         <v>858</v>
       </c>
-    </row>
-    <row r="450" spans="1:3">
-      <c r="A450" t="s">
+      <c r="C450" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" t="s">
         <v>887</v>
       </c>
-      <c r="B450" t="s">
+      <c r="B451" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="451" spans="1:3">
-      <c r="A451" t="s">
+      <c r="C451" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" t="s">
         <v>876</v>
       </c>
-      <c r="B451" t="s">
+      <c r="B452" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="452" spans="1:3">
-      <c r="A452" t="s">
+      <c r="C452" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" t="s">
         <v>875</v>
       </c>
-      <c r="B452" t="s">
+      <c r="B453" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="453" spans="1:3">
-      <c r="A453" t="s">
+      <c r="C453" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" t="s">
         <v>874</v>
       </c>
-      <c r="B453" t="s">
+      <c r="B454" t="s">
         <v>862</v>
       </c>
-    </row>
-    <row r="454" spans="1:3">
-      <c r="A454" t="s">
+      <c r="C454" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" t="s">
         <v>873</v>
       </c>
-      <c r="B454" s="7" t="s">
+      <c r="B455" s="7" t="s">
         <v>1134</v>
       </c>
-      <c r="C454" s="2" t="s">
+      <c r="C455" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D455" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="455" spans="1:3">
-      <c r="A455" t="s">
+    <row r="456" spans="1:4">
+      <c r="A456" t="s">
         <v>872</v>
       </c>
-      <c r="B455" t="s">
+      <c r="B456" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="456" spans="1:3">
-      <c r="A456" t="s">
+      <c r="C456" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" t="s">
         <v>871</v>
       </c>
-      <c r="B456" t="s">
+      <c r="B457" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="457" spans="1:3">
-      <c r="A457" t="s">
+      <c r="C457" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" t="s">
         <v>870</v>
       </c>
-      <c r="B457" t="s">
+      <c r="B458" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="458" spans="1:3">
-      <c r="A458" t="s">
+      <c r="C458" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" t="s">
         <v>869</v>
       </c>
-      <c r="B458" t="s">
+      <c r="B459" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="459" spans="1:3">
-      <c r="A459" t="s">
+      <c r="C459" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" t="s">
         <v>1084</v>
       </c>
-      <c r="B459" t="s">
+      <c r="B460" t="s">
         <v>1085</v>
       </c>
-    </row>
-    <row r="460" spans="1:3">
-      <c r="A460" t="s">
+      <c r="C460" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" t="s">
         <v>868</v>
       </c>
-      <c r="B460" s="5" t="s">
+      <c r="B461" s="5" t="s">
         <v>1182</v>
       </c>
-      <c r="C460" s="2" t="s">
+      <c r="C461" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D461" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="462" spans="1:3">
-      <c r="A462" t="s">
+    <row r="463" spans="1:4">
+      <c r="A463" t="s">
         <v>1077</v>
       </c>
-      <c r="B462" t="s">
+      <c r="B463" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="463" spans="1:3">
-      <c r="A463" t="s">
+      <c r="C463" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" t="s">
         <v>905</v>
       </c>
-      <c r="B463" t="s">
+      <c r="B464" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="464" spans="1:3">
-      <c r="A464" t="s">
+      <c r="C464" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" t="s">
         <v>896</v>
       </c>
-      <c r="B464" t="s">
+      <c r="B465" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="465" spans="1:3">
-      <c r="A465" t="s">
+      <c r="C465" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" t="s">
         <v>897</v>
       </c>
-      <c r="B465" t="s">
+      <c r="B466" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="466" spans="1:3">
-      <c r="A466" t="s">
+      <c r="C466" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" t="s">
         <v>898</v>
       </c>
-      <c r="B466" t="s">
+      <c r="B467" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="467" spans="1:3">
-      <c r="A467" t="s">
+      <c r="C467" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" t="s">
         <v>901</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B468" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="468" spans="1:3">
-      <c r="A468" t="s">
+      <c r="C468" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" t="s">
         <v>899</v>
       </c>
-      <c r="B468" t="s">
+      <c r="B469" t="s">
         <v>1103</v>
       </c>
-    </row>
-    <row r="469" spans="1:3">
-      <c r="A469" t="s">
+      <c r="C469" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" t="s">
         <v>902</v>
       </c>
-      <c r="B469" t="s">
+      <c r="B470" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="470" spans="1:3">
-      <c r="A470" t="s">
+      <c r="C470" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" t="s">
         <v>900</v>
       </c>
-      <c r="B470" t="s">
+      <c r="B471" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="471" spans="1:3">
-      <c r="A471" t="s">
+      <c r="C471" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" t="s">
         <v>904</v>
       </c>
-      <c r="B471" t="s">
+      <c r="B472" t="s">
         <v>1105</v>
       </c>
-    </row>
-    <row r="472" spans="1:3">
-      <c r="A472" t="s">
+      <c r="C472" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" t="s">
         <v>1092</v>
       </c>
-      <c r="B472" t="s">
+      <c r="B473" t="s">
         <v>1093</v>
       </c>
-    </row>
-    <row r="473" spans="1:3">
-      <c r="A473" t="s">
+      <c r="C473" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474" t="s">
         <v>903</v>
       </c>
-      <c r="B473" s="5" t="s">
+      <c r="B474" s="5" t="s">
         <v>1183</v>
       </c>
-      <c r="C473" s="2" t="s">
+      <c r="C474" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D474" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="475" spans="1:3">
-      <c r="A475" t="s">
+    <row r="476" spans="1:4">
+      <c r="A476" t="s">
         <v>910</v>
       </c>
-      <c r="B475" s="7" t="s">
+      <c r="B476" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="C475" s="2" t="s">
+      <c r="C476" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D476" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="476" spans="1:3" s="6" customFormat="1">
-      <c r="A476" s="6" t="s">
+    <row r="477" spans="1:4" s="6" customFormat="1">
+      <c r="A477" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="B476" s="6" t="s">
+      <c r="B477" s="6" t="s">
         <v>1185</v>
       </c>
-      <c r="C476" s="6" t="s">
+      <c r="C477" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D477" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="478" spans="1:3" s="6" customFormat="1">
-      <c r="A478" s="6" t="s">
+    <row r="479" spans="1:4" s="6" customFormat="1">
+      <c r="A479" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="B478" s="6" t="s">
+      <c r="B479" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="C478" s="6" t="s">
+      <c r="C479" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D479" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="479" spans="1:3">
-      <c r="A479" t="s">
+    <row r="480" spans="1:4">
+      <c r="A480" t="s">
         <v>920</v>
       </c>
-      <c r="B479" s="5" t="s">
+      <c r="B480" s="5" t="s">
         <v>1186</v>
       </c>
-      <c r="C479" s="2" t="s">
+      <c r="C480" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D480" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="481" spans="1:3">
-      <c r="A481" t="s">
+    <row r="482" spans="1:4">
+      <c r="A482" t="s">
         <v>917</v>
       </c>
-      <c r="B481" t="s">
+      <c r="B482" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="482" spans="1:3">
-      <c r="A482" t="s">
+      <c r="C482" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4">
+      <c r="A483" t="s">
         <v>918</v>
       </c>
-      <c r="B482" t="s">
+      <c r="B483" t="s">
         <v>916</v>
       </c>
-    </row>
-    <row r="483" spans="1:3">
-      <c r="A483" t="s">
+      <c r="C483" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4">
+      <c r="A484" t="s">
         <v>1109</v>
       </c>
-      <c r="B483" t="s">
+      <c r="B484" t="s">
         <v>1110</v>
       </c>
-    </row>
-    <row r="484" spans="1:3">
-      <c r="A484" t="s">
+      <c r="C484" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4">
+      <c r="A485" t="s">
         <v>914</v>
       </c>
-      <c r="B484" s="7" t="s">
+      <c r="B485" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="C484" s="2" t="s">
+      <c r="C485" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D485" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="486" spans="1:3">
-      <c r="A486" t="s">
+    <row r="487" spans="1:4">
+      <c r="A487" t="s">
         <v>927</v>
       </c>
-      <c r="B486" t="s">
+      <c r="B487" t="s">
         <v>1188</v>
       </c>
-    </row>
-    <row r="487" spans="1:3">
-      <c r="A487" t="s">
+      <c r="C487" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4">
+      <c r="A488" t="s">
         <v>928</v>
       </c>
-      <c r="B487" t="s">
+      <c r="B488" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="488" spans="1:3">
-      <c r="A488" t="s">
+      <c r="C488" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4">
+      <c r="A489" t="s">
         <v>929</v>
       </c>
-      <c r="B488" t="s">
+      <c r="B489" t="s">
         <v>923</v>
       </c>
-    </row>
-    <row r="489" spans="1:3">
-      <c r="A489" t="s">
+      <c r="C489" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4">
+      <c r="A490" t="s">
         <v>971</v>
       </c>
-      <c r="B489" t="s">
+      <c r="B490" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="490" spans="1:3">
-      <c r="A490" t="s">
+      <c r="C490" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4">
+      <c r="A491" t="s">
         <v>930</v>
       </c>
-      <c r="B490" t="s">
+      <c r="B491" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="491" spans="1:3">
-      <c r="A491" t="s">
+      <c r="C491" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4">
+      <c r="A492" t="s">
         <v>931</v>
       </c>
-      <c r="B491" t="s">
+      <c r="B492" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="492" spans="1:3">
-      <c r="A492" t="s">
+      <c r="C492" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4">
+      <c r="A493" t="s">
         <v>932</v>
       </c>
-      <c r="B492" s="7" t="s">
+      <c r="B493" s="7" t="s">
         <v>1189</v>
       </c>
-      <c r="C492" s="2" t="s">
+      <c r="C493" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D493" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="494" spans="1:3">
-      <c r="A494" t="s">
+    <row r="495" spans="1:4">
+      <c r="A495" t="s">
         <v>943</v>
       </c>
-      <c r="B494" t="s">
+      <c r="B495" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="495" spans="1:3">
-      <c r="A495" t="s">
+      <c r="C495" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4">
+      <c r="A496" t="s">
         <v>948</v>
       </c>
-      <c r="B495" t="s">
+      <c r="B496" t="s">
         <v>939</v>
       </c>
-    </row>
-    <row r="496" spans="1:3">
-      <c r="A496" t="s">
+      <c r="C496" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4">
+      <c r="A497" t="s">
         <v>944</v>
       </c>
-      <c r="B496" t="s">
+      <c r="B497" t="s">
         <v>940</v>
       </c>
-    </row>
-    <row r="497" spans="1:3">
-      <c r="A497" t="s">
+      <c r="C497" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4">
+      <c r="A498" t="s">
         <v>945</v>
       </c>
-      <c r="B497" t="s">
+      <c r="B498" t="s">
         <v>941</v>
       </c>
-    </row>
-    <row r="498" spans="1:3">
-      <c r="A498" t="s">
+      <c r="C498" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4">
+      <c r="A499" t="s">
         <v>947</v>
       </c>
-      <c r="B498" t="s">
+      <c r="B499" t="s">
         <v>942</v>
       </c>
-    </row>
-    <row r="499" spans="1:3">
-      <c r="A499" t="s">
+      <c r="C499" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4">
+      <c r="A500" t="s">
         <v>946</v>
       </c>
-      <c r="B499" s="7" t="s">
+      <c r="B500" s="7" t="s">
         <v>1139</v>
       </c>
-      <c r="C499" s="2" t="s">
+      <c r="C500" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D500" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="501" spans="1:3">
-      <c r="A501" t="s">
+    <row r="502" spans="1:4">
+      <c r="A502" t="s">
         <v>960</v>
       </c>
-      <c r="B501" t="s">
+      <c r="B502" t="s">
         <v>949</v>
       </c>
-    </row>
-    <row r="502" spans="1:3">
-      <c r="A502" t="s">
+      <c r="C502" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4">
+      <c r="A503" t="s">
         <v>955</v>
       </c>
-      <c r="B502" t="s">
+      <c r="B503" t="s">
         <v>950</v>
       </c>
-    </row>
-    <row r="503" spans="1:3">
-      <c r="A503" t="s">
+      <c r="C503" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504" t="s">
         <v>956</v>
       </c>
-      <c r="B503" t="s">
+      <c r="B504" t="s">
         <v>951</v>
       </c>
-    </row>
-    <row r="504" spans="1:3">
-      <c r="A504" t="s">
+      <c r="C504" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505" t="s">
         <v>957</v>
       </c>
-      <c r="B504" t="s">
+      <c r="B505" t="s">
         <v>952</v>
       </c>
-    </row>
-    <row r="505" spans="1:3">
-      <c r="A505" t="s">
+      <c r="C505" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506" t="s">
         <v>958</v>
       </c>
-      <c r="B505" t="s">
+      <c r="B506" t="s">
         <v>953</v>
       </c>
-    </row>
-    <row r="506" spans="1:3" s="6" customFormat="1">
-      <c r="A506" s="6" t="s">
+      <c r="C506" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" s="6" customFormat="1">
+      <c r="A507" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="B506" s="6" t="s">
+      <c r="B507" s="6" t="s">
         <v>1079</v>
       </c>
-      <c r="C506" s="6" t="s">
+      <c r="C507" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D507" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="508" spans="1:3" s="6" customFormat="1">
-      <c r="A508" s="6" t="s">
+    <row r="509" spans="1:4" s="6" customFormat="1">
+      <c r="A509" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="B508" s="6" t="s">
+      <c r="B509" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="C508" s="6" t="s">
+      <c r="C509" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D509" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="509" spans="1:3">
-      <c r="A509" t="s">
+    <row r="510" spans="1:4">
+      <c r="A510" t="s">
         <v>966</v>
       </c>
-      <c r="B509" t="s">
+      <c r="B510" t="s">
         <v>963</v>
       </c>
-    </row>
-    <row r="510" spans="1:3">
-      <c r="A510" t="s">
+      <c r="C510" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
+      <c r="A511" t="s">
         <v>967</v>
       </c>
-      <c r="B510" t="s">
+      <c r="B511" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="511" spans="1:3">
-      <c r="A511" t="s">
+      <c r="C511" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
+      <c r="A512" t="s">
         <v>968</v>
       </c>
-      <c r="B511" t="s">
+      <c r="B512" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="512" spans="1:3">
-      <c r="A512" t="s">
+      <c r="C512" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
+      <c r="A513" t="s">
         <v>969</v>
       </c>
-      <c r="B512" s="7" t="s">
+      <c r="B513" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="C512" s="2" t="s">
+      <c r="C513" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D513" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="514" spans="1:3">
-      <c r="A514" t="s">
+    <row r="515" spans="1:4">
+      <c r="A515" t="s">
         <v>990</v>
       </c>
-      <c r="B514" t="s">
+      <c r="B515" t="s">
         <v>991</v>
       </c>
-    </row>
-    <row r="515" spans="1:3">
-      <c r="A515" t="s">
+      <c r="C515" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4">
+      <c r="A516" t="s">
         <v>1005</v>
       </c>
-      <c r="B515" t="s">
+      <c r="B516" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="516" spans="1:3">
-      <c r="A516" t="s">
+      <c r="C516" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4">
+      <c r="A517" t="s">
         <v>1006</v>
       </c>
-      <c r="B516" t="s">
+      <c r="B517" t="s">
         <v>993</v>
       </c>
-    </row>
-    <row r="517" spans="1:3">
-      <c r="A517" t="s">
+      <c r="C517" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4">
+      <c r="A518" t="s">
         <v>1007</v>
       </c>
-      <c r="B517" t="s">
+      <c r="B518" t="s">
         <v>994</v>
       </c>
-    </row>
-    <row r="518" spans="1:3">
-      <c r="A518" t="s">
+      <c r="C518" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4">
+      <c r="A519" t="s">
         <v>1016</v>
       </c>
-      <c r="B518" t="s">
+      <c r="B519" t="s">
         <v>995</v>
       </c>
-    </row>
-    <row r="519" spans="1:3">
-      <c r="A519" t="s">
+      <c r="C519" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4">
+      <c r="A520" t="s">
         <v>1008</v>
       </c>
-      <c r="B519" t="s">
+      <c r="B520" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="520" spans="1:3">
-      <c r="A520" t="s">
+      <c r="C520" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4">
+      <c r="A521" t="s">
         <v>1009</v>
       </c>
-      <c r="B520" t="s">
+      <c r="B521" t="s">
         <v>997</v>
       </c>
-    </row>
-    <row r="521" spans="1:3">
-      <c r="A521" t="s">
+      <c r="C521" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4">
+      <c r="A522" t="s">
         <v>1010</v>
       </c>
-      <c r="B521" t="s">
+      <c r="B522" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="522" spans="1:3">
-      <c r="A522" t="s">
+      <c r="C522" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4">
+      <c r="A523" t="s">
         <v>1011</v>
       </c>
-      <c r="B522" t="s">
+      <c r="B523" t="s">
         <v>999</v>
       </c>
-    </row>
-    <row r="523" spans="1:3">
-      <c r="A523" t="s">
+      <c r="C523" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4">
+      <c r="A524" t="s">
         <v>1012</v>
       </c>
-      <c r="B523" t="s">
+      <c r="B524" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="524" spans="1:3">
-      <c r="A524" t="s">
+      <c r="C524" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4">
+      <c r="A525" t="s">
         <v>1013</v>
       </c>
-      <c r="B524" t="s">
+      <c r="B525" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="525" spans="1:3">
-      <c r="A525" t="s">
+      <c r="C525" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4">
+      <c r="A526" t="s">
         <v>1014</v>
       </c>
-      <c r="B525" t="s">
+      <c r="B526" t="s">
         <v>1002</v>
       </c>
-    </row>
-    <row r="526" spans="1:3">
-      <c r="A526" t="s">
+      <c r="C526" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4">
+      <c r="A527" t="s">
         <v>1015</v>
       </c>
-      <c r="B526" t="s">
+      <c r="B527" t="s">
         <v>1003</v>
       </c>
-    </row>
-    <row r="527" spans="1:3">
-      <c r="A527" t="s">
+      <c r="C527" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4">
+      <c r="A528" t="s">
         <v>1004</v>
       </c>
-      <c r="B527" s="7" t="s">
+      <c r="B528" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C527" s="2" t="s">
+      <c r="C528" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D528" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="529" spans="1:2">
-      <c r="A529" t="s">
+    <row r="530" spans="1:3">
+      <c r="A530" t="s">
         <v>1299</v>
       </c>
-      <c r="B529" t="s">
+      <c r="B530" t="s">
         <v>1209</v>
       </c>
-    </row>
-    <row r="530" spans="1:2">
-      <c r="A530" t="s">
+      <c r="C530" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3">
+      <c r="A531" t="s">
         <v>1300</v>
       </c>
-      <c r="B530" t="s">
+      <c r="B531" t="s">
         <v>1210</v>
       </c>
-    </row>
-    <row r="531" spans="1:2">
-      <c r="A531" t="s">
+      <c r="C531" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3">
+      <c r="A532" t="s">
         <v>1301</v>
       </c>
-      <c r="B531" t="s">
+      <c r="B532" t="s">
         <v>1211</v>
       </c>
-    </row>
-    <row r="532" spans="1:2">
-      <c r="A532" t="s">
+      <c r="C532" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3">
+      <c r="A533" t="s">
         <v>1302</v>
       </c>
-      <c r="B532" t="s">
+      <c r="B533" t="s">
         <v>1212</v>
       </c>
-    </row>
-    <row r="533" spans="1:2">
-      <c r="A533" t="s">
+      <c r="C533" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3">
+      <c r="A534" t="s">
         <v>1303</v>
       </c>
-      <c r="B533" t="s">
+      <c r="B534" t="s">
         <v>1213</v>
       </c>
-    </row>
-    <row r="534" spans="1:2">
-      <c r="A534" t="s">
+      <c r="C534" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3">
+      <c r="A535" t="s">
         <v>1315</v>
       </c>
-      <c r="B534" t="s">
+      <c r="B535" t="s">
         <v>1214</v>
       </c>
-    </row>
-    <row r="535" spans="1:2">
-      <c r="A535" t="s">
+      <c r="C535" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3">
+      <c r="A536" t="s">
         <v>1305</v>
       </c>
-      <c r="B535" t="s">
+      <c r="B536" t="s">
         <v>1215</v>
       </c>
-    </row>
-    <row r="536" spans="1:2">
-      <c r="A536" t="s">
+      <c r="C536" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3">
+      <c r="A537" t="s">
         <v>1304</v>
       </c>
-      <c r="B536" t="s">
+      <c r="B537" t="s">
         <v>1216</v>
       </c>
-    </row>
-    <row r="537" spans="1:2">
-      <c r="A537" t="s">
+      <c r="C537" s="10" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3">
+      <c r="A538" t="s">
         <v>1314</v>
       </c>
-      <c r="B537" t="s">
+      <c r="B538" t="s">
         <v>1217</v>
       </c>
-    </row>
-    <row r="538" spans="1:2">
-      <c r="A538" t="s">
+      <c r="C538" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3">
+      <c r="A539" t="s">
         <v>1306</v>
       </c>
-      <c r="B538" t="s">
+      <c r="B539" t="s">
         <v>1218</v>
       </c>
-    </row>
-    <row r="539" spans="1:2">
-      <c r="A539" t="s">
+      <c r="C539" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3">
+      <c r="A540" t="s">
         <v>1307</v>
       </c>
-      <c r="B539" t="s">
+      <c r="B540" t="s">
         <v>1219</v>
       </c>
-    </row>
-    <row r="540" spans="1:2">
-      <c r="A540" t="s">
+      <c r="C540" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3">
+      <c r="A541" t="s">
         <v>1317</v>
       </c>
-      <c r="B540" t="s">
+      <c r="B541" t="s">
         <v>1220</v>
       </c>
-    </row>
-    <row r="541" spans="1:2">
-      <c r="A541" t="s">
+      <c r="C541" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3">
+      <c r="A542" t="s">
         <v>1316</v>
       </c>
-      <c r="B541" t="s">
+      <c r="B542" t="s">
         <v>1221</v>
       </c>
-    </row>
-    <row r="542" spans="1:2">
-      <c r="A542" t="s">
+      <c r="C542" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3">
+      <c r="A543" t="s">
         <v>1318</v>
       </c>
-      <c r="B542" t="s">
+      <c r="B543" t="s">
         <v>1222</v>
       </c>
-    </row>
-    <row r="543" spans="1:2">
-      <c r="A543" t="s">
+      <c r="C543" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3">
+      <c r="A544" t="s">
         <v>1308</v>
       </c>
-      <c r="B543" t="s">
+      <c r="B544" t="s">
         <v>1223</v>
       </c>
-    </row>
-    <row r="544" spans="1:2">
-      <c r="A544" t="s">
+      <c r="C544" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3">
+      <c r="A545" t="s">
         <v>1319</v>
       </c>
-      <c r="B544" t="s">
+      <c r="B545" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="545" spans="1:2">
-      <c r="A545" t="s">
+      <c r="C545" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3">
+      <c r="A546" t="s">
         <v>1309</v>
       </c>
-      <c r="B545" t="s">
+      <c r="B546" t="s">
         <v>1225</v>
       </c>
-    </row>
-    <row r="546" spans="1:2">
-      <c r="A546" t="s">
+      <c r="C546" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3">
+      <c r="A547" t="s">
         <v>1320</v>
       </c>
-      <c r="B546" t="s">
+      <c r="B547" t="s">
         <v>1226</v>
       </c>
-    </row>
-    <row r="547" spans="1:2">
-      <c r="A547" t="s">
+      <c r="C547" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3">
+      <c r="A548" t="s">
         <v>1310</v>
       </c>
-      <c r="B547" t="s">
+      <c r="B548" t="s">
         <v>1227</v>
       </c>
-    </row>
-    <row r="548" spans="1:2">
-      <c r="A548" t="s">
+      <c r="C548" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3">
+      <c r="A549" t="s">
         <v>1321</v>
       </c>
-      <c r="B548" t="s">
+      <c r="B549" t="s">
         <v>1228</v>
       </c>
-    </row>
-    <row r="549" spans="1:2">
-      <c r="A549" t="s">
+      <c r="C549" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3">
+      <c r="A550" t="s">
         <v>1311</v>
       </c>
-      <c r="B549" t="s">
+      <c r="B550" t="s">
         <v>1229</v>
       </c>
-    </row>
-    <row r="550" spans="1:2">
-      <c r="A550" t="s">
+      <c r="C550" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3">
+      <c r="A551" t="s">
         <v>1322</v>
       </c>
-      <c r="B550" t="s">
+      <c r="B551" t="s">
         <v>1230</v>
       </c>
-    </row>
-    <row r="551" spans="1:2">
-      <c r="A551" t="s">
+      <c r="C551" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3">
+      <c r="A552" t="s">
         <v>1312</v>
       </c>
-      <c r="B551" t="s">
+      <c r="B552" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="552" spans="1:2">
-      <c r="A552" t="s">
+      <c r="C552" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3">
+      <c r="A553" t="s">
         <v>1323</v>
       </c>
-      <c r="B552" t="s">
+      <c r="B553" t="s">
         <v>1232</v>
       </c>
-    </row>
-    <row r="553" spans="1:2">
-      <c r="A553" t="s">
+      <c r="C553" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3">
+      <c r="A554" t="s">
         <v>1325</v>
       </c>
-      <c r="B553" t="s">
+      <c r="B554" t="s">
         <v>1233</v>
       </c>
-    </row>
-    <row r="554" spans="1:2">
-      <c r="A554" t="s">
+      <c r="C554" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3">
+      <c r="A555" t="s">
         <v>1313</v>
       </c>
-      <c r="B554" t="s">
+      <c r="B555" t="s">
         <v>1234</v>
       </c>
-    </row>
-    <row r="555" spans="1:2">
-      <c r="A555" t="s">
+      <c r="C555" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3">
+      <c r="A556" t="s">
         <v>1324</v>
       </c>
-      <c r="B555" t="s">
+      <c r="B556" t="s">
         <v>1235</v>
       </c>
-    </row>
-    <row r="556" spans="1:2">
-      <c r="A556" t="s">
+      <c r="C556" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3">
+      <c r="A557" t="s">
         <v>1326</v>
       </c>
-      <c r="B556" t="s">
+      <c r="B557" t="s">
         <v>1236</v>
       </c>
-    </row>
-    <row r="557" spans="1:2">
-      <c r="A557" t="s">
+      <c r="C557" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3">
+      <c r="A558" t="s">
         <v>1327</v>
       </c>
-      <c r="B557" t="s">
+      <c r="B558" t="s">
         <v>1237</v>
       </c>
-    </row>
-    <row r="558" spans="1:2">
-      <c r="A558" t="s">
+      <c r="C558" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3">
+      <c r="A559" t="s">
         <v>1332</v>
       </c>
-      <c r="B558" t="s">
+      <c r="B559" t="s">
         <v>1238</v>
       </c>
-    </row>
-    <row r="559" spans="1:2">
-      <c r="A559" t="s">
+      <c r="C559" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3">
+      <c r="A560" t="s">
         <v>1333</v>
       </c>
-      <c r="B559" t="s">
+      <c r="B560" t="s">
         <v>1239</v>
       </c>
-    </row>
-    <row r="560" spans="1:2">
-      <c r="A560" t="s">
+      <c r="C560" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3">
+      <c r="A561" t="s">
         <v>1334</v>
       </c>
-      <c r="B560" t="s">
+      <c r="B561" t="s">
         <v>1240</v>
       </c>
-    </row>
-    <row r="561" spans="1:2">
-      <c r="A561" t="s">
+      <c r="C561" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3">
+      <c r="A562" t="s">
         <v>1335</v>
       </c>
-      <c r="B561" t="s">
+      <c r="B562" t="s">
         <v>1241</v>
       </c>
-    </row>
-    <row r="562" spans="1:2">
-      <c r="A562" t="s">
+      <c r="C562" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3">
+      <c r="A563" t="s">
         <v>1336</v>
       </c>
-      <c r="B562" t="s">
+      <c r="B563" t="s">
         <v>1242</v>
       </c>
-    </row>
-    <row r="563" spans="1:2">
-      <c r="A563" t="s">
+      <c r="C563" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3">
+      <c r="A564" t="s">
         <v>1337</v>
       </c>
-      <c r="B563" t="s">
+      <c r="B564" t="s">
         <v>1243</v>
       </c>
-    </row>
-    <row r="564" spans="1:2">
-      <c r="A564" t="s">
+      <c r="C564" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3">
+      <c r="A565" t="s">
         <v>1338</v>
       </c>
-      <c r="B564" t="s">
+      <c r="B565" t="s">
         <v>1244</v>
       </c>
-    </row>
-    <row r="565" spans="1:2">
-      <c r="A565" t="s">
+      <c r="C565" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3">
+      <c r="A566" t="s">
         <v>1339</v>
       </c>
-      <c r="B565" t="s">
+      <c r="B566" t="s">
         <v>1245</v>
       </c>
-    </row>
-    <row r="566" spans="1:2">
-      <c r="A566" t="s">
+      <c r="C566" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3">
+      <c r="A567" t="s">
         <v>1340</v>
       </c>
-      <c r="B566" t="s">
+      <c r="B567" t="s">
         <v>1246</v>
       </c>
-    </row>
-    <row r="567" spans="1:2">
-      <c r="A567" t="s">
+      <c r="C567" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3">
+      <c r="A568" t="s">
         <v>1341</v>
       </c>
-      <c r="B567" t="s">
+      <c r="B568" t="s">
         <v>1247</v>
       </c>
-    </row>
-    <row r="568" spans="1:2">
-      <c r="A568" t="s">
+      <c r="C568" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3">
+      <c r="A569" t="s">
         <v>1331</v>
       </c>
-      <c r="B568" t="s">
+      <c r="B569" t="s">
         <v>1248</v>
       </c>
-    </row>
-    <row r="569" spans="1:2">
-      <c r="A569" t="s">
+      <c r="C569" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3">
+      <c r="A570" t="s">
         <v>1330</v>
       </c>
-      <c r="B569" t="s">
+      <c r="B570" t="s">
         <v>1249</v>
       </c>
-    </row>
-    <row r="570" spans="1:2">
-      <c r="A570" t="s">
+      <c r="C570" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3">
+      <c r="A571" t="s">
         <v>1329</v>
       </c>
-      <c r="B570" t="s">
+      <c r="B571" t="s">
         <v>1250</v>
       </c>
-    </row>
-    <row r="571" spans="1:2">
-      <c r="A571" t="s">
+      <c r="C571" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3">
+      <c r="A572" t="s">
         <v>1328</v>
       </c>
-      <c r="B571" t="s">
+      <c r="B572" t="s">
         <v>1251</v>
       </c>
-    </row>
-    <row r="572" spans="1:2">
-      <c r="A572" t="s">
+      <c r="C572" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3">
+      <c r="A573" t="s">
         <v>1342</v>
       </c>
-      <c r="B572" t="s">
+      <c r="B573" t="s">
         <v>1252</v>
       </c>
-    </row>
-    <row r="573" spans="1:2">
-      <c r="A573" t="s">
+      <c r="C573" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3">
+      <c r="A574" t="s">
         <v>1343</v>
       </c>
-      <c r="B573" t="s">
+      <c r="B574" t="s">
         <v>1253</v>
       </c>
-    </row>
-    <row r="574" spans="1:2">
-      <c r="A574" t="s">
+      <c r="C574" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3">
+      <c r="A575" t="s">
         <v>1344</v>
       </c>
-      <c r="B574" t="s">
+      <c r="B575" t="s">
         <v>1254</v>
       </c>
-    </row>
-    <row r="575" spans="1:2">
-      <c r="A575" t="s">
+      <c r="C575" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3">
+      <c r="A576" t="s">
         <v>1356</v>
       </c>
-      <c r="B575" t="s">
+      <c r="B576" t="s">
         <v>1255</v>
       </c>
-    </row>
-    <row r="576" spans="1:2">
-      <c r="A576" t="s">
+      <c r="C576" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3">
+      <c r="A577" t="s">
         <v>1357</v>
       </c>
-      <c r="B576" t="s">
+      <c r="B577" t="s">
         <v>1256</v>
       </c>
-    </row>
-    <row r="577" spans="1:2">
-      <c r="A577" t="s">
+      <c r="C577" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3">
+      <c r="A578" t="s">
         <v>1358</v>
       </c>
-      <c r="B577" t="s">
+      <c r="B578" t="s">
         <v>1257</v>
       </c>
-    </row>
-    <row r="578" spans="1:2">
-      <c r="A578" t="s">
+      <c r="C578" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3">
+      <c r="A579" t="s">
         <v>1359</v>
       </c>
-      <c r="B578" t="s">
+      <c r="B579" t="s">
         <v>1258</v>
       </c>
-    </row>
-    <row r="579" spans="1:2">
-      <c r="A579" t="s">
+      <c r="C579" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3">
+      <c r="A580" t="s">
         <v>1360</v>
       </c>
-      <c r="B579" t="s">
+      <c r="B580" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="580" spans="1:2">
-      <c r="A580" t="s">
+      <c r="C580" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3">
+      <c r="A581" t="s">
         <v>1361</v>
       </c>
-      <c r="B580" t="s">
+      <c r="B581" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="581" spans="1:2">
-      <c r="A581" t="s">
+      <c r="C581" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3">
+      <c r="A582" t="s">
         <v>1362</v>
       </c>
-      <c r="B581" t="s">
+      <c r="B582" t="s">
         <v>1261</v>
       </c>
-    </row>
-    <row r="582" spans="1:2">
-      <c r="A582" t="s">
+      <c r="C582" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3">
+      <c r="A583" t="s">
         <v>1363</v>
       </c>
-      <c r="B582" t="s">
+      <c r="B583" t="s">
         <v>1262</v>
       </c>
-    </row>
-    <row r="583" spans="1:2">
-      <c r="A583" t="s">
+      <c r="C583" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3">
+      <c r="A584" t="s">
         <v>1365</v>
       </c>
-      <c r="B583" t="s">
+      <c r="B584" t="s">
         <v>1263</v>
       </c>
-    </row>
-    <row r="584" spans="1:2">
-      <c r="A584" t="s">
+      <c r="C584" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3">
+      <c r="A585" t="s">
         <v>1364</v>
       </c>
-      <c r="B584" t="s">
+      <c r="B585" t="s">
         <v>1264</v>
       </c>
-    </row>
-    <row r="585" spans="1:2">
-      <c r="A585" t="s">
+      <c r="C585" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3">
+      <c r="A586" t="s">
         <v>1366</v>
       </c>
-      <c r="B585" t="s">
+      <c r="B586" t="s">
         <v>1265</v>
       </c>
-    </row>
-    <row r="586" spans="1:2">
-      <c r="A586" t="s">
+      <c r="C586" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3">
+      <c r="A587" t="s">
         <v>1367</v>
       </c>
-      <c r="B586" t="s">
+      <c r="B587" t="s">
         <v>1266</v>
       </c>
-    </row>
-    <row r="587" spans="1:2">
-      <c r="A587" t="s">
+      <c r="C587" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3">
+      <c r="A588" t="s">
         <v>1368</v>
       </c>
-      <c r="B587" t="s">
+      <c r="B588" t="s">
         <v>1267</v>
       </c>
-    </row>
-    <row r="588" spans="1:2">
-      <c r="A588" t="s">
+      <c r="C588" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3">
+      <c r="A589" t="s">
         <v>1369</v>
       </c>
-      <c r="B588" t="s">
+      <c r="B589" t="s">
         <v>1268</v>
       </c>
-    </row>
-    <row r="589" spans="1:2">
-      <c r="A589" t="s">
+      <c r="C589" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3">
+      <c r="A590" t="s">
         <v>1370</v>
       </c>
-      <c r="B589" t="s">
+      <c r="B590" t="s">
         <v>1269</v>
       </c>
-    </row>
-    <row r="590" spans="1:2">
-      <c r="A590" t="s">
+      <c r="C590" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3">
+      <c r="A591" t="s">
         <v>1371</v>
       </c>
-      <c r="B590" t="s">
+      <c r="B591" t="s">
         <v>1270</v>
       </c>
-    </row>
-    <row r="591" spans="1:2">
-      <c r="A591" t="s">
+      <c r="C591" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3">
+      <c r="A592" t="s">
         <v>1372</v>
       </c>
-      <c r="B591" t="s">
+      <c r="B592" t="s">
         <v>1271</v>
       </c>
-    </row>
-    <row r="592" spans="1:2">
-      <c r="A592" t="s">
+      <c r="C592" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3">
+      <c r="A593" t="s">
         <v>1373</v>
       </c>
-      <c r="B592" t="s">
+      <c r="B593" t="s">
         <v>1272</v>
       </c>
-    </row>
-    <row r="593" spans="1:2">
-      <c r="A593" t="s">
+      <c r="C593" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3">
+      <c r="A594" t="s">
         <v>1345</v>
       </c>
-      <c r="B593" t="s">
+      <c r="B594" t="s">
         <v>1273</v>
       </c>
-    </row>
-    <row r="594" spans="1:2">
-      <c r="A594" t="s">
+      <c r="C594" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3">
+      <c r="A595" t="s">
         <v>1353</v>
       </c>
-      <c r="B594" t="s">
+      <c r="B595" t="s">
         <v>1274</v>
       </c>
-    </row>
-    <row r="595" spans="1:2">
-      <c r="A595" t="s">
+      <c r="C595" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3">
+      <c r="A596" t="s">
         <v>1346</v>
       </c>
-      <c r="B595" t="s">
+      <c r="B596" t="s">
         <v>1275</v>
       </c>
-    </row>
-    <row r="596" spans="1:2">
-      <c r="A596" t="s">
+      <c r="C596" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3">
+      <c r="A597" t="s">
         <v>1354</v>
       </c>
-      <c r="B596" t="s">
+      <c r="B597" t="s">
         <v>1276</v>
       </c>
-    </row>
-    <row r="597" spans="1:2">
-      <c r="A597" t="s">
+      <c r="C597" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3">
+      <c r="A598" t="s">
         <v>1347</v>
       </c>
-      <c r="B597" t="s">
+      <c r="B598" t="s">
         <v>1277</v>
       </c>
-    </row>
-    <row r="598" spans="1:2">
-      <c r="A598" t="s">
+      <c r="C598" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3">
+      <c r="A599" t="s">
         <v>1374</v>
       </c>
-      <c r="B598" t="s">
+      <c r="B599" t="s">
         <v>1278</v>
       </c>
-    </row>
-    <row r="599" spans="1:2">
-      <c r="A599" t="s">
+      <c r="C599" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3">
+      <c r="A600" t="s">
         <v>1348</v>
       </c>
-      <c r="B599" t="s">
+      <c r="B600" t="s">
         <v>1279</v>
       </c>
-    </row>
-    <row r="600" spans="1:2">
-      <c r="A600" t="s">
+      <c r="C600" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3">
+      <c r="A601" t="s">
         <v>1377</v>
       </c>
-      <c r="B600" t="s">
+      <c r="B601" t="s">
         <v>1280</v>
       </c>
-    </row>
-    <row r="601" spans="1:2">
-      <c r="A601" t="s">
+      <c r="C601" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3">
+      <c r="A602" t="s">
         <v>1349</v>
       </c>
-      <c r="B601" t="s">
+      <c r="B602" t="s">
         <v>1281</v>
       </c>
-    </row>
-    <row r="602" spans="1:2">
-      <c r="A602" t="s">
+      <c r="C602" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3">
+      <c r="A603" t="s">
         <v>1355</v>
       </c>
-      <c r="B602" t="s">
+      <c r="B603" t="s">
         <v>1282</v>
       </c>
-    </row>
-    <row r="603" spans="1:2">
-      <c r="A603" t="s">
+      <c r="C603" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3">
+      <c r="A604" t="s">
         <v>1350</v>
       </c>
-      <c r="B603" t="s">
+      <c r="B604" t="s">
         <v>1283</v>
       </c>
-    </row>
-    <row r="604" spans="1:2">
-      <c r="A604" t="s">
+      <c r="C604" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3">
+      <c r="A605" t="s">
         <v>1378</v>
       </c>
-      <c r="B604" t="s">
+      <c r="B605" t="s">
         <v>1284</v>
       </c>
-    </row>
-    <row r="605" spans="1:2">
-      <c r="A605" t="s">
+      <c r="C605" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3">
+      <c r="A606" t="s">
         <v>1351</v>
       </c>
-      <c r="B605" t="s">
+      <c r="B606" t="s">
         <v>1285</v>
       </c>
-    </row>
-    <row r="606" spans="1:2">
-      <c r="A606" t="s">
+      <c r="C606" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3">
+      <c r="A607" t="s">
         <v>1379</v>
       </c>
-      <c r="B606" t="s">
+      <c r="B607" t="s">
         <v>1286</v>
       </c>
-    </row>
-    <row r="607" spans="1:2">
-      <c r="A607" t="s">
+      <c r="C607" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3">
+      <c r="A608" t="s">
         <v>1380</v>
       </c>
-      <c r="B607" t="s">
+      <c r="B608" t="s">
         <v>1287</v>
       </c>
-    </row>
-    <row r="608" spans="1:2">
-      <c r="A608" t="s">
+      <c r="C608" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3">
+      <c r="A609" t="s">
         <v>1352</v>
       </c>
-      <c r="B608" t="s">
+      <c r="B609" t="s">
         <v>1288</v>
       </c>
-    </row>
-    <row r="609" spans="1:2">
-      <c r="A609" t="s">
+      <c r="C609" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3">
+      <c r="A610" t="s">
         <v>1381</v>
       </c>
-      <c r="B609" t="s">
+      <c r="B610" t="s">
         <v>1289</v>
       </c>
-    </row>
-    <row r="610" spans="1:2">
-      <c r="A610" t="s">
+      <c r="C610" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3">
+      <c r="A611" t="s">
         <v>1375</v>
       </c>
-      <c r="B610" t="s">
+      <c r="B611" t="s">
         <v>1290</v>
       </c>
-    </row>
-    <row r="611" spans="1:2">
-      <c r="A611" t="s">
+      <c r="C611" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3">
+      <c r="A612" t="s">
         <v>1376</v>
       </c>
-      <c r="B611" t="s">
+      <c r="B612" t="s">
         <v>1291</v>
       </c>
-    </row>
-    <row r="612" spans="1:2">
-      <c r="A612" t="s">
+      <c r="C612" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3">
+      <c r="A613" t="s">
         <v>1382</v>
       </c>
-      <c r="B612" t="s">
+      <c r="B613" t="s">
         <v>1292</v>
       </c>
-    </row>
-    <row r="613" spans="1:2">
-      <c r="A613" t="s">
+      <c r="C613" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3">
+      <c r="A614" t="s">
         <v>1383</v>
       </c>
-      <c r="B613" t="s">
+      <c r="B614" t="s">
         <v>1293</v>
       </c>
-    </row>
-    <row r="614" spans="1:2">
-      <c r="A614" t="s">
+      <c r="C614" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3">
+      <c r="A615" t="s">
         <v>1384</v>
       </c>
-      <c r="B614" t="s">
+      <c r="B615" t="s">
         <v>1294</v>
       </c>
-    </row>
-    <row r="615" spans="1:2">
-      <c r="A615" t="s">
+      <c r="C615" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3">
+      <c r="A616" t="s">
         <v>1385</v>
       </c>
-      <c r="B615" t="s">
+      <c r="B616" t="s">
         <v>1295</v>
       </c>
-    </row>
-    <row r="616" spans="1:2">
-      <c r="A616" t="s">
+      <c r="C616" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3">
+      <c r="A617" t="s">
         <v>1386</v>
       </c>
-      <c r="B616" t="s">
+      <c r="B617" t="s">
         <v>1296</v>
       </c>
-    </row>
-    <row r="617" spans="1:2">
-      <c r="A617" t="s">
+      <c r="C617" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3">
+      <c r="A618" t="s">
         <v>1387</v>
       </c>
-      <c r="B617" t="s">
+      <c r="B618" t="s">
         <v>1297</v>
       </c>
-    </row>
-    <row r="618" spans="1:2">
-      <c r="A618" t="s">
+      <c r="C618" s="10" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3">
+      <c r="A619" t="s">
         <v>1388</v>
       </c>
-      <c r="B618" t="s">
+      <c r="B619" t="s">
         <v>1298</v>
       </c>
+      <c r="C619" s="10" t="s">
+        <v>1400</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C527" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
-  <conditionalFormatting sqref="A481:A483 A478:A479 A463:A473 A475:A476">
+  <autoFilter ref="A1:D528" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
+  <conditionalFormatting sqref="A482:A484 A479:A480 A464:A474 A476:A477">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1028\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69E4BD3-BEF7-491E-BC4C-C563923EDDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5571271E-9C6D-4B6F-A536-0A645DE5B364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28350" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -4233,9 +4233,6 @@
     <t>Updated by Harman</t>
   </si>
   <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>ICW_StudentFinding</t>
   </si>
   <si>
@@ -4249,6 +4246,9 @@
   </si>
   <si>
     <t>FYI Finding</t>
+  </si>
+  <si>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4324,7 +4324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4339,7 +4339,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4747,7 +4746,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -9356,7 +9355,7 @@
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="167.85546875" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" customWidth="1"/>
     <col min="4" max="4" width="60.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9368,7 +9367,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -9378,8 +9377,8 @@
       <c r="B3" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>1400</v>
+      <c r="C3" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -9389,8 +9388,8 @@
       <c r="B5" t="s">
         <v>1056</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>1400</v>
+      <c r="C5" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -9400,8 +9399,8 @@
       <c r="B6" t="s">
         <v>1392</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>1400</v>
+      <c r="C6" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -9411,8 +9410,8 @@
       <c r="B8" t="s">
         <v>646</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>1400</v>
+      <c r="C8" t="s">
+        <v>1399</v>
       </c>
       <c r="D8" t="s">
         <v>585</v>
@@ -9425,8 +9424,8 @@
       <c r="B9" t="s">
         <v>647</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>1400</v>
+      <c r="C9" t="s">
+        <v>1399</v>
       </c>
       <c r="D9" t="s">
         <v>585</v>
@@ -9439,8 +9438,8 @@
       <c r="B10" t="s">
         <v>648</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>1400</v>
+      <c r="C10" t="s">
+        <v>1399</v>
       </c>
       <c r="D10" t="s">
         <v>585</v>
@@ -9453,8 +9452,8 @@
       <c r="B11" t="s">
         <v>650</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>1400</v>
+      <c r="C11" t="s">
+        <v>1399</v>
       </c>
       <c r="D11" t="s">
         <v>585</v>
@@ -9467,8 +9466,8 @@
       <c r="B12" t="s">
         <v>649</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>1400</v>
+      <c r="C12" t="s">
+        <v>1399</v>
       </c>
       <c r="D12" t="s">
         <v>585</v>
@@ -9481,8 +9480,8 @@
       <c r="B13" t="s">
         <v>676</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>1400</v>
+      <c r="C13" t="s">
+        <v>1399</v>
       </c>
       <c r="D13" t="s">
         <v>585</v>
@@ -9495,8 +9494,8 @@
       <c r="B14" s="7" t="s">
         <v>1140</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>1400</v>
+      <c r="C14" t="s">
+        <v>1399</v>
       </c>
       <c r="D14" t="s">
         <v>1127</v>
@@ -9509,8 +9508,8 @@
       <c r="B16" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>1400</v>
+      <c r="C16" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -9520,8 +9519,8 @@
       <c r="B17" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>1400</v>
+      <c r="C17" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -9531,8 +9530,8 @@
       <c r="B18" t="s">
         <v>172</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>1400</v>
+      <c r="C18" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -9542,8 +9541,8 @@
       <c r="B19" t="s">
         <v>1100</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>1400</v>
+      <c r="C19" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -9553,8 +9552,8 @@
       <c r="B20" t="s">
         <v>198</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>1400</v>
+      <c r="C20" t="s">
+        <v>1399</v>
       </c>
       <c r="D20" t="s">
         <v>578</v>
@@ -9567,8 +9566,8 @@
       <c r="B21" t="s">
         <v>490</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>1400</v>
+      <c r="C21" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -9578,8 +9577,8 @@
       <c r="B22" s="5" t="s">
         <v>1126</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>1400</v>
+      <c r="C22" t="s">
+        <v>1399</v>
       </c>
       <c r="D22" t="s">
         <v>1127</v>
@@ -9592,8 +9591,8 @@
       <c r="B23" s="5" t="s">
         <v>1141</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>1400</v>
+      <c r="C23" t="s">
+        <v>1399</v>
       </c>
       <c r="D23" t="s">
         <v>1127</v>
@@ -9606,8 +9605,8 @@
       <c r="B24" t="s">
         <v>602</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>1400</v>
+      <c r="C24" t="s">
+        <v>1399</v>
       </c>
       <c r="D24" t="s">
         <v>585</v>
@@ -9620,8 +9619,8 @@
       <c r="B25" s="5" t="s">
         <v>1142</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>1400</v>
+      <c r="C25" t="s">
+        <v>1399</v>
       </c>
       <c r="D25" t="s">
         <v>1127</v>
@@ -9634,8 +9633,8 @@
       <c r="B26" s="5" t="s">
         <v>1143</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>1400</v>
+      <c r="C26" t="s">
+        <v>1399</v>
       </c>
       <c r="D26" t="s">
         <v>1127</v>
@@ -9648,8 +9647,8 @@
       <c r="B27" s="5" t="s">
         <v>1128</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>1400</v>
+      <c r="C27" t="s">
+        <v>1399</v>
       </c>
       <c r="D27" t="s">
         <v>1127</v>
@@ -9662,8 +9661,8 @@
       <c r="B28" s="5" t="s">
         <v>1144</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>1400</v>
+      <c r="C28" t="s">
+        <v>1399</v>
       </c>
       <c r="D28" t="s">
         <v>1127</v>
@@ -9676,8 +9675,8 @@
       <c r="B29" s="5" t="s">
         <v>1394</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>1400</v>
+      <c r="C29" t="s">
+        <v>1399</v>
       </c>
       <c r="D29" t="s">
         <v>1395</v>
@@ -9685,13 +9684,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>1397</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>1398</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>1400</v>
+      <c r="C30" t="s">
+        <v>1399</v>
       </c>
       <c r="D30" t="s">
         <v>585</v>
@@ -9704,8 +9703,8 @@
       <c r="B31" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>1400</v>
+      <c r="C31" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -9715,8 +9714,8 @@
       <c r="B33" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>1400</v>
+      <c r="C33" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -9726,8 +9725,8 @@
       <c r="B34" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>1400</v>
+      <c r="C34" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -9737,8 +9736,8 @@
       <c r="B35" t="s">
         <v>498</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>1400</v>
+      <c r="C35" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -9748,8 +9747,8 @@
       <c r="B36" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>1400</v>
+      <c r="C36" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -9759,8 +9758,8 @@
       <c r="B37" t="s">
         <v>1094</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>1400</v>
+      <c r="C37" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -9770,8 +9769,8 @@
       <c r="B38" t="s">
         <v>672</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>1400</v>
+      <c r="C38" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -9781,8 +9780,8 @@
       <c r="B39" t="s">
         <v>673</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>1400</v>
+      <c r="C39" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -9792,8 +9791,8 @@
       <c r="B40" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>1400</v>
+      <c r="C40" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -9803,8 +9802,8 @@
       <c r="B41" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>1400</v>
+      <c r="C41" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -9814,8 +9813,8 @@
       <c r="B42" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>1400</v>
+      <c r="C42" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -9825,8 +9824,8 @@
       <c r="B43" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>1400</v>
+      <c r="C43" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -9836,8 +9835,8 @@
       <c r="B44" t="s">
         <v>556</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>1400</v>
+      <c r="C44" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -9847,8 +9846,8 @@
       <c r="B45" t="s">
         <v>680</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>1400</v>
+      <c r="C45" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -9858,8 +9857,8 @@
       <c r="B46" t="s">
         <v>604</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>1400</v>
+      <c r="C46" t="s">
+        <v>1399</v>
       </c>
       <c r="D46" t="s">
         <v>585</v>
@@ -9872,8 +9871,8 @@
       <c r="B47" t="s">
         <v>678</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>1400</v>
+      <c r="C47" t="s">
+        <v>1399</v>
       </c>
       <c r="D47" t="s">
         <v>585</v>
@@ -9886,8 +9885,8 @@
       <c r="B48" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>1400</v>
+      <c r="C48" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -9897,8 +9896,8 @@
       <c r="B50" t="s">
         <v>179</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>1400</v>
+      <c r="C50" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -9908,8 +9907,8 @@
       <c r="B51" t="s">
         <v>1099</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>1400</v>
+      <c r="C51" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -9919,8 +9918,8 @@
       <c r="B52" t="s">
         <v>89</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>1400</v>
+      <c r="C52" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -9930,8 +9929,8 @@
       <c r="B53" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>1400</v>
+      <c r="C53" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -9941,8 +9940,8 @@
       <c r="B54" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>1400</v>
+      <c r="C54" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -9952,8 +9951,8 @@
       <c r="B55" t="s">
         <v>92</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>1400</v>
+      <c r="C55" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -9963,8 +9962,8 @@
       <c r="B56" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>1400</v>
+      <c r="C56" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -9974,8 +9973,8 @@
       <c r="B57" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>1400</v>
+      <c r="C57" t="s">
+        <v>1399</v>
       </c>
       <c r="D57" t="s">
         <v>522</v>
@@ -9988,8 +9987,8 @@
       <c r="B58" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>1400</v>
+      <c r="C58" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -9999,8 +9998,8 @@
       <c r="B59" t="s">
         <v>558</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>1400</v>
+      <c r="C59" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -10010,8 +10009,8 @@
       <c r="B60" t="s">
         <v>668</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>1400</v>
+      <c r="C60" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -10021,8 +10020,8 @@
       <c r="B61" t="s">
         <v>983</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>1400</v>
+      <c r="C61" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -10032,8 +10031,8 @@
       <c r="B62" s="5" t="s">
         <v>1147</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>1400</v>
+      <c r="C62" t="s">
+        <v>1399</v>
       </c>
       <c r="D62" t="s">
         <v>1127</v>
@@ -10046,8 +10045,8 @@
       <c r="B63" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>1400</v>
+      <c r="C63" t="s">
+        <v>1399</v>
       </c>
       <c r="D63" t="s">
         <v>1127</v>
@@ -10060,8 +10059,8 @@
       <c r="B65" t="s">
         <v>525</v>
       </c>
-      <c r="C65" s="10" t="s">
-        <v>1400</v>
+      <c r="C65" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -10071,8 +10070,8 @@
       <c r="B66" t="s">
         <v>103</v>
       </c>
-      <c r="C66" s="10" t="s">
-        <v>1400</v>
+      <c r="C66" t="s">
+        <v>1399</v>
       </c>
       <c r="D66" t="s">
         <v>522</v>
@@ -10085,8 +10084,8 @@
       <c r="B67" t="s">
         <v>112</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>1400</v>
+      <c r="C67" t="s">
+        <v>1399</v>
       </c>
       <c r="D67" t="s">
         <v>522</v>
@@ -10099,8 +10098,8 @@
       <c r="B68" t="s">
         <v>114</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>1400</v>
+      <c r="C68" t="s">
+        <v>1399</v>
       </c>
       <c r="D68" t="s">
         <v>522</v>
@@ -10113,8 +10112,8 @@
       <c r="B69" t="s">
         <v>104</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>1400</v>
+      <c r="C69" t="s">
+        <v>1399</v>
       </c>
       <c r="D69" t="s">
         <v>522</v>
@@ -10127,8 +10126,8 @@
       <c r="B70" t="s">
         <v>105</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>1400</v>
+      <c r="C70" t="s">
+        <v>1399</v>
       </c>
       <c r="D70" t="s">
         <v>522</v>
@@ -10141,8 +10140,8 @@
       <c r="B71" t="s">
         <v>106</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>1400</v>
+      <c r="C71" t="s">
+        <v>1399</v>
       </c>
       <c r="D71" t="s">
         <v>522</v>
@@ -10155,8 +10154,8 @@
       <c r="B72" t="s">
         <v>1095</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>1400</v>
+      <c r="C72" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -10166,8 +10165,8 @@
       <c r="B73" t="s">
         <v>1096</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>1400</v>
+      <c r="C73" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -10177,8 +10176,8 @@
       <c r="B74" t="s">
         <v>669</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>1400</v>
+      <c r="C74" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -10188,8 +10187,8 @@
       <c r="B75" t="s">
         <v>670</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>1400</v>
+      <c r="C75" t="s">
+        <v>1399</v>
       </c>
       <c r="D75" t="s">
         <v>522</v>
@@ -10202,8 +10201,8 @@
       <c r="B76" t="s">
         <v>671</v>
       </c>
-      <c r="C76" s="10" t="s">
-        <v>1400</v>
+      <c r="C76" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -10213,8 +10212,8 @@
       <c r="B77" t="s">
         <v>488</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>1400</v>
+      <c r="C77" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -10224,8 +10223,8 @@
       <c r="B78" t="s">
         <v>629</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>1400</v>
+      <c r="C78" t="s">
+        <v>1399</v>
       </c>
       <c r="D78" t="s">
         <v>585</v>
@@ -10238,8 +10237,8 @@
       <c r="B79" t="s">
         <v>1087</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>1400</v>
+      <c r="C79" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -10249,8 +10248,8 @@
       <c r="B80" t="s">
         <v>1088</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>1400</v>
+      <c r="C80" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -10260,8 +10259,8 @@
       <c r="B81" t="s">
         <v>1098</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>1400</v>
+      <c r="C81" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -10271,8 +10270,8 @@
       <c r="B82" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>1400</v>
+      <c r="C82" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -10282,8 +10281,8 @@
       <c r="B84" t="s">
         <v>115</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>1400</v>
+      <c r="C84" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -10293,8 +10292,8 @@
       <c r="B85" t="s">
         <v>526</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>1400</v>
+      <c r="C85" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -10304,8 +10303,8 @@
       <c r="B86" t="s">
         <v>117</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>1400</v>
+      <c r="C86" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -10315,8 +10314,8 @@
       <c r="B87" t="s">
         <v>560</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>1400</v>
+      <c r="C87" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -10326,8 +10325,8 @@
       <c r="B88" s="5" t="s">
         <v>1129</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>1400</v>
+      <c r="C88" t="s">
+        <v>1399</v>
       </c>
       <c r="D88" t="s">
         <v>1127</v>
@@ -10340,8 +10339,8 @@
       <c r="B89" t="s">
         <v>659</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>1400</v>
+      <c r="C89" t="s">
+        <v>1399</v>
       </c>
       <c r="D89" t="s">
         <v>585</v>
@@ -10354,8 +10353,8 @@
       <c r="B90" t="s">
         <v>660</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>1400</v>
+      <c r="C90" t="s">
+        <v>1399</v>
       </c>
       <c r="D90" t="s">
         <v>585</v>
@@ -10368,8 +10367,8 @@
       <c r="B91" t="s">
         <v>661</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>1400</v>
+      <c r="C91" t="s">
+        <v>1399</v>
       </c>
       <c r="D91" t="s">
         <v>585</v>
@@ -10382,8 +10381,8 @@
       <c r="B92" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>1400</v>
+      <c r="C92" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -10393,8 +10392,8 @@
       <c r="B94" t="s">
         <v>1041</v>
       </c>
-      <c r="C94" s="10" t="s">
-        <v>1400</v>
+      <c r="C94" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -10404,8 +10403,8 @@
       <c r="B95" t="s">
         <v>652</v>
       </c>
-      <c r="C95" s="10" t="s">
-        <v>1400</v>
+      <c r="C95" t="s">
+        <v>1399</v>
       </c>
       <c r="D95" t="s">
         <v>585</v>
@@ -10418,8 +10417,8 @@
       <c r="B96" t="s">
         <v>638</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>1400</v>
+      <c r="C96" t="s">
+        <v>1399</v>
       </c>
       <c r="D96" t="s">
         <v>585</v>
@@ -10432,8 +10431,8 @@
       <c r="B97" t="s">
         <v>121</v>
       </c>
-      <c r="C97" s="10" t="s">
-        <v>1400</v>
+      <c r="C97" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -10443,8 +10442,8 @@
       <c r="B98" t="s">
         <v>122</v>
       </c>
-      <c r="C98" s="10" t="s">
-        <v>1400</v>
+      <c r="C98" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -10454,8 +10453,8 @@
       <c r="B99" t="s">
         <v>527</v>
       </c>
-      <c r="C99" s="10" t="s">
-        <v>1400</v>
+      <c r="C99" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -10465,8 +10464,8 @@
       <c r="B100" t="s">
         <v>528</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>1400</v>
+      <c r="C100" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -10476,8 +10475,8 @@
       <c r="B101" t="s">
         <v>529</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>1400</v>
+      <c r="C101" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -10487,8 +10486,8 @@
       <c r="B102" t="s">
         <v>530</v>
       </c>
-      <c r="C102" s="10" t="s">
-        <v>1400</v>
+      <c r="C102" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -10498,8 +10497,8 @@
       <c r="B103" t="s">
         <v>441</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>1400</v>
+      <c r="C103" t="s">
+        <v>1399</v>
       </c>
       <c r="D103" t="s">
         <v>580</v>
@@ -10512,8 +10511,8 @@
       <c r="B104" t="s">
         <v>443</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>1400</v>
+      <c r="C104" t="s">
+        <v>1399</v>
       </c>
       <c r="D104" t="s">
         <v>495</v>
@@ -10526,8 +10525,8 @@
       <c r="B105" t="s">
         <v>444</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>1400</v>
+      <c r="C105" t="s">
+        <v>1399</v>
       </c>
       <c r="D105" t="s">
         <v>495</v>
@@ -10540,8 +10539,8 @@
       <c r="B106" t="s">
         <v>562</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>1400</v>
+      <c r="C106" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -10551,8 +10550,8 @@
       <c r="B107" t="s">
         <v>606</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>1400</v>
+      <c r="C107" t="s">
+        <v>1399</v>
       </c>
       <c r="D107" t="s">
         <v>585</v>
@@ -10565,8 +10564,8 @@
       <c r="B108" t="s">
         <v>841</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>1400</v>
+      <c r="C108" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -10576,8 +10575,8 @@
       <c r="B109" t="s">
         <v>632</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>1400</v>
+      <c r="C109" t="s">
+        <v>1399</v>
       </c>
       <c r="D109" t="s">
         <v>585</v>
@@ -10590,8 +10589,8 @@
       <c r="B110" t="s">
         <v>633</v>
       </c>
-      <c r="C110" s="10" t="s">
-        <v>1400</v>
+      <c r="C110" t="s">
+        <v>1399</v>
       </c>
       <c r="D110" t="s">
         <v>585</v>
@@ -10604,8 +10603,8 @@
       <c r="B111" t="s">
         <v>635</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>1400</v>
+      <c r="C111" t="s">
+        <v>1399</v>
       </c>
       <c r="D111" t="s">
         <v>585</v>
@@ -10618,8 +10617,8 @@
       <c r="B112" s="5" t="s">
         <v>1130</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>1400</v>
+      <c r="C112" t="s">
+        <v>1399</v>
       </c>
       <c r="D112" t="s">
         <v>1127</v>
@@ -10632,8 +10631,8 @@
       <c r="B113" t="s">
         <v>839</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>1400</v>
+      <c r="C113" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -10643,8 +10642,8 @@
       <c r="B114" t="s">
         <v>844</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>1400</v>
+      <c r="C114" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -10654,8 +10653,8 @@
       <c r="B115" t="s">
         <v>842</v>
       </c>
-      <c r="C115" s="10" t="s">
-        <v>1400</v>
+      <c r="C115" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -10665,8 +10664,8 @@
       <c r="B116" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>1400</v>
+      <c r="C116" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -10676,8 +10675,8 @@
       <c r="B118" t="s">
         <v>1124</v>
       </c>
-      <c r="C118" s="10" t="s">
-        <v>1400</v>
+      <c r="C118" t="s">
+        <v>1399</v>
       </c>
       <c r="D118" t="s">
         <v>585</v>
@@ -10690,8 +10689,8 @@
       <c r="B119" t="s">
         <v>144</v>
       </c>
-      <c r="C119" s="10" t="s">
-        <v>1400</v>
+      <c r="C119" t="s">
+        <v>1399</v>
       </c>
       <c r="D119" t="s">
         <v>578</v>
@@ -10704,8 +10703,8 @@
       <c r="B120" t="s">
         <v>145</v>
       </c>
-      <c r="C120" s="10" t="s">
-        <v>1400</v>
+      <c r="C120" t="s">
+        <v>1399</v>
       </c>
       <c r="D120" t="s">
         <v>578</v>
@@ -10718,8 +10717,8 @@
       <c r="B121" t="s">
         <v>146</v>
       </c>
-      <c r="C121" s="10" t="s">
-        <v>1400</v>
+      <c r="C121" t="s">
+        <v>1399</v>
       </c>
       <c r="D121" t="s">
         <v>578</v>
@@ -10732,8 +10731,8 @@
       <c r="B122" t="s">
         <v>514</v>
       </c>
-      <c r="C122" s="10" t="s">
-        <v>1400</v>
+      <c r="C122" t="s">
+        <v>1399</v>
       </c>
       <c r="D122" t="s">
         <v>584</v>
@@ -10746,8 +10745,8 @@
       <c r="B123" t="s">
         <v>514</v>
       </c>
-      <c r="C123" s="10" t="s">
-        <v>1400</v>
+      <c r="C123" t="s">
+        <v>1399</v>
       </c>
       <c r="D123" t="s">
         <v>578</v>
@@ -10760,8 +10759,8 @@
       <c r="B124" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>1400</v>
+      <c r="C124" t="s">
+        <v>1399</v>
       </c>
       <c r="D124" t="s">
         <v>578</v>
@@ -10774,8 +10773,8 @@
       <c r="B125" t="s">
         <v>531</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>1400</v>
+      <c r="C125" t="s">
+        <v>1399</v>
       </c>
       <c r="D125" t="s">
         <v>578</v>
@@ -10788,8 +10787,8 @@
       <c r="B126" t="s">
         <v>124</v>
       </c>
-      <c r="C126" s="10" t="s">
-        <v>1400</v>
+      <c r="C126" t="s">
+        <v>1399</v>
       </c>
       <c r="D126" t="s">
         <v>578</v>
@@ -10802,8 +10801,8 @@
       <c r="B127" t="s">
         <v>564</v>
       </c>
-      <c r="C127" s="10" t="s">
-        <v>1400</v>
+      <c r="C127" t="s">
+        <v>1399</v>
       </c>
       <c r="D127" t="s">
         <v>578</v>
@@ -10816,8 +10815,8 @@
       <c r="B128" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>1400</v>
+      <c r="C128" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -10827,8 +10826,8 @@
       <c r="B130" t="s">
         <v>182</v>
       </c>
-      <c r="C130" s="10" t="s">
-        <v>1400</v>
+      <c r="C130" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -10838,8 +10837,8 @@
       <c r="B131" t="s">
         <v>147</v>
       </c>
-      <c r="C131" s="10" t="s">
-        <v>1400</v>
+      <c r="C131" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -10849,8 +10848,8 @@
       <c r="B132" t="s">
         <v>148</v>
       </c>
-      <c r="C132" s="10" t="s">
-        <v>1400</v>
+      <c r="C132" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -10860,8 +10859,8 @@
       <c r="B133" t="s">
         <v>149</v>
       </c>
-      <c r="C133" s="10" t="s">
-        <v>1400</v>
+      <c r="C133" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -10871,8 +10870,8 @@
       <c r="B134" t="s">
         <v>681</v>
       </c>
-      <c r="C134" s="10" t="s">
-        <v>1400</v>
+      <c r="C134" t="s">
+        <v>1399</v>
       </c>
       <c r="D134" t="s">
         <v>585</v>
@@ -10885,8 +10884,8 @@
       <c r="B135" t="s">
         <v>150</v>
       </c>
-      <c r="C135" s="10" t="s">
-        <v>1400</v>
+      <c r="C135" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -10896,8 +10895,8 @@
       <c r="B136" t="s">
         <v>151</v>
       </c>
-      <c r="C136" s="10" t="s">
-        <v>1400</v>
+      <c r="C136" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -10907,8 +10906,8 @@
       <c r="B137" s="5" t="s">
         <v>1153</v>
       </c>
-      <c r="C137" s="10" t="s">
-        <v>1400</v>
+      <c r="C137" t="s">
+        <v>1399</v>
       </c>
       <c r="D137" t="s">
         <v>1127</v>
@@ -10921,8 +10920,8 @@
       <c r="B138" t="s">
         <v>566</v>
       </c>
-      <c r="C138" s="10" t="s">
-        <v>1400</v>
+      <c r="C138" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -10932,8 +10931,8 @@
       <c r="B139" t="s">
         <v>608</v>
       </c>
-      <c r="C139" s="10" t="s">
-        <v>1400</v>
+      <c r="C139" t="s">
+        <v>1399</v>
       </c>
       <c r="D139" t="s">
         <v>585</v>
@@ -10946,8 +10945,8 @@
       <c r="B140" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="C140" s="10" t="s">
-        <v>1400</v>
+      <c r="C140" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -10957,8 +10956,8 @@
       <c r="B142" t="s">
         <v>598</v>
       </c>
-      <c r="C142" s="10" t="s">
-        <v>1400</v>
+      <c r="C142" t="s">
+        <v>1399</v>
       </c>
       <c r="D142" t="s">
         <v>599</v>
@@ -10971,8 +10970,8 @@
       <c r="B143" t="s">
         <v>1155</v>
       </c>
-      <c r="C143" s="10" t="s">
-        <v>1400</v>
+      <c r="C143" t="s">
+        <v>1399</v>
       </c>
       <c r="D143" t="s">
         <v>599</v>
@@ -10985,8 +10984,8 @@
       <c r="B145" t="s">
         <v>157</v>
       </c>
-      <c r="C145" s="10" t="s">
-        <v>1400</v>
+      <c r="C145" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -10996,8 +10995,8 @@
       <c r="B146" t="s">
         <v>158</v>
       </c>
-      <c r="C146" s="10" t="s">
-        <v>1400</v>
+      <c r="C146" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -11007,8 +11006,8 @@
       <c r="B147" t="s">
         <v>159</v>
       </c>
-      <c r="C147" s="10" t="s">
-        <v>1400</v>
+      <c r="C147" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -11018,8 +11017,8 @@
       <c r="B148" t="s">
         <v>532</v>
       </c>
-      <c r="C148" s="10" t="s">
-        <v>1400</v>
+      <c r="C148" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -11029,8 +11028,8 @@
       <c r="B149" t="s">
         <v>620</v>
       </c>
-      <c r="C149" s="10" t="s">
-        <v>1400</v>
+      <c r="C149" t="s">
+        <v>1399</v>
       </c>
       <c r="D149" t="s">
         <v>621</v>
@@ -11043,8 +11042,8 @@
       <c r="B150" t="s">
         <v>1060</v>
       </c>
-      <c r="C150" s="10" t="s">
-        <v>1400</v>
+      <c r="C150" t="s">
+        <v>1399</v>
       </c>
       <c r="D150" t="s">
         <v>585</v>
@@ -11057,8 +11056,8 @@
       <c r="B151" t="s">
         <v>572</v>
       </c>
-      <c r="C151" s="10" t="s">
-        <v>1400</v>
+      <c r="C151" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -11068,8 +11067,8 @@
       <c r="B152" t="s">
         <v>1156</v>
       </c>
-      <c r="C152" s="10" t="s">
-        <v>1400</v>
+      <c r="C152" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -11079,8 +11078,8 @@
       <c r="B154" t="s">
         <v>186</v>
       </c>
-      <c r="C154" s="10" t="s">
-        <v>1400</v>
+      <c r="C154" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -11090,8 +11089,8 @@
       <c r="B155" t="s">
         <v>162</v>
       </c>
-      <c r="C155" s="10" t="s">
-        <v>1400</v>
+      <c r="C155" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -11101,8 +11100,8 @@
       <c r="B156" t="s">
         <v>163</v>
       </c>
-      <c r="C156" s="10" t="s">
-        <v>1400</v>
+      <c r="C156" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -11112,8 +11111,8 @@
       <c r="B157" t="s">
         <v>568</v>
       </c>
-      <c r="C157" s="10" t="s">
-        <v>1400</v>
+      <c r="C157" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -11123,8 +11122,8 @@
       <c r="B158" t="s">
         <v>1157</v>
       </c>
-      <c r="C158" s="10" t="s">
-        <v>1400</v>
+      <c r="C158" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -11134,8 +11133,8 @@
       <c r="B159" t="s">
         <v>610</v>
       </c>
-      <c r="C159" s="10" t="s">
-        <v>1400</v>
+      <c r="C159" t="s">
+        <v>1399</v>
       </c>
       <c r="D159" t="s">
         <v>585</v>
@@ -11148,8 +11147,8 @@
       <c r="B161" t="s">
         <v>184</v>
       </c>
-      <c r="C161" s="10" t="s">
-        <v>1400</v>
+      <c r="C161" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -11159,8 +11158,8 @@
       <c r="B162" t="s">
         <v>166</v>
       </c>
-      <c r="C162" s="10" t="s">
-        <v>1400</v>
+      <c r="C162" t="s">
+        <v>1399</v>
       </c>
       <c r="D162" t="s">
         <v>522</v>
@@ -11173,8 +11172,8 @@
       <c r="B163" t="s">
         <v>167</v>
       </c>
-      <c r="C163" s="10" t="s">
-        <v>1400</v>
+      <c r="C163" t="s">
+        <v>1399</v>
       </c>
       <c r="D163" t="s">
         <v>522</v>
@@ -11187,8 +11186,8 @@
       <c r="B164" t="s">
         <v>168</v>
       </c>
-      <c r="C164" s="10" t="s">
-        <v>1400</v>
+      <c r="C164" t="s">
+        <v>1399</v>
       </c>
       <c r="D164" t="s">
         <v>522</v>
@@ -11201,8 +11200,8 @@
       <c r="B165" t="s">
         <v>193</v>
       </c>
-      <c r="C165" s="10" t="s">
-        <v>1400</v>
+      <c r="C165" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -11212,8 +11211,8 @@
       <c r="B166" t="s">
         <v>192</v>
       </c>
-      <c r="C166" s="10" t="s">
-        <v>1400</v>
+      <c r="C166" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -11223,8 +11222,8 @@
       <c r="B167" t="s">
         <v>171</v>
       </c>
-      <c r="C167" s="10" t="s">
-        <v>1400</v>
+      <c r="C167" t="s">
+        <v>1399</v>
       </c>
       <c r="D167" t="s">
         <v>522</v>
@@ -11237,8 +11236,8 @@
       <c r="B168" t="s">
         <v>570</v>
       </c>
-      <c r="C168" s="10" t="s">
-        <v>1400</v>
+      <c r="C168" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="169" spans="1:4" s="6" customFormat="1">
@@ -11248,8 +11247,8 @@
       <c r="B169" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="C169" s="10" t="s">
-        <v>1400</v>
+      <c r="C169" t="s">
+        <v>1399</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>1131</v>
@@ -11262,8 +11261,8 @@
       <c r="B171" t="s">
         <v>756</v>
       </c>
-      <c r="C171" s="10" t="s">
-        <v>1400</v>
+      <c r="C171" t="s">
+        <v>1399</v>
       </c>
       <c r="D171" t="s">
         <v>1083</v>
@@ -11276,8 +11275,8 @@
       <c r="B172" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="C172" s="10" t="s">
-        <v>1400</v>
+      <c r="C172" t="s">
+        <v>1399</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>1131</v>
@@ -11290,8 +11289,8 @@
       <c r="B173" t="s">
         <v>613</v>
       </c>
-      <c r="C173" s="10" t="s">
-        <v>1400</v>
+      <c r="C173" t="s">
+        <v>1399</v>
       </c>
       <c r="D173" t="s">
         <v>585</v>
@@ -11304,8 +11303,8 @@
       <c r="B174" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="C174" s="10" t="s">
-        <v>1400</v>
+      <c r="C174" t="s">
+        <v>1399</v>
       </c>
       <c r="D174" s="6" t="s">
         <v>1131</v>
@@ -11318,8 +11317,8 @@
       <c r="B175" t="s">
         <v>819</v>
       </c>
-      <c r="C175" s="10" t="s">
-        <v>1400</v>
+      <c r="C175" t="s">
+        <v>1399</v>
       </c>
       <c r="D175" t="s">
         <v>585</v>
@@ -11332,8 +11331,8 @@
       <c r="B176" s="7" t="s">
         <v>1142</v>
       </c>
-      <c r="C176" s="10" t="s">
-        <v>1400</v>
+      <c r="C176" t="s">
+        <v>1399</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>1127</v>
@@ -11346,8 +11345,8 @@
       <c r="B177" t="s">
         <v>824</v>
       </c>
-      <c r="C177" s="10" t="s">
-        <v>1400</v>
+      <c r="C177" t="s">
+        <v>1399</v>
       </c>
       <c r="D177" t="s">
         <v>1045</v>
@@ -11360,8 +11359,8 @@
       <c r="B179" t="s">
         <v>1061</v>
       </c>
-      <c r="C179" s="10" t="s">
-        <v>1400</v>
+      <c r="C179" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -11371,8 +11370,8 @@
       <c r="B180" t="s">
         <v>1068</v>
       </c>
-      <c r="C180" s="10" t="s">
-        <v>1400</v>
+      <c r="C180" t="s">
+        <v>1399</v>
       </c>
       <c r="D180" t="s">
         <v>1069</v>
@@ -11385,8 +11384,8 @@
       <c r="B181" t="s">
         <v>820</v>
       </c>
-      <c r="C181" s="10" t="s">
-        <v>1400</v>
+      <c r="C181" t="s">
+        <v>1399</v>
       </c>
       <c r="D181" t="s">
         <v>522</v>
@@ -11399,8 +11398,8 @@
       <c r="B182" t="s">
         <v>821</v>
       </c>
-      <c r="C182" s="10" t="s">
-        <v>1400</v>
+      <c r="C182" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -11410,8 +11409,8 @@
       <c r="B183" t="s">
         <v>822</v>
       </c>
-      <c r="C183" s="10" t="s">
-        <v>1400</v>
+      <c r="C183" t="s">
+        <v>1399</v>
       </c>
       <c r="D183" t="s">
         <v>574</v>
@@ -11424,8 +11423,8 @@
       <c r="B184" t="s">
         <v>823</v>
       </c>
-      <c r="C184" s="10" t="s">
-        <v>1400</v>
+      <c r="C184" t="s">
+        <v>1399</v>
       </c>
       <c r="D184" t="s">
         <v>585</v>
@@ -11438,8 +11437,8 @@
       <c r="B185" t="s">
         <v>234</v>
       </c>
-      <c r="C185" s="10" t="s">
-        <v>1400</v>
+      <c r="C185" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -11449,8 +11448,8 @@
       <c r="B186" t="s">
         <v>457</v>
       </c>
-      <c r="C186" s="10" t="s">
-        <v>1400</v>
+      <c r="C186" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -11460,8 +11459,8 @@
       <c r="B187" t="s">
         <v>824</v>
       </c>
-      <c r="C187" s="10" t="s">
-        <v>1400</v>
+      <c r="C187" t="s">
+        <v>1399</v>
       </c>
       <c r="D187" t="s">
         <v>1046</v>
@@ -11474,8 +11473,8 @@
       <c r="B188" t="s">
         <v>825</v>
       </c>
-      <c r="C188" s="10" t="s">
-        <v>1400</v>
+      <c r="C188" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -11485,8 +11484,8 @@
       <c r="B189" t="s">
         <v>826</v>
       </c>
-      <c r="C189" s="10" t="s">
-        <v>1400</v>
+      <c r="C189" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -11496,8 +11495,8 @@
       <c r="B190" t="s">
         <v>827</v>
       </c>
-      <c r="C190" s="10" t="s">
-        <v>1400</v>
+      <c r="C190" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -11507,8 +11506,8 @@
       <c r="B191" t="s">
         <v>756</v>
       </c>
-      <c r="C191" s="10" t="s">
-        <v>1400</v>
+      <c r="C191" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -11518,8 +11517,8 @@
       <c r="B192" t="s">
         <v>824</v>
       </c>
-      <c r="C192" s="10" t="s">
-        <v>1400</v>
+      <c r="C192" t="s">
+        <v>1399</v>
       </c>
       <c r="D192" t="s">
         <v>1046</v>
@@ -11532,8 +11531,8 @@
       <c r="B193" t="s">
         <v>298</v>
       </c>
-      <c r="C193" s="10" t="s">
-        <v>1400</v>
+      <c r="C193" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -11543,8 +11542,8 @@
       <c r="B194" t="s">
         <v>1042</v>
       </c>
-      <c r="C194" s="10" t="s">
-        <v>1400</v>
+      <c r="C194" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -11554,8 +11553,8 @@
       <c r="B195" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C195" s="10" t="s">
-        <v>1400</v>
+      <c r="C195" t="s">
+        <v>1399</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>1127</v>
@@ -11568,8 +11567,8 @@
       <c r="B196" s="6" t="s">
         <v>654</v>
       </c>
-      <c r="C196" s="10" t="s">
-        <v>1400</v>
+      <c r="C196" t="s">
+        <v>1399</v>
       </c>
       <c r="D196" s="6" t="s">
         <v>1131</v>
@@ -11582,8 +11581,8 @@
       <c r="B197" s="7" t="s">
         <v>1159</v>
       </c>
-      <c r="C197" s="10" t="s">
-        <v>1400</v>
+      <c r="C197" t="s">
+        <v>1399</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>1127</v>
@@ -11596,8 +11595,8 @@
       <c r="B198" s="7" t="s">
         <v>1133</v>
       </c>
-      <c r="C198" s="10" t="s">
-        <v>1400</v>
+      <c r="C198" t="s">
+        <v>1399</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>1127</v>
@@ -11610,8 +11609,8 @@
       <c r="B199" t="s">
         <v>1107</v>
       </c>
-      <c r="C199" s="10" t="s">
-        <v>1400</v>
+      <c r="C199" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -11621,16 +11620,16 @@
       <c r="B200" s="7" t="s">
         <v>1160</v>
       </c>
-      <c r="C200" s="10" t="s">
-        <v>1400</v>
+      <c r="C200" t="s">
+        <v>1399</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="201" spans="1:4">
-      <c r="C201" s="10" t="s">
-        <v>1400</v>
+      <c r="C201" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -11640,8 +11639,8 @@
       <c r="B202" s="7" t="s">
         <v>1161</v>
       </c>
-      <c r="C202" s="10" t="s">
-        <v>1400</v>
+      <c r="C202" t="s">
+        <v>1399</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>1127</v>
@@ -11654,8 +11653,8 @@
       <c r="B203" t="s">
         <v>1062</v>
       </c>
-      <c r="C203" s="10" t="s">
-        <v>1400</v>
+      <c r="C203" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -11665,8 +11664,8 @@
       <c r="B204" t="s">
         <v>828</v>
       </c>
-      <c r="C204" s="10" t="s">
-        <v>1400</v>
+      <c r="C204" t="s">
+        <v>1399</v>
       </c>
       <c r="D204" t="s">
         <v>579</v>
@@ -11679,8 +11678,8 @@
       <c r="B205" t="s">
         <v>829</v>
       </c>
-      <c r="C205" s="10" t="s">
-        <v>1400</v>
+      <c r="C205" t="s">
+        <v>1399</v>
       </c>
       <c r="D205" t="s">
         <v>587</v>
@@ -11693,8 +11692,8 @@
       <c r="B206" t="s">
         <v>791</v>
       </c>
-      <c r="C206" s="10" t="s">
-        <v>1400</v>
+      <c r="C206" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -11704,8 +11703,8 @@
       <c r="B207" s="7" t="s">
         <v>1162</v>
       </c>
-      <c r="C207" s="10" t="s">
-        <v>1400</v>
+      <c r="C207" t="s">
+        <v>1399</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>1127</v>
@@ -11718,8 +11717,8 @@
       <c r="B208" t="s">
         <v>247</v>
       </c>
-      <c r="C208" s="10" t="s">
-        <v>1400</v>
+      <c r="C208" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -11729,8 +11728,8 @@
       <c r="B209" t="s">
         <v>248</v>
       </c>
-      <c r="C209" s="10" t="s">
-        <v>1400</v>
+      <c r="C209" t="s">
+        <v>1399</v>
       </c>
       <c r="D209" t="s">
         <v>579</v>
@@ -11743,8 +11742,8 @@
       <c r="B210" t="s">
         <v>504</v>
       </c>
-      <c r="C210" s="10" t="s">
-        <v>1400</v>
+      <c r="C210" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -11754,8 +11753,8 @@
       <c r="B211" t="s">
         <v>793</v>
       </c>
-      <c r="C211" s="10" t="s">
-        <v>1400</v>
+      <c r="C211" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -11765,8 +11764,8 @@
       <c r="B212" t="s">
         <v>252</v>
       </c>
-      <c r="C212" s="10" t="s">
-        <v>1400</v>
+      <c r="C212" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -11776,8 +11775,8 @@
       <c r="B213" t="s">
         <v>794</v>
       </c>
-      <c r="C213" s="10" t="s">
-        <v>1400</v>
+      <c r="C213" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -11787,8 +11786,8 @@
       <c r="B214" t="s">
         <v>795</v>
       </c>
-      <c r="C214" s="10" t="s">
-        <v>1400</v>
+      <c r="C214" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -11798,8 +11797,8 @@
       <c r="B215" t="s">
         <v>830</v>
       </c>
-      <c r="C215" s="10" t="s">
-        <v>1400</v>
+      <c r="C215" t="s">
+        <v>1399</v>
       </c>
       <c r="D215" t="s">
         <v>579</v>
@@ -11812,8 +11811,8 @@
       <c r="B216" t="s">
         <v>796</v>
       </c>
-      <c r="C216" s="10" t="s">
-        <v>1400</v>
+      <c r="C216" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -11823,8 +11822,8 @@
       <c r="B217" t="s">
         <v>831</v>
       </c>
-      <c r="C217" s="10" t="s">
-        <v>1400</v>
+      <c r="C217" t="s">
+        <v>1399</v>
       </c>
       <c r="D217" t="s">
         <v>579</v>
@@ -11837,8 +11836,8 @@
       <c r="B218" t="s">
         <v>797</v>
       </c>
-      <c r="C218" s="10" t="s">
-        <v>1400</v>
+      <c r="C218" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -11848,8 +11847,8 @@
       <c r="B219" t="s">
         <v>269</v>
       </c>
-      <c r="C219" s="10" t="s">
-        <v>1400</v>
+      <c r="C219" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -11859,8 +11858,8 @@
       <c r="B220" t="s">
         <v>824</v>
       </c>
-      <c r="C220" s="10" t="s">
-        <v>1400</v>
+      <c r="C220" t="s">
+        <v>1399</v>
       </c>
       <c r="D220" t="s">
         <v>1046</v>
@@ -11873,8 +11872,8 @@
       <c r="B221" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="C221" s="10" t="s">
-        <v>1400</v>
+      <c r="C221" t="s">
+        <v>1399</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>1127</v>
@@ -11887,8 +11886,8 @@
       <c r="B222" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C222" s="10" t="s">
-        <v>1400</v>
+      <c r="C222" t="s">
+        <v>1399</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>1127</v>
@@ -11901,8 +11900,8 @@
       <c r="B223" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="C223" s="10" t="s">
-        <v>1400</v>
+      <c r="C223" t="s">
+        <v>1399</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>1127</v>
@@ -11915,8 +11914,8 @@
       <c r="B224" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="C224" s="10" t="s">
-        <v>1400</v>
+      <c r="C224" t="s">
+        <v>1399</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>1127</v>
@@ -11929,8 +11928,8 @@
       <c r="B226" t="s">
         <v>1063</v>
       </c>
-      <c r="C226" s="10" t="s">
-        <v>1400</v>
+      <c r="C226" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -11940,8 +11939,8 @@
       <c r="B227" t="s">
         <v>505</v>
       </c>
-      <c r="C227" s="10" t="s">
-        <v>1400</v>
+      <c r="C227" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -11951,8 +11950,8 @@
       <c r="B228" t="s">
         <v>757</v>
       </c>
-      <c r="C228" s="10" t="s">
-        <v>1400</v>
+      <c r="C228" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -11962,8 +11961,8 @@
       <c r="B229" t="s">
         <v>758</v>
       </c>
-      <c r="C229" s="10" t="s">
-        <v>1400</v>
+      <c r="C229" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -11973,8 +11972,8 @@
       <c r="B230" t="s">
         <v>759</v>
       </c>
-      <c r="C230" s="10" t="s">
-        <v>1400</v>
+      <c r="C230" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -11984,8 +11983,8 @@
       <c r="B231" t="s">
         <v>761</v>
       </c>
-      <c r="C231" s="10" t="s">
-        <v>1400</v>
+      <c r="C231" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -11995,8 +11994,8 @@
       <c r="B232" t="s">
         <v>760</v>
       </c>
-      <c r="C232" s="10" t="s">
-        <v>1400</v>
+      <c r="C232" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -12006,8 +12005,8 @@
       <c r="B233" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C233" s="10" t="s">
-        <v>1400</v>
+      <c r="C233" t="s">
+        <v>1399</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>1127</v>
@@ -12020,8 +12019,8 @@
       <c r="B234" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="C234" s="10" t="s">
-        <v>1400</v>
+      <c r="C234" t="s">
+        <v>1399</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>1127</v>
@@ -12034,8 +12033,8 @@
       <c r="B236" t="s">
         <v>1064</v>
       </c>
-      <c r="C236" s="10" t="s">
-        <v>1400</v>
+      <c r="C236" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -12045,8 +12044,8 @@
       <c r="B237" t="s">
         <v>506</v>
       </c>
-      <c r="C237" s="10" t="s">
-        <v>1400</v>
+      <c r="C237" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -12056,8 +12055,8 @@
       <c r="B238" t="s">
         <v>751</v>
       </c>
-      <c r="C238" s="10" t="s">
-        <v>1400</v>
+      <c r="C238" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -12067,8 +12066,8 @@
       <c r="B239" t="s">
         <v>281</v>
       </c>
-      <c r="C239" s="10" t="s">
-        <v>1400</v>
+      <c r="C239" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -12078,8 +12077,8 @@
       <c r="B240" t="s">
         <v>752</v>
       </c>
-      <c r="C240" s="10" t="s">
-        <v>1400</v>
+      <c r="C240" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -12089,8 +12088,8 @@
       <c r="B241" t="s">
         <v>754</v>
       </c>
-      <c r="C241" s="10" t="s">
-        <v>1400</v>
+      <c r="C241" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -12100,8 +12099,8 @@
       <c r="B242" t="s">
         <v>753</v>
       </c>
-      <c r="C242" s="10" t="s">
-        <v>1400</v>
+      <c r="C242" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -12111,8 +12110,8 @@
       <c r="B243" t="s">
         <v>755</v>
       </c>
-      <c r="C243" s="10" t="s">
-        <v>1400</v>
+      <c r="C243" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -12122,8 +12121,8 @@
       <c r="B244" t="s">
         <v>756</v>
       </c>
-      <c r="C244" s="10" t="s">
-        <v>1400</v>
+      <c r="C244" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -12133,8 +12132,8 @@
       <c r="B245" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C245" s="10" t="s">
-        <v>1400</v>
+      <c r="C245" t="s">
+        <v>1399</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>1127</v>
@@ -12147,8 +12146,8 @@
       <c r="B246" t="s">
         <v>1119</v>
       </c>
-      <c r="C246" s="10" t="s">
-        <v>1400</v>
+      <c r="C246" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -12158,8 +12157,8 @@
       <c r="B247" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="C247" s="10" t="s">
-        <v>1400</v>
+      <c r="C247" t="s">
+        <v>1399</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>1127</v>
@@ -12172,8 +12171,8 @@
       <c r="B249" t="s">
         <v>1065</v>
       </c>
-      <c r="C249" s="10" t="s">
-        <v>1400</v>
+      <c r="C249" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -12183,8 +12182,8 @@
       <c r="B250" t="s">
         <v>291</v>
       </c>
-      <c r="C250" s="10" t="s">
-        <v>1400</v>
+      <c r="C250" t="s">
+        <v>1399</v>
       </c>
       <c r="D250" t="s">
         <v>522</v>
@@ -12197,8 +12196,8 @@
       <c r="B251" t="s">
         <v>507</v>
       </c>
-      <c r="C251" s="10" t="s">
-        <v>1400</v>
+      <c r="C251" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -12208,8 +12207,8 @@
       <c r="B252" t="s">
         <v>832</v>
       </c>
-      <c r="C252" s="10" t="s">
-        <v>1400</v>
+      <c r="C252" t="s">
+        <v>1399</v>
       </c>
       <c r="D252" t="s">
         <v>522</v>
@@ -12222,8 +12221,8 @@
       <c r="B253" t="s">
         <v>815</v>
       </c>
-      <c r="C253" s="10" t="s">
-        <v>1400</v>
+      <c r="C253" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -12233,8 +12232,8 @@
       <c r="B254" t="s">
         <v>816</v>
       </c>
-      <c r="C254" s="10" t="s">
-        <v>1400</v>
+      <c r="C254" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -12244,8 +12243,8 @@
       <c r="B255" t="s">
         <v>824</v>
       </c>
-      <c r="C255" s="10" t="s">
-        <v>1400</v>
+      <c r="C255" t="s">
+        <v>1399</v>
       </c>
       <c r="D255" t="s">
         <v>1043</v>
@@ -12258,8 +12257,8 @@
       <c r="B256" t="s">
         <v>833</v>
       </c>
-      <c r="C256" s="10" t="s">
-        <v>1400</v>
+      <c r="C256" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -12269,8 +12268,8 @@
       <c r="B257" t="s">
         <v>834</v>
       </c>
-      <c r="C257" s="10" t="s">
-        <v>1400</v>
+      <c r="C257" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -12280,8 +12279,8 @@
       <c r="B258" t="s">
         <v>835</v>
       </c>
-      <c r="C258" s="10" t="s">
-        <v>1400</v>
+      <c r="C258" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -12291,8 +12290,8 @@
       <c r="B259" t="s">
         <v>756</v>
       </c>
-      <c r="C259" s="10" t="s">
-        <v>1400</v>
+      <c r="C259" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -12302,8 +12301,8 @@
       <c r="B260" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C260" s="10" t="s">
-        <v>1400</v>
+      <c r="C260" t="s">
+        <v>1399</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>1127</v>
@@ -12316,8 +12315,8 @@
       <c r="B261" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="C261" s="10" t="s">
-        <v>1400</v>
+      <c r="C261" t="s">
+        <v>1399</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>1127</v>
@@ -12330,8 +12329,8 @@
       <c r="B263" t="s">
         <v>627</v>
       </c>
-      <c r="C263" s="10" t="s">
-        <v>1400</v>
+      <c r="C263" t="s">
+        <v>1399</v>
       </c>
       <c r="D263" t="s">
         <v>585</v>
@@ -12344,8 +12343,8 @@
       <c r="B264" t="s">
         <v>1192</v>
       </c>
-      <c r="C264" s="10" t="s">
-        <v>1400</v>
+      <c r="C264" t="s">
+        <v>1399</v>
       </c>
       <c r="D264" t="s">
         <v>520</v>
@@ -12358,8 +12357,8 @@
       <c r="B265" t="s">
         <v>493</v>
       </c>
-      <c r="C265" s="10" t="s">
-        <v>1400</v>
+      <c r="C265" t="s">
+        <v>1399</v>
       </c>
       <c r="D265" t="s">
         <v>521</v>
@@ -12372,8 +12371,8 @@
       <c r="B266" t="s">
         <v>533</v>
       </c>
-      <c r="C266" s="10" t="s">
-        <v>1400</v>
+      <c r="C266" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -12383,8 +12382,8 @@
       <c r="B267" t="s">
         <v>299</v>
       </c>
-      <c r="C267" s="10" t="s">
-        <v>1400</v>
+      <c r="C267" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -12394,8 +12393,8 @@
       <c r="B268" t="s">
         <v>300</v>
       </c>
-      <c r="C268" s="10" t="s">
-        <v>1400</v>
+      <c r="C268" t="s">
+        <v>1399</v>
       </c>
       <c r="D268" t="s">
         <v>522</v>
@@ -12408,8 +12407,8 @@
       <c r="B269" t="s">
         <v>508</v>
       </c>
-      <c r="C269" s="10" t="s">
-        <v>1400</v>
+      <c r="C269" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -12419,8 +12418,8 @@
       <c r="B270" t="s">
         <v>301</v>
       </c>
-      <c r="C270" s="10" t="s">
-        <v>1400</v>
+      <c r="C270" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -12430,8 +12429,8 @@
       <c r="B271" t="s">
         <v>302</v>
       </c>
-      <c r="C271" s="10" t="s">
-        <v>1400</v>
+      <c r="C271" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -12441,8 +12440,8 @@
       <c r="B272" t="s">
         <v>303</v>
       </c>
-      <c r="C272" s="10" t="s">
-        <v>1400</v>
+      <c r="C272" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="273" spans="1:4" s="6" customFormat="1">
@@ -12452,8 +12451,8 @@
       <c r="B273" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C273" s="10" t="s">
-        <v>1400</v>
+      <c r="C273" t="s">
+        <v>1399</v>
       </c>
       <c r="D273" s="6" t="s">
         <v>522</v>
@@ -12466,8 +12465,8 @@
       <c r="B274" t="s">
         <v>305</v>
       </c>
-      <c r="C274" s="10" t="s">
-        <v>1400</v>
+      <c r="C274" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -12477,8 +12476,8 @@
       <c r="B275" t="s">
         <v>306</v>
       </c>
-      <c r="C275" s="10" t="s">
-        <v>1400</v>
+      <c r="C275" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -12488,8 +12487,8 @@
       <c r="B276" t="s">
         <v>307</v>
       </c>
-      <c r="C276" s="10" t="s">
-        <v>1400</v>
+      <c r="C276" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -12499,8 +12498,8 @@
       <c r="B277" t="s">
         <v>308</v>
       </c>
-      <c r="C277" s="10" t="s">
-        <v>1400</v>
+      <c r="C277" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="278" spans="1:4" s="6" customFormat="1">
@@ -12510,8 +12509,8 @@
       <c r="B278" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="C278" s="10" t="s">
-        <v>1400</v>
+      <c r="C278" t="s">
+        <v>1399</v>
       </c>
       <c r="D278" s="6" t="s">
         <v>522</v>
@@ -12524,8 +12523,8 @@
       <c r="B279" t="s">
         <v>736</v>
       </c>
-      <c r="C279" s="10" t="s">
-        <v>1400</v>
+      <c r="C279" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -12535,8 +12534,8 @@
       <c r="B280" t="s">
         <v>310</v>
       </c>
-      <c r="C280" s="10" t="s">
-        <v>1400</v>
+      <c r="C280" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -12546,8 +12545,8 @@
       <c r="B281" t="s">
         <v>311</v>
       </c>
-      <c r="C281" s="10" t="s">
-        <v>1400</v>
+      <c r="C281" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -12557,8 +12556,8 @@
       <c r="B282" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="C282" s="10" t="s">
-        <v>1400</v>
+      <c r="C282" t="s">
+        <v>1399</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>1127</v>
@@ -12571,8 +12570,8 @@
       <c r="B284" t="s">
         <v>538</v>
       </c>
-      <c r="C284" s="10" t="s">
-        <v>1400</v>
+      <c r="C284" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -12582,8 +12581,8 @@
       <c r="B285" t="s">
         <v>350</v>
       </c>
-      <c r="C285" s="10" t="s">
-        <v>1400</v>
+      <c r="C285" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -12593,8 +12592,8 @@
       <c r="B286" t="s">
         <v>347</v>
       </c>
-      <c r="C286" s="10" t="s">
-        <v>1400</v>
+      <c r="C286" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -12604,8 +12603,8 @@
       <c r="B287" t="s">
         <v>348</v>
       </c>
-      <c r="C287" s="10" t="s">
-        <v>1400</v>
+      <c r="C287" t="s">
+        <v>1399</v>
       </c>
       <c r="D287" t="s">
         <v>522</v>
@@ -12618,8 +12617,8 @@
       <c r="B288" t="s">
         <v>509</v>
       </c>
-      <c r="C288" s="10" t="s">
-        <v>1400</v>
+      <c r="C288" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -12629,8 +12628,8 @@
       <c r="B289" t="s">
         <v>349</v>
       </c>
-      <c r="C289" s="10" t="s">
-        <v>1400</v>
+      <c r="C289" t="s">
+        <v>1399</v>
       </c>
       <c r="D289" t="s">
         <v>522</v>
@@ -12643,8 +12642,8 @@
       <c r="B290" t="s">
         <v>341</v>
       </c>
-      <c r="C290" s="10" t="s">
-        <v>1400</v>
+      <c r="C290" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -12654,8 +12653,8 @@
       <c r="B291" t="s">
         <v>342</v>
       </c>
-      <c r="C291" s="10" t="s">
-        <v>1400</v>
+      <c r="C291" t="s">
+        <v>1399</v>
       </c>
       <c r="D291" t="s">
         <v>499</v>
@@ -12668,8 +12667,8 @@
       <c r="B292" t="s">
         <v>343</v>
       </c>
-      <c r="C292" s="10" t="s">
-        <v>1400</v>
+      <c r="C292" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -12679,8 +12678,8 @@
       <c r="B293" t="s">
         <v>344</v>
       </c>
-      <c r="C293" s="10" t="s">
-        <v>1400</v>
+      <c r="C293" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -12690,8 +12689,8 @@
       <c r="B294" t="s">
         <v>345</v>
       </c>
-      <c r="C294" s="10" t="s">
-        <v>1400</v>
+      <c r="C294" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -12701,8 +12700,8 @@
       <c r="B295" t="s">
         <v>346</v>
       </c>
-      <c r="C295" s="10" t="s">
-        <v>1400</v>
+      <c r="C295" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -12712,8 +12711,8 @@
       <c r="B296" t="s">
         <v>343</v>
       </c>
-      <c r="C296" s="10" t="s">
-        <v>1400</v>
+      <c r="C296" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -12723,8 +12722,8 @@
       <c r="B297" t="s">
         <v>977</v>
       </c>
-      <c r="C297" s="10" t="s">
-        <v>1400</v>
+      <c r="C297" t="s">
+        <v>1399</v>
       </c>
       <c r="D297" t="s">
         <v>973</v>
@@ -12737,8 +12736,8 @@
       <c r="B298" t="s">
         <v>979</v>
       </c>
-      <c r="C298" s="10" t="s">
-        <v>1400</v>
+      <c r="C298" t="s">
+        <v>1399</v>
       </c>
       <c r="D298" t="s">
         <v>973</v>
@@ -12751,8 +12750,8 @@
       <c r="B299" t="s">
         <v>981</v>
       </c>
-      <c r="C299" s="10" t="s">
-        <v>1400</v>
+      <c r="C299" t="s">
+        <v>1399</v>
       </c>
       <c r="D299" t="s">
         <v>973</v>
@@ -12765,8 +12764,8 @@
       <c r="B300" t="s">
         <v>1112</v>
       </c>
-      <c r="C300" s="10" t="s">
-        <v>1400</v>
+      <c r="C300" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -12776,8 +12775,8 @@
       <c r="B301" s="5" t="s">
         <v>1170</v>
       </c>
-      <c r="C301" s="10" t="s">
-        <v>1400</v>
+      <c r="C301" t="s">
+        <v>1399</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>1127</v>
@@ -12790,8 +12789,8 @@
       <c r="B303" t="s">
         <v>645</v>
       </c>
-      <c r="C303" s="10" t="s">
-        <v>1400</v>
+      <c r="C303" t="s">
+        <v>1399</v>
       </c>
       <c r="D303" t="s">
         <v>585</v>
@@ -12804,8 +12803,8 @@
       <c r="B304" s="7" t="s">
         <v>1135</v>
       </c>
-      <c r="C304" s="10" t="s">
-        <v>1400</v>
+      <c r="C304" t="s">
+        <v>1399</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>1127</v>
@@ -12818,8 +12817,8 @@
       <c r="B305" s="7" t="s">
         <v>1136</v>
       </c>
-      <c r="C305" s="10" t="s">
-        <v>1400</v>
+      <c r="C305" t="s">
+        <v>1399</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>1127</v>
@@ -12832,16 +12831,16 @@
       <c r="B306" s="5" t="s">
         <v>1171</v>
       </c>
-      <c r="C306" s="10" t="s">
-        <v>1400</v>
+      <c r="C306" t="s">
+        <v>1399</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="307" spans="1:4">
-      <c r="C307" s="10" t="s">
-        <v>1400</v>
+      <c r="C307" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -12851,8 +12850,8 @@
       <c r="B308" t="s">
         <v>625</v>
       </c>
-      <c r="C308" s="10" t="s">
-        <v>1400</v>
+      <c r="C308" t="s">
+        <v>1399</v>
       </c>
       <c r="D308" t="s">
         <v>585</v>
@@ -12865,8 +12864,8 @@
       <c r="B309" t="s">
         <v>464</v>
       </c>
-      <c r="C309" s="10" t="s">
-        <v>1400</v>
+      <c r="C309" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -12876,8 +12875,8 @@
       <c r="B310" t="s">
         <v>369</v>
       </c>
-      <c r="C310" s="10" t="s">
-        <v>1400</v>
+      <c r="C310" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -12887,8 +12886,8 @@
       <c r="B311" t="s">
         <v>370</v>
       </c>
-      <c r="C311" s="10" t="s">
-        <v>1400</v>
+      <c r="C311" t="s">
+        <v>1399</v>
       </c>
       <c r="D311" t="s">
         <v>522</v>
@@ -12901,8 +12900,8 @@
       <c r="B312" t="s">
         <v>511</v>
       </c>
-      <c r="C312" s="10" t="s">
-        <v>1400</v>
+      <c r="C312" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -12912,8 +12911,8 @@
       <c r="B313" t="s">
         <v>371</v>
       </c>
-      <c r="C313" s="10" t="s">
-        <v>1400</v>
+      <c r="C313" t="s">
+        <v>1399</v>
       </c>
       <c r="D313" t="s">
         <v>522</v>
@@ -12926,8 +12925,8 @@
       <c r="B314" t="s">
         <v>372</v>
       </c>
-      <c r="C314" s="10" t="s">
-        <v>1400</v>
+      <c r="C314" t="s">
+        <v>1399</v>
       </c>
       <c r="D314" t="s">
         <v>522</v>
@@ -12940,8 +12939,8 @@
       <c r="B315" t="s">
         <v>523</v>
       </c>
-      <c r="C315" s="10" t="s">
-        <v>1400</v>
+      <c r="C315" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -12951,8 +12950,8 @@
       <c r="B316" t="s">
         <v>373</v>
       </c>
-      <c r="C316" s="10" t="s">
-        <v>1400</v>
+      <c r="C316" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -12962,8 +12961,8 @@
       <c r="B317" t="s">
         <v>374</v>
       </c>
-      <c r="C317" s="10" t="s">
-        <v>1400</v>
+      <c r="C317" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -12973,8 +12972,8 @@
       <c r="B318" t="s">
         <v>375</v>
       </c>
-      <c r="C318" s="10" t="s">
-        <v>1400</v>
+      <c r="C318" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -12984,8 +12983,8 @@
       <c r="B319" t="s">
         <v>376</v>
       </c>
-      <c r="C319" s="10" t="s">
-        <v>1400</v>
+      <c r="C319" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -12995,8 +12994,8 @@
       <c r="B320" t="s">
         <v>377</v>
       </c>
-      <c r="C320" s="10" t="s">
-        <v>1400</v>
+      <c r="C320" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -13006,8 +13005,8 @@
       <c r="B321" t="s">
         <v>378</v>
       </c>
-      <c r="C321" s="10" t="s">
-        <v>1400</v>
+      <c r="C321" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -13017,8 +13016,8 @@
       <c r="B322" s="7" t="s">
         <v>1137</v>
       </c>
-      <c r="C322" s="10" t="s">
-        <v>1400</v>
+      <c r="C322" t="s">
+        <v>1399</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>1127</v>
@@ -13031,8 +13030,8 @@
       <c r="B323" t="s">
         <v>1058</v>
       </c>
-      <c r="C323" s="10" t="s">
-        <v>1400</v>
+      <c r="C323" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -13042,8 +13041,8 @@
       <c r="B324" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="C324" s="10" t="s">
-        <v>1400</v>
+      <c r="C324" t="s">
+        <v>1399</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>1127</v>
@@ -13056,8 +13055,8 @@
       <c r="B325" t="s">
         <v>1115</v>
       </c>
-      <c r="C325" s="10" t="s">
-        <v>1400</v>
+      <c r="C325" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -13067,8 +13066,8 @@
       <c r="B326" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C326" s="10" t="s">
-        <v>1400</v>
+      <c r="C326" t="s">
+        <v>1399</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>1127</v>
@@ -13081,8 +13080,8 @@
       <c r="B328" t="s">
         <v>464</v>
       </c>
-      <c r="C328" s="10" t="s">
-        <v>1400</v>
+      <c r="C328" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -13092,8 +13091,8 @@
       <c r="B329" t="s">
         <v>396</v>
       </c>
-      <c r="C329" s="10" t="s">
-        <v>1400</v>
+      <c r="C329" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -13103,8 +13102,8 @@
       <c r="B330" t="s">
         <v>397</v>
       </c>
-      <c r="C330" s="10" t="s">
-        <v>1400</v>
+      <c r="C330" t="s">
+        <v>1399</v>
       </c>
       <c r="D330" t="s">
         <v>522</v>
@@ -13117,8 +13116,8 @@
       <c r="B331" t="s">
         <v>512</v>
       </c>
-      <c r="C331" s="10" t="s">
-        <v>1400</v>
+      <c r="C331" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -13128,8 +13127,8 @@
       <c r="B332" t="s">
         <v>398</v>
       </c>
-      <c r="C332" s="10" t="s">
-        <v>1400</v>
+      <c r="C332" t="s">
+        <v>1399</v>
       </c>
       <c r="D332" t="s">
         <v>522</v>
@@ -13142,8 +13141,8 @@
       <c r="B333" t="s">
         <v>399</v>
       </c>
-      <c r="C333" s="10" t="s">
-        <v>1400</v>
+      <c r="C333" t="s">
+        <v>1399</v>
       </c>
       <c r="D333" t="s">
         <v>522</v>
@@ -13156,8 +13155,8 @@
       <c r="B334" t="s">
         <v>524</v>
       </c>
-      <c r="C334" s="10" t="s">
-        <v>1400</v>
+      <c r="C334" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -13167,8 +13166,8 @@
       <c r="B335" t="s">
         <v>373</v>
       </c>
-      <c r="C335" s="10" t="s">
-        <v>1400</v>
+      <c r="C335" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -13178,8 +13177,8 @@
       <c r="B336" t="s">
         <v>374</v>
       </c>
-      <c r="C336" s="10" t="s">
-        <v>1400</v>
+      <c r="C336" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -13189,8 +13188,8 @@
       <c r="B337" t="s">
         <v>400</v>
       </c>
-      <c r="C337" s="10" t="s">
-        <v>1400</v>
+      <c r="C337" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -13200,8 +13199,8 @@
       <c r="B338" t="s">
         <v>401</v>
       </c>
-      <c r="C338" s="10" t="s">
-        <v>1400</v>
+      <c r="C338" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -13211,8 +13210,8 @@
       <c r="B339" t="s">
         <v>377</v>
       </c>
-      <c r="C339" s="10" t="s">
-        <v>1400</v>
+      <c r="C339" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -13222,8 +13221,8 @@
       <c r="B340" t="s">
         <v>378</v>
       </c>
-      <c r="C340" s="10" t="s">
-        <v>1400</v>
+      <c r="C340" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -13233,8 +13232,8 @@
       <c r="B341" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="C341" s="10" t="s">
-        <v>1400</v>
+      <c r="C341" t="s">
+        <v>1399</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>1127</v>
@@ -13247,8 +13246,8 @@
       <c r="B342" t="s">
         <v>1117</v>
       </c>
-      <c r="C342" s="10" t="s">
-        <v>1400</v>
+      <c r="C342" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -13258,8 +13257,8 @@
       <c r="B343" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C343" s="10" t="s">
-        <v>1400</v>
+      <c r="C343" t="s">
+        <v>1399</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>1127</v>
@@ -13272,8 +13271,8 @@
       <c r="B345" t="s">
         <v>623</v>
       </c>
-      <c r="C345" s="10" t="s">
-        <v>1400</v>
+      <c r="C345" t="s">
+        <v>1399</v>
       </c>
       <c r="D345" t="s">
         <v>585</v>
@@ -13286,8 +13285,8 @@
       <c r="B346" t="s">
         <v>1195</v>
       </c>
-      <c r="C346" s="10" t="s">
-        <v>1400</v>
+      <c r="C346" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -13297,8 +13296,8 @@
       <c r="B347" t="s">
         <v>1196</v>
       </c>
-      <c r="C347" s="10" t="s">
-        <v>1400</v>
+      <c r="C347" t="s">
+        <v>1399</v>
       </c>
       <c r="D347" t="s">
         <v>522</v>
@@ -13311,8 +13310,8 @@
       <c r="B348" t="s">
         <v>1197</v>
       </c>
-      <c r="C348" s="10" t="s">
-        <v>1400</v>
+      <c r="C348" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -13322,8 +13321,8 @@
       <c r="B349" t="s">
         <v>1198</v>
       </c>
-      <c r="C349" s="10" t="s">
-        <v>1400</v>
+      <c r="C349" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -13333,8 +13332,8 @@
       <c r="B350" t="s">
         <v>1199</v>
       </c>
-      <c r="C350" s="10" t="s">
-        <v>1400</v>
+      <c r="C350" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -13344,8 +13343,8 @@
       <c r="B351" t="s">
         <v>1200</v>
       </c>
-      <c r="C351" s="10" t="s">
-        <v>1400</v>
+      <c r="C351" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -13355,8 +13354,8 @@
       <c r="B352" t="s">
         <v>1075</v>
       </c>
-      <c r="C352" s="10" t="s">
-        <v>1400</v>
+      <c r="C352" t="s">
+        <v>1399</v>
       </c>
       <c r="D352" t="s">
         <v>1076</v>
@@ -13369,8 +13368,8 @@
       <c r="B353" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="C353" s="10" t="s">
-        <v>1400</v>
+      <c r="C353" t="s">
+        <v>1399</v>
       </c>
       <c r="D353" s="2" t="s">
         <v>1127</v>
@@ -13383,8 +13382,8 @@
       <c r="B355" t="s">
         <v>688</v>
       </c>
-      <c r="C355" s="10" t="s">
-        <v>1400</v>
+      <c r="C355" t="s">
+        <v>1399</v>
       </c>
       <c r="D355" t="s">
         <v>585</v>
@@ -13397,8 +13396,8 @@
       <c r="B356" s="5" t="s">
         <v>1174</v>
       </c>
-      <c r="C356" s="10" t="s">
-        <v>1400</v>
+      <c r="C356" t="s">
+        <v>1399</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>1127</v>
@@ -13411,8 +13410,8 @@
       <c r="B358" t="s">
         <v>695</v>
       </c>
-      <c r="C358" s="10" t="s">
-        <v>1400</v>
+      <c r="C358" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -13422,8 +13421,8 @@
       <c r="B359" t="s">
         <v>1194</v>
       </c>
-      <c r="C359" s="10" t="s">
-        <v>1400</v>
+      <c r="C359" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -13433,8 +13432,8 @@
       <c r="B360" t="s">
         <v>698</v>
       </c>
-      <c r="C360" s="10" t="s">
-        <v>1400</v>
+      <c r="C360" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -13444,8 +13443,8 @@
       <c r="B361" t="s">
         <v>700</v>
       </c>
-      <c r="C361" s="10" t="s">
-        <v>1400</v>
+      <c r="C361" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -13455,8 +13454,8 @@
       <c r="B362" t="s">
         <v>702</v>
       </c>
-      <c r="C362" s="10" t="s">
-        <v>1400</v>
+      <c r="C362" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -13466,8 +13465,8 @@
       <c r="B363" t="s">
         <v>704</v>
       </c>
-      <c r="C363" s="10" t="s">
-        <v>1400</v>
+      <c r="C363" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -13477,8 +13476,8 @@
       <c r="B364" t="s">
         <v>706</v>
       </c>
-      <c r="C364" s="10" t="s">
-        <v>1400</v>
+      <c r="C364" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -13488,8 +13487,8 @@
       <c r="B365" t="s">
         <v>708</v>
       </c>
-      <c r="C365" s="10" t="s">
-        <v>1400</v>
+      <c r="C365" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -13499,8 +13498,8 @@
       <c r="B366" t="s">
         <v>1101</v>
       </c>
-      <c r="C366" s="10" t="s">
-        <v>1400</v>
+      <c r="C366" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -13510,8 +13509,8 @@
       <c r="B367" s="7" t="s">
         <v>1175</v>
       </c>
-      <c r="C367" s="10" t="s">
-        <v>1400</v>
+      <c r="C367" t="s">
+        <v>1399</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>1127</v>
@@ -13524,8 +13523,8 @@
       <c r="B368" t="s">
         <v>712</v>
       </c>
-      <c r="C368" s="10" t="s">
-        <v>1400</v>
+      <c r="C368" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -13535,8 +13534,8 @@
       <c r="B369" t="s">
         <v>714</v>
       </c>
-      <c r="C369" s="10" t="s">
-        <v>1400</v>
+      <c r="C369" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -13546,8 +13545,8 @@
       <c r="B370" t="s">
         <v>716</v>
       </c>
-      <c r="C370" s="10" t="s">
-        <v>1400</v>
+      <c r="C370" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -13557,8 +13556,8 @@
       <c r="B371" t="s">
         <v>718</v>
       </c>
-      <c r="C371" s="10" t="s">
-        <v>1400</v>
+      <c r="C371" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -13568,8 +13567,8 @@
       <c r="B372" t="s">
         <v>720</v>
       </c>
-      <c r="C372" s="10" t="s">
-        <v>1400</v>
+      <c r="C372" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -13579,8 +13578,8 @@
       <c r="B373" t="s">
         <v>722</v>
       </c>
-      <c r="C373" s="10" t="s">
-        <v>1400</v>
+      <c r="C373" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -13590,8 +13589,8 @@
       <c r="B374" t="s">
         <v>1051</v>
       </c>
-      <c r="C374" s="10" t="s">
-        <v>1400</v>
+      <c r="C374" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -13601,8 +13600,8 @@
       <c r="B375" t="s">
         <v>724</v>
       </c>
-      <c r="C375" s="10" t="s">
-        <v>1400</v>
+      <c r="C375" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -13612,8 +13611,8 @@
       <c r="B376" t="s">
         <v>1091</v>
       </c>
-      <c r="C376" s="10" t="s">
-        <v>1400</v>
+      <c r="C376" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -13623,8 +13622,8 @@
       <c r="B377" s="5" t="s">
         <v>1176</v>
       </c>
-      <c r="C377" s="10" t="s">
-        <v>1400</v>
+      <c r="C377" t="s">
+        <v>1399</v>
       </c>
       <c r="D377" s="2" t="s">
         <v>1127</v>
@@ -13637,8 +13636,8 @@
       <c r="B379" t="s">
         <v>726</v>
       </c>
-      <c r="C379" s="10" t="s">
-        <v>1400</v>
+      <c r="C379" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -13648,8 +13647,8 @@
       <c r="B380" t="s">
         <v>728</v>
       </c>
-      <c r="C380" s="10" t="s">
-        <v>1400</v>
+      <c r="C380" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -13659,8 +13658,8 @@
       <c r="B381" t="s">
         <v>730</v>
       </c>
-      <c r="C381" s="10" t="s">
-        <v>1400</v>
+      <c r="C381" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -13670,8 +13669,8 @@
       <c r="B382" t="s">
         <v>732</v>
       </c>
-      <c r="C382" s="10" t="s">
-        <v>1400</v>
+      <c r="C382" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -13681,8 +13680,8 @@
       <c r="B383" t="s">
         <v>734</v>
       </c>
-      <c r="C383" s="10" t="s">
-        <v>1400</v>
+      <c r="C383" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -13692,8 +13691,8 @@
       <c r="B384" t="s">
         <v>736</v>
       </c>
-      <c r="C384" s="10" t="s">
-        <v>1400</v>
+      <c r="C384" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -13703,8 +13702,8 @@
       <c r="B385" t="s">
         <v>738</v>
       </c>
-      <c r="C385" s="10" t="s">
-        <v>1400</v>
+      <c r="C385" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -13714,8 +13713,8 @@
       <c r="B386" t="s">
         <v>311</v>
       </c>
-      <c r="C386" s="10" t="s">
-        <v>1400</v>
+      <c r="C386" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -13725,8 +13724,8 @@
       <c r="B387" t="s">
         <v>741</v>
       </c>
-      <c r="C387" s="10" t="s">
-        <v>1400</v>
+      <c r="C387" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -13736,8 +13735,8 @@
       <c r="B388" t="s">
         <v>743</v>
       </c>
-      <c r="C388" s="10" t="s">
-        <v>1400</v>
+      <c r="C388" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -13747,8 +13746,8 @@
       <c r="B389" t="s">
         <v>1193</v>
       </c>
-      <c r="C389" s="10" t="s">
-        <v>1400</v>
+      <c r="C389" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -13758,8 +13757,8 @@
       <c r="B390" s="7" t="s">
         <v>1177</v>
       </c>
-      <c r="C390" s="10" t="s">
-        <v>1400</v>
+      <c r="C390" t="s">
+        <v>1399</v>
       </c>
       <c r="D390" s="2" t="s">
         <v>1127</v>
@@ -13772,8 +13771,8 @@
       <c r="B392" t="s">
         <v>305</v>
       </c>
-      <c r="C392" s="10" t="s">
-        <v>1400</v>
+      <c r="C392" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -13783,8 +13782,8 @@
       <c r="B393" t="s">
         <v>748</v>
       </c>
-      <c r="C393" s="10" t="s">
-        <v>1400</v>
+      <c r="C393" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -13794,8 +13793,8 @@
       <c r="B394" t="s">
         <v>307</v>
       </c>
-      <c r="C394" s="10" t="s">
-        <v>1400</v>
+      <c r="C394" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -13805,8 +13804,8 @@
       <c r="B395" t="s">
         <v>1102</v>
       </c>
-      <c r="C395" s="10" t="s">
-        <v>1400</v>
+      <c r="C395" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -13816,8 +13815,8 @@
       <c r="B397" t="s">
         <v>772</v>
       </c>
-      <c r="C397" s="10" t="s">
-        <v>1400</v>
+      <c r="C397" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -13827,8 +13826,8 @@
       <c r="B398" t="s">
         <v>769</v>
       </c>
-      <c r="C398" s="10" t="s">
-        <v>1400</v>
+      <c r="C398" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -13838,8 +13837,8 @@
       <c r="B399" t="s">
         <v>765</v>
       </c>
-      <c r="C399" s="10" t="s">
-        <v>1400</v>
+      <c r="C399" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -13849,8 +13848,8 @@
       <c r="B400" t="s">
         <v>766</v>
       </c>
-      <c r="C400" s="10" t="s">
-        <v>1400</v>
+      <c r="C400" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -13860,8 +13859,8 @@
       <c r="B401" t="s">
         <v>767</v>
       </c>
-      <c r="C401" s="10" t="s">
-        <v>1400</v>
+      <c r="C401" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -13871,8 +13870,8 @@
       <c r="B402" s="5" t="s">
         <v>1178</v>
       </c>
-      <c r="C402" s="10" t="s">
-        <v>1400</v>
+      <c r="C402" t="s">
+        <v>1399</v>
       </c>
       <c r="D402" s="2" t="s">
         <v>1127</v>
@@ -13885,8 +13884,8 @@
       <c r="B404" t="s">
         <v>780</v>
       </c>
-      <c r="C404" s="10" t="s">
-        <v>1400</v>
+      <c r="C404" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -13896,8 +13895,8 @@
       <c r="B405" t="s">
         <v>781</v>
       </c>
-      <c r="C405" s="10" t="s">
-        <v>1400</v>
+      <c r="C405" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -13907,8 +13906,8 @@
       <c r="B406" t="s">
         <v>765</v>
       </c>
-      <c r="C406" s="10" t="s">
-        <v>1400</v>
+      <c r="C406" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -13918,8 +13917,8 @@
       <c r="B407" t="s">
         <v>766</v>
       </c>
-      <c r="C407" s="10" t="s">
-        <v>1400</v>
+      <c r="C407" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -13929,8 +13928,8 @@
       <c r="B408" t="s">
         <v>767</v>
       </c>
-      <c r="C408" s="10" t="s">
-        <v>1400</v>
+      <c r="C408" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -13940,8 +13939,8 @@
       <c r="B409" s="5" t="s">
         <v>1179</v>
       </c>
-      <c r="C409" s="10" t="s">
-        <v>1400</v>
+      <c r="C409" t="s">
+        <v>1399</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>1127</v>
@@ -13954,8 +13953,8 @@
       <c r="B411" t="s">
         <v>788</v>
       </c>
-      <c r="C411" s="10" t="s">
-        <v>1400</v>
+      <c r="C411" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -13965,8 +13964,8 @@
       <c r="B412" t="s">
         <v>1066</v>
       </c>
-      <c r="C412" s="10" t="s">
-        <v>1400</v>
+      <c r="C412" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -13976,8 +13975,8 @@
       <c r="B413" s="7" t="s">
         <v>1161</v>
       </c>
-      <c r="C413" s="10" t="s">
-        <v>1400</v>
+      <c r="C413" t="s">
+        <v>1399</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>1127</v>
@@ -13990,8 +13989,8 @@
       <c r="B414" t="s">
         <v>1030</v>
       </c>
-      <c r="C414" s="10" t="s">
-        <v>1400</v>
+      <c r="C414" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -14001,8 +14000,8 @@
       <c r="B415" s="7" t="s">
         <v>1180</v>
       </c>
-      <c r="C415" s="10" t="s">
-        <v>1400</v>
+      <c r="C415" t="s">
+        <v>1399</v>
       </c>
       <c r="D415" s="2" t="s">
         <v>1127</v>
@@ -14015,8 +14014,8 @@
       <c r="B416" t="s">
         <v>1017</v>
       </c>
-      <c r="C416" s="10" t="s">
-        <v>1400</v>
+      <c r="C416" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -14026,8 +14025,8 @@
       <c r="B417" t="s">
         <v>1036</v>
       </c>
-      <c r="C417" s="10" t="s">
-        <v>1400</v>
+      <c r="C417" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -14037,8 +14036,8 @@
       <c r="B418" t="s">
         <v>1035</v>
       </c>
-      <c r="C418" s="10" t="s">
-        <v>1400</v>
+      <c r="C418" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -14048,8 +14047,8 @@
       <c r="B419" t="s">
         <v>1034</v>
       </c>
-      <c r="C419" s="10" t="s">
-        <v>1400</v>
+      <c r="C419" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -14059,8 +14058,8 @@
       <c r="B420" t="s">
         <v>1033</v>
       </c>
-      <c r="C420" s="10" t="s">
-        <v>1400</v>
+      <c r="C420" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -14070,8 +14069,8 @@
       <c r="B421" t="s">
         <v>1032</v>
       </c>
-      <c r="C421" s="10" t="s">
-        <v>1400</v>
+      <c r="C421" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -14081,8 +14080,8 @@
       <c r="B422" t="s">
         <v>1031</v>
       </c>
-      <c r="C422" s="10" t="s">
-        <v>1400</v>
+      <c r="C422" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -14092,8 +14091,8 @@
       <c r="B423" t="s">
         <v>797</v>
       </c>
-      <c r="C423" s="10" t="s">
-        <v>1400</v>
+      <c r="C423" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -14103,8 +14102,8 @@
       <c r="B424" t="s">
         <v>1037</v>
       </c>
-      <c r="C424" s="10" t="s">
-        <v>1400</v>
+      <c r="C424" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -14114,8 +14113,8 @@
       <c r="B425" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="C425" s="10" t="s">
-        <v>1400</v>
+      <c r="C425" t="s">
+        <v>1399</v>
       </c>
       <c r="D425" s="2" t="s">
         <v>1127</v>
@@ -14128,8 +14127,8 @@
       <c r="B426" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C426" s="10" t="s">
-        <v>1400</v>
+      <c r="C426" t="s">
+        <v>1399</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>1127</v>
@@ -14142,8 +14141,8 @@
       <c r="B427" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="C427" s="10" t="s">
-        <v>1400</v>
+      <c r="C427" t="s">
+        <v>1399</v>
       </c>
       <c r="D427" s="2" t="s">
         <v>1127</v>
@@ -14156,8 +14155,8 @@
       <c r="B428" s="5" t="s">
         <v>1181</v>
       </c>
-      <c r="C428" s="10" t="s">
-        <v>1400</v>
+      <c r="C428" t="s">
+        <v>1399</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>1127</v>
@@ -14170,8 +14169,8 @@
       <c r="B429" t="s">
         <v>1107</v>
       </c>
-      <c r="C429" s="10" t="s">
-        <v>1400</v>
+      <c r="C429" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -14181,8 +14180,8 @@
       <c r="B430" t="s">
         <v>1018</v>
       </c>
-      <c r="C430" s="10" t="s">
-        <v>1400</v>
+      <c r="C430" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -14192,8 +14191,8 @@
       <c r="B431" t="s">
         <v>1019</v>
       </c>
-      <c r="C431" s="10" t="s">
-        <v>1400</v>
+      <c r="C431" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -14203,8 +14202,8 @@
       <c r="B432" t="s">
         <v>1022</v>
       </c>
-      <c r="C432" s="10" t="s">
-        <v>1400</v>
+      <c r="C432" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -14214,8 +14213,8 @@
       <c r="B433" t="s">
         <v>1024</v>
       </c>
-      <c r="C433" s="10" t="s">
-        <v>1400</v>
+      <c r="C433" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -14225,8 +14224,8 @@
       <c r="B434" t="s">
         <v>1025</v>
       </c>
-      <c r="C434" s="10" t="s">
-        <v>1400</v>
+      <c r="C434" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -14236,8 +14235,8 @@
       <c r="B435" t="s">
         <v>1026</v>
       </c>
-      <c r="C435" s="10" t="s">
-        <v>1400</v>
+      <c r="C435" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -14247,8 +14246,8 @@
       <c r="B436" t="s">
         <v>1038</v>
       </c>
-      <c r="C436" s="10" t="s">
-        <v>1400</v>
+      <c r="C436" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -14258,8 +14257,8 @@
       <c r="B437" s="7" t="s">
         <v>1138</v>
       </c>
-      <c r="C437" s="10" t="s">
-        <v>1400</v>
+      <c r="C437" t="s">
+        <v>1399</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>1127</v>
@@ -14272,8 +14271,8 @@
       <c r="B438" t="s">
         <v>1081</v>
       </c>
-      <c r="C438" s="10" t="s">
-        <v>1400</v>
+      <c r="C438" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -14283,8 +14282,8 @@
       <c r="B440" t="s">
         <v>848</v>
       </c>
-      <c r="C440" s="10" t="s">
-        <v>1400</v>
+      <c r="C440" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -14294,8 +14293,8 @@
       <c r="B441" t="s">
         <v>849</v>
       </c>
-      <c r="C441" s="10" t="s">
-        <v>1400</v>
+      <c r="C441" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -14305,8 +14304,8 @@
       <c r="B442" t="s">
         <v>850</v>
       </c>
-      <c r="C442" s="10" t="s">
-        <v>1400</v>
+      <c r="C442" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -14316,8 +14315,8 @@
       <c r="B443" t="s">
         <v>851</v>
       </c>
-      <c r="C443" s="10" t="s">
-        <v>1400</v>
+      <c r="C443" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -14327,8 +14326,8 @@
       <c r="B444" t="s">
         <v>852</v>
       </c>
-      <c r="C444" s="10" t="s">
-        <v>1400</v>
+      <c r="C444" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -14338,8 +14337,8 @@
       <c r="B445" t="s">
         <v>853</v>
       </c>
-      <c r="C445" s="10" t="s">
-        <v>1400</v>
+      <c r="C445" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -14349,8 +14348,8 @@
       <c r="B446" t="s">
         <v>854</v>
       </c>
-      <c r="C446" s="10" t="s">
-        <v>1400</v>
+      <c r="C446" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -14360,8 +14359,8 @@
       <c r="B447" t="s">
         <v>855</v>
       </c>
-      <c r="C447" s="10" t="s">
-        <v>1400</v>
+      <c r="C447" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -14371,8 +14370,8 @@
       <c r="B448" t="s">
         <v>856</v>
       </c>
-      <c r="C448" s="10" t="s">
-        <v>1400</v>
+      <c r="C448" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -14382,8 +14381,8 @@
       <c r="B449" t="s">
         <v>857</v>
       </c>
-      <c r="C449" s="10" t="s">
-        <v>1400</v>
+      <c r="C449" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -14393,8 +14392,8 @@
       <c r="B450" t="s">
         <v>858</v>
       </c>
-      <c r="C450" s="10" t="s">
-        <v>1400</v>
+      <c r="C450" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -14404,8 +14403,8 @@
       <c r="B451" t="s">
         <v>859</v>
       </c>
-      <c r="C451" s="10" t="s">
-        <v>1400</v>
+      <c r="C451" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -14415,8 +14414,8 @@
       <c r="B452" t="s">
         <v>860</v>
       </c>
-      <c r="C452" s="10" t="s">
-        <v>1400</v>
+      <c r="C452" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -14426,8 +14425,8 @@
       <c r="B453" t="s">
         <v>861</v>
       </c>
-      <c r="C453" s="10" t="s">
-        <v>1400</v>
+      <c r="C453" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -14437,8 +14436,8 @@
       <c r="B454" t="s">
         <v>862</v>
       </c>
-      <c r="C454" s="10" t="s">
-        <v>1400</v>
+      <c r="C454" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -14448,8 +14447,8 @@
       <c r="B455" s="7" t="s">
         <v>1134</v>
       </c>
-      <c r="C455" s="10" t="s">
-        <v>1400</v>
+      <c r="C455" t="s">
+        <v>1399</v>
       </c>
       <c r="D455" s="2" t="s">
         <v>1127</v>
@@ -14462,8 +14461,8 @@
       <c r="B456" t="s">
         <v>863</v>
       </c>
-      <c r="C456" s="10" t="s">
-        <v>1400</v>
+      <c r="C456" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -14473,8 +14472,8 @@
       <c r="B457" t="s">
         <v>864</v>
       </c>
-      <c r="C457" s="10" t="s">
-        <v>1400</v>
+      <c r="C457" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -14484,8 +14483,8 @@
       <c r="B458" t="s">
         <v>865</v>
       </c>
-      <c r="C458" s="10" t="s">
-        <v>1400</v>
+      <c r="C458" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -14495,8 +14494,8 @@
       <c r="B459" t="s">
         <v>866</v>
       </c>
-      <c r="C459" s="10" t="s">
-        <v>1400</v>
+      <c r="C459" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -14506,8 +14505,8 @@
       <c r="B460" t="s">
         <v>1085</v>
       </c>
-      <c r="C460" s="10" t="s">
-        <v>1400</v>
+      <c r="C460" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -14517,8 +14516,8 @@
       <c r="B461" s="5" t="s">
         <v>1182</v>
       </c>
-      <c r="C461" s="10" t="s">
-        <v>1400</v>
+      <c r="C461" t="s">
+        <v>1399</v>
       </c>
       <c r="D461" s="2" t="s">
         <v>1127</v>
@@ -14531,8 +14530,8 @@
       <c r="B463" t="s">
         <v>1078</v>
       </c>
-      <c r="C463" s="10" t="s">
-        <v>1400</v>
+      <c r="C463" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -14542,8 +14541,8 @@
       <c r="B464" t="s">
         <v>890</v>
       </c>
-      <c r="C464" s="10" t="s">
-        <v>1400</v>
+      <c r="C464" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -14553,8 +14552,8 @@
       <c r="B465" t="s">
         <v>891</v>
       </c>
-      <c r="C465" s="10" t="s">
-        <v>1400</v>
+      <c r="C465" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -14564,8 +14563,8 @@
       <c r="B466" t="s">
         <v>892</v>
       </c>
-      <c r="C466" s="10" t="s">
-        <v>1400</v>
+      <c r="C466" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -14575,8 +14574,8 @@
       <c r="B467" t="s">
         <v>893</v>
       </c>
-      <c r="C467" s="10" t="s">
-        <v>1400</v>
+      <c r="C467" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -14586,8 +14585,8 @@
       <c r="B468" t="s">
         <v>894</v>
       </c>
-      <c r="C468" s="10" t="s">
-        <v>1400</v>
+      <c r="C468" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -14597,8 +14596,8 @@
       <c r="B469" t="s">
         <v>1103</v>
       </c>
-      <c r="C469" s="10" t="s">
-        <v>1400</v>
+      <c r="C469" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -14608,8 +14607,8 @@
       <c r="B470" t="s">
         <v>895</v>
       </c>
-      <c r="C470" s="10" t="s">
-        <v>1400</v>
+      <c r="C470" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -14619,8 +14618,8 @@
       <c r="B471" t="s">
         <v>1104</v>
       </c>
-      <c r="C471" s="10" t="s">
-        <v>1400</v>
+      <c r="C471" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -14630,8 +14629,8 @@
       <c r="B472" t="s">
         <v>1105</v>
       </c>
-      <c r="C472" s="10" t="s">
-        <v>1400</v>
+      <c r="C472" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -14641,8 +14640,8 @@
       <c r="B473" t="s">
         <v>1093</v>
       </c>
-      <c r="C473" s="10" t="s">
-        <v>1400</v>
+      <c r="C473" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -14652,8 +14651,8 @@
       <c r="B474" s="5" t="s">
         <v>1183</v>
       </c>
-      <c r="C474" s="10" t="s">
-        <v>1400</v>
+      <c r="C474" t="s">
+        <v>1399</v>
       </c>
       <c r="D474" s="2" t="s">
         <v>1127</v>
@@ -14666,8 +14665,8 @@
       <c r="B476" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="C476" s="10" t="s">
-        <v>1400</v>
+      <c r="C476" t="s">
+        <v>1399</v>
       </c>
       <c r="D476" s="2" t="s">
         <v>1127</v>
@@ -14680,8 +14679,8 @@
       <c r="B477" s="6" t="s">
         <v>1185</v>
       </c>
-      <c r="C477" s="10" t="s">
-        <v>1400</v>
+      <c r="C477" t="s">
+        <v>1399</v>
       </c>
       <c r="D477" s="6" t="s">
         <v>1131</v>
@@ -14694,8 +14693,8 @@
       <c r="B479" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="C479" s="10" t="s">
-        <v>1400</v>
+      <c r="C479" t="s">
+        <v>1399</v>
       </c>
       <c r="D479" s="6" t="s">
         <v>1131</v>
@@ -14708,8 +14707,8 @@
       <c r="B480" s="5" t="s">
         <v>1186</v>
       </c>
-      <c r="C480" s="10" t="s">
-        <v>1400</v>
+      <c r="C480" t="s">
+        <v>1399</v>
       </c>
       <c r="D480" s="2" t="s">
         <v>1127</v>
@@ -14722,8 +14721,8 @@
       <c r="B482" t="s">
         <v>915</v>
       </c>
-      <c r="C482" s="10" t="s">
-        <v>1400</v>
+      <c r="C482" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -14733,8 +14732,8 @@
       <c r="B483" t="s">
         <v>916</v>
       </c>
-      <c r="C483" s="10" t="s">
-        <v>1400</v>
+      <c r="C483" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -14744,8 +14743,8 @@
       <c r="B484" t="s">
         <v>1110</v>
       </c>
-      <c r="C484" s="10" t="s">
-        <v>1400</v>
+      <c r="C484" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -14755,8 +14754,8 @@
       <c r="B485" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="C485" s="10" t="s">
-        <v>1400</v>
+      <c r="C485" t="s">
+        <v>1399</v>
       </c>
       <c r="D485" s="2" t="s">
         <v>1127</v>
@@ -14769,8 +14768,8 @@
       <c r="B487" t="s">
         <v>1188</v>
       </c>
-      <c r="C487" s="10" t="s">
-        <v>1400</v>
+      <c r="C487" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -14780,8 +14779,8 @@
       <c r="B488" t="s">
         <v>922</v>
       </c>
-      <c r="C488" s="10" t="s">
-        <v>1400</v>
+      <c r="C488" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -14791,8 +14790,8 @@
       <c r="B489" t="s">
         <v>923</v>
       </c>
-      <c r="C489" s="10" t="s">
-        <v>1400</v>
+      <c r="C489" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -14802,8 +14801,8 @@
       <c r="B490" t="s">
         <v>924</v>
       </c>
-      <c r="C490" s="10" t="s">
-        <v>1400</v>
+      <c r="C490" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -14813,8 +14812,8 @@
       <c r="B491" t="s">
         <v>925</v>
       </c>
-      <c r="C491" s="10" t="s">
-        <v>1400</v>
+      <c r="C491" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -14824,8 +14823,8 @@
       <c r="B492" t="s">
         <v>926</v>
       </c>
-      <c r="C492" s="10" t="s">
-        <v>1400</v>
+      <c r="C492" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -14835,8 +14834,8 @@
       <c r="B493" s="7" t="s">
         <v>1189</v>
       </c>
-      <c r="C493" s="10" t="s">
-        <v>1400</v>
+      <c r="C493" t="s">
+        <v>1399</v>
       </c>
       <c r="D493" s="2" t="s">
         <v>1127</v>
@@ -14849,8 +14848,8 @@
       <c r="B495" t="s">
         <v>938</v>
       </c>
-      <c r="C495" s="10" t="s">
-        <v>1400</v>
+      <c r="C495" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -14860,8 +14859,8 @@
       <c r="B496" t="s">
         <v>939</v>
       </c>
-      <c r="C496" s="10" t="s">
-        <v>1400</v>
+      <c r="C496" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -14871,8 +14870,8 @@
       <c r="B497" t="s">
         <v>940</v>
       </c>
-      <c r="C497" s="10" t="s">
-        <v>1400</v>
+      <c r="C497" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -14882,8 +14881,8 @@
       <c r="B498" t="s">
         <v>941</v>
       </c>
-      <c r="C498" s="10" t="s">
-        <v>1400</v>
+      <c r="C498" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -14893,8 +14892,8 @@
       <c r="B499" t="s">
         <v>942</v>
       </c>
-      <c r="C499" s="10" t="s">
-        <v>1400</v>
+      <c r="C499" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -14904,8 +14903,8 @@
       <c r="B500" s="7" t="s">
         <v>1139</v>
       </c>
-      <c r="C500" s="10" t="s">
-        <v>1400</v>
+      <c r="C500" t="s">
+        <v>1399</v>
       </c>
       <c r="D500" s="2" t="s">
         <v>1127</v>
@@ -14918,8 +14917,8 @@
       <c r="B502" t="s">
         <v>949</v>
       </c>
-      <c r="C502" s="10" t="s">
-        <v>1400</v>
+      <c r="C502" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -14929,8 +14928,8 @@
       <c r="B503" t="s">
         <v>950</v>
       </c>
-      <c r="C503" s="10" t="s">
-        <v>1400</v>
+      <c r="C503" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -14940,8 +14939,8 @@
       <c r="B504" t="s">
         <v>951</v>
       </c>
-      <c r="C504" s="10" t="s">
-        <v>1400</v>
+      <c r="C504" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -14951,8 +14950,8 @@
       <c r="B505" t="s">
         <v>952</v>
       </c>
-      <c r="C505" s="10" t="s">
-        <v>1400</v>
+      <c r="C505" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -14962,8 +14961,8 @@
       <c r="B506" t="s">
         <v>953</v>
       </c>
-      <c r="C506" s="10" t="s">
-        <v>1400</v>
+      <c r="C506" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="507" spans="1:4" s="6" customFormat="1">
@@ -14973,8 +14972,8 @@
       <c r="B507" s="6" t="s">
         <v>1079</v>
       </c>
-      <c r="C507" s="10" t="s">
-        <v>1400</v>
+      <c r="C507" t="s">
+        <v>1399</v>
       </c>
       <c r="D507" s="6" t="s">
         <v>1131</v>
@@ -14987,8 +14986,8 @@
       <c r="B509" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="C509" s="10" t="s">
-        <v>1400</v>
+      <c r="C509" t="s">
+        <v>1399</v>
       </c>
       <c r="D509" s="6" t="s">
         <v>1131</v>
@@ -15001,8 +15000,8 @@
       <c r="B510" t="s">
         <v>963</v>
       </c>
-      <c r="C510" s="10" t="s">
-        <v>1400</v>
+      <c r="C510" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -15012,8 +15011,8 @@
       <c r="B511" t="s">
         <v>964</v>
       </c>
-      <c r="C511" s="10" t="s">
-        <v>1400</v>
+      <c r="C511" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -15023,8 +15022,8 @@
       <c r="B512" t="s">
         <v>965</v>
       </c>
-      <c r="C512" s="10" t="s">
-        <v>1400</v>
+      <c r="C512" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -15034,8 +15033,8 @@
       <c r="B513" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="C513" s="10" t="s">
-        <v>1400</v>
+      <c r="C513" t="s">
+        <v>1399</v>
       </c>
       <c r="D513" s="2" t="s">
         <v>1127</v>
@@ -15048,8 +15047,8 @@
       <c r="B515" t="s">
         <v>991</v>
       </c>
-      <c r="C515" s="10" t="s">
-        <v>1400</v>
+      <c r="C515" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -15059,8 +15058,8 @@
       <c r="B516" t="s">
         <v>992</v>
       </c>
-      <c r="C516" s="10" t="s">
-        <v>1400</v>
+      <c r="C516" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -15070,8 +15069,8 @@
       <c r="B517" t="s">
         <v>993</v>
       </c>
-      <c r="C517" s="10" t="s">
-        <v>1400</v>
+      <c r="C517" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -15081,8 +15080,8 @@
       <c r="B518" t="s">
         <v>994</v>
       </c>
-      <c r="C518" s="10" t="s">
-        <v>1400</v>
+      <c r="C518" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -15092,8 +15091,8 @@
       <c r="B519" t="s">
         <v>995</v>
       </c>
-      <c r="C519" s="10" t="s">
-        <v>1400</v>
+      <c r="C519" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -15103,8 +15102,8 @@
       <c r="B520" t="s">
         <v>996</v>
       </c>
-      <c r="C520" s="10" t="s">
-        <v>1400</v>
+      <c r="C520" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -15114,8 +15113,8 @@
       <c r="B521" t="s">
         <v>997</v>
       </c>
-      <c r="C521" s="10" t="s">
-        <v>1400</v>
+      <c r="C521" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -15125,8 +15124,8 @@
       <c r="B522" t="s">
         <v>998</v>
       </c>
-      <c r="C522" s="10" t="s">
-        <v>1400</v>
+      <c r="C522" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -15136,8 +15135,8 @@
       <c r="B523" t="s">
         <v>999</v>
       </c>
-      <c r="C523" s="10" t="s">
-        <v>1400</v>
+      <c r="C523" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -15147,8 +15146,8 @@
       <c r="B524" t="s">
         <v>1000</v>
       </c>
-      <c r="C524" s="10" t="s">
-        <v>1400</v>
+      <c r="C524" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -15158,8 +15157,8 @@
       <c r="B525" t="s">
         <v>1001</v>
       </c>
-      <c r="C525" s="10" t="s">
-        <v>1400</v>
+      <c r="C525" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -15169,8 +15168,8 @@
       <c r="B526" t="s">
         <v>1002</v>
       </c>
-      <c r="C526" s="10" t="s">
-        <v>1400</v>
+      <c r="C526" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -15180,8 +15179,8 @@
       <c r="B527" t="s">
         <v>1003</v>
       </c>
-      <c r="C527" s="10" t="s">
-        <v>1400</v>
+      <c r="C527" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -15191,8 +15190,8 @@
       <c r="B528" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C528" s="10" t="s">
-        <v>1400</v>
+      <c r="C528" t="s">
+        <v>1399</v>
       </c>
       <c r="D528" s="2" t="s">
         <v>1127</v>
@@ -15205,8 +15204,8 @@
       <c r="B530" t="s">
         <v>1209</v>
       </c>
-      <c r="C530" s="10" t="s">
-        <v>1400</v>
+      <c r="C530" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -15216,8 +15215,8 @@
       <c r="B531" t="s">
         <v>1210</v>
       </c>
-      <c r="C531" s="10" t="s">
-        <v>1400</v>
+      <c r="C531" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -15227,8 +15226,8 @@
       <c r="B532" t="s">
         <v>1211</v>
       </c>
-      <c r="C532" s="10" t="s">
-        <v>1400</v>
+      <c r="C532" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -15238,8 +15237,8 @@
       <c r="B533" t="s">
         <v>1212</v>
       </c>
-      <c r="C533" s="10" t="s">
-        <v>1400</v>
+      <c r="C533" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -15249,8 +15248,8 @@
       <c r="B534" t="s">
         <v>1213</v>
       </c>
-      <c r="C534" s="10" t="s">
-        <v>1400</v>
+      <c r="C534" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -15260,8 +15259,8 @@
       <c r="B535" t="s">
         <v>1214</v>
       </c>
-      <c r="C535" s="10" t="s">
-        <v>1400</v>
+      <c r="C535" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -15271,8 +15270,8 @@
       <c r="B536" t="s">
         <v>1215</v>
       </c>
-      <c r="C536" s="10" t="s">
-        <v>1400</v>
+      <c r="C536" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -15282,8 +15281,8 @@
       <c r="B537" t="s">
         <v>1216</v>
       </c>
-      <c r="C537" s="10" t="s">
-        <v>1401</v>
+      <c r="C537" t="s">
+        <v>1400</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -15293,8 +15292,8 @@
       <c r="B538" t="s">
         <v>1217</v>
       </c>
-      <c r="C538" s="10" t="s">
-        <v>1400</v>
+      <c r="C538" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -15304,8 +15303,8 @@
       <c r="B539" t="s">
         <v>1218</v>
       </c>
-      <c r="C539" s="10" t="s">
-        <v>1400</v>
+      <c r="C539" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -15315,8 +15314,8 @@
       <c r="B540" t="s">
         <v>1219</v>
       </c>
-      <c r="C540" s="10" t="s">
-        <v>1400</v>
+      <c r="C540" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -15326,8 +15325,8 @@
       <c r="B541" t="s">
         <v>1220</v>
       </c>
-      <c r="C541" s="10" t="s">
-        <v>1400</v>
+      <c r="C541" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -15337,8 +15336,8 @@
       <c r="B542" t="s">
         <v>1221</v>
       </c>
-      <c r="C542" s="10" t="s">
-        <v>1400</v>
+      <c r="C542" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -15348,8 +15347,8 @@
       <c r="B543" t="s">
         <v>1222</v>
       </c>
-      <c r="C543" s="10" t="s">
-        <v>1400</v>
+      <c r="C543" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -15359,8 +15358,8 @@
       <c r="B544" t="s">
         <v>1223</v>
       </c>
-      <c r="C544" s="10" t="s">
-        <v>1400</v>
+      <c r="C544" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -15370,8 +15369,8 @@
       <c r="B545" t="s">
         <v>1224</v>
       </c>
-      <c r="C545" s="10" t="s">
-        <v>1400</v>
+      <c r="C545" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -15381,8 +15380,8 @@
       <c r="B546" t="s">
         <v>1225</v>
       </c>
-      <c r="C546" s="10" t="s">
-        <v>1400</v>
+      <c r="C546" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -15392,8 +15391,8 @@
       <c r="B547" t="s">
         <v>1226</v>
       </c>
-      <c r="C547" s="10" t="s">
-        <v>1400</v>
+      <c r="C547" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -15403,8 +15402,8 @@
       <c r="B548" t="s">
         <v>1227</v>
       </c>
-      <c r="C548" s="10" t="s">
-        <v>1400</v>
+      <c r="C548" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -15414,8 +15413,8 @@
       <c r="B549" t="s">
         <v>1228</v>
       </c>
-      <c r="C549" s="10" t="s">
-        <v>1400</v>
+      <c r="C549" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -15425,8 +15424,8 @@
       <c r="B550" t="s">
         <v>1229</v>
       </c>
-      <c r="C550" s="10" t="s">
-        <v>1400</v>
+      <c r="C550" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -15436,8 +15435,8 @@
       <c r="B551" t="s">
         <v>1230</v>
       </c>
-      <c r="C551" s="10" t="s">
-        <v>1400</v>
+      <c r="C551" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -15447,8 +15446,8 @@
       <c r="B552" t="s">
         <v>1231</v>
       </c>
-      <c r="C552" s="10" t="s">
-        <v>1400</v>
+      <c r="C552" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -15458,8 +15457,8 @@
       <c r="B553" t="s">
         <v>1232</v>
       </c>
-      <c r="C553" s="10" t="s">
-        <v>1400</v>
+      <c r="C553" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -15469,8 +15468,8 @@
       <c r="B554" t="s">
         <v>1233</v>
       </c>
-      <c r="C554" s="10" t="s">
-        <v>1400</v>
+      <c r="C554" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -15480,8 +15479,8 @@
       <c r="B555" t="s">
         <v>1234</v>
       </c>
-      <c r="C555" s="10" t="s">
-        <v>1400</v>
+      <c r="C555" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -15491,8 +15490,8 @@
       <c r="B556" t="s">
         <v>1235</v>
       </c>
-      <c r="C556" s="10" t="s">
-        <v>1400</v>
+      <c r="C556" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -15502,8 +15501,8 @@
       <c r="B557" t="s">
         <v>1236</v>
       </c>
-      <c r="C557" s="10" t="s">
-        <v>1400</v>
+      <c r="C557" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -15513,8 +15512,8 @@
       <c r="B558" t="s">
         <v>1237</v>
       </c>
-      <c r="C558" s="10" t="s">
-        <v>1400</v>
+      <c r="C558" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -15524,8 +15523,8 @@
       <c r="B559" t="s">
         <v>1238</v>
       </c>
-      <c r="C559" s="10" t="s">
-        <v>1400</v>
+      <c r="C559" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -15535,8 +15534,8 @@
       <c r="B560" t="s">
         <v>1239</v>
       </c>
-      <c r="C560" s="10" t="s">
-        <v>1400</v>
+      <c r="C560" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -15546,8 +15545,8 @@
       <c r="B561" t="s">
         <v>1240</v>
       </c>
-      <c r="C561" s="10" t="s">
-        <v>1400</v>
+      <c r="C561" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -15557,8 +15556,8 @@
       <c r="B562" t="s">
         <v>1241</v>
       </c>
-      <c r="C562" s="10" t="s">
-        <v>1400</v>
+      <c r="C562" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -15568,8 +15567,8 @@
       <c r="B563" t="s">
         <v>1242</v>
       </c>
-      <c r="C563" s="10" t="s">
-        <v>1400</v>
+      <c r="C563" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -15579,8 +15578,8 @@
       <c r="B564" t="s">
         <v>1243</v>
       </c>
-      <c r="C564" s="10" t="s">
-        <v>1400</v>
+      <c r="C564" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -15590,8 +15589,8 @@
       <c r="B565" t="s">
         <v>1244</v>
       </c>
-      <c r="C565" s="10" t="s">
-        <v>1400</v>
+      <c r="C565" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -15601,8 +15600,8 @@
       <c r="B566" t="s">
         <v>1245</v>
       </c>
-      <c r="C566" s="10" t="s">
-        <v>1400</v>
+      <c r="C566" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -15612,8 +15611,8 @@
       <c r="B567" t="s">
         <v>1246</v>
       </c>
-      <c r="C567" s="10" t="s">
-        <v>1400</v>
+      <c r="C567" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -15623,8 +15622,8 @@
       <c r="B568" t="s">
         <v>1247</v>
       </c>
-      <c r="C568" s="10" t="s">
-        <v>1400</v>
+      <c r="C568" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -15634,8 +15633,8 @@
       <c r="B569" t="s">
         <v>1248</v>
       </c>
-      <c r="C569" s="10" t="s">
-        <v>1400</v>
+      <c r="C569" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -15645,8 +15644,8 @@
       <c r="B570" t="s">
         <v>1249</v>
       </c>
-      <c r="C570" s="10" t="s">
-        <v>1400</v>
+      <c r="C570" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -15656,8 +15655,8 @@
       <c r="B571" t="s">
         <v>1250</v>
       </c>
-      <c r="C571" s="10" t="s">
-        <v>1400</v>
+      <c r="C571" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -15667,8 +15666,8 @@
       <c r="B572" t="s">
         <v>1251</v>
       </c>
-      <c r="C572" s="10" t="s">
-        <v>1400</v>
+      <c r="C572" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -15678,8 +15677,8 @@
       <c r="B573" t="s">
         <v>1252</v>
       </c>
-      <c r="C573" s="10" t="s">
-        <v>1400</v>
+      <c r="C573" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -15689,8 +15688,8 @@
       <c r="B574" t="s">
         <v>1253</v>
       </c>
-      <c r="C574" s="10" t="s">
-        <v>1400</v>
+      <c r="C574" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -15700,8 +15699,8 @@
       <c r="B575" t="s">
         <v>1254</v>
       </c>
-      <c r="C575" s="10" t="s">
-        <v>1400</v>
+      <c r="C575" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -15711,8 +15710,8 @@
       <c r="B576" t="s">
         <v>1255</v>
       </c>
-      <c r="C576" s="10" t="s">
-        <v>1400</v>
+      <c r="C576" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -15722,8 +15721,8 @@
       <c r="B577" t="s">
         <v>1256</v>
       </c>
-      <c r="C577" s="10" t="s">
-        <v>1400</v>
+      <c r="C577" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -15733,8 +15732,8 @@
       <c r="B578" t="s">
         <v>1257</v>
       </c>
-      <c r="C578" s="10" t="s">
-        <v>1400</v>
+      <c r="C578" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -15744,8 +15743,8 @@
       <c r="B579" t="s">
         <v>1258</v>
       </c>
-      <c r="C579" s="10" t="s">
-        <v>1400</v>
+      <c r="C579" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -15755,8 +15754,8 @@
       <c r="B580" t="s">
         <v>1259</v>
       </c>
-      <c r="C580" s="10" t="s">
-        <v>1400</v>
+      <c r="C580" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -15766,8 +15765,8 @@
       <c r="B581" t="s">
         <v>1260</v>
       </c>
-      <c r="C581" s="10" t="s">
-        <v>1400</v>
+      <c r="C581" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -15777,8 +15776,8 @@
       <c r="B582" t="s">
         <v>1261</v>
       </c>
-      <c r="C582" s="10" t="s">
-        <v>1400</v>
+      <c r="C582" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -15788,8 +15787,8 @@
       <c r="B583" t="s">
         <v>1262</v>
       </c>
-      <c r="C583" s="10" t="s">
-        <v>1400</v>
+      <c r="C583" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -15799,8 +15798,8 @@
       <c r="B584" t="s">
         <v>1263</v>
       </c>
-      <c r="C584" s="10" t="s">
-        <v>1400</v>
+      <c r="C584" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -15810,8 +15809,8 @@
       <c r="B585" t="s">
         <v>1264</v>
       </c>
-      <c r="C585" s="10" t="s">
-        <v>1400</v>
+      <c r="C585" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -15821,8 +15820,8 @@
       <c r="B586" t="s">
         <v>1265</v>
       </c>
-      <c r="C586" s="10" t="s">
-        <v>1400</v>
+      <c r="C586" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -15832,8 +15831,8 @@
       <c r="B587" t="s">
         <v>1266</v>
       </c>
-      <c r="C587" s="10" t="s">
-        <v>1400</v>
+      <c r="C587" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -15843,8 +15842,8 @@
       <c r="B588" t="s">
         <v>1267</v>
       </c>
-      <c r="C588" s="10" t="s">
-        <v>1400</v>
+      <c r="C588" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -15854,8 +15853,8 @@
       <c r="B589" t="s">
         <v>1268</v>
       </c>
-      <c r="C589" s="10" t="s">
-        <v>1400</v>
+      <c r="C589" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -15865,8 +15864,8 @@
       <c r="B590" t="s">
         <v>1269</v>
       </c>
-      <c r="C590" s="10" t="s">
-        <v>1400</v>
+      <c r="C590" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -15876,8 +15875,8 @@
       <c r="B591" t="s">
         <v>1270</v>
       </c>
-      <c r="C591" s="10" t="s">
-        <v>1400</v>
+      <c r="C591" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -15887,8 +15886,8 @@
       <c r="B592" t="s">
         <v>1271</v>
       </c>
-      <c r="C592" s="10" t="s">
-        <v>1400</v>
+      <c r="C592" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -15898,8 +15897,8 @@
       <c r="B593" t="s">
         <v>1272</v>
       </c>
-      <c r="C593" s="10" t="s">
-        <v>1400</v>
+      <c r="C593" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -15909,8 +15908,8 @@
       <c r="B594" t="s">
         <v>1273</v>
       </c>
-      <c r="C594" s="10" t="s">
-        <v>1400</v>
+      <c r="C594" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -15920,8 +15919,8 @@
       <c r="B595" t="s">
         <v>1274</v>
       </c>
-      <c r="C595" s="10" t="s">
-        <v>1400</v>
+      <c r="C595" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -15931,8 +15930,8 @@
       <c r="B596" t="s">
         <v>1275</v>
       </c>
-      <c r="C596" s="10" t="s">
-        <v>1400</v>
+      <c r="C596" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -15942,8 +15941,8 @@
       <c r="B597" t="s">
         <v>1276</v>
       </c>
-      <c r="C597" s="10" t="s">
-        <v>1400</v>
+      <c r="C597" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -15953,8 +15952,8 @@
       <c r="B598" t="s">
         <v>1277</v>
       </c>
-      <c r="C598" s="10" t="s">
-        <v>1400</v>
+      <c r="C598" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -15964,8 +15963,8 @@
       <c r="B599" t="s">
         <v>1278</v>
       </c>
-      <c r="C599" s="10" t="s">
-        <v>1400</v>
+      <c r="C599" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -15975,8 +15974,8 @@
       <c r="B600" t="s">
         <v>1279</v>
       </c>
-      <c r="C600" s="10" t="s">
-        <v>1400</v>
+      <c r="C600" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -15986,8 +15985,8 @@
       <c r="B601" t="s">
         <v>1280</v>
       </c>
-      <c r="C601" s="10" t="s">
-        <v>1400</v>
+      <c r="C601" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -15997,8 +15996,8 @@
       <c r="B602" t="s">
         <v>1281</v>
       </c>
-      <c r="C602" s="10" t="s">
-        <v>1400</v>
+      <c r="C602" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -16008,8 +16007,8 @@
       <c r="B603" t="s">
         <v>1282</v>
       </c>
-      <c r="C603" s="10" t="s">
-        <v>1400</v>
+      <c r="C603" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -16019,8 +16018,8 @@
       <c r="B604" t="s">
         <v>1283</v>
       </c>
-      <c r="C604" s="10" t="s">
-        <v>1400</v>
+      <c r="C604" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -16030,8 +16029,8 @@
       <c r="B605" t="s">
         <v>1284</v>
       </c>
-      <c r="C605" s="10" t="s">
-        <v>1400</v>
+      <c r="C605" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -16041,8 +16040,8 @@
       <c r="B606" t="s">
         <v>1285</v>
       </c>
-      <c r="C606" s="10" t="s">
-        <v>1400</v>
+      <c r="C606" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -16052,8 +16051,8 @@
       <c r="B607" t="s">
         <v>1286</v>
       </c>
-      <c r="C607" s="10" t="s">
-        <v>1400</v>
+      <c r="C607" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -16063,8 +16062,8 @@
       <c r="B608" t="s">
         <v>1287</v>
       </c>
-      <c r="C608" s="10" t="s">
-        <v>1400</v>
+      <c r="C608" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -16074,8 +16073,8 @@
       <c r="B609" t="s">
         <v>1288</v>
       </c>
-      <c r="C609" s="10" t="s">
-        <v>1400</v>
+      <c r="C609" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -16085,8 +16084,8 @@
       <c r="B610" t="s">
         <v>1289</v>
       </c>
-      <c r="C610" s="10" t="s">
-        <v>1400</v>
+      <c r="C610" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -16096,8 +16095,8 @@
       <c r="B611" t="s">
         <v>1290</v>
       </c>
-      <c r="C611" s="10" t="s">
-        <v>1400</v>
+      <c r="C611" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -16107,8 +16106,8 @@
       <c r="B612" t="s">
         <v>1291</v>
       </c>
-      <c r="C612" s="10" t="s">
-        <v>1400</v>
+      <c r="C612" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -16118,8 +16117,8 @@
       <c r="B613" t="s">
         <v>1292</v>
       </c>
-      <c r="C613" s="10" t="s">
-        <v>1400</v>
+      <c r="C613" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -16129,8 +16128,8 @@
       <c r="B614" t="s">
         <v>1293</v>
       </c>
-      <c r="C614" s="10" t="s">
-        <v>1400</v>
+      <c r="C614" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -16140,8 +16139,8 @@
       <c r="B615" t="s">
         <v>1294</v>
       </c>
-      <c r="C615" s="10" t="s">
-        <v>1400</v>
+      <c r="C615" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -16151,8 +16150,8 @@
       <c r="B616" t="s">
         <v>1295</v>
       </c>
-      <c r="C616" s="10" t="s">
-        <v>1400</v>
+      <c r="C616" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -16162,8 +16161,8 @@
       <c r="B617" t="s">
         <v>1296</v>
       </c>
-      <c r="C617" s="10" t="s">
-        <v>1400</v>
+      <c r="C617" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -16173,8 +16172,8 @@
       <c r="B618" t="s">
         <v>1297</v>
       </c>
-      <c r="C618" s="10" t="s">
-        <v>1400</v>
+      <c r="C618" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -16184,8 +16183,8 @@
       <c r="B619" t="s">
         <v>1298</v>
       </c>
-      <c r="C619" s="10" t="s">
-        <v>1400</v>
+      <c r="C619" t="s">
+        <v>1399</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1028\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5571271E-9C6D-4B6F-A536-0A645DE5B364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059DD523-6F96-4FA2-B934-F7A3DBD700F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22560" windowHeight="11655" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="1402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="1403">
   <si>
     <t>Name</t>
   </si>
@@ -4249,6 +4249,9 @@
   </si>
   <si>
     <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>COLACalcDate</t>
   </si>
 </sst>
 </file>
@@ -8384,7 +8387,14 @@
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="60" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A60" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1402</v>
+      </c>
+    </row>
     <row r="61" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="62" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="63" spans="1:4" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Audit-Findings-Library\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1030\Application-Review-Audit-Findings-Library\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139B8686-1B9F-41B4-95AB-9377B86A07D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6403A797-F270-4DFC-9F2F-C2E6D11ECDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22560" windowHeight="11655" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -4251,9 +4251,6 @@
     <t>COLACalcDate</t>
   </si>
   <si>
-    <t>C:\Users\Raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
     <t>Finding</t>
   </si>
   <si>
@@ -4261,6 +4258,9 @@
   </si>
   <si>
     <t>HAP Contract</t>
+  </si>
+  <si>
+    <t>C:\Users\harmandeep.singh\Documents\AZApplicationReview\Prompts\</t>
   </si>
 </sst>
 </file>
@@ -4336,7 +4336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4351,7 +4351,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4759,7 +4758,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -9375,7 +9374,7 @@
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="148.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="102.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -9388,7 +9387,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1398</v>
@@ -9401,8 +9400,8 @@
       <c r="B3" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>1404</v>
+      <c r="C3" t="s">
+        <v>1403</v>
       </c>
       <c r="D3" t="s">
         <v>1399</v>
@@ -9415,8 +9414,8 @@
       <c r="B5" t="s">
         <v>1056</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>1404</v>
+      <c r="C5" t="s">
+        <v>1403</v>
       </c>
       <c r="D5" t="s">
         <v>1399</v>
@@ -9429,8 +9428,8 @@
       <c r="B6" t="s">
         <v>1392</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>1404</v>
+      <c r="C6" t="s">
+        <v>1403</v>
       </c>
       <c r="D6" t="s">
         <v>1399</v>
@@ -9443,8 +9442,8 @@
       <c r="B8" t="s">
         <v>646</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>1404</v>
+      <c r="C8" t="s">
+        <v>1403</v>
       </c>
       <c r="D8" t="s">
         <v>1399</v>
@@ -9460,8 +9459,8 @@
       <c r="B9" t="s">
         <v>647</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>1404</v>
+      <c r="C9" t="s">
+        <v>1403</v>
       </c>
       <c r="D9" t="s">
         <v>1399</v>
@@ -9477,8 +9476,8 @@
       <c r="B10" t="s">
         <v>648</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>1404</v>
+      <c r="C10" t="s">
+        <v>1403</v>
       </c>
       <c r="D10" t="s">
         <v>1399</v>
@@ -9494,8 +9493,8 @@
       <c r="B11" t="s">
         <v>650</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>1404</v>
+      <c r="C11" t="s">
+        <v>1403</v>
       </c>
       <c r="D11" t="s">
         <v>1399</v>
@@ -9511,8 +9510,8 @@
       <c r="B12" t="s">
         <v>649</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>1404</v>
+      <c r="C12" t="s">
+        <v>1403</v>
       </c>
       <c r="D12" t="s">
         <v>1399</v>
@@ -9528,8 +9527,8 @@
       <c r="B13" t="s">
         <v>676</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>1404</v>
+      <c r="C13" t="s">
+        <v>1403</v>
       </c>
       <c r="D13" t="s">
         <v>1399</v>
@@ -9545,8 +9544,8 @@
       <c r="B14" s="7" t="s">
         <v>1140</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>1404</v>
+      <c r="C14" t="s">
+        <v>1403</v>
       </c>
       <c r="D14" t="s">
         <v>1399</v>
@@ -9562,8 +9561,8 @@
       <c r="B16" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>1404</v>
+      <c r="C16" t="s">
+        <v>1403</v>
       </c>
       <c r="D16" t="s">
         <v>1399</v>
@@ -9576,8 +9575,8 @@
       <c r="B17" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>1404</v>
+      <c r="C17" t="s">
+        <v>1403</v>
       </c>
       <c r="D17" t="s">
         <v>1399</v>
@@ -9590,8 +9589,8 @@
       <c r="B18" t="s">
         <v>172</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>1404</v>
+      <c r="C18" t="s">
+        <v>1403</v>
       </c>
       <c r="D18" t="s">
         <v>1399</v>
@@ -9604,8 +9603,8 @@
       <c r="B19" t="s">
         <v>1100</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>1404</v>
+      <c r="C19" t="s">
+        <v>1403</v>
       </c>
       <c r="D19" t="s">
         <v>1399</v>
@@ -9618,8 +9617,8 @@
       <c r="B20" t="s">
         <v>198</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>1404</v>
+      <c r="C20" t="s">
+        <v>1403</v>
       </c>
       <c r="D20" t="s">
         <v>1399</v>
@@ -9635,8 +9634,8 @@
       <c r="B21" t="s">
         <v>490</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>1404</v>
+      <c r="C21" t="s">
+        <v>1403</v>
       </c>
       <c r="D21" t="s">
         <v>1399</v>
@@ -9649,8 +9648,8 @@
       <c r="B22" s="5" t="s">
         <v>1126</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>1404</v>
+      <c r="C22" t="s">
+        <v>1403</v>
       </c>
       <c r="D22" t="s">
         <v>1399</v>
@@ -9666,8 +9665,8 @@
       <c r="B23" s="5" t="s">
         <v>1141</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>1404</v>
+      <c r="C23" t="s">
+        <v>1403</v>
       </c>
       <c r="D23" t="s">
         <v>1399</v>
@@ -9683,8 +9682,8 @@
       <c r="B24" t="s">
         <v>602</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>1404</v>
+      <c r="C24" t="s">
+        <v>1403</v>
       </c>
       <c r="D24" t="s">
         <v>1399</v>
@@ -9700,8 +9699,8 @@
       <c r="B25" s="5" t="s">
         <v>1142</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>1404</v>
+      <c r="C25" t="s">
+        <v>1403</v>
       </c>
       <c r="D25" t="s">
         <v>1399</v>
@@ -9717,8 +9716,8 @@
       <c r="B26" s="5" t="s">
         <v>1143</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>1404</v>
+      <c r="C26" t="s">
+        <v>1403</v>
       </c>
       <c r="D26" t="s">
         <v>1399</v>
@@ -9734,8 +9733,8 @@
       <c r="B27" s="5" t="s">
         <v>1128</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>1404</v>
+      <c r="C27" t="s">
+        <v>1403</v>
       </c>
       <c r="D27" t="s">
         <v>1399</v>
@@ -9751,8 +9750,8 @@
       <c r="B28" s="5" t="s">
         <v>1144</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>1404</v>
+      <c r="C28" t="s">
+        <v>1403</v>
       </c>
       <c r="D28" t="s">
         <v>1399</v>
@@ -9768,8 +9767,8 @@
       <c r="B29" s="5" t="s">
         <v>1394</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>1404</v>
+      <c r="C29" t="s">
+        <v>1403</v>
       </c>
       <c r="D29" t="s">
         <v>1399</v>
@@ -9785,8 +9784,8 @@
       <c r="B30" s="5" t="s">
         <v>1397</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>1404</v>
+      <c r="C30" t="s">
+        <v>1403</v>
       </c>
       <c r="D30" t="s">
         <v>1399</v>
@@ -9802,8 +9801,8 @@
       <c r="B31" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>1404</v>
+      <c r="C31" t="s">
+        <v>1403</v>
       </c>
       <c r="D31" t="s">
         <v>1399</v>
@@ -9816,8 +9815,8 @@
       <c r="B33" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>1404</v>
+      <c r="C33" t="s">
+        <v>1403</v>
       </c>
       <c r="D33" t="s">
         <v>1399</v>
@@ -9830,8 +9829,8 @@
       <c r="B34" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>1404</v>
+      <c r="C34" t="s">
+        <v>1403</v>
       </c>
       <c r="D34" t="s">
         <v>1399</v>
@@ -9844,8 +9843,8 @@
       <c r="B35" t="s">
         <v>498</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>1404</v>
+      <c r="C35" t="s">
+        <v>1403</v>
       </c>
       <c r="D35" t="s">
         <v>1399</v>
@@ -9858,8 +9857,8 @@
       <c r="B36" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>1404</v>
+      <c r="C36" t="s">
+        <v>1403</v>
       </c>
       <c r="D36" t="s">
         <v>1399</v>
@@ -9872,8 +9871,8 @@
       <c r="B37" t="s">
         <v>1094</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>1404</v>
+      <c r="C37" t="s">
+        <v>1403</v>
       </c>
       <c r="D37" t="s">
         <v>1399</v>
@@ -9886,8 +9885,8 @@
       <c r="B38" t="s">
         <v>672</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>1404</v>
+      <c r="C38" t="s">
+        <v>1403</v>
       </c>
       <c r="D38" t="s">
         <v>1399</v>
@@ -9900,8 +9899,8 @@
       <c r="B39" t="s">
         <v>673</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>1404</v>
+      <c r="C39" t="s">
+        <v>1403</v>
       </c>
       <c r="D39" t="s">
         <v>1399</v>
@@ -9914,8 +9913,8 @@
       <c r="B40" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>1404</v>
+      <c r="C40" t="s">
+        <v>1403</v>
       </c>
       <c r="D40" t="s">
         <v>1399</v>
@@ -9928,8 +9927,8 @@
       <c r="B41" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>1404</v>
+      <c r="C41" t="s">
+        <v>1403</v>
       </c>
       <c r="D41" t="s">
         <v>1399</v>
@@ -9942,8 +9941,8 @@
       <c r="B42" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>1404</v>
+      <c r="C42" t="s">
+        <v>1403</v>
       </c>
       <c r="D42" t="s">
         <v>1399</v>
@@ -9956,8 +9955,8 @@
       <c r="B43" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>1404</v>
+      <c r="C43" t="s">
+        <v>1403</v>
       </c>
       <c r="D43" t="s">
         <v>1399</v>
@@ -9970,8 +9969,8 @@
       <c r="B44" t="s">
         <v>556</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>1404</v>
+      <c r="C44" t="s">
+        <v>1403</v>
       </c>
       <c r="D44" t="s">
         <v>1399</v>
@@ -9984,8 +9983,8 @@
       <c r="B45" t="s">
         <v>680</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>1404</v>
+      <c r="C45" t="s">
+        <v>1403</v>
       </c>
       <c r="D45" t="s">
         <v>1399</v>
@@ -9998,8 +9997,8 @@
       <c r="B46" t="s">
         <v>604</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>1404</v>
+      <c r="C46" t="s">
+        <v>1403</v>
       </c>
       <c r="D46" t="s">
         <v>1399</v>
@@ -10015,8 +10014,8 @@
       <c r="B47" t="s">
         <v>678</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>1404</v>
+      <c r="C47" t="s">
+        <v>1403</v>
       </c>
       <c r="D47" t="s">
         <v>1399</v>
@@ -10032,8 +10031,8 @@
       <c r="B48" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>1404</v>
+      <c r="C48" t="s">
+        <v>1403</v>
       </c>
       <c r="D48" t="s">
         <v>1399</v>
@@ -10046,8 +10045,8 @@
       <c r="B50" t="s">
         <v>179</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>1404</v>
+      <c r="C50" t="s">
+        <v>1403</v>
       </c>
       <c r="D50" t="s">
         <v>1399</v>
@@ -10060,8 +10059,8 @@
       <c r="B51" t="s">
         <v>1099</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>1404</v>
+      <c r="C51" t="s">
+        <v>1403</v>
       </c>
       <c r="D51" t="s">
         <v>1399</v>
@@ -10074,8 +10073,8 @@
       <c r="B52" t="s">
         <v>89</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>1404</v>
+      <c r="C52" t="s">
+        <v>1403</v>
       </c>
       <c r="D52" t="s">
         <v>1399</v>
@@ -10088,8 +10087,8 @@
       <c r="B53" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>1404</v>
+      <c r="C53" t="s">
+        <v>1403</v>
       </c>
       <c r="D53" t="s">
         <v>1399</v>
@@ -10102,8 +10101,8 @@
       <c r="B54" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>1404</v>
+      <c r="C54" t="s">
+        <v>1403</v>
       </c>
       <c r="D54" t="s">
         <v>1399</v>
@@ -10116,8 +10115,8 @@
       <c r="B55" t="s">
         <v>92</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>1404</v>
+      <c r="C55" t="s">
+        <v>1403</v>
       </c>
       <c r="D55" t="s">
         <v>1399</v>
@@ -10130,8 +10129,8 @@
       <c r="B56" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>1404</v>
+      <c r="C56" t="s">
+        <v>1403</v>
       </c>
       <c r="D56" t="s">
         <v>1399</v>
@@ -10144,8 +10143,8 @@
       <c r="B57" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>1404</v>
+      <c r="C57" t="s">
+        <v>1403</v>
       </c>
       <c r="D57" t="s">
         <v>1399</v>
@@ -10161,8 +10160,8 @@
       <c r="B58" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>1404</v>
+      <c r="C58" t="s">
+        <v>1403</v>
       </c>
       <c r="D58" t="s">
         <v>1399</v>
@@ -10175,8 +10174,8 @@
       <c r="B59" t="s">
         <v>558</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>1404</v>
+      <c r="C59" t="s">
+        <v>1403</v>
       </c>
       <c r="D59" t="s">
         <v>1399</v>
@@ -10189,8 +10188,8 @@
       <c r="B60" t="s">
         <v>668</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>1404</v>
+      <c r="C60" t="s">
+        <v>1403</v>
       </c>
       <c r="D60" t="s">
         <v>1399</v>
@@ -10203,8 +10202,8 @@
       <c r="B61" t="s">
         <v>983</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>1404</v>
+      <c r="C61" t="s">
+        <v>1403</v>
       </c>
       <c r="D61" t="s">
         <v>1399</v>
@@ -10217,8 +10216,8 @@
       <c r="B62" s="5" t="s">
         <v>1147</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>1404</v>
+      <c r="C62" t="s">
+        <v>1403</v>
       </c>
       <c r="D62" t="s">
         <v>1399</v>
@@ -10234,8 +10233,8 @@
       <c r="B63" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>1404</v>
+      <c r="C63" t="s">
+        <v>1403</v>
       </c>
       <c r="D63" t="s">
         <v>1399</v>
@@ -10251,8 +10250,8 @@
       <c r="B65" t="s">
         <v>525</v>
       </c>
-      <c r="C65" s="10" t="s">
-        <v>1404</v>
+      <c r="C65" t="s">
+        <v>1403</v>
       </c>
       <c r="D65" t="s">
         <v>1399</v>
@@ -10265,8 +10264,8 @@
       <c r="B66" t="s">
         <v>103</v>
       </c>
-      <c r="C66" s="10" t="s">
-        <v>1404</v>
+      <c r="C66" t="s">
+        <v>1403</v>
       </c>
       <c r="D66" t="s">
         <v>1399</v>
@@ -10282,8 +10281,8 @@
       <c r="B67" t="s">
         <v>112</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>1404</v>
+      <c r="C67" t="s">
+        <v>1403</v>
       </c>
       <c r="D67" t="s">
         <v>1399</v>
@@ -10299,8 +10298,8 @@
       <c r="B68" t="s">
         <v>114</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>1404</v>
+      <c r="C68" t="s">
+        <v>1403</v>
       </c>
       <c r="D68" t="s">
         <v>1399</v>
@@ -10316,8 +10315,8 @@
       <c r="B69" t="s">
         <v>104</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>1404</v>
+      <c r="C69" t="s">
+        <v>1403</v>
       </c>
       <c r="D69" t="s">
         <v>1399</v>
@@ -10333,8 +10332,8 @@
       <c r="B70" t="s">
         <v>105</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>1404</v>
+      <c r="C70" t="s">
+        <v>1403</v>
       </c>
       <c r="D70" t="s">
         <v>1399</v>
@@ -10350,8 +10349,8 @@
       <c r="B71" t="s">
         <v>106</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>1404</v>
+      <c r="C71" t="s">
+        <v>1403</v>
       </c>
       <c r="D71" t="s">
         <v>1399</v>
@@ -10367,8 +10366,8 @@
       <c r="B72" t="s">
         <v>1095</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>1404</v>
+      <c r="C72" t="s">
+        <v>1403</v>
       </c>
       <c r="D72" t="s">
         <v>1399</v>
@@ -10381,8 +10380,8 @@
       <c r="B73" t="s">
         <v>1096</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>1404</v>
+      <c r="C73" t="s">
+        <v>1403</v>
       </c>
       <c r="D73" t="s">
         <v>1399</v>
@@ -10395,8 +10394,8 @@
       <c r="B74" t="s">
         <v>669</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>1404</v>
+      <c r="C74" t="s">
+        <v>1403</v>
       </c>
       <c r="D74" t="s">
         <v>1399</v>
@@ -10409,8 +10408,8 @@
       <c r="B75" t="s">
         <v>670</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>1404</v>
+      <c r="C75" t="s">
+        <v>1403</v>
       </c>
       <c r="D75" t="s">
         <v>1399</v>
@@ -10426,8 +10425,8 @@
       <c r="B76" t="s">
         <v>671</v>
       </c>
-      <c r="C76" s="10" t="s">
-        <v>1404</v>
+      <c r="C76" t="s">
+        <v>1403</v>
       </c>
       <c r="D76" t="s">
         <v>1399</v>
@@ -10440,8 +10439,8 @@
       <c r="B77" t="s">
         <v>488</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>1404</v>
+      <c r="C77" t="s">
+        <v>1403</v>
       </c>
       <c r="D77" t="s">
         <v>1399</v>
@@ -10454,8 +10453,8 @@
       <c r="B78" t="s">
         <v>629</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>1404</v>
+      <c r="C78" t="s">
+        <v>1403</v>
       </c>
       <c r="D78" t="s">
         <v>1399</v>
@@ -10471,8 +10470,8 @@
       <c r="B79" t="s">
         <v>1087</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>1404</v>
+      <c r="C79" t="s">
+        <v>1403</v>
       </c>
       <c r="D79" t="s">
         <v>1399</v>
@@ -10485,8 +10484,8 @@
       <c r="B80" t="s">
         <v>1088</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>1404</v>
+      <c r="C80" t="s">
+        <v>1403</v>
       </c>
       <c r="D80" t="s">
         <v>1399</v>
@@ -10499,8 +10498,8 @@
       <c r="B81" t="s">
         <v>1098</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>1404</v>
+      <c r="C81" t="s">
+        <v>1403</v>
       </c>
       <c r="D81" t="s">
         <v>1399</v>
@@ -10513,8 +10512,8 @@
       <c r="B82" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>1404</v>
+      <c r="C82" t="s">
+        <v>1403</v>
       </c>
       <c r="D82" t="s">
         <v>1399</v>
@@ -10527,8 +10526,8 @@
       <c r="B84" t="s">
         <v>115</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>1404</v>
+      <c r="C84" t="s">
+        <v>1403</v>
       </c>
       <c r="D84" t="s">
         <v>1399</v>
@@ -10541,8 +10540,8 @@
       <c r="B85" t="s">
         <v>526</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>1404</v>
+      <c r="C85" t="s">
+        <v>1403</v>
       </c>
       <c r="D85" t="s">
         <v>1399</v>
@@ -10555,8 +10554,8 @@
       <c r="B86" t="s">
         <v>117</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>1404</v>
+      <c r="C86" t="s">
+        <v>1403</v>
       </c>
       <c r="D86" t="s">
         <v>1399</v>
@@ -10569,8 +10568,8 @@
       <c r="B87" t="s">
         <v>560</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>1404</v>
+      <c r="C87" t="s">
+        <v>1403</v>
       </c>
       <c r="D87" t="s">
         <v>1399</v>
@@ -10583,8 +10582,8 @@
       <c r="B88" s="5" t="s">
         <v>1129</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>1404</v>
+      <c r="C88" t="s">
+        <v>1403</v>
       </c>
       <c r="D88" t="s">
         <v>1399</v>
@@ -10600,8 +10599,8 @@
       <c r="B89" t="s">
         <v>659</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>1404</v>
+      <c r="C89" t="s">
+        <v>1403</v>
       </c>
       <c r="D89" t="s">
         <v>1399</v>
@@ -10617,8 +10616,8 @@
       <c r="B90" t="s">
         <v>660</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>1404</v>
+      <c r="C90" t="s">
+        <v>1403</v>
       </c>
       <c r="D90" t="s">
         <v>1399</v>
@@ -10634,8 +10633,8 @@
       <c r="B91" t="s">
         <v>661</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>1404</v>
+      <c r="C91" t="s">
+        <v>1403</v>
       </c>
       <c r="D91" t="s">
         <v>1399</v>
@@ -10651,8 +10650,8 @@
       <c r="B92" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>1404</v>
+      <c r="C92" t="s">
+        <v>1403</v>
       </c>
       <c r="D92" t="s">
         <v>1399</v>
@@ -10665,8 +10664,8 @@
       <c r="B94" t="s">
         <v>1041</v>
       </c>
-      <c r="C94" s="10" t="s">
-        <v>1404</v>
+      <c r="C94" t="s">
+        <v>1403</v>
       </c>
       <c r="D94" t="s">
         <v>1399</v>
@@ -10679,8 +10678,8 @@
       <c r="B95" t="s">
         <v>652</v>
       </c>
-      <c r="C95" s="10" t="s">
-        <v>1404</v>
+      <c r="C95" t="s">
+        <v>1403</v>
       </c>
       <c r="D95" t="s">
         <v>1399</v>
@@ -10696,8 +10695,8 @@
       <c r="B96" t="s">
         <v>638</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>1404</v>
+      <c r="C96" t="s">
+        <v>1403</v>
       </c>
       <c r="D96" t="s">
         <v>1399</v>
@@ -10713,8 +10712,8 @@
       <c r="B97" t="s">
         <v>121</v>
       </c>
-      <c r="C97" s="10" t="s">
-        <v>1404</v>
+      <c r="C97" t="s">
+        <v>1403</v>
       </c>
       <c r="D97" t="s">
         <v>1399</v>
@@ -10727,8 +10726,8 @@
       <c r="B98" t="s">
         <v>122</v>
       </c>
-      <c r="C98" s="10" t="s">
-        <v>1404</v>
+      <c r="C98" t="s">
+        <v>1403</v>
       </c>
       <c r="D98" t="s">
         <v>1399</v>
@@ -10741,8 +10740,8 @@
       <c r="B99" t="s">
         <v>527</v>
       </c>
-      <c r="C99" s="10" t="s">
-        <v>1404</v>
+      <c r="C99" t="s">
+        <v>1403</v>
       </c>
       <c r="D99" t="s">
         <v>1399</v>
@@ -10755,8 +10754,8 @@
       <c r="B100" t="s">
         <v>528</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>1404</v>
+      <c r="C100" t="s">
+        <v>1403</v>
       </c>
       <c r="D100" t="s">
         <v>1399</v>
@@ -10769,8 +10768,8 @@
       <c r="B101" t="s">
         <v>529</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>1404</v>
+      <c r="C101" t="s">
+        <v>1403</v>
       </c>
       <c r="D101" t="s">
         <v>1399</v>
@@ -10783,8 +10782,8 @@
       <c r="B102" t="s">
         <v>530</v>
       </c>
-      <c r="C102" s="10" t="s">
-        <v>1404</v>
+      <c r="C102" t="s">
+        <v>1403</v>
       </c>
       <c r="D102" t="s">
         <v>1399</v>
@@ -10797,8 +10796,8 @@
       <c r="B103" t="s">
         <v>441</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>1404</v>
+      <c r="C103" t="s">
+        <v>1403</v>
       </c>
       <c r="D103" t="s">
         <v>1399</v>
@@ -10814,8 +10813,8 @@
       <c r="B104" t="s">
         <v>443</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>1404</v>
+      <c r="C104" t="s">
+        <v>1403</v>
       </c>
       <c r="D104" t="s">
         <v>1399</v>
@@ -10831,8 +10830,8 @@
       <c r="B105" t="s">
         <v>444</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>1404</v>
+      <c r="C105" t="s">
+        <v>1403</v>
       </c>
       <c r="D105" t="s">
         <v>1399</v>
@@ -10848,8 +10847,8 @@
       <c r="B106" t="s">
         <v>562</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>1404</v>
+      <c r="C106" t="s">
+        <v>1403</v>
       </c>
       <c r="D106" t="s">
         <v>1399</v>
@@ -10862,8 +10861,8 @@
       <c r="B107" t="s">
         <v>606</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>1404</v>
+      <c r="C107" t="s">
+        <v>1403</v>
       </c>
       <c r="D107" t="s">
         <v>1399</v>
@@ -10879,8 +10878,8 @@
       <c r="B108" t="s">
         <v>841</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>1404</v>
+      <c r="C108" t="s">
+        <v>1403</v>
       </c>
       <c r="D108" t="s">
         <v>1399</v>
@@ -10893,8 +10892,8 @@
       <c r="B109" t="s">
         <v>632</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>1404</v>
+      <c r="C109" t="s">
+        <v>1403</v>
       </c>
       <c r="D109" t="s">
         <v>1399</v>
@@ -10910,8 +10909,8 @@
       <c r="B110" t="s">
         <v>633</v>
       </c>
-      <c r="C110" s="10" t="s">
-        <v>1404</v>
+      <c r="C110" t="s">
+        <v>1403</v>
       </c>
       <c r="D110" t="s">
         <v>1399</v>
@@ -10927,8 +10926,8 @@
       <c r="B111" t="s">
         <v>635</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>1404</v>
+      <c r="C111" t="s">
+        <v>1403</v>
       </c>
       <c r="D111" t="s">
         <v>1399</v>
@@ -10944,8 +10943,8 @@
       <c r="B112" s="5" t="s">
         <v>1130</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>1404</v>
+      <c r="C112" t="s">
+        <v>1403</v>
       </c>
       <c r="D112" t="s">
         <v>1399</v>
@@ -10961,8 +10960,8 @@
       <c r="B113" t="s">
         <v>839</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>1404</v>
+      <c r="C113" t="s">
+        <v>1403</v>
       </c>
       <c r="D113" t="s">
         <v>1399</v>
@@ -10975,8 +10974,8 @@
       <c r="B114" t="s">
         <v>844</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>1404</v>
+      <c r="C114" t="s">
+        <v>1403</v>
       </c>
       <c r="D114" t="s">
         <v>1399</v>
@@ -10989,8 +10988,8 @@
       <c r="B115" t="s">
         <v>842</v>
       </c>
-      <c r="C115" s="10" t="s">
-        <v>1404</v>
+      <c r="C115" t="s">
+        <v>1403</v>
       </c>
       <c r="D115" t="s">
         <v>1399</v>
@@ -11003,8 +11002,8 @@
       <c r="B116" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>1404</v>
+      <c r="C116" t="s">
+        <v>1403</v>
       </c>
       <c r="D116" t="s">
         <v>1399</v>
@@ -11017,8 +11016,8 @@
       <c r="B118" t="s">
         <v>1124</v>
       </c>
-      <c r="C118" s="10" t="s">
-        <v>1404</v>
+      <c r="C118" t="s">
+        <v>1403</v>
       </c>
       <c r="D118" t="s">
         <v>1399</v>
@@ -11034,8 +11033,8 @@
       <c r="B119" t="s">
         <v>144</v>
       </c>
-      <c r="C119" s="10" t="s">
-        <v>1404</v>
+      <c r="C119" t="s">
+        <v>1403</v>
       </c>
       <c r="D119" t="s">
         <v>1399</v>
@@ -11051,8 +11050,8 @@
       <c r="B120" t="s">
         <v>145</v>
       </c>
-      <c r="C120" s="10" t="s">
-        <v>1404</v>
+      <c r="C120" t="s">
+        <v>1403</v>
       </c>
       <c r="D120" t="s">
         <v>1399</v>
@@ -11068,8 +11067,8 @@
       <c r="B121" t="s">
         <v>146</v>
       </c>
-      <c r="C121" s="10" t="s">
-        <v>1404</v>
+      <c r="C121" t="s">
+        <v>1403</v>
       </c>
       <c r="D121" t="s">
         <v>1399</v>
@@ -11085,8 +11084,8 @@
       <c r="B122" t="s">
         <v>514</v>
       </c>
-      <c r="C122" s="10" t="s">
-        <v>1404</v>
+      <c r="C122" t="s">
+        <v>1403</v>
       </c>
       <c r="D122" t="s">
         <v>1399</v>
@@ -11102,8 +11101,8 @@
       <c r="B123" t="s">
         <v>514</v>
       </c>
-      <c r="C123" s="10" t="s">
-        <v>1404</v>
+      <c r="C123" t="s">
+        <v>1403</v>
       </c>
       <c r="D123" t="s">
         <v>1399</v>
@@ -11119,8 +11118,8 @@
       <c r="B124" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>1404</v>
+      <c r="C124" t="s">
+        <v>1403</v>
       </c>
       <c r="D124" t="s">
         <v>1399</v>
@@ -11136,8 +11135,8 @@
       <c r="B125" t="s">
         <v>531</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>1404</v>
+      <c r="C125" t="s">
+        <v>1403</v>
       </c>
       <c r="D125" t="s">
         <v>1399</v>
@@ -11153,8 +11152,8 @@
       <c r="B126" t="s">
         <v>124</v>
       </c>
-      <c r="C126" s="10" t="s">
-        <v>1404</v>
+      <c r="C126" t="s">
+        <v>1403</v>
       </c>
       <c r="D126" t="s">
         <v>1399</v>
@@ -11170,8 +11169,8 @@
       <c r="B127" t="s">
         <v>564</v>
       </c>
-      <c r="C127" s="10" t="s">
-        <v>1404</v>
+      <c r="C127" t="s">
+        <v>1403</v>
       </c>
       <c r="D127" t="s">
         <v>1399</v>
@@ -11187,8 +11186,8 @@
       <c r="B128" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>1404</v>
+      <c r="C128" t="s">
+        <v>1403</v>
       </c>
       <c r="D128" t="s">
         <v>1399</v>
@@ -11201,8 +11200,8 @@
       <c r="B130" t="s">
         <v>182</v>
       </c>
-      <c r="C130" s="10" t="s">
-        <v>1404</v>
+      <c r="C130" t="s">
+        <v>1403</v>
       </c>
       <c r="D130" t="s">
         <v>1399</v>
@@ -11215,8 +11214,8 @@
       <c r="B131" t="s">
         <v>147</v>
       </c>
-      <c r="C131" s="10" t="s">
-        <v>1404</v>
+      <c r="C131" t="s">
+        <v>1403</v>
       </c>
       <c r="D131" t="s">
         <v>1399</v>
@@ -11229,8 +11228,8 @@
       <c r="B132" t="s">
         <v>148</v>
       </c>
-      <c r="C132" s="10" t="s">
-        <v>1404</v>
+      <c r="C132" t="s">
+        <v>1403</v>
       </c>
       <c r="D132" t="s">
         <v>1399</v>
@@ -11243,8 +11242,8 @@
       <c r="B133" t="s">
         <v>149</v>
       </c>
-      <c r="C133" s="10" t="s">
-        <v>1404</v>
+      <c r="C133" t="s">
+        <v>1403</v>
       </c>
       <c r="D133" t="s">
         <v>1399</v>
@@ -11257,8 +11256,8 @@
       <c r="B134" t="s">
         <v>681</v>
       </c>
-      <c r="C134" s="10" t="s">
-        <v>1404</v>
+      <c r="C134" t="s">
+        <v>1403</v>
       </c>
       <c r="D134" t="s">
         <v>1399</v>
@@ -11274,8 +11273,8 @@
       <c r="B135" t="s">
         <v>150</v>
       </c>
-      <c r="C135" s="10" t="s">
-        <v>1404</v>
+      <c r="C135" t="s">
+        <v>1403</v>
       </c>
       <c r="D135" t="s">
         <v>1399</v>
@@ -11288,8 +11287,8 @@
       <c r="B136" t="s">
         <v>151</v>
       </c>
-      <c r="C136" s="10" t="s">
-        <v>1404</v>
+      <c r="C136" t="s">
+        <v>1403</v>
       </c>
       <c r="D136" t="s">
         <v>1399</v>
@@ -11302,8 +11301,8 @@
       <c r="B137" s="5" t="s">
         <v>1153</v>
       </c>
-      <c r="C137" s="10" t="s">
-        <v>1404</v>
+      <c r="C137" t="s">
+        <v>1403</v>
       </c>
       <c r="D137" t="s">
         <v>1399</v>
@@ -11319,8 +11318,8 @@
       <c r="B138" t="s">
         <v>566</v>
       </c>
-      <c r="C138" s="10" t="s">
-        <v>1404</v>
+      <c r="C138" t="s">
+        <v>1403</v>
       </c>
       <c r="D138" t="s">
         <v>1399</v>
@@ -11333,8 +11332,8 @@
       <c r="B139" t="s">
         <v>608</v>
       </c>
-      <c r="C139" s="10" t="s">
-        <v>1404</v>
+      <c r="C139" t="s">
+        <v>1403</v>
       </c>
       <c r="D139" t="s">
         <v>1399</v>
@@ -11350,8 +11349,8 @@
       <c r="B140" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="C140" s="10" t="s">
-        <v>1404</v>
+      <c r="C140" t="s">
+        <v>1403</v>
       </c>
       <c r="D140" t="s">
         <v>1399</v>
@@ -11364,8 +11363,8 @@
       <c r="B142" t="s">
         <v>598</v>
       </c>
-      <c r="C142" s="10" t="s">
-        <v>1404</v>
+      <c r="C142" t="s">
+        <v>1403</v>
       </c>
       <c r="D142" t="s">
         <v>1399</v>
@@ -11381,8 +11380,8 @@
       <c r="B143" t="s">
         <v>1155</v>
       </c>
-      <c r="C143" s="10" t="s">
-        <v>1404</v>
+      <c r="C143" t="s">
+        <v>1403</v>
       </c>
       <c r="D143" t="s">
         <v>1399</v>
@@ -11398,8 +11397,8 @@
       <c r="B145" t="s">
         <v>157</v>
       </c>
-      <c r="C145" s="10" t="s">
-        <v>1404</v>
+      <c r="C145" t="s">
+        <v>1403</v>
       </c>
       <c r="D145" t="s">
         <v>1399</v>
@@ -11412,8 +11411,8 @@
       <c r="B146" t="s">
         <v>158</v>
       </c>
-      <c r="C146" s="10" t="s">
-        <v>1404</v>
+      <c r="C146" t="s">
+        <v>1403</v>
       </c>
       <c r="D146" t="s">
         <v>1399</v>
@@ -11426,8 +11425,8 @@
       <c r="B147" t="s">
         <v>159</v>
       </c>
-      <c r="C147" s="10" t="s">
-        <v>1404</v>
+      <c r="C147" t="s">
+        <v>1403</v>
       </c>
       <c r="D147" t="s">
         <v>1399</v>
@@ -11440,8 +11439,8 @@
       <c r="B148" t="s">
         <v>532</v>
       </c>
-      <c r="C148" s="10" t="s">
-        <v>1404</v>
+      <c r="C148" t="s">
+        <v>1403</v>
       </c>
       <c r="D148" t="s">
         <v>1399</v>
@@ -11454,8 +11453,8 @@
       <c r="B149" t="s">
         <v>620</v>
       </c>
-      <c r="C149" s="10" t="s">
-        <v>1404</v>
+      <c r="C149" t="s">
+        <v>1403</v>
       </c>
       <c r="D149" t="s">
         <v>1399</v>
@@ -11471,8 +11470,8 @@
       <c r="B150" t="s">
         <v>1060</v>
       </c>
-      <c r="C150" s="10" t="s">
-        <v>1404</v>
+      <c r="C150" t="s">
+        <v>1403</v>
       </c>
       <c r="D150" t="s">
         <v>1399</v>
@@ -11488,8 +11487,8 @@
       <c r="B151" t="s">
         <v>572</v>
       </c>
-      <c r="C151" s="10" t="s">
-        <v>1404</v>
+      <c r="C151" t="s">
+        <v>1403</v>
       </c>
       <c r="D151" t="s">
         <v>1399</v>
@@ -11502,8 +11501,8 @@
       <c r="B152" t="s">
         <v>1156</v>
       </c>
-      <c r="C152" s="10" t="s">
-        <v>1404</v>
+      <c r="C152" t="s">
+        <v>1403</v>
       </c>
       <c r="D152" t="s">
         <v>1399</v>
@@ -11516,8 +11515,8 @@
       <c r="B154" t="s">
         <v>186</v>
       </c>
-      <c r="C154" s="10" t="s">
-        <v>1404</v>
+      <c r="C154" t="s">
+        <v>1403</v>
       </c>
       <c r="D154" t="s">
         <v>1399</v>
@@ -11530,8 +11529,8 @@
       <c r="B155" t="s">
         <v>162</v>
       </c>
-      <c r="C155" s="10" t="s">
-        <v>1404</v>
+      <c r="C155" t="s">
+        <v>1403</v>
       </c>
       <c r="D155" t="s">
         <v>1399</v>
@@ -11544,8 +11543,8 @@
       <c r="B156" t="s">
         <v>163</v>
       </c>
-      <c r="C156" s="10" t="s">
-        <v>1404</v>
+      <c r="C156" t="s">
+        <v>1403</v>
       </c>
       <c r="D156" t="s">
         <v>1399</v>
@@ -11558,8 +11557,8 @@
       <c r="B157" t="s">
         <v>568</v>
       </c>
-      <c r="C157" s="10" t="s">
-        <v>1404</v>
+      <c r="C157" t="s">
+        <v>1403</v>
       </c>
       <c r="D157" t="s">
         <v>1399</v>
@@ -11572,8 +11571,8 @@
       <c r="B158" t="s">
         <v>1157</v>
       </c>
-      <c r="C158" s="10" t="s">
-        <v>1404</v>
+      <c r="C158" t="s">
+        <v>1403</v>
       </c>
       <c r="D158" t="s">
         <v>1399</v>
@@ -11586,8 +11585,8 @@
       <c r="B159" t="s">
         <v>610</v>
       </c>
-      <c r="C159" s="10" t="s">
-        <v>1404</v>
+      <c r="C159" t="s">
+        <v>1403</v>
       </c>
       <c r="D159" t="s">
         <v>1399</v>
@@ -11603,8 +11602,8 @@
       <c r="B161" t="s">
         <v>184</v>
       </c>
-      <c r="C161" s="10" t="s">
-        <v>1404</v>
+      <c r="C161" t="s">
+        <v>1403</v>
       </c>
       <c r="D161" t="s">
         <v>1399</v>
@@ -11617,8 +11616,8 @@
       <c r="B162" t="s">
         <v>166</v>
       </c>
-      <c r="C162" s="10" t="s">
-        <v>1404</v>
+      <c r="C162" t="s">
+        <v>1403</v>
       </c>
       <c r="D162" t="s">
         <v>1399</v>
@@ -11634,8 +11633,8 @@
       <c r="B163" t="s">
         <v>167</v>
       </c>
-      <c r="C163" s="10" t="s">
-        <v>1404</v>
+      <c r="C163" t="s">
+        <v>1403</v>
       </c>
       <c r="D163" t="s">
         <v>1399</v>
@@ -11651,8 +11650,8 @@
       <c r="B164" t="s">
         <v>168</v>
       </c>
-      <c r="C164" s="10" t="s">
-        <v>1404</v>
+      <c r="C164" t="s">
+        <v>1403</v>
       </c>
       <c r="D164" t="s">
         <v>1399</v>
@@ -11668,8 +11667,8 @@
       <c r="B165" t="s">
         <v>193</v>
       </c>
-      <c r="C165" s="10" t="s">
-        <v>1404</v>
+      <c r="C165" t="s">
+        <v>1403</v>
       </c>
       <c r="D165" t="s">
         <v>1399</v>
@@ -11682,8 +11681,8 @@
       <c r="B166" t="s">
         <v>192</v>
       </c>
-      <c r="C166" s="10" t="s">
-        <v>1404</v>
+      <c r="C166" t="s">
+        <v>1403</v>
       </c>
       <c r="D166" t="s">
         <v>1399</v>
@@ -11696,8 +11695,8 @@
       <c r="B167" t="s">
         <v>171</v>
       </c>
-      <c r="C167" s="10" t="s">
-        <v>1404</v>
+      <c r="C167" t="s">
+        <v>1403</v>
       </c>
       <c r="D167" t="s">
         <v>1399</v>
@@ -11713,8 +11712,8 @@
       <c r="B168" t="s">
         <v>570</v>
       </c>
-      <c r="C168" s="10" t="s">
-        <v>1404</v>
+      <c r="C168" t="s">
+        <v>1403</v>
       </c>
       <c r="D168" t="s">
         <v>1399</v>
@@ -11727,8 +11726,8 @@
       <c r="B169" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="C169" s="10" t="s">
-        <v>1404</v>
+      <c r="C169" t="s">
+        <v>1403</v>
       </c>
       <c r="D169" t="s">
         <v>1399</v>
@@ -11744,8 +11743,8 @@
       <c r="B171" t="s">
         <v>756</v>
       </c>
-      <c r="C171" s="10" t="s">
-        <v>1404</v>
+      <c r="C171" t="s">
+        <v>1403</v>
       </c>
       <c r="D171" t="s">
         <v>1399</v>
@@ -11761,8 +11760,8 @@
       <c r="B172" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="C172" s="10" t="s">
-        <v>1404</v>
+      <c r="C172" t="s">
+        <v>1403</v>
       </c>
       <c r="D172" t="s">
         <v>1399</v>
@@ -11778,8 +11777,8 @@
       <c r="B173" t="s">
         <v>613</v>
       </c>
-      <c r="C173" s="10" t="s">
-        <v>1404</v>
+      <c r="C173" t="s">
+        <v>1403</v>
       </c>
       <c r="D173" t="s">
         <v>1399</v>
@@ -11795,8 +11794,8 @@
       <c r="B174" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="C174" s="10" t="s">
-        <v>1404</v>
+      <c r="C174" t="s">
+        <v>1403</v>
       </c>
       <c r="D174" t="s">
         <v>1399</v>
@@ -11812,8 +11811,8 @@
       <c r="B175" t="s">
         <v>819</v>
       </c>
-      <c r="C175" s="10" t="s">
-        <v>1404</v>
+      <c r="C175" t="s">
+        <v>1403</v>
       </c>
       <c r="D175" t="s">
         <v>1399</v>
@@ -11829,8 +11828,8 @@
       <c r="B176" s="7" t="s">
         <v>1142</v>
       </c>
-      <c r="C176" s="10" t="s">
-        <v>1404</v>
+      <c r="C176" t="s">
+        <v>1403</v>
       </c>
       <c r="D176" t="s">
         <v>1399</v>
@@ -11846,8 +11845,8 @@
       <c r="B177" t="s">
         <v>824</v>
       </c>
-      <c r="C177" s="10" t="s">
-        <v>1404</v>
+      <c r="C177" t="s">
+        <v>1403</v>
       </c>
       <c r="D177" t="s">
         <v>1399</v>
@@ -11863,8 +11862,8 @@
       <c r="B179" t="s">
         <v>1061</v>
       </c>
-      <c r="C179" s="10" t="s">
-        <v>1404</v>
+      <c r="C179" t="s">
+        <v>1403</v>
       </c>
       <c r="D179" t="s">
         <v>1399</v>
@@ -11877,8 +11876,8 @@
       <c r="B180" t="s">
         <v>1068</v>
       </c>
-      <c r="C180" s="10" t="s">
-        <v>1404</v>
+      <c r="C180" t="s">
+        <v>1403</v>
       </c>
       <c r="D180" t="s">
         <v>1399</v>
@@ -11894,8 +11893,8 @@
       <c r="B181" t="s">
         <v>820</v>
       </c>
-      <c r="C181" s="10" t="s">
-        <v>1404</v>
+      <c r="C181" t="s">
+        <v>1403</v>
       </c>
       <c r="D181" t="s">
         <v>1399</v>
@@ -11911,8 +11910,8 @@
       <c r="B182" t="s">
         <v>821</v>
       </c>
-      <c r="C182" s="10" t="s">
-        <v>1404</v>
+      <c r="C182" t="s">
+        <v>1403</v>
       </c>
       <c r="D182" t="s">
         <v>1399</v>
@@ -11925,8 +11924,8 @@
       <c r="B183" t="s">
         <v>822</v>
       </c>
-      <c r="C183" s="10" t="s">
-        <v>1404</v>
+      <c r="C183" t="s">
+        <v>1403</v>
       </c>
       <c r="D183" t="s">
         <v>1399</v>
@@ -11942,8 +11941,8 @@
       <c r="B184" t="s">
         <v>823</v>
       </c>
-      <c r="C184" s="10" t="s">
-        <v>1404</v>
+      <c r="C184" t="s">
+        <v>1403</v>
       </c>
       <c r="D184" t="s">
         <v>1399</v>
@@ -11959,8 +11958,8 @@
       <c r="B185" t="s">
         <v>234</v>
       </c>
-      <c r="C185" s="10" t="s">
-        <v>1404</v>
+      <c r="C185" t="s">
+        <v>1403</v>
       </c>
       <c r="D185" t="s">
         <v>1399</v>
@@ -11973,8 +11972,8 @@
       <c r="B186" t="s">
         <v>457</v>
       </c>
-      <c r="C186" s="10" t="s">
-        <v>1404</v>
+      <c r="C186" t="s">
+        <v>1403</v>
       </c>
       <c r="D186" t="s">
         <v>1399</v>
@@ -11987,8 +11986,8 @@
       <c r="B187" t="s">
         <v>824</v>
       </c>
-      <c r="C187" s="10" t="s">
-        <v>1404</v>
+      <c r="C187" t="s">
+        <v>1403</v>
       </c>
       <c r="D187" t="s">
         <v>1399</v>
@@ -12004,8 +12003,8 @@
       <c r="B188" t="s">
         <v>825</v>
       </c>
-      <c r="C188" s="10" t="s">
-        <v>1404</v>
+      <c r="C188" t="s">
+        <v>1403</v>
       </c>
       <c r="D188" t="s">
         <v>1399</v>
@@ -12018,8 +12017,8 @@
       <c r="B189" t="s">
         <v>826</v>
       </c>
-      <c r="C189" s="10" t="s">
-        <v>1404</v>
+      <c r="C189" t="s">
+        <v>1403</v>
       </c>
       <c r="D189" t="s">
         <v>1399</v>
@@ -12032,8 +12031,8 @@
       <c r="B190" t="s">
         <v>827</v>
       </c>
-      <c r="C190" s="10" t="s">
-        <v>1404</v>
+      <c r="C190" t="s">
+        <v>1403</v>
       </c>
       <c r="D190" t="s">
         <v>1399</v>
@@ -12046,8 +12045,8 @@
       <c r="B191" t="s">
         <v>756</v>
       </c>
-      <c r="C191" s="10" t="s">
-        <v>1404</v>
+      <c r="C191" t="s">
+        <v>1403</v>
       </c>
       <c r="D191" t="s">
         <v>1399</v>
@@ -12060,8 +12059,8 @@
       <c r="B192" t="s">
         <v>824</v>
       </c>
-      <c r="C192" s="10" t="s">
-        <v>1404</v>
+      <c r="C192" t="s">
+        <v>1403</v>
       </c>
       <c r="D192" t="s">
         <v>1399</v>
@@ -12077,8 +12076,8 @@
       <c r="B193" t="s">
         <v>298</v>
       </c>
-      <c r="C193" s="10" t="s">
-        <v>1404</v>
+      <c r="C193" t="s">
+        <v>1403</v>
       </c>
       <c r="D193" t="s">
         <v>1399</v>
@@ -12091,8 +12090,8 @@
       <c r="B194" t="s">
         <v>1042</v>
       </c>
-      <c r="C194" s="10" t="s">
-        <v>1404</v>
+      <c r="C194" t="s">
+        <v>1403</v>
       </c>
       <c r="D194" t="s">
         <v>1399</v>
@@ -12105,8 +12104,8 @@
       <c r="B195" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C195" s="10" t="s">
-        <v>1404</v>
+      <c r="C195" t="s">
+        <v>1403</v>
       </c>
       <c r="D195" t="s">
         <v>1399</v>
@@ -12122,8 +12121,8 @@
       <c r="B196" s="6" t="s">
         <v>654</v>
       </c>
-      <c r="C196" s="10" t="s">
-        <v>1404</v>
+      <c r="C196" t="s">
+        <v>1403</v>
       </c>
       <c r="D196" t="s">
         <v>1399</v>
@@ -12139,8 +12138,8 @@
       <c r="B197" s="7" t="s">
         <v>1159</v>
       </c>
-      <c r="C197" s="10" t="s">
-        <v>1404</v>
+      <c r="C197" t="s">
+        <v>1403</v>
       </c>
       <c r="D197" t="s">
         <v>1399</v>
@@ -12156,8 +12155,8 @@
       <c r="B198" s="7" t="s">
         <v>1133</v>
       </c>
-      <c r="C198" s="10" t="s">
-        <v>1404</v>
+      <c r="C198" t="s">
+        <v>1403</v>
       </c>
       <c r="D198" t="s">
         <v>1399</v>
@@ -12173,8 +12172,8 @@
       <c r="B199" t="s">
         <v>1107</v>
       </c>
-      <c r="C199" s="10" t="s">
-        <v>1404</v>
+      <c r="C199" t="s">
+        <v>1403</v>
       </c>
       <c r="D199" t="s">
         <v>1399</v>
@@ -12187,8 +12186,8 @@
       <c r="B200" s="7" t="s">
         <v>1160</v>
       </c>
-      <c r="C200" s="10" t="s">
-        <v>1404</v>
+      <c r="C200" t="s">
+        <v>1403</v>
       </c>
       <c r="D200" t="s">
         <v>1399</v>
@@ -12204,8 +12203,8 @@
       <c r="B202" s="7" t="s">
         <v>1161</v>
       </c>
-      <c r="C202" s="10" t="s">
-        <v>1404</v>
+      <c r="C202" t="s">
+        <v>1403</v>
       </c>
       <c r="D202" t="s">
         <v>1399</v>
@@ -12221,8 +12220,8 @@
       <c r="B203" t="s">
         <v>1062</v>
       </c>
-      <c r="C203" s="10" t="s">
-        <v>1404</v>
+      <c r="C203" t="s">
+        <v>1403</v>
       </c>
       <c r="D203" t="s">
         <v>1399</v>
@@ -12235,8 +12234,8 @@
       <c r="B204" t="s">
         <v>828</v>
       </c>
-      <c r="C204" s="10" t="s">
-        <v>1404</v>
+      <c r="C204" t="s">
+        <v>1403</v>
       </c>
       <c r="D204" t="s">
         <v>1399</v>
@@ -12252,8 +12251,8 @@
       <c r="B205" t="s">
         <v>829</v>
       </c>
-      <c r="C205" s="10" t="s">
-        <v>1404</v>
+      <c r="C205" t="s">
+        <v>1403</v>
       </c>
       <c r="D205" t="s">
         <v>1399</v>
@@ -12269,8 +12268,8 @@
       <c r="B206" t="s">
         <v>791</v>
       </c>
-      <c r="C206" s="10" t="s">
-        <v>1404</v>
+      <c r="C206" t="s">
+        <v>1403</v>
       </c>
       <c r="D206" t="s">
         <v>1399</v>
@@ -12283,8 +12282,8 @@
       <c r="B207" s="7" t="s">
         <v>1162</v>
       </c>
-      <c r="C207" s="10" t="s">
-        <v>1404</v>
+      <c r="C207" t="s">
+        <v>1403</v>
       </c>
       <c r="D207" t="s">
         <v>1399</v>
@@ -12300,8 +12299,8 @@
       <c r="B208" t="s">
         <v>247</v>
       </c>
-      <c r="C208" s="10" t="s">
-        <v>1404</v>
+      <c r="C208" t="s">
+        <v>1403</v>
       </c>
       <c r="D208" t="s">
         <v>1399</v>
@@ -12314,8 +12313,8 @@
       <c r="B209" t="s">
         <v>248</v>
       </c>
-      <c r="C209" s="10" t="s">
-        <v>1404</v>
+      <c r="C209" t="s">
+        <v>1403</v>
       </c>
       <c r="D209" t="s">
         <v>1399</v>
@@ -12331,8 +12330,8 @@
       <c r="B210" t="s">
         <v>504</v>
       </c>
-      <c r="C210" s="10" t="s">
-        <v>1404</v>
+      <c r="C210" t="s">
+        <v>1403</v>
       </c>
       <c r="D210" t="s">
         <v>1399</v>
@@ -12345,8 +12344,8 @@
       <c r="B211" t="s">
         <v>793</v>
       </c>
-      <c r="C211" s="10" t="s">
-        <v>1404</v>
+      <c r="C211" t="s">
+        <v>1403</v>
       </c>
       <c r="D211" t="s">
         <v>1399</v>
@@ -12359,8 +12358,8 @@
       <c r="B212" t="s">
         <v>252</v>
       </c>
-      <c r="C212" s="10" t="s">
-        <v>1404</v>
+      <c r="C212" t="s">
+        <v>1403</v>
       </c>
       <c r="D212" t="s">
         <v>1399</v>
@@ -12373,8 +12372,8 @@
       <c r="B213" t="s">
         <v>794</v>
       </c>
-      <c r="C213" s="10" t="s">
-        <v>1404</v>
+      <c r="C213" t="s">
+        <v>1403</v>
       </c>
       <c r="D213" t="s">
         <v>1399</v>
@@ -12387,8 +12386,8 @@
       <c r="B214" t="s">
         <v>795</v>
       </c>
-      <c r="C214" s="10" t="s">
-        <v>1404</v>
+      <c r="C214" t="s">
+        <v>1403</v>
       </c>
       <c r="D214" t="s">
         <v>1399</v>
@@ -12401,8 +12400,8 @@
       <c r="B215" t="s">
         <v>830</v>
       </c>
-      <c r="C215" s="10" t="s">
-        <v>1404</v>
+      <c r="C215" t="s">
+        <v>1403</v>
       </c>
       <c r="D215" t="s">
         <v>1399</v>
@@ -12418,8 +12417,8 @@
       <c r="B216" t="s">
         <v>796</v>
       </c>
-      <c r="C216" s="10" t="s">
-        <v>1404</v>
+      <c r="C216" t="s">
+        <v>1403</v>
       </c>
       <c r="D216" t="s">
         <v>1399</v>
@@ -12432,8 +12431,8 @@
       <c r="B217" t="s">
         <v>831</v>
       </c>
-      <c r="C217" s="10" t="s">
-        <v>1404</v>
+      <c r="C217" t="s">
+        <v>1403</v>
       </c>
       <c r="D217" t="s">
         <v>1399</v>
@@ -12449,8 +12448,8 @@
       <c r="B218" t="s">
         <v>797</v>
       </c>
-      <c r="C218" s="10" t="s">
-        <v>1404</v>
+      <c r="C218" t="s">
+        <v>1403</v>
       </c>
       <c r="D218" t="s">
         <v>1399</v>
@@ -12463,8 +12462,8 @@
       <c r="B219" t="s">
         <v>269</v>
       </c>
-      <c r="C219" s="10" t="s">
-        <v>1404</v>
+      <c r="C219" t="s">
+        <v>1403</v>
       </c>
       <c r="D219" t="s">
         <v>1399</v>
@@ -12477,8 +12476,8 @@
       <c r="B220" t="s">
         <v>824</v>
       </c>
-      <c r="C220" s="10" t="s">
-        <v>1404</v>
+      <c r="C220" t="s">
+        <v>1403</v>
       </c>
       <c r="D220" t="s">
         <v>1399</v>
@@ -12494,8 +12493,8 @@
       <c r="B221" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="C221" s="10" t="s">
-        <v>1404</v>
+      <c r="C221" t="s">
+        <v>1403</v>
       </c>
       <c r="D221" t="s">
         <v>1399</v>
@@ -12511,8 +12510,8 @@
       <c r="B222" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C222" s="10" t="s">
-        <v>1404</v>
+      <c r="C222" t="s">
+        <v>1403</v>
       </c>
       <c r="D222" t="s">
         <v>1399</v>
@@ -12528,8 +12527,8 @@
       <c r="B223" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="C223" s="10" t="s">
-        <v>1404</v>
+      <c r="C223" t="s">
+        <v>1403</v>
       </c>
       <c r="D223" t="s">
         <v>1399</v>
@@ -12545,8 +12544,8 @@
       <c r="B224" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="C224" s="10" t="s">
-        <v>1404</v>
+      <c r="C224" t="s">
+        <v>1403</v>
       </c>
       <c r="D224" t="s">
         <v>1399</v>
@@ -12562,8 +12561,8 @@
       <c r="B226" t="s">
         <v>1063</v>
       </c>
-      <c r="C226" s="10" t="s">
-        <v>1404</v>
+      <c r="C226" t="s">
+        <v>1403</v>
       </c>
       <c r="D226" t="s">
         <v>1399</v>
@@ -12576,8 +12575,8 @@
       <c r="B227" t="s">
         <v>505</v>
       </c>
-      <c r="C227" s="10" t="s">
-        <v>1404</v>
+      <c r="C227" t="s">
+        <v>1403</v>
       </c>
       <c r="D227" t="s">
         <v>1399</v>
@@ -12590,8 +12589,8 @@
       <c r="B228" t="s">
         <v>757</v>
       </c>
-      <c r="C228" s="10" t="s">
-        <v>1404</v>
+      <c r="C228" t="s">
+        <v>1403</v>
       </c>
       <c r="D228" t="s">
         <v>1399</v>
@@ -12604,8 +12603,8 @@
       <c r="B229" t="s">
         <v>758</v>
       </c>
-      <c r="C229" s="10" t="s">
-        <v>1404</v>
+      <c r="C229" t="s">
+        <v>1403</v>
       </c>
       <c r="D229" t="s">
         <v>1399</v>
@@ -12618,8 +12617,8 @@
       <c r="B230" t="s">
         <v>759</v>
       </c>
-      <c r="C230" s="10" t="s">
-        <v>1404</v>
+      <c r="C230" t="s">
+        <v>1403</v>
       </c>
       <c r="D230" t="s">
         <v>1399</v>
@@ -12632,8 +12631,8 @@
       <c r="B231" t="s">
         <v>761</v>
       </c>
-      <c r="C231" s="10" t="s">
-        <v>1404</v>
+      <c r="C231" t="s">
+        <v>1403</v>
       </c>
       <c r="D231" t="s">
         <v>1399</v>
@@ -12646,8 +12645,8 @@
       <c r="B232" t="s">
         <v>760</v>
       </c>
-      <c r="C232" s="10" t="s">
-        <v>1404</v>
+      <c r="C232" t="s">
+        <v>1403</v>
       </c>
       <c r="D232" t="s">
         <v>1399</v>
@@ -12660,8 +12659,8 @@
       <c r="B233" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C233" s="10" t="s">
-        <v>1404</v>
+      <c r="C233" t="s">
+        <v>1403</v>
       </c>
       <c r="D233" t="s">
         <v>1399</v>
@@ -12677,8 +12676,8 @@
       <c r="B234" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="C234" s="10" t="s">
-        <v>1404</v>
+      <c r="C234" t="s">
+        <v>1403</v>
       </c>
       <c r="D234" t="s">
         <v>1399</v>
@@ -12694,8 +12693,8 @@
       <c r="B236" t="s">
         <v>1064</v>
       </c>
-      <c r="C236" s="10" t="s">
-        <v>1404</v>
+      <c r="C236" t="s">
+        <v>1403</v>
       </c>
       <c r="D236" t="s">
         <v>1399</v>
@@ -12708,8 +12707,8 @@
       <c r="B237" t="s">
         <v>506</v>
       </c>
-      <c r="C237" s="10" t="s">
-        <v>1404</v>
+      <c r="C237" t="s">
+        <v>1403</v>
       </c>
       <c r="D237" t="s">
         <v>1399</v>
@@ -12722,8 +12721,8 @@
       <c r="B238" t="s">
         <v>751</v>
       </c>
-      <c r="C238" s="10" t="s">
-        <v>1404</v>
+      <c r="C238" t="s">
+        <v>1403</v>
       </c>
       <c r="D238" t="s">
         <v>1399</v>
@@ -12736,8 +12735,8 @@
       <c r="B239" t="s">
         <v>281</v>
       </c>
-      <c r="C239" s="10" t="s">
-        <v>1404</v>
+      <c r="C239" t="s">
+        <v>1403</v>
       </c>
       <c r="D239" t="s">
         <v>1399</v>
@@ -12750,8 +12749,8 @@
       <c r="B240" t="s">
         <v>752</v>
       </c>
-      <c r="C240" s="10" t="s">
-        <v>1404</v>
+      <c r="C240" t="s">
+        <v>1403</v>
       </c>
       <c r="D240" t="s">
         <v>1399</v>
@@ -12764,8 +12763,8 @@
       <c r="B241" t="s">
         <v>754</v>
       </c>
-      <c r="C241" s="10" t="s">
-        <v>1404</v>
+      <c r="C241" t="s">
+        <v>1403</v>
       </c>
       <c r="D241" t="s">
         <v>1399</v>
@@ -12778,8 +12777,8 @@
       <c r="B242" t="s">
         <v>753</v>
       </c>
-      <c r="C242" s="10" t="s">
-        <v>1404</v>
+      <c r="C242" t="s">
+        <v>1403</v>
       </c>
       <c r="D242" t="s">
         <v>1399</v>
@@ -12792,8 +12791,8 @@
       <c r="B243" t="s">
         <v>755</v>
       </c>
-      <c r="C243" s="10" t="s">
-        <v>1404</v>
+      <c r="C243" t="s">
+        <v>1403</v>
       </c>
       <c r="D243" t="s">
         <v>1399</v>
@@ -12806,8 +12805,8 @@
       <c r="B244" t="s">
         <v>756</v>
       </c>
-      <c r="C244" s="10" t="s">
-        <v>1404</v>
+      <c r="C244" t="s">
+        <v>1403</v>
       </c>
       <c r="D244" t="s">
         <v>1399</v>
@@ -12820,8 +12819,8 @@
       <c r="B245" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C245" s="10" t="s">
-        <v>1404</v>
+      <c r="C245" t="s">
+        <v>1403</v>
       </c>
       <c r="D245" t="s">
         <v>1399</v>
@@ -12837,8 +12836,8 @@
       <c r="B246" t="s">
         <v>1119</v>
       </c>
-      <c r="C246" s="10" t="s">
-        <v>1404</v>
+      <c r="C246" t="s">
+        <v>1403</v>
       </c>
       <c r="D246" t="s">
         <v>1399</v>
@@ -12851,8 +12850,8 @@
       <c r="B247" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="C247" s="10" t="s">
-        <v>1404</v>
+      <c r="C247" t="s">
+        <v>1403</v>
       </c>
       <c r="D247" t="s">
         <v>1399</v>
@@ -12868,8 +12867,8 @@
       <c r="B249" t="s">
         <v>1065</v>
       </c>
-      <c r="C249" s="10" t="s">
-        <v>1404</v>
+      <c r="C249" t="s">
+        <v>1403</v>
       </c>
       <c r="D249" t="s">
         <v>1399</v>
@@ -12882,8 +12881,8 @@
       <c r="B250" t="s">
         <v>291</v>
       </c>
-      <c r="C250" s="10" t="s">
-        <v>1404</v>
+      <c r="C250" t="s">
+        <v>1403</v>
       </c>
       <c r="D250" t="s">
         <v>1399</v>
@@ -12899,8 +12898,8 @@
       <c r="B251" t="s">
         <v>507</v>
       </c>
-      <c r="C251" s="10" t="s">
-        <v>1404</v>
+      <c r="C251" t="s">
+        <v>1403</v>
       </c>
       <c r="D251" t="s">
         <v>1399</v>
@@ -12913,8 +12912,8 @@
       <c r="B252" t="s">
         <v>832</v>
       </c>
-      <c r="C252" s="10" t="s">
-        <v>1404</v>
+      <c r="C252" t="s">
+        <v>1403</v>
       </c>
       <c r="D252" t="s">
         <v>1399</v>
@@ -12930,8 +12929,8 @@
       <c r="B253" t="s">
         <v>815</v>
       </c>
-      <c r="C253" s="10" t="s">
-        <v>1404</v>
+      <c r="C253" t="s">
+        <v>1403</v>
       </c>
       <c r="D253" t="s">
         <v>1399</v>
@@ -12944,8 +12943,8 @@
       <c r="B254" t="s">
         <v>816</v>
       </c>
-      <c r="C254" s="10" t="s">
-        <v>1404</v>
+      <c r="C254" t="s">
+        <v>1403</v>
       </c>
       <c r="D254" t="s">
         <v>1399</v>
@@ -12958,8 +12957,8 @@
       <c r="B255" t="s">
         <v>824</v>
       </c>
-      <c r="C255" s="10" t="s">
-        <v>1404</v>
+      <c r="C255" t="s">
+        <v>1403</v>
       </c>
       <c r="D255" t="s">
         <v>1399</v>
@@ -12975,8 +12974,8 @@
       <c r="B256" t="s">
         <v>833</v>
       </c>
-      <c r="C256" s="10" t="s">
-        <v>1404</v>
+      <c r="C256" t="s">
+        <v>1403</v>
       </c>
       <c r="D256" t="s">
         <v>1399</v>
@@ -12989,8 +12988,8 @@
       <c r="B257" t="s">
         <v>834</v>
       </c>
-      <c r="C257" s="10" t="s">
-        <v>1404</v>
+      <c r="C257" t="s">
+        <v>1403</v>
       </c>
       <c r="D257" t="s">
         <v>1399</v>
@@ -13003,8 +13002,8 @@
       <c r="B258" t="s">
         <v>835</v>
       </c>
-      <c r="C258" s="10" t="s">
-        <v>1404</v>
+      <c r="C258" t="s">
+        <v>1403</v>
       </c>
       <c r="D258" t="s">
         <v>1399</v>
@@ -13017,8 +13016,8 @@
       <c r="B259" t="s">
         <v>756</v>
       </c>
-      <c r="C259" s="10" t="s">
-        <v>1404</v>
+      <c r="C259" t="s">
+        <v>1403</v>
       </c>
       <c r="D259" t="s">
         <v>1399</v>
@@ -13031,8 +13030,8 @@
       <c r="B260" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C260" s="10" t="s">
-        <v>1404</v>
+      <c r="C260" t="s">
+        <v>1403</v>
       </c>
       <c r="D260" t="s">
         <v>1399</v>
@@ -13048,8 +13047,8 @@
       <c r="B261" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="C261" s="10" t="s">
-        <v>1404</v>
+      <c r="C261" t="s">
+        <v>1403</v>
       </c>
       <c r="D261" t="s">
         <v>1399</v>
@@ -13065,8 +13064,8 @@
       <c r="B263" t="s">
         <v>627</v>
       </c>
-      <c r="C263" s="10" t="s">
-        <v>1404</v>
+      <c r="C263" t="s">
+        <v>1403</v>
       </c>
       <c r="D263" t="s">
         <v>1399</v>
@@ -13082,8 +13081,8 @@
       <c r="B264" t="s">
         <v>1192</v>
       </c>
-      <c r="C264" s="10" t="s">
-        <v>1404</v>
+      <c r="C264" t="s">
+        <v>1403</v>
       </c>
       <c r="D264" t="s">
         <v>1399</v>
@@ -13099,8 +13098,8 @@
       <c r="B265" t="s">
         <v>493</v>
       </c>
-      <c r="C265" s="10" t="s">
-        <v>1404</v>
+      <c r="C265" t="s">
+        <v>1403</v>
       </c>
       <c r="D265" t="s">
         <v>1399</v>
@@ -13116,8 +13115,8 @@
       <c r="B266" t="s">
         <v>533</v>
       </c>
-      <c r="C266" s="10" t="s">
-        <v>1404</v>
+      <c r="C266" t="s">
+        <v>1403</v>
       </c>
       <c r="D266" t="s">
         <v>1399</v>
@@ -13130,8 +13129,8 @@
       <c r="B267" t="s">
         <v>299</v>
       </c>
-      <c r="C267" s="10" t="s">
-        <v>1404</v>
+      <c r="C267" t="s">
+        <v>1403</v>
       </c>
       <c r="D267" t="s">
         <v>1399</v>
@@ -13144,8 +13143,8 @@
       <c r="B268" t="s">
         <v>300</v>
       </c>
-      <c r="C268" s="10" t="s">
-        <v>1404</v>
+      <c r="C268" t="s">
+        <v>1403</v>
       </c>
       <c r="D268" t="s">
         <v>1399</v>
@@ -13161,8 +13160,8 @@
       <c r="B269" t="s">
         <v>508</v>
       </c>
-      <c r="C269" s="10" t="s">
-        <v>1404</v>
+      <c r="C269" t="s">
+        <v>1403</v>
       </c>
       <c r="D269" t="s">
         <v>1399</v>
@@ -13175,8 +13174,8 @@
       <c r="B270" t="s">
         <v>301</v>
       </c>
-      <c r="C270" s="10" t="s">
-        <v>1404</v>
+      <c r="C270" t="s">
+        <v>1403</v>
       </c>
       <c r="D270" t="s">
         <v>1399</v>
@@ -13189,8 +13188,8 @@
       <c r="B271" t="s">
         <v>302</v>
       </c>
-      <c r="C271" s="10" t="s">
-        <v>1404</v>
+      <c r="C271" t="s">
+        <v>1403</v>
       </c>
       <c r="D271" t="s">
         <v>1399</v>
@@ -13203,8 +13202,8 @@
       <c r="B272" t="s">
         <v>303</v>
       </c>
-      <c r="C272" s="10" t="s">
-        <v>1404</v>
+      <c r="C272" t="s">
+        <v>1403</v>
       </c>
       <c r="D272" t="s">
         <v>1399</v>
@@ -13217,8 +13216,8 @@
       <c r="B273" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C273" s="10" t="s">
-        <v>1404</v>
+      <c r="C273" t="s">
+        <v>1403</v>
       </c>
       <c r="D273" t="s">
         <v>1399</v>
@@ -13234,8 +13233,8 @@
       <c r="B274" t="s">
         <v>305</v>
       </c>
-      <c r="C274" s="10" t="s">
-        <v>1404</v>
+      <c r="C274" t="s">
+        <v>1403</v>
       </c>
       <c r="D274" t="s">
         <v>1399</v>
@@ -13248,8 +13247,8 @@
       <c r="B275" t="s">
         <v>306</v>
       </c>
-      <c r="C275" s="10" t="s">
-        <v>1404</v>
+      <c r="C275" t="s">
+        <v>1403</v>
       </c>
       <c r="D275" t="s">
         <v>1399</v>
@@ -13262,8 +13261,8 @@
       <c r="B276" t="s">
         <v>307</v>
       </c>
-      <c r="C276" s="10" t="s">
-        <v>1404</v>
+      <c r="C276" t="s">
+        <v>1403</v>
       </c>
       <c r="D276" t="s">
         <v>1399</v>
@@ -13276,8 +13275,8 @@
       <c r="B277" t="s">
         <v>308</v>
       </c>
-      <c r="C277" s="10" t="s">
-        <v>1404</v>
+      <c r="C277" t="s">
+        <v>1403</v>
       </c>
       <c r="D277" t="s">
         <v>1399</v>
@@ -13290,8 +13289,8 @@
       <c r="B278" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="C278" s="10" t="s">
-        <v>1404</v>
+      <c r="C278" t="s">
+        <v>1403</v>
       </c>
       <c r="D278" t="s">
         <v>1399</v>
@@ -13307,8 +13306,8 @@
       <c r="B279" t="s">
         <v>736</v>
       </c>
-      <c r="C279" s="10" t="s">
-        <v>1404</v>
+      <c r="C279" t="s">
+        <v>1403</v>
       </c>
       <c r="D279" t="s">
         <v>1399</v>
@@ -13321,8 +13320,8 @@
       <c r="B280" t="s">
         <v>310</v>
       </c>
-      <c r="C280" s="10" t="s">
-        <v>1404</v>
+      <c r="C280" t="s">
+        <v>1403</v>
       </c>
       <c r="D280" t="s">
         <v>1399</v>
@@ -13335,8 +13334,8 @@
       <c r="B281" t="s">
         <v>311</v>
       </c>
-      <c r="C281" s="10" t="s">
-        <v>1404</v>
+      <c r="C281" t="s">
+        <v>1403</v>
       </c>
       <c r="D281" t="s">
         <v>1399</v>
@@ -13349,8 +13348,8 @@
       <c r="B282" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="C282" s="10" t="s">
-        <v>1404</v>
+      <c r="C282" t="s">
+        <v>1403</v>
       </c>
       <c r="D282" t="s">
         <v>1399</v>
@@ -13366,8 +13365,8 @@
       <c r="B284" t="s">
         <v>538</v>
       </c>
-      <c r="C284" s="10" t="s">
-        <v>1404</v>
+      <c r="C284" t="s">
+        <v>1403</v>
       </c>
       <c r="D284" t="s">
         <v>1399</v>
@@ -13380,8 +13379,8 @@
       <c r="B285" t="s">
         <v>350</v>
       </c>
-      <c r="C285" s="10" t="s">
-        <v>1404</v>
+      <c r="C285" t="s">
+        <v>1403</v>
       </c>
       <c r="D285" t="s">
         <v>1399</v>
@@ -13394,8 +13393,8 @@
       <c r="B286" t="s">
         <v>347</v>
       </c>
-      <c r="C286" s="10" t="s">
-        <v>1404</v>
+      <c r="C286" t="s">
+        <v>1403</v>
       </c>
       <c r="D286" t="s">
         <v>1399</v>
@@ -13408,8 +13407,8 @@
       <c r="B287" t="s">
         <v>348</v>
       </c>
-      <c r="C287" s="10" t="s">
-        <v>1404</v>
+      <c r="C287" t="s">
+        <v>1403</v>
       </c>
       <c r="D287" t="s">
         <v>1399</v>
@@ -13425,8 +13424,8 @@
       <c r="B288" t="s">
         <v>509</v>
       </c>
-      <c r="C288" s="10" t="s">
-        <v>1404</v>
+      <c r="C288" t="s">
+        <v>1403</v>
       </c>
       <c r="D288" t="s">
         <v>1399</v>
@@ -13439,8 +13438,8 @@
       <c r="B289" t="s">
         <v>349</v>
       </c>
-      <c r="C289" s="10" t="s">
-        <v>1404</v>
+      <c r="C289" t="s">
+        <v>1403</v>
       </c>
       <c r="D289" t="s">
         <v>1399</v>
@@ -13456,8 +13455,8 @@
       <c r="B290" t="s">
         <v>341</v>
       </c>
-      <c r="C290" s="10" t="s">
-        <v>1404</v>
+      <c r="C290" t="s">
+        <v>1403</v>
       </c>
       <c r="D290" t="s">
         <v>1399</v>
@@ -13470,8 +13469,8 @@
       <c r="B291" t="s">
         <v>342</v>
       </c>
-      <c r="C291" s="10" t="s">
-        <v>1404</v>
+      <c r="C291" t="s">
+        <v>1403</v>
       </c>
       <c r="D291" t="s">
         <v>1399</v>
@@ -13487,8 +13486,8 @@
       <c r="B292" t="s">
         <v>343</v>
       </c>
-      <c r="C292" s="10" t="s">
-        <v>1404</v>
+      <c r="C292" t="s">
+        <v>1403</v>
       </c>
       <c r="D292" t="s">
         <v>1399</v>
@@ -13501,8 +13500,8 @@
       <c r="B293" t="s">
         <v>344</v>
       </c>
-      <c r="C293" s="10" t="s">
-        <v>1404</v>
+      <c r="C293" t="s">
+        <v>1403</v>
       </c>
       <c r="D293" t="s">
         <v>1399</v>
@@ -13515,8 +13514,8 @@
       <c r="B294" t="s">
         <v>345</v>
       </c>
-      <c r="C294" s="10" t="s">
-        <v>1404</v>
+      <c r="C294" t="s">
+        <v>1403</v>
       </c>
       <c r="D294" t="s">
         <v>1399</v>
@@ -13529,8 +13528,8 @@
       <c r="B295" t="s">
         <v>346</v>
       </c>
-      <c r="C295" s="10" t="s">
-        <v>1404</v>
+      <c r="C295" t="s">
+        <v>1403</v>
       </c>
       <c r="D295" t="s">
         <v>1399</v>
@@ -13543,8 +13542,8 @@
       <c r="B296" t="s">
         <v>343</v>
       </c>
-      <c r="C296" s="10" t="s">
-        <v>1404</v>
+      <c r="C296" t="s">
+        <v>1403</v>
       </c>
       <c r="D296" t="s">
         <v>1399</v>
@@ -13557,8 +13556,8 @@
       <c r="B297" t="s">
         <v>977</v>
       </c>
-      <c r="C297" s="10" t="s">
-        <v>1404</v>
+      <c r="C297" t="s">
+        <v>1403</v>
       </c>
       <c r="D297" t="s">
         <v>1399</v>
@@ -13574,8 +13573,8 @@
       <c r="B298" t="s">
         <v>979</v>
       </c>
-      <c r="C298" s="10" t="s">
-        <v>1404</v>
+      <c r="C298" t="s">
+        <v>1403</v>
       </c>
       <c r="D298" t="s">
         <v>1399</v>
@@ -13591,8 +13590,8 @@
       <c r="B299" t="s">
         <v>981</v>
       </c>
-      <c r="C299" s="10" t="s">
-        <v>1404</v>
+      <c r="C299" t="s">
+        <v>1403</v>
       </c>
       <c r="D299" t="s">
         <v>1399</v>
@@ -13608,8 +13607,8 @@
       <c r="B300" t="s">
         <v>1112</v>
       </c>
-      <c r="C300" s="10" t="s">
-        <v>1404</v>
+      <c r="C300" t="s">
+        <v>1403</v>
       </c>
       <c r="D300" t="s">
         <v>1399</v>
@@ -13622,8 +13621,8 @@
       <c r="B301" s="5" t="s">
         <v>1170</v>
       </c>
-      <c r="C301" s="10" t="s">
-        <v>1404</v>
+      <c r="C301" t="s">
+        <v>1403</v>
       </c>
       <c r="D301" t="s">
         <v>1399</v>
@@ -13639,8 +13638,8 @@
       <c r="B303" t="s">
         <v>645</v>
       </c>
-      <c r="C303" s="10" t="s">
-        <v>1404</v>
+      <c r="C303" t="s">
+        <v>1403</v>
       </c>
       <c r="D303" t="s">
         <v>1399</v>
@@ -13656,8 +13655,8 @@
       <c r="B304" s="7" t="s">
         <v>1135</v>
       </c>
-      <c r="C304" s="10" t="s">
-        <v>1404</v>
+      <c r="C304" t="s">
+        <v>1403</v>
       </c>
       <c r="D304" t="s">
         <v>1399</v>
@@ -13673,8 +13672,8 @@
       <c r="B305" s="7" t="s">
         <v>1136</v>
       </c>
-      <c r="C305" s="10" t="s">
-        <v>1404</v>
+      <c r="C305" t="s">
+        <v>1403</v>
       </c>
       <c r="D305" t="s">
         <v>1399</v>
@@ -13690,8 +13689,8 @@
       <c r="B306" s="5" t="s">
         <v>1171</v>
       </c>
-      <c r="C306" s="10" t="s">
-        <v>1404</v>
+      <c r="C306" t="s">
+        <v>1403</v>
       </c>
       <c r="D306" t="s">
         <v>1399</v>
@@ -13707,8 +13706,8 @@
       <c r="B308" t="s">
         <v>625</v>
       </c>
-      <c r="C308" s="10" t="s">
-        <v>1404</v>
+      <c r="C308" t="s">
+        <v>1403</v>
       </c>
       <c r="D308" t="s">
         <v>1399</v>
@@ -13724,8 +13723,8 @@
       <c r="B309" t="s">
         <v>464</v>
       </c>
-      <c r="C309" s="10" t="s">
-        <v>1404</v>
+      <c r="C309" t="s">
+        <v>1403</v>
       </c>
       <c r="D309" t="s">
         <v>1399</v>
@@ -13738,8 +13737,8 @@
       <c r="B310" t="s">
         <v>369</v>
       </c>
-      <c r="C310" s="10" t="s">
-        <v>1404</v>
+      <c r="C310" t="s">
+        <v>1403</v>
       </c>
       <c r="D310" t="s">
         <v>1399</v>
@@ -13752,8 +13751,8 @@
       <c r="B311" t="s">
         <v>370</v>
       </c>
-      <c r="C311" s="10" t="s">
-        <v>1404</v>
+      <c r="C311" t="s">
+        <v>1403</v>
       </c>
       <c r="D311" t="s">
         <v>1399</v>
@@ -13769,8 +13768,8 @@
       <c r="B312" t="s">
         <v>511</v>
       </c>
-      <c r="C312" s="10" t="s">
-        <v>1404</v>
+      <c r="C312" t="s">
+        <v>1403</v>
       </c>
       <c r="D312" t="s">
         <v>1399</v>
@@ -13783,8 +13782,8 @@
       <c r="B313" t="s">
         <v>371</v>
       </c>
-      <c r="C313" s="10" t="s">
-        <v>1404</v>
+      <c r="C313" t="s">
+        <v>1403</v>
       </c>
       <c r="D313" t="s">
         <v>1399</v>
@@ -13800,8 +13799,8 @@
       <c r="B314" t="s">
         <v>372</v>
       </c>
-      <c r="C314" s="10" t="s">
-        <v>1404</v>
+      <c r="C314" t="s">
+        <v>1403</v>
       </c>
       <c r="D314" t="s">
         <v>1399</v>
@@ -13817,8 +13816,8 @@
       <c r="B315" t="s">
         <v>523</v>
       </c>
-      <c r="C315" s="10" t="s">
-        <v>1404</v>
+      <c r="C315" t="s">
+        <v>1403</v>
       </c>
       <c r="D315" t="s">
         <v>1399</v>
@@ -13831,8 +13830,8 @@
       <c r="B316" t="s">
         <v>373</v>
       </c>
-      <c r="C316" s="10" t="s">
-        <v>1404</v>
+      <c r="C316" t="s">
+        <v>1403</v>
       </c>
       <c r="D316" t="s">
         <v>1399</v>
@@ -13845,8 +13844,8 @@
       <c r="B317" t="s">
         <v>374</v>
       </c>
-      <c r="C317" s="10" t="s">
-        <v>1404</v>
+      <c r="C317" t="s">
+        <v>1403</v>
       </c>
       <c r="D317" t="s">
         <v>1399</v>
@@ -13859,8 +13858,8 @@
       <c r="B318" t="s">
         <v>375</v>
       </c>
-      <c r="C318" s="10" t="s">
-        <v>1404</v>
+      <c r="C318" t="s">
+        <v>1403</v>
       </c>
       <c r="D318" t="s">
         <v>1399</v>
@@ -13873,8 +13872,8 @@
       <c r="B319" t="s">
         <v>376</v>
       </c>
-      <c r="C319" s="10" t="s">
-        <v>1404</v>
+      <c r="C319" t="s">
+        <v>1403</v>
       </c>
       <c r="D319" t="s">
         <v>1399</v>
@@ -13887,8 +13886,8 @@
       <c r="B320" t="s">
         <v>377</v>
       </c>
-      <c r="C320" s="10" t="s">
-        <v>1404</v>
+      <c r="C320" t="s">
+        <v>1403</v>
       </c>
       <c r="D320" t="s">
         <v>1399</v>
@@ -13901,8 +13900,8 @@
       <c r="B321" t="s">
         <v>378</v>
       </c>
-      <c r="C321" s="10" t="s">
-        <v>1404</v>
+      <c r="C321" t="s">
+        <v>1403</v>
       </c>
       <c r="D321" t="s">
         <v>1399</v>
@@ -13915,8 +13914,8 @@
       <c r="B322" s="7" t="s">
         <v>1137</v>
       </c>
-      <c r="C322" s="10" t="s">
-        <v>1404</v>
+      <c r="C322" t="s">
+        <v>1403</v>
       </c>
       <c r="D322" t="s">
         <v>1399</v>
@@ -13932,8 +13931,8 @@
       <c r="B323" t="s">
         <v>1058</v>
       </c>
-      <c r="C323" s="10" t="s">
-        <v>1404</v>
+      <c r="C323" t="s">
+        <v>1403</v>
       </c>
       <c r="D323" t="s">
         <v>1399</v>
@@ -13946,8 +13945,8 @@
       <c r="B324" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="C324" s="10" t="s">
-        <v>1404</v>
+      <c r="C324" t="s">
+        <v>1403</v>
       </c>
       <c r="D324" t="s">
         <v>1399</v>
@@ -13963,8 +13962,8 @@
       <c r="B325" t="s">
         <v>1115</v>
       </c>
-      <c r="C325" s="10" t="s">
-        <v>1404</v>
+      <c r="C325" t="s">
+        <v>1403</v>
       </c>
       <c r="D325" t="s">
         <v>1399</v>
@@ -13977,8 +13976,8 @@
       <c r="B326" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C326" s="10" t="s">
-        <v>1404</v>
+      <c r="C326" t="s">
+        <v>1403</v>
       </c>
       <c r="D326" t="s">
         <v>1399</v>
@@ -13994,8 +13993,8 @@
       <c r="B328" t="s">
         <v>464</v>
       </c>
-      <c r="C328" s="10" t="s">
-        <v>1404</v>
+      <c r="C328" t="s">
+        <v>1403</v>
       </c>
       <c r="D328" t="s">
         <v>1399</v>
@@ -14008,8 +14007,8 @@
       <c r="B329" t="s">
         <v>396</v>
       </c>
-      <c r="C329" s="10" t="s">
-        <v>1404</v>
+      <c r="C329" t="s">
+        <v>1403</v>
       </c>
       <c r="D329" t="s">
         <v>1399</v>
@@ -14022,8 +14021,8 @@
       <c r="B330" t="s">
         <v>397</v>
       </c>
-      <c r="C330" s="10" t="s">
-        <v>1404</v>
+      <c r="C330" t="s">
+        <v>1403</v>
       </c>
       <c r="D330" t="s">
         <v>1399</v>
@@ -14039,8 +14038,8 @@
       <c r="B331" t="s">
         <v>512</v>
       </c>
-      <c r="C331" s="10" t="s">
-        <v>1404</v>
+      <c r="C331" t="s">
+        <v>1403</v>
       </c>
       <c r="D331" t="s">
         <v>1399</v>
@@ -14053,8 +14052,8 @@
       <c r="B332" t="s">
         <v>398</v>
       </c>
-      <c r="C332" s="10" t="s">
-        <v>1404</v>
+      <c r="C332" t="s">
+        <v>1403</v>
       </c>
       <c r="D332" t="s">
         <v>1399</v>
@@ -14070,8 +14069,8 @@
       <c r="B333" t="s">
         <v>399</v>
       </c>
-      <c r="C333" s="10" t="s">
-        <v>1404</v>
+      <c r="C333" t="s">
+        <v>1403</v>
       </c>
       <c r="D333" t="s">
         <v>1399</v>
@@ -14087,8 +14086,8 @@
       <c r="B334" t="s">
         <v>524</v>
       </c>
-      <c r="C334" s="10" t="s">
-        <v>1404</v>
+      <c r="C334" t="s">
+        <v>1403</v>
       </c>
       <c r="D334" t="s">
         <v>1399</v>
@@ -14101,8 +14100,8 @@
       <c r="B335" t="s">
         <v>373</v>
       </c>
-      <c r="C335" s="10" t="s">
-        <v>1404</v>
+      <c r="C335" t="s">
+        <v>1403</v>
       </c>
       <c r="D335" t="s">
         <v>1399</v>
@@ -14115,8 +14114,8 @@
       <c r="B336" t="s">
         <v>374</v>
       </c>
-      <c r="C336" s="10" t="s">
-        <v>1404</v>
+      <c r="C336" t="s">
+        <v>1403</v>
       </c>
       <c r="D336" t="s">
         <v>1399</v>
@@ -14129,8 +14128,8 @@
       <c r="B337" t="s">
         <v>400</v>
       </c>
-      <c r="C337" s="10" t="s">
-        <v>1404</v>
+      <c r="C337" t="s">
+        <v>1403</v>
       </c>
       <c r="D337" t="s">
         <v>1399</v>
@@ -14143,8 +14142,8 @@
       <c r="B338" t="s">
         <v>401</v>
       </c>
-      <c r="C338" s="10" t="s">
-        <v>1404</v>
+      <c r="C338" t="s">
+        <v>1403</v>
       </c>
       <c r="D338" t="s">
         <v>1399</v>
@@ -14157,8 +14156,8 @@
       <c r="B339" t="s">
         <v>377</v>
       </c>
-      <c r="C339" s="10" t="s">
-        <v>1404</v>
+      <c r="C339" t="s">
+        <v>1403</v>
       </c>
       <c r="D339" t="s">
         <v>1399</v>
@@ -14171,8 +14170,8 @@
       <c r="B340" t="s">
         <v>378</v>
       </c>
-      <c r="C340" s="10" t="s">
-        <v>1404</v>
+      <c r="C340" t="s">
+        <v>1403</v>
       </c>
       <c r="D340" t="s">
         <v>1399</v>
@@ -14185,8 +14184,8 @@
       <c r="B341" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="C341" s="10" t="s">
-        <v>1404</v>
+      <c r="C341" t="s">
+        <v>1403</v>
       </c>
       <c r="D341" t="s">
         <v>1399</v>
@@ -14202,8 +14201,8 @@
       <c r="B342" t="s">
         <v>1117</v>
       </c>
-      <c r="C342" s="10" t="s">
-        <v>1404</v>
+      <c r="C342" t="s">
+        <v>1403</v>
       </c>
       <c r="D342" t="s">
         <v>1399</v>
@@ -14216,8 +14215,8 @@
       <c r="B343" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C343" s="10" t="s">
-        <v>1404</v>
+      <c r="C343" t="s">
+        <v>1403</v>
       </c>
       <c r="D343" t="s">
         <v>1399</v>
@@ -14233,8 +14232,8 @@
       <c r="B345" t="s">
         <v>623</v>
       </c>
-      <c r="C345" s="10" t="s">
-        <v>1404</v>
+      <c r="C345" t="s">
+        <v>1403</v>
       </c>
       <c r="D345" t="s">
         <v>1399</v>
@@ -14250,8 +14249,8 @@
       <c r="B346" t="s">
         <v>1195</v>
       </c>
-      <c r="C346" s="10" t="s">
-        <v>1404</v>
+      <c r="C346" t="s">
+        <v>1403</v>
       </c>
       <c r="D346" t="s">
         <v>1399</v>
@@ -14264,8 +14263,8 @@
       <c r="B347" t="s">
         <v>1196</v>
       </c>
-      <c r="C347" s="10" t="s">
-        <v>1404</v>
+      <c r="C347" t="s">
+        <v>1403</v>
       </c>
       <c r="D347" t="s">
         <v>1399</v>
@@ -14281,8 +14280,8 @@
       <c r="B348" t="s">
         <v>1197</v>
       </c>
-      <c r="C348" s="10" t="s">
-        <v>1404</v>
+      <c r="C348" t="s">
+        <v>1403</v>
       </c>
       <c r="D348" t="s">
         <v>1399</v>
@@ -14295,8 +14294,8 @@
       <c r="B349" t="s">
         <v>1198</v>
       </c>
-      <c r="C349" s="10" t="s">
-        <v>1404</v>
+      <c r="C349" t="s">
+        <v>1403</v>
       </c>
       <c r="D349" t="s">
         <v>1399</v>
@@ -14309,8 +14308,8 @@
       <c r="B350" t="s">
         <v>1199</v>
       </c>
-      <c r="C350" s="10" t="s">
-        <v>1404</v>
+      <c r="C350" t="s">
+        <v>1403</v>
       </c>
       <c r="D350" t="s">
         <v>1399</v>
@@ -14323,8 +14322,8 @@
       <c r="B351" t="s">
         <v>1200</v>
       </c>
-      <c r="C351" s="10" t="s">
-        <v>1404</v>
+      <c r="C351" t="s">
+        <v>1403</v>
       </c>
       <c r="D351" t="s">
         <v>1399</v>
@@ -14337,8 +14336,8 @@
       <c r="B352" t="s">
         <v>1075</v>
       </c>
-      <c r="C352" s="10" t="s">
-        <v>1404</v>
+      <c r="C352" t="s">
+        <v>1403</v>
       </c>
       <c r="D352" t="s">
         <v>1399</v>
@@ -14354,8 +14353,8 @@
       <c r="B353" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="C353" s="10" t="s">
-        <v>1404</v>
+      <c r="C353" t="s">
+        <v>1403</v>
       </c>
       <c r="D353" t="s">
         <v>1399</v>
@@ -14371,8 +14370,8 @@
       <c r="B355" t="s">
         <v>688</v>
       </c>
-      <c r="C355" s="10" t="s">
-        <v>1404</v>
+      <c r="C355" t="s">
+        <v>1403</v>
       </c>
       <c r="D355" t="s">
         <v>1399</v>
@@ -14388,8 +14387,8 @@
       <c r="B356" s="5" t="s">
         <v>1174</v>
       </c>
-      <c r="C356" s="10" t="s">
-        <v>1404</v>
+      <c r="C356" t="s">
+        <v>1403</v>
       </c>
       <c r="D356" t="s">
         <v>1399</v>
@@ -14405,8 +14404,8 @@
       <c r="B358" t="s">
         <v>695</v>
       </c>
-      <c r="C358" s="10" t="s">
-        <v>1404</v>
+      <c r="C358" t="s">
+        <v>1403</v>
       </c>
       <c r="D358" t="s">
         <v>1399</v>
@@ -14419,8 +14418,8 @@
       <c r="B359" t="s">
         <v>1194</v>
       </c>
-      <c r="C359" s="10" t="s">
-        <v>1404</v>
+      <c r="C359" t="s">
+        <v>1403</v>
       </c>
       <c r="D359" t="s">
         <v>1399</v>
@@ -14433,8 +14432,8 @@
       <c r="B360" t="s">
         <v>698</v>
       </c>
-      <c r="C360" s="10" t="s">
-        <v>1404</v>
+      <c r="C360" t="s">
+        <v>1403</v>
       </c>
       <c r="D360" t="s">
         <v>1399</v>
@@ -14447,8 +14446,8 @@
       <c r="B361" t="s">
         <v>700</v>
       </c>
-      <c r="C361" s="10" t="s">
-        <v>1404</v>
+      <c r="C361" t="s">
+        <v>1403</v>
       </c>
       <c r="D361" t="s">
         <v>1399</v>
@@ -14461,8 +14460,8 @@
       <c r="B362" t="s">
         <v>702</v>
       </c>
-      <c r="C362" s="10" t="s">
-        <v>1404</v>
+      <c r="C362" t="s">
+        <v>1403</v>
       </c>
       <c r="D362" t="s">
         <v>1399</v>
@@ -14475,8 +14474,8 @@
       <c r="B363" t="s">
         <v>704</v>
       </c>
-      <c r="C363" s="10" t="s">
-        <v>1404</v>
+      <c r="C363" t="s">
+        <v>1403</v>
       </c>
       <c r="D363" t="s">
         <v>1399</v>
@@ -14489,8 +14488,8 @@
       <c r="B364" t="s">
         <v>706</v>
       </c>
-      <c r="C364" s="10" t="s">
-        <v>1404</v>
+      <c r="C364" t="s">
+        <v>1403</v>
       </c>
       <c r="D364" t="s">
         <v>1399</v>
@@ -14503,8 +14502,8 @@
       <c r="B365" t="s">
         <v>708</v>
       </c>
-      <c r="C365" s="10" t="s">
-        <v>1404</v>
+      <c r="C365" t="s">
+        <v>1403</v>
       </c>
       <c r="D365" t="s">
         <v>1399</v>
@@ -14517,8 +14516,8 @@
       <c r="B366" t="s">
         <v>1101</v>
       </c>
-      <c r="C366" s="10" t="s">
-        <v>1404</v>
+      <c r="C366" t="s">
+        <v>1403</v>
       </c>
       <c r="D366" t="s">
         <v>1399</v>
@@ -14531,8 +14530,8 @@
       <c r="B367" s="7" t="s">
         <v>1175</v>
       </c>
-      <c r="C367" s="10" t="s">
-        <v>1404</v>
+      <c r="C367" t="s">
+        <v>1403</v>
       </c>
       <c r="D367" t="s">
         <v>1399</v>
@@ -14548,8 +14547,8 @@
       <c r="B368" t="s">
         <v>712</v>
       </c>
-      <c r="C368" s="10" t="s">
-        <v>1404</v>
+      <c r="C368" t="s">
+        <v>1403</v>
       </c>
       <c r="D368" t="s">
         <v>1399</v>
@@ -14562,8 +14561,8 @@
       <c r="B369" t="s">
         <v>714</v>
       </c>
-      <c r="C369" s="10" t="s">
-        <v>1404</v>
+      <c r="C369" t="s">
+        <v>1403</v>
       </c>
       <c r="D369" t="s">
         <v>1399</v>
@@ -14576,8 +14575,8 @@
       <c r="B370" t="s">
         <v>716</v>
       </c>
-      <c r="C370" s="10" t="s">
-        <v>1404</v>
+      <c r="C370" t="s">
+        <v>1403</v>
       </c>
       <c r="D370" t="s">
         <v>1399</v>
@@ -14590,8 +14589,8 @@
       <c r="B371" t="s">
         <v>718</v>
       </c>
-      <c r="C371" s="10" t="s">
-        <v>1404</v>
+      <c r="C371" t="s">
+        <v>1403</v>
       </c>
       <c r="D371" t="s">
         <v>1399</v>
@@ -14604,8 +14603,8 @@
       <c r="B372" t="s">
         <v>720</v>
       </c>
-      <c r="C372" s="10" t="s">
-        <v>1404</v>
+      <c r="C372" t="s">
+        <v>1403</v>
       </c>
       <c r="D372" t="s">
         <v>1399</v>
@@ -14618,8 +14617,8 @@
       <c r="B373" t="s">
         <v>722</v>
       </c>
-      <c r="C373" s="10" t="s">
-        <v>1404</v>
+      <c r="C373" t="s">
+        <v>1403</v>
       </c>
       <c r="D373" t="s">
         <v>1399</v>
@@ -14632,8 +14631,8 @@
       <c r="B374" t="s">
         <v>1051</v>
       </c>
-      <c r="C374" s="10" t="s">
-        <v>1404</v>
+      <c r="C374" t="s">
+        <v>1403</v>
       </c>
       <c r="D374" t="s">
         <v>1399</v>
@@ -14646,8 +14645,8 @@
       <c r="B375" t="s">
         <v>724</v>
       </c>
-      <c r="C375" s="10" t="s">
-        <v>1404</v>
+      <c r="C375" t="s">
+        <v>1403</v>
       </c>
       <c r="D375" t="s">
         <v>1399</v>
@@ -14660,8 +14659,8 @@
       <c r="B376" t="s">
         <v>1091</v>
       </c>
-      <c r="C376" s="10" t="s">
-        <v>1404</v>
+      <c r="C376" t="s">
+        <v>1403</v>
       </c>
       <c r="D376" t="s">
         <v>1399</v>
@@ -14674,8 +14673,8 @@
       <c r="B377" s="5" t="s">
         <v>1176</v>
       </c>
-      <c r="C377" s="10" t="s">
-        <v>1404</v>
+      <c r="C377" t="s">
+        <v>1403</v>
       </c>
       <c r="D377" t="s">
         <v>1399</v>
@@ -14691,8 +14690,8 @@
       <c r="B379" t="s">
         <v>726</v>
       </c>
-      <c r="C379" s="10" t="s">
-        <v>1404</v>
+      <c r="C379" t="s">
+        <v>1403</v>
       </c>
       <c r="D379" t="s">
         <v>1399</v>
@@ -14705,8 +14704,8 @@
       <c r="B380" t="s">
         <v>728</v>
       </c>
-      <c r="C380" s="10" t="s">
-        <v>1404</v>
+      <c r="C380" t="s">
+        <v>1403</v>
       </c>
       <c r="D380" t="s">
         <v>1399</v>
@@ -14719,8 +14718,8 @@
       <c r="B381" t="s">
         <v>730</v>
       </c>
-      <c r="C381" s="10" t="s">
-        <v>1404</v>
+      <c r="C381" t="s">
+        <v>1403</v>
       </c>
       <c r="D381" t="s">
         <v>1399</v>
@@ -14733,8 +14732,8 @@
       <c r="B382" t="s">
         <v>732</v>
       </c>
-      <c r="C382" s="10" t="s">
-        <v>1404</v>
+      <c r="C382" t="s">
+        <v>1403</v>
       </c>
       <c r="D382" t="s">
         <v>1399</v>
@@ -14747,8 +14746,8 @@
       <c r="B383" t="s">
         <v>734</v>
       </c>
-      <c r="C383" s="10" t="s">
-        <v>1404</v>
+      <c r="C383" t="s">
+        <v>1403</v>
       </c>
       <c r="D383" t="s">
         <v>1399</v>
@@ -14761,8 +14760,8 @@
       <c r="B384" t="s">
         <v>736</v>
       </c>
-      <c r="C384" s="10" t="s">
-        <v>1404</v>
+      <c r="C384" t="s">
+        <v>1403</v>
       </c>
       <c r="D384" t="s">
         <v>1399</v>
@@ -14775,8 +14774,8 @@
       <c r="B385" t="s">
         <v>738</v>
       </c>
-      <c r="C385" s="10" t="s">
-        <v>1404</v>
+      <c r="C385" t="s">
+        <v>1403</v>
       </c>
       <c r="D385" t="s">
         <v>1399</v>
@@ -14789,8 +14788,8 @@
       <c r="B386" t="s">
         <v>311</v>
       </c>
-      <c r="C386" s="10" t="s">
-        <v>1404</v>
+      <c r="C386" t="s">
+        <v>1403</v>
       </c>
       <c r="D386" t="s">
         <v>1399</v>
@@ -14803,8 +14802,8 @@
       <c r="B387" t="s">
         <v>741</v>
       </c>
-      <c r="C387" s="10" t="s">
-        <v>1404</v>
+      <c r="C387" t="s">
+        <v>1403</v>
       </c>
       <c r="D387" t="s">
         <v>1399</v>
@@ -14817,8 +14816,8 @@
       <c r="B388" t="s">
         <v>743</v>
       </c>
-      <c r="C388" s="10" t="s">
-        <v>1404</v>
+      <c r="C388" t="s">
+        <v>1403</v>
       </c>
       <c r="D388" t="s">
         <v>1399</v>
@@ -14831,8 +14830,8 @@
       <c r="B389" t="s">
         <v>1193</v>
       </c>
-      <c r="C389" s="10" t="s">
-        <v>1404</v>
+      <c r="C389" t="s">
+        <v>1403</v>
       </c>
       <c r="D389" t="s">
         <v>1399</v>
@@ -14845,8 +14844,8 @@
       <c r="B390" s="7" t="s">
         <v>1177</v>
       </c>
-      <c r="C390" s="10" t="s">
-        <v>1404</v>
+      <c r="C390" t="s">
+        <v>1403</v>
       </c>
       <c r="D390" t="s">
         <v>1399</v>
@@ -14862,8 +14861,8 @@
       <c r="B392" t="s">
         <v>305</v>
       </c>
-      <c r="C392" s="10" t="s">
-        <v>1404</v>
+      <c r="C392" t="s">
+        <v>1403</v>
       </c>
       <c r="D392" t="s">
         <v>1399</v>
@@ -14876,8 +14875,8 @@
       <c r="B393" t="s">
         <v>748</v>
       </c>
-      <c r="C393" s="10" t="s">
-        <v>1404</v>
+      <c r="C393" t="s">
+        <v>1403</v>
       </c>
       <c r="D393" t="s">
         <v>1399</v>
@@ -14890,8 +14889,8 @@
       <c r="B394" t="s">
         <v>307</v>
       </c>
-      <c r="C394" s="10" t="s">
-        <v>1404</v>
+      <c r="C394" t="s">
+        <v>1403</v>
       </c>
       <c r="D394" t="s">
         <v>1399</v>
@@ -14904,16 +14903,16 @@
       <c r="B395" t="s">
         <v>1102</v>
       </c>
-      <c r="C395" s="10" t="s">
-        <v>1404</v>
+      <c r="C395" t="s">
+        <v>1403</v>
       </c>
       <c r="D395" t="s">
         <v>1399</v>
       </c>
     </row>
     <row r="396" spans="1:5">
-      <c r="C396" s="10" t="s">
-        <v>1404</v>
+      <c r="C396" t="s">
+        <v>1403</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -14923,8 +14922,8 @@
       <c r="B397" t="s">
         <v>772</v>
       </c>
-      <c r="C397" s="10" t="s">
-        <v>1404</v>
+      <c r="C397" t="s">
+        <v>1403</v>
       </c>
       <c r="D397" t="s">
         <v>1399</v>
@@ -14937,8 +14936,8 @@
       <c r="B398" t="s">
         <v>769</v>
       </c>
-      <c r="C398" s="10" t="s">
-        <v>1404</v>
+      <c r="C398" t="s">
+        <v>1403</v>
       </c>
       <c r="D398" t="s">
         <v>1399</v>
@@ -14951,8 +14950,8 @@
       <c r="B399" t="s">
         <v>765</v>
       </c>
-      <c r="C399" s="10" t="s">
-        <v>1404</v>
+      <c r="C399" t="s">
+        <v>1403</v>
       </c>
       <c r="D399" t="s">
         <v>1399</v>
@@ -14965,8 +14964,8 @@
       <c r="B400" t="s">
         <v>766</v>
       </c>
-      <c r="C400" s="10" t="s">
-        <v>1404</v>
+      <c r="C400" t="s">
+        <v>1403</v>
       </c>
       <c r="D400" t="s">
         <v>1399</v>
@@ -14979,8 +14978,8 @@
       <c r="B401" t="s">
         <v>767</v>
       </c>
-      <c r="C401" s="10" t="s">
-        <v>1404</v>
+      <c r="C401" t="s">
+        <v>1403</v>
       </c>
       <c r="D401" t="s">
         <v>1399</v>
@@ -14993,8 +14992,8 @@
       <c r="B402" s="5" t="s">
         <v>1178</v>
       </c>
-      <c r="C402" s="10" t="s">
-        <v>1404</v>
+      <c r="C402" t="s">
+        <v>1403</v>
       </c>
       <c r="D402" t="s">
         <v>1399</v>
@@ -15010,8 +15009,8 @@
       <c r="B404" t="s">
         <v>780</v>
       </c>
-      <c r="C404" s="10" t="s">
-        <v>1404</v>
+      <c r="C404" t="s">
+        <v>1403</v>
       </c>
       <c r="D404" t="s">
         <v>1399</v>
@@ -15024,8 +15023,8 @@
       <c r="B405" t="s">
         <v>781</v>
       </c>
-      <c r="C405" s="10" t="s">
-        <v>1404</v>
+      <c r="C405" t="s">
+        <v>1403</v>
       </c>
       <c r="D405" t="s">
         <v>1399</v>
@@ -15038,8 +15037,8 @@
       <c r="B406" t="s">
         <v>765</v>
       </c>
-      <c r="C406" s="10" t="s">
-        <v>1404</v>
+      <c r="C406" t="s">
+        <v>1403</v>
       </c>
       <c r="D406" t="s">
         <v>1399</v>
@@ -15052,8 +15051,8 @@
       <c r="B407" t="s">
         <v>766</v>
       </c>
-      <c r="C407" s="10" t="s">
-        <v>1404</v>
+      <c r="C407" t="s">
+        <v>1403</v>
       </c>
       <c r="D407" t="s">
         <v>1399</v>
@@ -15066,8 +15065,8 @@
       <c r="B408" t="s">
         <v>767</v>
       </c>
-      <c r="C408" s="10" t="s">
-        <v>1404</v>
+      <c r="C408" t="s">
+        <v>1403</v>
       </c>
       <c r="D408" t="s">
         <v>1399</v>
@@ -15080,8 +15079,8 @@
       <c r="B409" s="5" t="s">
         <v>1179</v>
       </c>
-      <c r="C409" s="10" t="s">
-        <v>1404</v>
+      <c r="C409" t="s">
+        <v>1403</v>
       </c>
       <c r="D409" t="s">
         <v>1399</v>
@@ -15097,8 +15096,8 @@
       <c r="B411" t="s">
         <v>788</v>
       </c>
-      <c r="C411" s="10" t="s">
-        <v>1404</v>
+      <c r="C411" t="s">
+        <v>1403</v>
       </c>
       <c r="D411" t="s">
         <v>1399</v>
@@ -15111,8 +15110,8 @@
       <c r="B412" t="s">
         <v>1066</v>
       </c>
-      <c r="C412" s="10" t="s">
-        <v>1404</v>
+      <c r="C412" t="s">
+        <v>1403</v>
       </c>
       <c r="D412" t="s">
         <v>1399</v>
@@ -15125,8 +15124,8 @@
       <c r="B413" s="7" t="s">
         <v>1161</v>
       </c>
-      <c r="C413" s="10" t="s">
-        <v>1404</v>
+      <c r="C413" t="s">
+        <v>1403</v>
       </c>
       <c r="D413" t="s">
         <v>1399</v>
@@ -15142,8 +15141,8 @@
       <c r="B414" t="s">
         <v>1030</v>
       </c>
-      <c r="C414" s="10" t="s">
-        <v>1404</v>
+      <c r="C414" t="s">
+        <v>1403</v>
       </c>
       <c r="D414" t="s">
         <v>1399</v>
@@ -15156,8 +15155,8 @@
       <c r="B415" s="7" t="s">
         <v>1180</v>
       </c>
-      <c r="C415" s="10" t="s">
-        <v>1404</v>
+      <c r="C415" t="s">
+        <v>1403</v>
       </c>
       <c r="D415" t="s">
         <v>1399</v>
@@ -15173,8 +15172,8 @@
       <c r="B416" t="s">
         <v>1017</v>
       </c>
-      <c r="C416" s="10" t="s">
-        <v>1404</v>
+      <c r="C416" t="s">
+        <v>1403</v>
       </c>
       <c r="D416" t="s">
         <v>1399</v>
@@ -15187,8 +15186,8 @@
       <c r="B417" t="s">
         <v>1036</v>
       </c>
-      <c r="C417" s="10" t="s">
-        <v>1404</v>
+      <c r="C417" t="s">
+        <v>1403</v>
       </c>
       <c r="D417" t="s">
         <v>1399</v>
@@ -15201,8 +15200,8 @@
       <c r="B418" t="s">
         <v>1035</v>
       </c>
-      <c r="C418" s="10" t="s">
-        <v>1404</v>
+      <c r="C418" t="s">
+        <v>1403</v>
       </c>
       <c r="D418" t="s">
         <v>1399</v>
@@ -15215,8 +15214,8 @@
       <c r="B419" t="s">
         <v>1034</v>
       </c>
-      <c r="C419" s="10" t="s">
-        <v>1404</v>
+      <c r="C419" t="s">
+        <v>1403</v>
       </c>
       <c r="D419" t="s">
         <v>1399</v>
@@ -15229,8 +15228,8 @@
       <c r="B420" t="s">
         <v>1033</v>
       </c>
-      <c r="C420" s="10" t="s">
-        <v>1404</v>
+      <c r="C420" t="s">
+        <v>1403</v>
       </c>
       <c r="D420" t="s">
         <v>1399</v>
@@ -15243,8 +15242,8 @@
       <c r="B421" t="s">
         <v>1032</v>
       </c>
-      <c r="C421" s="10" t="s">
-        <v>1404</v>
+      <c r="C421" t="s">
+        <v>1403</v>
       </c>
       <c r="D421" t="s">
         <v>1399</v>
@@ -15257,8 +15256,8 @@
       <c r="B422" t="s">
         <v>1031</v>
       </c>
-      <c r="C422" s="10" t="s">
-        <v>1404</v>
+      <c r="C422" t="s">
+        <v>1403</v>
       </c>
       <c r="D422" t="s">
         <v>1399</v>
@@ -15271,8 +15270,8 @@
       <c r="B423" t="s">
         <v>797</v>
       </c>
-      <c r="C423" s="10" t="s">
-        <v>1404</v>
+      <c r="C423" t="s">
+        <v>1403</v>
       </c>
       <c r="D423" t="s">
         <v>1399</v>
@@ -15285,8 +15284,8 @@
       <c r="B424" t="s">
         <v>1037</v>
       </c>
-      <c r="C424" s="10" t="s">
-        <v>1404</v>
+      <c r="C424" t="s">
+        <v>1403</v>
       </c>
       <c r="D424" t="s">
         <v>1399</v>
@@ -15299,8 +15298,8 @@
       <c r="B425" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="C425" s="10" t="s">
-        <v>1404</v>
+      <c r="C425" t="s">
+        <v>1403</v>
       </c>
       <c r="D425" t="s">
         <v>1399</v>
@@ -15316,8 +15315,8 @@
       <c r="B426" s="7" t="s">
         <v>1132</v>
       </c>
-      <c r="C426" s="10" t="s">
-        <v>1404</v>
+      <c r="C426" t="s">
+        <v>1403</v>
       </c>
       <c r="D426" t="s">
         <v>1399</v>
@@ -15333,8 +15332,8 @@
       <c r="B427" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="C427" s="10" t="s">
-        <v>1404</v>
+      <c r="C427" t="s">
+        <v>1403</v>
       </c>
       <c r="D427" t="s">
         <v>1399</v>
@@ -15350,8 +15349,8 @@
       <c r="B428" s="5" t="s">
         <v>1181</v>
       </c>
-      <c r="C428" s="10" t="s">
-        <v>1404</v>
+      <c r="C428" t="s">
+        <v>1403</v>
       </c>
       <c r="D428" t="s">
         <v>1399</v>
@@ -15367,8 +15366,8 @@
       <c r="B429" t="s">
         <v>1107</v>
       </c>
-      <c r="C429" s="10" t="s">
-        <v>1404</v>
+      <c r="C429" t="s">
+        <v>1403</v>
       </c>
       <c r="D429" t="s">
         <v>1399</v>
@@ -15381,8 +15380,8 @@
       <c r="B430" t="s">
         <v>1018</v>
       </c>
-      <c r="C430" s="10" t="s">
-        <v>1404</v>
+      <c r="C430" t="s">
+        <v>1403</v>
       </c>
       <c r="D430" t="s">
         <v>1399</v>
@@ -15395,8 +15394,8 @@
       <c r="B431" t="s">
         <v>1019</v>
       </c>
-      <c r="C431" s="10" t="s">
-        <v>1404</v>
+      <c r="C431" t="s">
+        <v>1403</v>
       </c>
       <c r="D431" t="s">
         <v>1399</v>
@@ -15409,8 +15408,8 @@
       <c r="B432" t="s">
         <v>1022</v>
       </c>
-      <c r="C432" s="10" t="s">
-        <v>1404</v>
+      <c r="C432" t="s">
+        <v>1403</v>
       </c>
       <c r="D432" t="s">
         <v>1399</v>
@@ -15423,8 +15422,8 @@
       <c r="B433" t="s">
         <v>1024</v>
       </c>
-      <c r="C433" s="10" t="s">
-        <v>1404</v>
+      <c r="C433" t="s">
+        <v>1403</v>
       </c>
       <c r="D433" t="s">
         <v>1399</v>
@@ -15437,8 +15436,8 @@
       <c r="B434" t="s">
         <v>1025</v>
       </c>
-      <c r="C434" s="10" t="s">
-        <v>1404</v>
+      <c r="C434" t="s">
+        <v>1403</v>
       </c>
       <c r="D434" t="s">
         <v>1399</v>
@@ -15451,8 +15450,8 @@
       <c r="B435" t="s">
         <v>1026</v>
       </c>
-      <c r="C435" s="10" t="s">
-        <v>1404</v>
+      <c r="C435" t="s">
+        <v>1403</v>
       </c>
       <c r="D435" t="s">
         <v>1399</v>
@@ -15465,8 +15464,8 @@
       <c r="B436" t="s">
         <v>1038</v>
       </c>
-      <c r="C436" s="10" t="s">
-        <v>1404</v>
+      <c r="C436" t="s">
+        <v>1403</v>
       </c>
       <c r="D436" t="s">
         <v>1399</v>
@@ -15479,8 +15478,8 @@
       <c r="B437" s="7" t="s">
         <v>1138</v>
       </c>
-      <c r="C437" s="10" t="s">
-        <v>1404</v>
+      <c r="C437" t="s">
+        <v>1403</v>
       </c>
       <c r="D437" t="s">
         <v>1399</v>
@@ -15496,8 +15495,8 @@
       <c r="B438" t="s">
         <v>1081</v>
       </c>
-      <c r="C438" s="10" t="s">
-        <v>1404</v>
+      <c r="C438" t="s">
+        <v>1403</v>
       </c>
       <c r="D438" t="s">
         <v>1399</v>
@@ -15510,8 +15509,8 @@
       <c r="B440" t="s">
         <v>848</v>
       </c>
-      <c r="C440" s="10" t="s">
-        <v>1404</v>
+      <c r="C440" t="s">
+        <v>1403</v>
       </c>
       <c r="D440" t="s">
         <v>1399</v>
@@ -15524,8 +15523,8 @@
       <c r="B441" t="s">
         <v>849</v>
       </c>
-      <c r="C441" s="10" t="s">
-        <v>1404</v>
+      <c r="C441" t="s">
+        <v>1403</v>
       </c>
       <c r="D441" t="s">
         <v>1399</v>
@@ -15538,8 +15537,8 @@
       <c r="B442" t="s">
         <v>850</v>
       </c>
-      <c r="C442" s="10" t="s">
-        <v>1404</v>
+      <c r="C442" t="s">
+        <v>1403</v>
       </c>
       <c r="D442" t="s">
         <v>1399</v>
@@ -15552,8 +15551,8 @@
       <c r="B443" t="s">
         <v>851</v>
       </c>
-      <c r="C443" s="10" t="s">
-        <v>1404</v>
+      <c r="C443" t="s">
+        <v>1403</v>
       </c>
       <c r="D443" t="s">
         <v>1399</v>
@@ -15566,8 +15565,8 @@
       <c r="B444" t="s">
         <v>852</v>
       </c>
-      <c r="C444" s="10" t="s">
-        <v>1404</v>
+      <c r="C444" t="s">
+        <v>1403</v>
       </c>
       <c r="D444" t="s">
         <v>1399</v>
@@ -15580,8 +15579,8 @@
       <c r="B445" t="s">
         <v>853</v>
       </c>
-      <c r="C445" s="10" t="s">
-        <v>1404</v>
+      <c r="C445" t="s">
+        <v>1403</v>
       </c>
       <c r="D445" t="s">
         <v>1399</v>
@@ -15594,8 +15593,8 @@
       <c r="B446" t="s">
         <v>854</v>
       </c>
-      <c r="C446" s="10" t="s">
-        <v>1404</v>
+      <c r="C446" t="s">
+        <v>1403</v>
       </c>
       <c r="D446" t="s">
         <v>1399</v>
@@ -15608,8 +15607,8 @@
       <c r="B447" t="s">
         <v>855</v>
       </c>
-      <c r="C447" s="10" t="s">
-        <v>1404</v>
+      <c r="C447" t="s">
+        <v>1403</v>
       </c>
       <c r="D447" t="s">
         <v>1399</v>
@@ -15622,8 +15621,8 @@
       <c r="B448" t="s">
         <v>856</v>
       </c>
-      <c r="C448" s="10" t="s">
-        <v>1404</v>
+      <c r="C448" t="s">
+        <v>1403</v>
       </c>
       <c r="D448" t="s">
         <v>1399</v>
@@ -15636,8 +15635,8 @@
       <c r="B449" t="s">
         <v>857</v>
       </c>
-      <c r="C449" s="10" t="s">
-        <v>1404</v>
+      <c r="C449" t="s">
+        <v>1403</v>
       </c>
       <c r="D449" t="s">
         <v>1399</v>
@@ -15650,8 +15649,8 @@
       <c r="B450" t="s">
         <v>858</v>
       </c>
-      <c r="C450" s="10" t="s">
-        <v>1404</v>
+      <c r="C450" t="s">
+        <v>1403</v>
       </c>
       <c r="D450" t="s">
         <v>1399</v>
@@ -15664,8 +15663,8 @@
       <c r="B451" t="s">
         <v>859</v>
       </c>
-      <c r="C451" s="10" t="s">
-        <v>1404</v>
+      <c r="C451" t="s">
+        <v>1403</v>
       </c>
       <c r="D451" t="s">
         <v>1399</v>
@@ -15678,8 +15677,8 @@
       <c r="B452" t="s">
         <v>860</v>
       </c>
-      <c r="C452" s="10" t="s">
-        <v>1404</v>
+      <c r="C452" t="s">
+        <v>1403</v>
       </c>
       <c r="D452" t="s">
         <v>1399</v>
@@ -15692,8 +15691,8 @@
       <c r="B453" t="s">
         <v>861</v>
       </c>
-      <c r="C453" s="10" t="s">
-        <v>1404</v>
+      <c r="C453" t="s">
+        <v>1403</v>
       </c>
       <c r="D453" t="s">
         <v>1399</v>
@@ -15706,8 +15705,8 @@
       <c r="B454" t="s">
         <v>862</v>
       </c>
-      <c r="C454" s="10" t="s">
-        <v>1404</v>
+      <c r="C454" t="s">
+        <v>1403</v>
       </c>
       <c r="D454" t="s">
         <v>1399</v>
@@ -15720,8 +15719,8 @@
       <c r="B455" s="7" t="s">
         <v>1134</v>
       </c>
-      <c r="C455" s="10" t="s">
-        <v>1404</v>
+      <c r="C455" t="s">
+        <v>1403</v>
       </c>
       <c r="D455" t="s">
         <v>1399</v>
@@ -15737,8 +15736,8 @@
       <c r="B456" t="s">
         <v>863</v>
       </c>
-      <c r="C456" s="10" t="s">
-        <v>1404</v>
+      <c r="C456" t="s">
+        <v>1403</v>
       </c>
       <c r="D456" t="s">
         <v>1399</v>
@@ -15751,8 +15750,8 @@
       <c r="B457" t="s">
         <v>864</v>
       </c>
-      <c r="C457" s="10" t="s">
-        <v>1404</v>
+      <c r="C457" t="s">
+        <v>1403</v>
       </c>
       <c r="D457" t="s">
         <v>1399</v>
@@ -15765,8 +15764,8 @@
       <c r="B458" t="s">
         <v>865</v>
       </c>
-      <c r="C458" s="10" t="s">
-        <v>1404</v>
+      <c r="C458" t="s">
+        <v>1403</v>
       </c>
       <c r="D458" t="s">
         <v>1399</v>
@@ -15779,8 +15778,8 @@
       <c r="B459" t="s">
         <v>866</v>
       </c>
-      <c r="C459" s="10" t="s">
-        <v>1404</v>
+      <c r="C459" t="s">
+        <v>1403</v>
       </c>
       <c r="D459" t="s">
         <v>1399</v>
@@ -15793,8 +15792,8 @@
       <c r="B460" t="s">
         <v>1085</v>
       </c>
-      <c r="C460" s="10" t="s">
-        <v>1404</v>
+      <c r="C460" t="s">
+        <v>1403</v>
       </c>
       <c r="D460" t="s">
         <v>1399</v>
@@ -15807,8 +15806,8 @@
       <c r="B461" s="5" t="s">
         <v>1182</v>
       </c>
-      <c r="C461" s="10" t="s">
-        <v>1404</v>
+      <c r="C461" t="s">
+        <v>1403</v>
       </c>
       <c r="D461" t="s">
         <v>1399</v>
@@ -15824,8 +15823,8 @@
       <c r="B463" t="s">
         <v>1078</v>
       </c>
-      <c r="C463" s="10" t="s">
-        <v>1404</v>
+      <c r="C463" t="s">
+        <v>1403</v>
       </c>
       <c r="D463" t="s">
         <v>1399</v>
@@ -15838,8 +15837,8 @@
       <c r="B464" t="s">
         <v>890</v>
       </c>
-      <c r="C464" s="10" t="s">
-        <v>1404</v>
+      <c r="C464" t="s">
+        <v>1403</v>
       </c>
       <c r="D464" t="s">
         <v>1399</v>
@@ -15852,8 +15851,8 @@
       <c r="B465" t="s">
         <v>891</v>
       </c>
-      <c r="C465" s="10" t="s">
-        <v>1404</v>
+      <c r="C465" t="s">
+        <v>1403</v>
       </c>
       <c r="D465" t="s">
         <v>1399</v>
@@ -15866,8 +15865,8 @@
       <c r="B466" t="s">
         <v>892</v>
       </c>
-      <c r="C466" s="10" t="s">
-        <v>1404</v>
+      <c r="C466" t="s">
+        <v>1403</v>
       </c>
       <c r="D466" t="s">
         <v>1399</v>
@@ -15880,8 +15879,8 @@
       <c r="B467" t="s">
         <v>893</v>
       </c>
-      <c r="C467" s="10" t="s">
-        <v>1404</v>
+      <c r="C467" t="s">
+        <v>1403</v>
       </c>
       <c r="D467" t="s">
         <v>1399</v>
@@ -15894,8 +15893,8 @@
       <c r="B468" t="s">
         <v>894</v>
       </c>
-      <c r="C468" s="10" t="s">
-        <v>1404</v>
+      <c r="C468" t="s">
+        <v>1403</v>
       </c>
       <c r="D468" t="s">
         <v>1399</v>
@@ -15908,8 +15907,8 @@
       <c r="B469" t="s">
         <v>1103</v>
       </c>
-      <c r="C469" s="10" t="s">
-        <v>1404</v>
+      <c r="C469" t="s">
+        <v>1403</v>
       </c>
       <c r="D469" t="s">
         <v>1399</v>
@@ -15922,8 +15921,8 @@
       <c r="B470" t="s">
         <v>895</v>
       </c>
-      <c r="C470" s="10" t="s">
-        <v>1404</v>
+      <c r="C470" t="s">
+        <v>1403</v>
       </c>
       <c r="D470" t="s">
         <v>1399</v>
@@ -15936,8 +15935,8 @@
       <c r="B471" t="s">
         <v>1104</v>
       </c>
-      <c r="C471" s="10" t="s">
-        <v>1404</v>
+      <c r="C471" t="s">
+        <v>1403</v>
       </c>
       <c r="D471" t="s">
         <v>1399</v>
@@ -15950,8 +15949,8 @@
       <c r="B472" t="s">
         <v>1105</v>
       </c>
-      <c r="C472" s="10" t="s">
-        <v>1404</v>
+      <c r="C472" t="s">
+        <v>1403</v>
       </c>
       <c r="D472" t="s">
         <v>1399</v>
@@ -15964,8 +15963,8 @@
       <c r="B473" t="s">
         <v>1093</v>
       </c>
-      <c r="C473" s="10" t="s">
-        <v>1404</v>
+      <c r="C473" t="s">
+        <v>1403</v>
       </c>
       <c r="D473" t="s">
         <v>1399</v>
@@ -15978,8 +15977,8 @@
       <c r="B474" s="5" t="s">
         <v>1183</v>
       </c>
-      <c r="C474" s="10" t="s">
-        <v>1404</v>
+      <c r="C474" t="s">
+        <v>1403</v>
       </c>
       <c r="D474" t="s">
         <v>1399</v>
@@ -15995,8 +15994,8 @@
       <c r="B476" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="C476" s="10" t="s">
-        <v>1404</v>
+      <c r="C476" t="s">
+        <v>1403</v>
       </c>
       <c r="D476" t="s">
         <v>1399</v>
@@ -16012,8 +16011,8 @@
       <c r="B477" s="6" t="s">
         <v>1185</v>
       </c>
-      <c r="C477" s="10" t="s">
-        <v>1404</v>
+      <c r="C477" t="s">
+        <v>1403</v>
       </c>
       <c r="D477" t="s">
         <v>1399</v>
@@ -16029,8 +16028,8 @@
       <c r="B479" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="C479" s="10" t="s">
-        <v>1404</v>
+      <c r="C479" t="s">
+        <v>1403</v>
       </c>
       <c r="D479" t="s">
         <v>1399</v>
@@ -16046,8 +16045,8 @@
       <c r="B480" s="5" t="s">
         <v>1186</v>
       </c>
-      <c r="C480" s="10" t="s">
-        <v>1404</v>
+      <c r="C480" t="s">
+        <v>1403</v>
       </c>
       <c r="D480" t="s">
         <v>1399</v>
@@ -16063,8 +16062,8 @@
       <c r="B482" t="s">
         <v>915</v>
       </c>
-      <c r="C482" s="10" t="s">
-        <v>1404</v>
+      <c r="C482" t="s">
+        <v>1403</v>
       </c>
       <c r="D482" t="s">
         <v>1399</v>
@@ -16077,8 +16076,8 @@
       <c r="B483" t="s">
         <v>916</v>
       </c>
-      <c r="C483" s="10" t="s">
-        <v>1404</v>
+      <c r="C483" t="s">
+        <v>1403</v>
       </c>
       <c r="D483" t="s">
         <v>1399</v>
@@ -16091,8 +16090,8 @@
       <c r="B484" t="s">
         <v>1110</v>
       </c>
-      <c r="C484" s="10" t="s">
-        <v>1404</v>
+      <c r="C484" t="s">
+        <v>1403</v>
       </c>
       <c r="D484" t="s">
         <v>1399</v>
@@ -16105,8 +16104,8 @@
       <c r="B485" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="C485" s="10" t="s">
-        <v>1404</v>
+      <c r="C485" t="s">
+        <v>1403</v>
       </c>
       <c r="D485" t="s">
         <v>1399</v>
@@ -16122,8 +16121,8 @@
       <c r="B487" t="s">
         <v>1188</v>
       </c>
-      <c r="C487" s="10" t="s">
-        <v>1404</v>
+      <c r="C487" t="s">
+        <v>1403</v>
       </c>
       <c r="D487" t="s">
         <v>1399</v>
@@ -16136,8 +16135,8 @@
       <c r="B488" t="s">
         <v>922</v>
       </c>
-      <c r="C488" s="10" t="s">
-        <v>1404</v>
+      <c r="C488" t="s">
+        <v>1403</v>
       </c>
       <c r="D488" t="s">
         <v>1399</v>
@@ -16150,8 +16149,8 @@
       <c r="B489" t="s">
         <v>923</v>
       </c>
-      <c r="C489" s="10" t="s">
-        <v>1404</v>
+      <c r="C489" t="s">
+        <v>1403</v>
       </c>
       <c r="D489" t="s">
         <v>1399</v>
@@ -16164,8 +16163,8 @@
       <c r="B490" t="s">
         <v>924</v>
       </c>
-      <c r="C490" s="10" t="s">
-        <v>1404</v>
+      <c r="C490" t="s">
+        <v>1403</v>
       </c>
       <c r="D490" t="s">
         <v>1399</v>
@@ -16178,8 +16177,8 @@
       <c r="B491" t="s">
         <v>925</v>
       </c>
-      <c r="C491" s="10" t="s">
-        <v>1404</v>
+      <c r="C491" t="s">
+        <v>1403</v>
       </c>
       <c r="D491" t="s">
         <v>1399</v>
@@ -16192,8 +16191,8 @@
       <c r="B492" t="s">
         <v>926</v>
       </c>
-      <c r="C492" s="10" t="s">
-        <v>1404</v>
+      <c r="C492" t="s">
+        <v>1403</v>
       </c>
       <c r="D492" t="s">
         <v>1399</v>
@@ -16206,8 +16205,8 @@
       <c r="B493" s="7" t="s">
         <v>1189</v>
       </c>
-      <c r="C493" s="10" t="s">
-        <v>1404</v>
+      <c r="C493" t="s">
+        <v>1403</v>
       </c>
       <c r="D493" t="s">
         <v>1399</v>
@@ -16223,8 +16222,8 @@
       <c r="B495" t="s">
         <v>938</v>
       </c>
-      <c r="C495" s="10" t="s">
-        <v>1404</v>
+      <c r="C495" t="s">
+        <v>1403</v>
       </c>
       <c r="D495" t="s">
         <v>1399</v>
@@ -16237,8 +16236,8 @@
       <c r="B496" t="s">
         <v>939</v>
       </c>
-      <c r="C496" s="10" t="s">
-        <v>1404</v>
+      <c r="C496" t="s">
+        <v>1403</v>
       </c>
       <c r="D496" t="s">
         <v>1399</v>
@@ -16251,8 +16250,8 @@
       <c r="B497" t="s">
         <v>940</v>
       </c>
-      <c r="C497" s="10" t="s">
-        <v>1404</v>
+      <c r="C497" t="s">
+        <v>1403</v>
       </c>
       <c r="D497" t="s">
         <v>1399</v>
@@ -16265,8 +16264,8 @@
       <c r="B498" t="s">
         <v>941</v>
       </c>
-      <c r="C498" s="10" t="s">
-        <v>1404</v>
+      <c r="C498" t="s">
+        <v>1403</v>
       </c>
       <c r="D498" t="s">
         <v>1399</v>
@@ -16279,8 +16278,8 @@
       <c r="B499" t="s">
         <v>942</v>
       </c>
-      <c r="C499" s="10" t="s">
-        <v>1404</v>
+      <c r="C499" t="s">
+        <v>1403</v>
       </c>
       <c r="D499" t="s">
         <v>1399</v>
@@ -16293,8 +16292,8 @@
       <c r="B500" s="7" t="s">
         <v>1139</v>
       </c>
-      <c r="C500" s="10" t="s">
-        <v>1404</v>
+      <c r="C500" t="s">
+        <v>1403</v>
       </c>
       <c r="D500" t="s">
         <v>1399</v>
@@ -16310,8 +16309,8 @@
       <c r="B502" t="s">
         <v>949</v>
       </c>
-      <c r="C502" s="10" t="s">
-        <v>1404</v>
+      <c r="C502" t="s">
+        <v>1403</v>
       </c>
       <c r="D502" t="s">
         <v>1399</v>
@@ -16324,8 +16323,8 @@
       <c r="B503" t="s">
         <v>950</v>
       </c>
-      <c r="C503" s="10" t="s">
-        <v>1404</v>
+      <c r="C503" t="s">
+        <v>1403</v>
       </c>
       <c r="D503" t="s">
         <v>1399</v>
@@ -16338,8 +16337,8 @@
       <c r="B504" t="s">
         <v>951</v>
       </c>
-      <c r="C504" s="10" t="s">
-        <v>1404</v>
+      <c r="C504" t="s">
+        <v>1403</v>
       </c>
       <c r="D504" t="s">
         <v>1399</v>
@@ -16352,8 +16351,8 @@
       <c r="B505" t="s">
         <v>952</v>
       </c>
-      <c r="C505" s="10" t="s">
-        <v>1404</v>
+      <c r="C505" t="s">
+        <v>1403</v>
       </c>
       <c r="D505" t="s">
         <v>1399</v>
@@ -16366,8 +16365,8 @@
       <c r="B506" t="s">
         <v>953</v>
       </c>
-      <c r="C506" s="10" t="s">
-        <v>1404</v>
+      <c r="C506" t="s">
+        <v>1403</v>
       </c>
       <c r="D506" t="s">
         <v>1399</v>
@@ -16380,8 +16379,8 @@
       <c r="B507" s="6" t="s">
         <v>1079</v>
       </c>
-      <c r="C507" s="10" t="s">
-        <v>1404</v>
+      <c r="C507" t="s">
+        <v>1403</v>
       </c>
       <c r="D507" t="s">
         <v>1399</v>
@@ -16397,8 +16396,8 @@
       <c r="B509" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="C509" s="10" t="s">
-        <v>1404</v>
+      <c r="C509" t="s">
+        <v>1403</v>
       </c>
       <c r="D509" t="s">
         <v>1399</v>
@@ -16414,8 +16413,8 @@
       <c r="B510" t="s">
         <v>963</v>
       </c>
-      <c r="C510" s="10" t="s">
-        <v>1404</v>
+      <c r="C510" t="s">
+        <v>1403</v>
       </c>
       <c r="D510" t="s">
         <v>1399</v>
@@ -16428,8 +16427,8 @@
       <c r="B511" t="s">
         <v>964</v>
       </c>
-      <c r="C511" s="10" t="s">
-        <v>1404</v>
+      <c r="C511" t="s">
+        <v>1403</v>
       </c>
       <c r="D511" t="s">
         <v>1399</v>
@@ -16442,8 +16441,8 @@
       <c r="B512" t="s">
         <v>965</v>
       </c>
-      <c r="C512" s="10" t="s">
-        <v>1404</v>
+      <c r="C512" t="s">
+        <v>1403</v>
       </c>
       <c r="D512" t="s">
         <v>1399</v>
@@ -16456,8 +16455,8 @@
       <c r="B513" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="C513" s="10" t="s">
-        <v>1404</v>
+      <c r="C513" t="s">
+        <v>1403</v>
       </c>
       <c r="D513" t="s">
         <v>1399</v>
@@ -16473,8 +16472,8 @@
       <c r="B515" t="s">
         <v>991</v>
       </c>
-      <c r="C515" s="10" t="s">
-        <v>1404</v>
+      <c r="C515" t="s">
+        <v>1403</v>
       </c>
       <c r="D515" t="s">
         <v>1399</v>
@@ -16487,8 +16486,8 @@
       <c r="B516" t="s">
         <v>992</v>
       </c>
-      <c r="C516" s="10" t="s">
-        <v>1404</v>
+      <c r="C516" t="s">
+        <v>1403</v>
       </c>
       <c r="D516" t="s">
         <v>1399</v>
@@ -16501,8 +16500,8 @@
       <c r="B517" t="s">
         <v>993</v>
       </c>
-      <c r="C517" s="10" t="s">
-        <v>1404</v>
+      <c r="C517" t="s">
+        <v>1403</v>
       </c>
       <c r="D517" t="s">
         <v>1399</v>
@@ -16515,8 +16514,8 @@
       <c r="B518" t="s">
         <v>994</v>
       </c>
-      <c r="C518" s="10" t="s">
-        <v>1404</v>
+      <c r="C518" t="s">
+        <v>1403</v>
       </c>
       <c r="D518" t="s">
         <v>1399</v>
@@ -16529,8 +16528,8 @@
       <c r="B519" t="s">
         <v>995</v>
       </c>
-      <c r="C519" s="10" t="s">
-        <v>1404</v>
+      <c r="C519" t="s">
+        <v>1403</v>
       </c>
       <c r="D519" t="s">
         <v>1399</v>
@@ -16543,8 +16542,8 @@
       <c r="B520" t="s">
         <v>996</v>
       </c>
-      <c r="C520" s="10" t="s">
-        <v>1404</v>
+      <c r="C520" t="s">
+        <v>1403</v>
       </c>
       <c r="D520" t="s">
         <v>1399</v>
@@ -16557,8 +16556,8 @@
       <c r="B521" t="s">
         <v>997</v>
       </c>
-      <c r="C521" s="10" t="s">
-        <v>1404</v>
+      <c r="C521" t="s">
+        <v>1403</v>
       </c>
       <c r="D521" t="s">
         <v>1399</v>
@@ -16571,8 +16570,8 @@
       <c r="B522" t="s">
         <v>998</v>
       </c>
-      <c r="C522" s="10" t="s">
-        <v>1404</v>
+      <c r="C522" t="s">
+        <v>1403</v>
       </c>
       <c r="D522" t="s">
         <v>1399</v>
@@ -16585,8 +16584,8 @@
       <c r="B523" t="s">
         <v>999</v>
       </c>
-      <c r="C523" s="10" t="s">
-        <v>1404</v>
+      <c r="C523" t="s">
+        <v>1403</v>
       </c>
       <c r="D523" t="s">
         <v>1399</v>
@@ -16599,8 +16598,8 @@
       <c r="B524" t="s">
         <v>1000</v>
       </c>
-      <c r="C524" s="10" t="s">
-        <v>1404</v>
+      <c r="C524" t="s">
+        <v>1403</v>
       </c>
       <c r="D524" t="s">
         <v>1399</v>
@@ -16613,8 +16612,8 @@
       <c r="B525" t="s">
         <v>1001</v>
       </c>
-      <c r="C525" s="10" t="s">
-        <v>1404</v>
+      <c r="C525" t="s">
+        <v>1403</v>
       </c>
       <c r="D525" t="s">
         <v>1399</v>
@@ -16627,8 +16626,8 @@
       <c r="B526" t="s">
         <v>1002</v>
       </c>
-      <c r="C526" s="10" t="s">
-        <v>1404</v>
+      <c r="C526" t="s">
+        <v>1403</v>
       </c>
       <c r="D526" t="s">
         <v>1399</v>
@@ -16641,8 +16640,8 @@
       <c r="B527" t="s">
         <v>1003</v>
       </c>
-      <c r="C527" s="10" t="s">
-        <v>1404</v>
+      <c r="C527" t="s">
+        <v>1403</v>
       </c>
       <c r="D527" t="s">
         <v>1399</v>
@@ -16655,8 +16654,8 @@
       <c r="B528" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C528" s="10" t="s">
-        <v>1404</v>
+      <c r="C528" t="s">
+        <v>1403</v>
       </c>
       <c r="D528" t="s">
         <v>1399</v>
@@ -16672,8 +16671,8 @@
       <c r="B530" t="s">
         <v>1209</v>
       </c>
-      <c r="C530" s="10" t="s">
-        <v>1404</v>
+      <c r="C530" t="s">
+        <v>1403</v>
       </c>
       <c r="D530" t="s">
         <v>1399</v>
@@ -16686,8 +16685,8 @@
       <c r="B531" t="s">
         <v>1210</v>
       </c>
-      <c r="C531" s="10" t="s">
-        <v>1404</v>
+      <c r="C531" t="s">
+        <v>1403</v>
       </c>
       <c r="D531" t="s">
         <v>1399</v>
@@ -16700,8 +16699,8 @@
       <c r="B532" t="s">
         <v>1211</v>
       </c>
-      <c r="C532" s="10" t="s">
-        <v>1404</v>
+      <c r="C532" t="s">
+        <v>1403</v>
       </c>
       <c r="D532" t="s">
         <v>1399</v>
@@ -16714,8 +16713,8 @@
       <c r="B533" t="s">
         <v>1212</v>
       </c>
-      <c r="C533" s="10" t="s">
-        <v>1404</v>
+      <c r="C533" t="s">
+        <v>1403</v>
       </c>
       <c r="D533" t="s">
         <v>1399</v>
@@ -16728,8 +16727,8 @@
       <c r="B534" t="s">
         <v>1213</v>
       </c>
-      <c r="C534" s="10" t="s">
-        <v>1404</v>
+      <c r="C534" t="s">
+        <v>1403</v>
       </c>
       <c r="D534" t="s">
         <v>1399</v>
@@ -16742,8 +16741,8 @@
       <c r="B535" t="s">
         <v>1214</v>
       </c>
-      <c r="C535" s="10" t="s">
-        <v>1404</v>
+      <c r="C535" t="s">
+        <v>1403</v>
       </c>
       <c r="D535" t="s">
         <v>1399</v>
@@ -16756,8 +16755,8 @@
       <c r="B536" t="s">
         <v>1215</v>
       </c>
-      <c r="C536" s="10" t="s">
-        <v>1404</v>
+      <c r="C536" t="s">
+        <v>1403</v>
       </c>
       <c r="D536" t="s">
         <v>1399</v>
@@ -16770,8 +16769,8 @@
       <c r="B537" t="s">
         <v>1216</v>
       </c>
-      <c r="C537" s="10" t="s">
-        <v>1405</v>
+      <c r="C537" t="s">
+        <v>1404</v>
       </c>
       <c r="D537" t="s">
         <v>1400</v>
@@ -16784,8 +16783,8 @@
       <c r="B538" t="s">
         <v>1217</v>
       </c>
-      <c r="C538" s="10" t="s">
-        <v>1404</v>
+      <c r="C538" t="s">
+        <v>1403</v>
       </c>
       <c r="D538" t="s">
         <v>1399</v>
@@ -16798,8 +16797,8 @@
       <c r="B539" t="s">
         <v>1218</v>
       </c>
-      <c r="C539" s="10" t="s">
-        <v>1404</v>
+      <c r="C539" t="s">
+        <v>1403</v>
       </c>
       <c r="D539" t="s">
         <v>1399</v>
@@ -16812,8 +16811,8 @@
       <c r="B540" t="s">
         <v>1219</v>
       </c>
-      <c r="C540" s="10" t="s">
-        <v>1404</v>
+      <c r="C540" t="s">
+        <v>1403</v>
       </c>
       <c r="D540" t="s">
         <v>1399</v>
@@ -16826,8 +16825,8 @@
       <c r="B541" t="s">
         <v>1220</v>
       </c>
-      <c r="C541" s="10" t="s">
-        <v>1404</v>
+      <c r="C541" t="s">
+        <v>1403</v>
       </c>
       <c r="D541" t="s">
         <v>1399</v>
@@ -16840,8 +16839,8 @@
       <c r="B542" t="s">
         <v>1221</v>
       </c>
-      <c r="C542" s="10" t="s">
-        <v>1404</v>
+      <c r="C542" t="s">
+        <v>1403</v>
       </c>
       <c r="D542" t="s">
         <v>1399</v>
@@ -16854,8 +16853,8 @@
       <c r="B543" t="s">
         <v>1222</v>
       </c>
-      <c r="C543" s="10" t="s">
-        <v>1404</v>
+      <c r="C543" t="s">
+        <v>1403</v>
       </c>
       <c r="D543" t="s">
         <v>1399</v>
@@ -16868,8 +16867,8 @@
       <c r="B544" t="s">
         <v>1223</v>
       </c>
-      <c r="C544" s="10" t="s">
-        <v>1404</v>
+      <c r="C544" t="s">
+        <v>1403</v>
       </c>
       <c r="D544" t="s">
         <v>1399</v>
@@ -16882,8 +16881,8 @@
       <c r="B545" t="s">
         <v>1224</v>
       </c>
-      <c r="C545" s="10" t="s">
-        <v>1404</v>
+      <c r="C545" t="s">
+        <v>1403</v>
       </c>
       <c r="D545" t="s">
         <v>1399</v>
@@ -16896,8 +16895,8 @@
       <c r="B546" t="s">
         <v>1225</v>
       </c>
-      <c r="C546" s="10" t="s">
-        <v>1404</v>
+      <c r="C546" t="s">
+        <v>1403</v>
       </c>
       <c r="D546" t="s">
         <v>1399</v>
@@ -16910,8 +16909,8 @@
       <c r="B547" t="s">
         <v>1226</v>
       </c>
-      <c r="C547" s="10" t="s">
-        <v>1404</v>
+      <c r="C547" t="s">
+        <v>1403</v>
       </c>
       <c r="D547" t="s">
         <v>1399</v>
@@ -16924,8 +16923,8 @@
       <c r="B548" t="s">
         <v>1227</v>
       </c>
-      <c r="C548" s="10" t="s">
-        <v>1404</v>
+      <c r="C548" t="s">
+        <v>1403</v>
       </c>
       <c r="D548" t="s">
         <v>1399</v>
@@ -16938,8 +16937,8 @@
       <c r="B549" t="s">
         <v>1228</v>
       </c>
-      <c r="C549" s="10" t="s">
-        <v>1404</v>
+      <c r="C549" t="s">
+        <v>1403</v>
       </c>
       <c r="D549" t="s">
         <v>1399</v>
@@ -16952,8 +16951,8 @@
       <c r="B550" t="s">
         <v>1229</v>
       </c>
-      <c r="C550" s="10" t="s">
-        <v>1404</v>
+      <c r="C550" t="s">
+        <v>1403</v>
       </c>
       <c r="D550" t="s">
         <v>1399</v>
@@ -16966,8 +16965,8 @@
       <c r="B551" t="s">
         <v>1230</v>
       </c>
-      <c r="C551" s="10" t="s">
-        <v>1404</v>
+      <c r="C551" t="s">
+        <v>1403</v>
       </c>
       <c r="D551" t="s">
         <v>1399</v>
@@ -16980,8 +16979,8 @@
       <c r="B552" t="s">
         <v>1231</v>
       </c>
-      <c r="C552" s="10" t="s">
-        <v>1404</v>
+      <c r="C552" t="s">
+        <v>1403</v>
       </c>
       <c r="D552" t="s">
         <v>1399</v>
@@ -16994,8 +16993,8 @@
       <c r="B553" t="s">
         <v>1232</v>
       </c>
-      <c r="C553" s="10" t="s">
-        <v>1404</v>
+      <c r="C553" t="s">
+        <v>1403</v>
       </c>
       <c r="D553" t="s">
         <v>1399</v>
@@ -17008,8 +17007,8 @@
       <c r="B554" t="s">
         <v>1233</v>
       </c>
-      <c r="C554" s="10" t="s">
-        <v>1404</v>
+      <c r="C554" t="s">
+        <v>1403</v>
       </c>
       <c r="D554" t="s">
         <v>1399</v>
@@ -17022,8 +17021,8 @@
       <c r="B555" t="s">
         <v>1234</v>
       </c>
-      <c r="C555" s="10" t="s">
-        <v>1404</v>
+      <c r="C555" t="s">
+        <v>1403</v>
       </c>
       <c r="D555" t="s">
         <v>1399</v>
@@ -17036,8 +17035,8 @@
       <c r="B556" t="s">
         <v>1235</v>
       </c>
-      <c r="C556" s="10" t="s">
-        <v>1404</v>
+      <c r="C556" t="s">
+        <v>1403</v>
       </c>
       <c r="D556" t="s">
         <v>1399</v>
@@ -17050,8 +17049,8 @@
       <c r="B557" t="s">
         <v>1236</v>
       </c>
-      <c r="C557" s="10" t="s">
-        <v>1404</v>
+      <c r="C557" t="s">
+        <v>1403</v>
       </c>
       <c r="D557" t="s">
         <v>1399</v>
@@ -17064,8 +17063,8 @@
       <c r="B558" t="s">
         <v>1237</v>
       </c>
-      <c r="C558" s="10" t="s">
-        <v>1404</v>
+      <c r="C558" t="s">
+        <v>1403</v>
       </c>
       <c r="D558" t="s">
         <v>1399</v>
@@ -17078,8 +17077,8 @@
       <c r="B559" t="s">
         <v>1238</v>
       </c>
-      <c r="C559" s="10" t="s">
-        <v>1404</v>
+      <c r="C559" t="s">
+        <v>1403</v>
       </c>
       <c r="D559" t="s">
         <v>1399</v>
@@ -17092,8 +17091,8 @@
       <c r="B560" t="s">
         <v>1239</v>
       </c>
-      <c r="C560" s="10" t="s">
-        <v>1404</v>
+      <c r="C560" t="s">
+        <v>1403</v>
       </c>
       <c r="D560" t="s">
         <v>1399</v>
@@ -17106,8 +17105,8 @@
       <c r="B561" t="s">
         <v>1240</v>
       </c>
-      <c r="C561" s="10" t="s">
-        <v>1404</v>
+      <c r="C561" t="s">
+        <v>1403</v>
       </c>
       <c r="D561" t="s">
         <v>1399</v>
@@ -17120,8 +17119,8 @@
       <c r="B562" t="s">
         <v>1241</v>
       </c>
-      <c r="C562" s="10" t="s">
-        <v>1404</v>
+      <c r="C562" t="s">
+        <v>1403</v>
       </c>
       <c r="D562" t="s">
         <v>1399</v>
@@ -17134,8 +17133,8 @@
       <c r="B563" t="s">
         <v>1242</v>
       </c>
-      <c r="C563" s="10" t="s">
-        <v>1404</v>
+      <c r="C563" t="s">
+        <v>1403</v>
       </c>
       <c r="D563" t="s">
         <v>1399</v>
@@ -17148,8 +17147,8 @@
       <c r="B564" t="s">
         <v>1243</v>
       </c>
-      <c r="C564" s="10" t="s">
-        <v>1404</v>
+      <c r="C564" t="s">
+        <v>1403</v>
       </c>
       <c r="D564" t="s">
         <v>1399</v>
@@ -17162,8 +17161,8 @@
       <c r="B565" t="s">
         <v>1244</v>
       </c>
-      <c r="C565" s="10" t="s">
-        <v>1404</v>
+      <c r="C565" t="s">
+        <v>1403</v>
       </c>
       <c r="D565" t="s">
         <v>1399</v>
@@ -17176,8 +17175,8 @@
       <c r="B566" t="s">
         <v>1245</v>
       </c>
-      <c r="C566" s="10" t="s">
-        <v>1404</v>
+      <c r="C566" t="s">
+        <v>1403</v>
       </c>
       <c r="D566" t="s">
         <v>1399</v>
@@ -17190,8 +17189,8 @@
       <c r="B567" t="s">
         <v>1246</v>
       </c>
-      <c r="C567" s="10" t="s">
-        <v>1404</v>
+      <c r="C567" t="s">
+        <v>1403</v>
       </c>
       <c r="D567" t="s">
         <v>1399</v>
@@ -17204,8 +17203,8 @@
       <c r="B568" t="s">
         <v>1247</v>
       </c>
-      <c r="C568" s="10" t="s">
-        <v>1404</v>
+      <c r="C568" t="s">
+        <v>1403</v>
       </c>
       <c r="D568" t="s">
         <v>1399</v>
@@ -17218,8 +17217,8 @@
       <c r="B569" t="s">
         <v>1248</v>
       </c>
-      <c r="C569" s="10" t="s">
-        <v>1404</v>
+      <c r="C569" t="s">
+        <v>1403</v>
       </c>
       <c r="D569" t="s">
         <v>1399</v>
@@ -17232,8 +17231,8 @@
       <c r="B570" t="s">
         <v>1249</v>
       </c>
-      <c r="C570" s="10" t="s">
-        <v>1404</v>
+      <c r="C570" t="s">
+        <v>1403</v>
       </c>
       <c r="D570" t="s">
         <v>1399</v>
@@ -17246,8 +17245,8 @@
       <c r="B571" t="s">
         <v>1250</v>
       </c>
-      <c r="C571" s="10" t="s">
-        <v>1404</v>
+      <c r="C571" t="s">
+        <v>1403</v>
       </c>
       <c r="D571" t="s">
         <v>1399</v>
@@ -17260,8 +17259,8 @@
       <c r="B572" t="s">
         <v>1251</v>
       </c>
-      <c r="C572" s="10" t="s">
-        <v>1404</v>
+      <c r="C572" t="s">
+        <v>1403</v>
       </c>
       <c r="D572" t="s">
         <v>1399</v>
@@ -17274,8 +17273,8 @@
       <c r="B573" t="s">
         <v>1252</v>
       </c>
-      <c r="C573" s="10" t="s">
-        <v>1404</v>
+      <c r="C573" t="s">
+        <v>1403</v>
       </c>
       <c r="D573" t="s">
         <v>1399</v>
@@ -17288,8 +17287,8 @@
       <c r="B574" t="s">
         <v>1253</v>
       </c>
-      <c r="C574" s="10" t="s">
-        <v>1404</v>
+      <c r="C574" t="s">
+        <v>1403</v>
       </c>
       <c r="D574" t="s">
         <v>1399</v>
@@ -17302,8 +17301,8 @@
       <c r="B575" t="s">
         <v>1254</v>
       </c>
-      <c r="C575" s="10" t="s">
-        <v>1404</v>
+      <c r="C575" t="s">
+        <v>1403</v>
       </c>
       <c r="D575" t="s">
         <v>1399</v>
@@ -17316,8 +17315,8 @@
       <c r="B576" t="s">
         <v>1255</v>
       </c>
-      <c r="C576" s="10" t="s">
-        <v>1404</v>
+      <c r="C576" t="s">
+        <v>1403</v>
       </c>
       <c r="D576" t="s">
         <v>1399</v>
@@ -17330,8 +17329,8 @@
       <c r="B577" t="s">
         <v>1256</v>
       </c>
-      <c r="C577" s="10" t="s">
-        <v>1404</v>
+      <c r="C577" t="s">
+        <v>1403</v>
       </c>
       <c r="D577" t="s">
         <v>1399</v>
@@ -17344,8 +17343,8 @@
       <c r="B578" t="s">
         <v>1257</v>
       </c>
-      <c r="C578" s="10" t="s">
-        <v>1404</v>
+      <c r="C578" t="s">
+        <v>1403</v>
       </c>
       <c r="D578" t="s">
         <v>1399</v>
@@ -17358,8 +17357,8 @@
       <c r="B579" t="s">
         <v>1258</v>
       </c>
-      <c r="C579" s="10" t="s">
-        <v>1404</v>
+      <c r="C579" t="s">
+        <v>1403</v>
       </c>
       <c r="D579" t="s">
         <v>1399</v>
@@ -17372,8 +17371,8 @@
       <c r="B580" t="s">
         <v>1259</v>
       </c>
-      <c r="C580" s="10" t="s">
-        <v>1404</v>
+      <c r="C580" t="s">
+        <v>1403</v>
       </c>
       <c r="D580" t="s">
         <v>1399</v>
@@ -17386,8 +17385,8 @@
       <c r="B581" t="s">
         <v>1260</v>
       </c>
-      <c r="C581" s="10" t="s">
-        <v>1404</v>
+      <c r="C581" t="s">
+        <v>1403</v>
       </c>
       <c r="D581" t="s">
         <v>1399</v>
@@ -17400,8 +17399,8 @@
       <c r="B582" t="s">
         <v>1261</v>
       </c>
-      <c r="C582" s="10" t="s">
-        <v>1404</v>
+      <c r="C582" t="s">
+        <v>1403</v>
       </c>
       <c r="D582" t="s">
         <v>1399</v>
@@ -17414,8 +17413,8 @@
       <c r="B583" t="s">
         <v>1262</v>
       </c>
-      <c r="C583" s="10" t="s">
-        <v>1404</v>
+      <c r="C583" t="s">
+        <v>1403</v>
       </c>
       <c r="D583" t="s">
         <v>1399</v>
@@ -17428,8 +17427,8 @@
       <c r="B584" t="s">
         <v>1263</v>
       </c>
-      <c r="C584" s="10" t="s">
-        <v>1404</v>
+      <c r="C584" t="s">
+        <v>1403</v>
       </c>
       <c r="D584" t="s">
         <v>1399</v>
@@ -17442,8 +17441,8 @@
       <c r="B585" t="s">
         <v>1264</v>
       </c>
-      <c r="C585" s="10" t="s">
-        <v>1404</v>
+      <c r="C585" t="s">
+        <v>1403</v>
       </c>
       <c r="D585" t="s">
         <v>1399</v>
@@ -17456,8 +17455,8 @@
       <c r="B586" t="s">
         <v>1265</v>
       </c>
-      <c r="C586" s="10" t="s">
-        <v>1404</v>
+      <c r="C586" t="s">
+        <v>1403</v>
       </c>
       <c r="D586" t="s">
         <v>1399</v>
@@ -17470,8 +17469,8 @@
       <c r="B587" t="s">
         <v>1266</v>
       </c>
-      <c r="C587" s="10" t="s">
-        <v>1404</v>
+      <c r="C587" t="s">
+        <v>1403</v>
       </c>
       <c r="D587" t="s">
         <v>1399</v>
@@ -17484,8 +17483,8 @@
       <c r="B588" t="s">
         <v>1267</v>
       </c>
-      <c r="C588" s="10" t="s">
-        <v>1404</v>
+      <c r="C588" t="s">
+        <v>1403</v>
       </c>
       <c r="D588" t="s">
         <v>1399</v>
@@ -17498,8 +17497,8 @@
       <c r="B589" t="s">
         <v>1268</v>
       </c>
-      <c r="C589" s="10" t="s">
-        <v>1404</v>
+      <c r="C589" t="s">
+        <v>1403</v>
       </c>
       <c r="D589" t="s">
         <v>1399</v>
@@ -17512,8 +17511,8 @@
       <c r="B590" t="s">
         <v>1269</v>
       </c>
-      <c r="C590" s="10" t="s">
-        <v>1404</v>
+      <c r="C590" t="s">
+        <v>1403</v>
       </c>
       <c r="D590" t="s">
         <v>1399</v>
@@ -17526,8 +17525,8 @@
       <c r="B591" t="s">
         <v>1270</v>
       </c>
-      <c r="C591" s="10" t="s">
-        <v>1404</v>
+      <c r="C591" t="s">
+        <v>1403</v>
       </c>
       <c r="D591" t="s">
         <v>1399</v>
@@ -17540,8 +17539,8 @@
       <c r="B592" t="s">
         <v>1271</v>
       </c>
-      <c r="C592" s="10" t="s">
-        <v>1404</v>
+      <c r="C592" t="s">
+        <v>1403</v>
       </c>
       <c r="D592" t="s">
         <v>1399</v>
@@ -17554,8 +17553,8 @@
       <c r="B593" t="s">
         <v>1272</v>
       </c>
-      <c r="C593" s="10" t="s">
-        <v>1404</v>
+      <c r="C593" t="s">
+        <v>1403</v>
       </c>
       <c r="D593" t="s">
         <v>1399</v>
@@ -17568,8 +17567,8 @@
       <c r="B594" t="s">
         <v>1273</v>
       </c>
-      <c r="C594" s="10" t="s">
-        <v>1404</v>
+      <c r="C594" t="s">
+        <v>1403</v>
       </c>
       <c r="D594" t="s">
         <v>1399</v>
@@ -17582,8 +17581,8 @@
       <c r="B595" t="s">
         <v>1274</v>
       </c>
-      <c r="C595" s="10" t="s">
-        <v>1404</v>
+      <c r="C595" t="s">
+        <v>1403</v>
       </c>
       <c r="D595" t="s">
         <v>1399</v>
@@ -17596,8 +17595,8 @@
       <c r="B596" t="s">
         <v>1275</v>
       </c>
-      <c r="C596" s="10" t="s">
-        <v>1404</v>
+      <c r="C596" t="s">
+        <v>1403</v>
       </c>
       <c r="D596" t="s">
         <v>1399</v>
@@ -17610,8 +17609,8 @@
       <c r="B597" t="s">
         <v>1276</v>
       </c>
-      <c r="C597" s="10" t="s">
-        <v>1404</v>
+      <c r="C597" t="s">
+        <v>1403</v>
       </c>
       <c r="D597" t="s">
         <v>1399</v>
@@ -17624,8 +17623,8 @@
       <c r="B598" t="s">
         <v>1277</v>
       </c>
-      <c r="C598" s="10" t="s">
-        <v>1404</v>
+      <c r="C598" t="s">
+        <v>1403</v>
       </c>
       <c r="D598" t="s">
         <v>1399</v>
@@ -17638,8 +17637,8 @@
       <c r="B599" t="s">
         <v>1278</v>
       </c>
-      <c r="C599" s="10" t="s">
-        <v>1404</v>
+      <c r="C599" t="s">
+        <v>1403</v>
       </c>
       <c r="D599" t="s">
         <v>1399</v>
@@ -17652,8 +17651,8 @@
       <c r="B600" t="s">
         <v>1279</v>
       </c>
-      <c r="C600" s="10" t="s">
-        <v>1404</v>
+      <c r="C600" t="s">
+        <v>1403</v>
       </c>
       <c r="D600" t="s">
         <v>1399</v>
@@ -17666,8 +17665,8 @@
       <c r="B601" t="s">
         <v>1280</v>
       </c>
-      <c r="C601" s="10" t="s">
-        <v>1404</v>
+      <c r="C601" t="s">
+        <v>1403</v>
       </c>
       <c r="D601" t="s">
         <v>1399</v>
@@ -17680,8 +17679,8 @@
       <c r="B602" t="s">
         <v>1281</v>
       </c>
-      <c r="C602" s="10" t="s">
-        <v>1404</v>
+      <c r="C602" t="s">
+        <v>1403</v>
       </c>
       <c r="D602" t="s">
         <v>1399</v>
@@ -17694,8 +17693,8 @@
       <c r="B603" t="s">
         <v>1282</v>
       </c>
-      <c r="C603" s="10" t="s">
-        <v>1404</v>
+      <c r="C603" t="s">
+        <v>1403</v>
       </c>
       <c r="D603" t="s">
         <v>1399</v>
@@ -17708,8 +17707,8 @@
       <c r="B604" t="s">
         <v>1283</v>
       </c>
-      <c r="C604" s="10" t="s">
-        <v>1404</v>
+      <c r="C604" t="s">
+        <v>1403</v>
       </c>
       <c r="D604" t="s">
         <v>1399</v>
@@ -17722,8 +17721,8 @@
       <c r="B605" t="s">
         <v>1284</v>
       </c>
-      <c r="C605" s="10" t="s">
-        <v>1404</v>
+      <c r="C605" t="s">
+        <v>1403</v>
       </c>
       <c r="D605" t="s">
         <v>1399</v>
@@ -17736,8 +17735,8 @@
       <c r="B606" t="s">
         <v>1285</v>
       </c>
-      <c r="C606" s="10" t="s">
-        <v>1404</v>
+      <c r="C606" t="s">
+        <v>1403</v>
       </c>
       <c r="D606" t="s">
         <v>1399</v>
@@ -17750,8 +17749,8 @@
       <c r="B607" t="s">
         <v>1286</v>
       </c>
-      <c r="C607" s="10" t="s">
-        <v>1404</v>
+      <c r="C607" t="s">
+        <v>1403</v>
       </c>
       <c r="D607" t="s">
         <v>1399</v>
@@ -17764,8 +17763,8 @@
       <c r="B608" t="s">
         <v>1287</v>
       </c>
-      <c r="C608" s="10" t="s">
-        <v>1404</v>
+      <c r="C608" t="s">
+        <v>1403</v>
       </c>
       <c r="D608" t="s">
         <v>1399</v>
@@ -17778,8 +17777,8 @@
       <c r="B609" t="s">
         <v>1288</v>
       </c>
-      <c r="C609" s="10" t="s">
-        <v>1404</v>
+      <c r="C609" t="s">
+        <v>1403</v>
       </c>
       <c r="D609" t="s">
         <v>1399</v>
@@ -17792,8 +17791,8 @@
       <c r="B610" t="s">
         <v>1289</v>
       </c>
-      <c r="C610" s="10" t="s">
-        <v>1404</v>
+      <c r="C610" t="s">
+        <v>1403</v>
       </c>
       <c r="D610" t="s">
         <v>1399</v>
@@ -17806,8 +17805,8 @@
       <c r="B611" t="s">
         <v>1290</v>
       </c>
-      <c r="C611" s="10" t="s">
-        <v>1404</v>
+      <c r="C611" t="s">
+        <v>1403</v>
       </c>
       <c r="D611" t="s">
         <v>1399</v>
@@ -17820,8 +17819,8 @@
       <c r="B612" t="s">
         <v>1291</v>
       </c>
-      <c r="C612" s="10" t="s">
-        <v>1404</v>
+      <c r="C612" t="s">
+        <v>1403</v>
       </c>
       <c r="D612" t="s">
         <v>1399</v>
@@ -17834,8 +17833,8 @@
       <c r="B613" t="s">
         <v>1292</v>
       </c>
-      <c r="C613" s="10" t="s">
-        <v>1404</v>
+      <c r="C613" t="s">
+        <v>1403</v>
       </c>
       <c r="D613" t="s">
         <v>1399</v>
@@ -17848,8 +17847,8 @@
       <c r="B614" t="s">
         <v>1293</v>
       </c>
-      <c r="C614" s="10" t="s">
-        <v>1404</v>
+      <c r="C614" t="s">
+        <v>1403</v>
       </c>
       <c r="D614" t="s">
         <v>1399</v>
@@ -17862,8 +17861,8 @@
       <c r="B615" t="s">
         <v>1294</v>
       </c>
-      <c r="C615" s="10" t="s">
-        <v>1404</v>
+      <c r="C615" t="s">
+        <v>1403</v>
       </c>
       <c r="D615" t="s">
         <v>1399</v>
@@ -17876,8 +17875,8 @@
       <c r="B616" t="s">
         <v>1295</v>
       </c>
-      <c r="C616" s="10" t="s">
-        <v>1404</v>
+      <c r="C616" t="s">
+        <v>1403</v>
       </c>
       <c r="D616" t="s">
         <v>1399</v>
@@ -17890,8 +17889,8 @@
       <c r="B617" t="s">
         <v>1296</v>
       </c>
-      <c r="C617" s="10" t="s">
-        <v>1404</v>
+      <c r="C617" t="s">
+        <v>1403</v>
       </c>
       <c r="D617" t="s">
         <v>1399</v>
@@ -17904,8 +17903,8 @@
       <c r="B618" t="s">
         <v>1297</v>
       </c>
-      <c r="C618" s="10" t="s">
-        <v>1404</v>
+      <c r="C618" t="s">
+        <v>1403</v>
       </c>
       <c r="D618" t="s">
         <v>1399</v>
@@ -17918,8 +17917,8 @@
       <c r="B619" t="s">
         <v>1298</v>
       </c>
-      <c r="C619" s="10" t="s">
-        <v>1404</v>
+      <c r="C619" t="s">
+        <v>1403</v>
       </c>
       <c r="D619" t="s">
         <v>1399</v>
